--- a/pin_points_with_normals.xlsx
+++ b/pin_points_with_normals.xlsx
@@ -102,28 +102,28 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>10.625</v>
+        <v>6.01147643</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3.19355908</v>
+        <v>2.09455331</v>
       </c>
       <c r="F3">
-        <v>19.65709983</v>
+        <v>19.89001876</v>
       </c>
       <c r="G3">
-        <v>1.8438022</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-0.15967795</v>
+        <v>-0.10472767</v>
       </c>
       <c r="I3">
-        <v>-0.98285499</v>
+        <v>-0.99450094</v>
       </c>
       <c r="J3">
-        <v>-0.09219011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -131,31 +131,31 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>10.625</v>
+        <v>8.50542008</v>
       </c>
       <c r="D4">
-        <v>90</v>
+        <v>137.50776405</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>-2.18118094</v>
       </c>
       <c r="F4">
-        <v>19.65709983</v>
+        <v>19.78003753</v>
       </c>
       <c r="G4">
-        <v>3.68760439</v>
+        <v>1.99814041</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.10905905</v>
       </c>
       <c r="I4">
-        <v>-0.98285499</v>
+        <v>-0.98900188</v>
       </c>
       <c r="J4">
-        <v>-0.18438022</v>
+        <v>-0.09990702</v>
       </c>
     </row>
     <row r="5">
@@ -163,31 +163,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>10.625</v>
+        <v>10.42176856</v>
       </c>
       <c r="D5">
-        <v>150</v>
+        <v>275.0155281</v>
       </c>
       <c r="E5">
-        <v>-3.19355908</v>
+        <v>0.31629372</v>
       </c>
       <c r="F5">
-        <v>19.65709983</v>
+        <v>19.67005629</v>
       </c>
       <c r="G5">
-        <v>1.8438022</v>
+        <v>-3.60400385</v>
       </c>
       <c r="H5">
-        <v>0.15967795</v>
+        <v>-0.01581469</v>
       </c>
       <c r="I5">
-        <v>-0.98285499</v>
+        <v>-0.98350281</v>
       </c>
       <c r="J5">
-        <v>-0.09219011</v>
+        <v>0.18020019</v>
       </c>
     </row>
     <row r="6">
@@ -195,31 +195,31 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>10.625</v>
+        <v>12.03957694</v>
       </c>
       <c r="D6">
-        <v>210</v>
+        <v>52.52329215</v>
       </c>
       <c r="E6">
-        <v>-3.19355908</v>
+        <v>2.53825232</v>
       </c>
       <c r="F6">
-        <v>19.65709983</v>
+        <v>19.56007506</v>
       </c>
       <c r="G6">
-        <v>-1.8438022</v>
+        <v>3.31070067</v>
       </c>
       <c r="H6">
-        <v>0.15967795</v>
+        <v>-0.12691262</v>
       </c>
       <c r="I6">
-        <v>-0.98285499</v>
+        <v>-0.97800375</v>
       </c>
       <c r="J6">
-        <v>0.09219011</v>
+        <v>-0.16553503</v>
       </c>
     </row>
     <row r="7">
@@ -227,31 +227,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>10.625</v>
+        <v>13.46688263</v>
       </c>
       <c r="D7">
-        <v>270</v>
+        <v>190.0310562</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>-4.58646629</v>
       </c>
       <c r="F7">
-        <v>19.65709983</v>
+        <v>19.45009382</v>
       </c>
       <c r="G7">
-        <v>-3.68760439</v>
+        <v>-0.81128131</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.22932331</v>
       </c>
       <c r="I7">
-        <v>-0.98285499</v>
+        <v>-0.97250469</v>
       </c>
       <c r="J7">
-        <v>0.18438022</v>
+        <v>0.04056407</v>
       </c>
     </row>
     <row r="8">
@@ -259,31 +259,31 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>10.625</v>
+        <v>14.75906858</v>
       </c>
       <c r="D8">
-        <v>330</v>
+        <v>327.53882025</v>
       </c>
       <c r="E8">
-        <v>3.19355908</v>
+        <v>4.2990177</v>
       </c>
       <c r="F8">
-        <v>19.65709983</v>
+        <v>19.34011259</v>
       </c>
       <c r="G8">
-        <v>-1.8438022</v>
+        <v>-2.73468316</v>
       </c>
       <c r="H8">
-        <v>-0.15967795</v>
+        <v>-0.21495089</v>
       </c>
       <c r="I8">
-        <v>-0.98285499</v>
+        <v>-0.96700563</v>
       </c>
       <c r="J8">
-        <v>0.09219011</v>
+        <v>0.13673416</v>
       </c>
     </row>
     <row r="9">
@@ -291,31 +291,31 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>21.25</v>
+        <v>15.94902031</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>105.0465843</v>
       </c>
       <c r="E9">
-        <v>7.24876077</v>
+        <v>-1.42669155</v>
       </c>
       <c r="F9">
-        <v>18.64015739</v>
+        <v>19.23013135</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>5.30722145</v>
       </c>
       <c r="H9">
-        <v>-0.36243804</v>
+        <v>0.07133458</v>
       </c>
       <c r="I9">
-        <v>-0.93200787</v>
+        <v>-0.96150657</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>-0.26536107</v>
       </c>
     </row>
     <row r="10">
@@ -323,31 +323,31 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>21.25</v>
+        <v>17.05815531</v>
       </c>
       <c r="D10">
-        <v>32.72727273</v>
+        <v>242.55434835</v>
       </c>
       <c r="E10">
-        <v>6.0980456</v>
+        <v>-2.70406966</v>
       </c>
       <c r="F10">
-        <v>18.64015739</v>
+        <v>19.12015011</v>
       </c>
       <c r="G10">
-        <v>3.91897595</v>
+        <v>-5.20652158</v>
       </c>
       <c r="H10">
-        <v>-0.30490228</v>
+        <v>0.13520348</v>
       </c>
       <c r="I10">
-        <v>-0.93200787</v>
+        <v>-0.95600751</v>
       </c>
       <c r="J10">
-        <v>-0.1959488</v>
+        <v>0.26032608</v>
       </c>
     </row>
     <row r="11">
@@ -355,31 +355,31 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>21.25</v>
+        <v>18.10134398</v>
       </c>
       <c r="D11">
-        <v>65.45454545</v>
+        <v>20.0621124</v>
       </c>
       <c r="E11">
-        <v>3.01124405</v>
+        <v>5.83691859</v>
       </c>
       <c r="F11">
-        <v>18.64015739</v>
+        <v>19.01016888</v>
       </c>
       <c r="G11">
-        <v>6.59370472</v>
+        <v>2.13163331</v>
       </c>
       <c r="H11">
-        <v>-0.1505622</v>
+        <v>-0.29184593</v>
       </c>
       <c r="I11">
-        <v>-0.93200787</v>
+        <v>-0.95050844</v>
       </c>
       <c r="J11">
-        <v>-0.32968524</v>
+        <v>-0.10658167</v>
       </c>
     </row>
     <row r="12">
@@ -387,31 +387,31 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>21.25</v>
+        <v>19.0894089</v>
       </c>
       <c r="D12">
-        <v>98.18181818</v>
+        <v>157.56987645</v>
       </c>
       <c r="E12">
-        <v>-1.03160622</v>
+        <v>-6.04601894</v>
       </c>
       <c r="F12">
-        <v>18.64015739</v>
+        <v>18.90018764</v>
       </c>
       <c r="G12">
-        <v>7.17497883</v>
+        <v>2.49570873</v>
       </c>
       <c r="H12">
-        <v>0.05158031</v>
+        <v>0.30230095</v>
       </c>
       <c r="I12">
-        <v>-0.93200787</v>
+        <v>-0.94500938</v>
       </c>
       <c r="J12">
-        <v>-0.35874894</v>
+        <v>-0.12478544</v>
       </c>
     </row>
     <row r="13">
@@ -419,31 +419,31 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>21.25</v>
+        <v>20.03051695</v>
       </c>
       <c r="D13">
-        <v>130.90909091</v>
+        <v>295.0776405</v>
       </c>
       <c r="E13">
-        <v>-4.7469288</v>
+        <v>2.90351965</v>
       </c>
       <c r="F13">
-        <v>18.64015739</v>
+        <v>18.79020641</v>
       </c>
       <c r="G13">
-        <v>5.47824786</v>
+        <v>-6.20465284</v>
       </c>
       <c r="H13">
-        <v>0.23734644</v>
+        <v>-0.14517598</v>
       </c>
       <c r="I13">
-        <v>-0.93200787</v>
+        <v>-0.93951032</v>
       </c>
       <c r="J13">
-        <v>-0.27391239</v>
+        <v>0.31023264</v>
       </c>
     </row>
     <row r="14">
@@ -451,31 +451,31 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>21.25</v>
+        <v>20.93101046</v>
       </c>
       <c r="D14">
-        <v>163.63636364</v>
+        <v>72.58540455</v>
       </c>
       <c r="E14">
-        <v>-6.95513502</v>
+        <v>2.13834473</v>
       </c>
       <c r="F14">
-        <v>18.64015739</v>
+        <v>18.68022517</v>
       </c>
       <c r="G14">
-        <v>2.0422119</v>
+        <v>6.81737995</v>
       </c>
       <c r="H14">
-        <v>0.34775675</v>
+        <v>-0.10691724</v>
       </c>
       <c r="I14">
-        <v>-0.93200787</v>
+        <v>-0.93401126</v>
       </c>
       <c r="J14">
-        <v>-0.1021106</v>
+        <v>-0.340869</v>
       </c>
     </row>
     <row r="15">
@@ -483,31 +483,31 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>21.25</v>
+        <v>21.79593122</v>
       </c>
       <c r="D15">
-        <v>196.36363636</v>
+        <v>210.0931686</v>
       </c>
       <c r="E15">
-        <v>-6.95513502</v>
+        <v>-6.42509131</v>
       </c>
       <c r="F15">
-        <v>18.64015739</v>
+        <v>18.57024393</v>
       </c>
       <c r="G15">
-        <v>-2.0422119</v>
+        <v>-3.72347175</v>
       </c>
       <c r="H15">
-        <v>0.34775675</v>
+        <v>0.32125457</v>
       </c>
       <c r="I15">
-        <v>-0.93200787</v>
+        <v>-0.9285122</v>
       </c>
       <c r="J15">
-        <v>0.1021106</v>
+        <v>0.18617359</v>
       </c>
     </row>
     <row r="16">
@@ -515,31 +515,31 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>21.25</v>
+        <v>22.62936552</v>
       </c>
       <c r="D16">
-        <v>229.09090909</v>
+        <v>347.60093265</v>
       </c>
       <c r="E16">
-        <v>-4.7469288</v>
+        <v>7.51588028</v>
       </c>
       <c r="F16">
-        <v>18.64015739</v>
+        <v>18.4602627</v>
       </c>
       <c r="G16">
-        <v>-5.47824786</v>
+        <v>-1.6523452</v>
       </c>
       <c r="H16">
-        <v>0.23734644</v>
+        <v>-0.37579401</v>
       </c>
       <c r="I16">
-        <v>-0.93200787</v>
+        <v>-0.92301313</v>
       </c>
       <c r="J16">
-        <v>0.27391239</v>
+        <v>0.08261726</v>
       </c>
     </row>
     <row r="17">
@@ -547,31 +547,31 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>21.25</v>
+        <v>23.43467981</v>
       </c>
       <c r="D17">
-        <v>261.81818182</v>
+        <v>125.1086967</v>
       </c>
       <c r="E17">
-        <v>-1.03160622</v>
+        <v>-4.57461759</v>
       </c>
       <c r="F17">
-        <v>18.64015739</v>
+        <v>18.35028146</v>
       </c>
       <c r="G17">
-        <v>-7.17497883</v>
+        <v>6.50692278</v>
       </c>
       <c r="H17">
-        <v>0.05158031</v>
+        <v>0.22873088</v>
       </c>
       <c r="I17">
-        <v>-0.93200787</v>
+        <v>-0.91751407</v>
       </c>
       <c r="J17">
-        <v>0.35874894</v>
+        <v>-0.32534614</v>
       </c>
     </row>
     <row r="18">
@@ -579,31 +579,31 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>21.25</v>
+        <v>24.21468653</v>
       </c>
       <c r="D18">
-        <v>294.54545455</v>
+        <v>262.61646075</v>
       </c>
       <c r="E18">
-        <v>3.01124405</v>
+        <v>-1.05419072</v>
       </c>
       <c r="F18">
-        <v>18.64015739</v>
+        <v>18.24030023</v>
       </c>
       <c r="G18">
-        <v>-6.59370472</v>
+        <v>-8.13511706</v>
       </c>
       <c r="H18">
-        <v>-0.1505622</v>
+        <v>0.05270954</v>
       </c>
       <c r="I18">
-        <v>-0.93200787</v>
+        <v>-0.91201501</v>
       </c>
       <c r="J18">
-        <v>0.32968524</v>
+        <v>0.40675585</v>
       </c>
     </row>
     <row r="19">
@@ -611,31 +611,31 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>21.25</v>
+        <v>24.97176378</v>
       </c>
       <c r="D19">
-        <v>327.27272727</v>
+        <v>40.1242248</v>
       </c>
       <c r="E19">
-        <v>6.0980456</v>
+        <v>6.45626131</v>
       </c>
       <c r="F19">
-        <v>18.64015739</v>
+        <v>18.13031899</v>
       </c>
       <c r="G19">
-        <v>-3.91897595</v>
+        <v>5.44134387</v>
       </c>
       <c r="H19">
-        <v>-0.30490228</v>
+        <v>-0.32281307</v>
       </c>
       <c r="I19">
-        <v>-0.93200787</v>
+        <v>-0.90651595</v>
       </c>
       <c r="J19">
-        <v>0.1959488</v>
+        <v>-0.27206719</v>
       </c>
     </row>
     <row r="20">
@@ -643,31 +643,31 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C20">
-        <v>31.875</v>
+        <v>25.7079438</v>
       </c>
       <c r="D20">
-        <v>10.58823529</v>
+        <v>177.63198885</v>
       </c>
       <c r="E20">
-        <v>10.38152984</v>
+        <v>-8.66827165</v>
       </c>
       <c r="F20">
-        <v>16.98404363</v>
+        <v>18.02033776</v>
       </c>
       <c r="G20">
-        <v>1.94064426</v>
+        <v>0.35846025</v>
       </c>
       <c r="H20">
-        <v>-0.51907649</v>
+        <v>0.43341358</v>
       </c>
       <c r="I20">
-        <v>-0.84920218</v>
+        <v>-0.90101689</v>
       </c>
       <c r="J20">
-        <v>-0.09703221</v>
+        <v>-0.01792301</v>
       </c>
     </row>
     <row r="21">
@@ -675,31 +675,31 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>31.875</v>
+        <v>26.42497944</v>
       </c>
       <c r="D21">
-        <v>31.76470588</v>
+        <v>315.1397529</v>
       </c>
       <c r="E21">
-        <v>8.97944671</v>
+        <v>6.30894532</v>
       </c>
       <c r="F21">
-        <v>16.98404363</v>
+        <v>17.91035652</v>
       </c>
       <c r="G21">
-        <v>5.55983802</v>
+        <v>-6.27824324</v>
       </c>
       <c r="H21">
-        <v>-0.44897234</v>
+        <v>-0.31544727</v>
       </c>
       <c r="I21">
-        <v>-0.84920218</v>
+        <v>-0.89551783</v>
       </c>
       <c r="J21">
-        <v>-0.2779919</v>
+        <v>0.31391216</v>
       </c>
     </row>
     <row r="22">
@@ -707,31 +707,31 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>31.875</v>
+        <v>27.12439512</v>
       </c>
       <c r="D22">
-        <v>52.94117647</v>
+        <v>92.64751695</v>
       </c>
       <c r="E22">
-        <v>6.36463954</v>
+        <v>-0.42119568</v>
       </c>
       <c r="F22">
-        <v>16.98404363</v>
+        <v>17.80037528</v>
       </c>
       <c r="G22">
-        <v>8.42814484</v>
+        <v>9.10874492</v>
       </c>
       <c r="H22">
-        <v>-0.31823198</v>
+        <v>0.02105978</v>
       </c>
       <c r="I22">
-        <v>-0.84920218</v>
+        <v>-0.89001876</v>
       </c>
       <c r="J22">
-        <v>-0.42140724</v>
+        <v>-0.45543725</v>
       </c>
     </row>
     <row r="23">
@@ -739,31 +739,31 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C23">
-        <v>31.875</v>
+        <v>27.80752645</v>
       </c>
       <c r="D23">
-        <v>74.11764706</v>
+        <v>230.155281</v>
       </c>
       <c r="E23">
-        <v>2.89025254</v>
+        <v>-5.97785266</v>
       </c>
       <c r="F23">
-        <v>16.98404363</v>
+        <v>17.69039405</v>
       </c>
       <c r="G23">
-        <v>10.158184</v>
+        <v>-7.16346536</v>
       </c>
       <c r="H23">
-        <v>-0.14451263</v>
+        <v>0.29889263</v>
       </c>
       <c r="I23">
-        <v>-0.84920218</v>
+        <v>-0.8845197</v>
       </c>
       <c r="J23">
-        <v>-0.5079092</v>
+        <v>0.35817327</v>
       </c>
     </row>
     <row r="24">
@@ -771,31 +771,31 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C24">
-        <v>31.875</v>
+        <v>28.47555137</v>
       </c>
       <c r="D24">
-        <v>95.29411765</v>
+        <v>7.66304505</v>
       </c>
       <c r="E24">
-        <v>-0.97447909</v>
+        <v>9.45051518</v>
       </c>
       <c r="F24">
-        <v>16.98404363</v>
+        <v>17.58041281</v>
       </c>
       <c r="G24">
-        <v>10.51630413</v>
+        <v>1.27155345</v>
       </c>
       <c r="H24">
-        <v>0.04872395</v>
+        <v>-0.47252576</v>
       </c>
       <c r="I24">
-        <v>-0.84920218</v>
+        <v>-0.87902064</v>
       </c>
       <c r="J24">
-        <v>-0.52581521</v>
+        <v>-0.06357767</v>
       </c>
     </row>
     <row r="25">
@@ -803,31 +803,31 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>31.875</v>
+        <v>29.12951505</v>
       </c>
       <c r="D25">
-        <v>116.47058824</v>
+        <v>145.1708091</v>
       </c>
       <c r="E25">
-        <v>-4.70760191</v>
+        <v>-7.99163751</v>
       </c>
       <c r="F25">
-        <v>16.98404363</v>
+        <v>17.47043158</v>
       </c>
       <c r="G25">
-        <v>9.4541391</v>
+        <v>5.56037323</v>
       </c>
       <c r="H25">
-        <v>0.2353801</v>
+        <v>0.39958188</v>
       </c>
       <c r="I25">
-        <v>-0.84920218</v>
+        <v>-0.87352158</v>
       </c>
       <c r="J25">
-        <v>-0.47270696</v>
+        <v>-0.27801866</v>
       </c>
     </row>
     <row r="26">
@@ -835,31 +835,31 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>31.875</v>
+        <v>29.77034991</v>
       </c>
       <c r="D26">
-        <v>137.64705882</v>
+        <v>282.67857315</v>
       </c>
       <c r="E26">
-        <v>-7.80493701</v>
+        <v>2.179559</v>
       </c>
       <c r="F26">
-        <v>16.98404363</v>
+        <v>17.36045034</v>
       </c>
       <c r="G26">
-        <v>7.11514021</v>
+        <v>-9.6883583</v>
       </c>
       <c r="H26">
-        <v>0.39024685</v>
+        <v>-0.10897795</v>
       </c>
       <c r="I26">
-        <v>-0.84920218</v>
+        <v>-0.86802252</v>
       </c>
       <c r="J26">
-        <v>-0.35575701</v>
+        <v>0.48441791</v>
       </c>
     </row>
     <row r="27">
@@ -867,31 +867,31 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>31.875</v>
+        <v>30.39889196</v>
       </c>
       <c r="D27">
-        <v>158.82352941</v>
+        <v>60.1863372</v>
       </c>
       <c r="E27">
-        <v>-9.84817212</v>
+        <v>5.03164033</v>
       </c>
       <c r="F27">
-        <v>16.98404363</v>
+        <v>17.2504691</v>
       </c>
       <c r="G27">
-        <v>3.8152022</v>
+        <v>8.78088328</v>
       </c>
       <c r="H27">
-        <v>0.49240861</v>
+        <v>-0.25158202</v>
       </c>
       <c r="I27">
-        <v>-0.84920218</v>
+        <v>-0.86252346</v>
       </c>
       <c r="J27">
-        <v>-0.19076011</v>
+        <v>-0.43904416</v>
       </c>
     </row>
     <row r="28">
@@ -899,31 +899,31 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>31.875</v>
+        <v>31.01589415</v>
       </c>
       <c r="D28">
-        <v>180</v>
+        <v>197.69410125</v>
       </c>
       <c r="E28">
-        <v>-10.56135701</v>
+        <v>-9.81799138</v>
       </c>
       <c r="F28">
-        <v>16.98404363</v>
+        <v>17.14048787</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>-3.13220703</v>
       </c>
       <c r="H28">
-        <v>0.52806785</v>
+        <v>0.49089957</v>
       </c>
       <c r="I28">
-        <v>-0.84920218</v>
+        <v>-0.85702439</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>0.15661035</v>
       </c>
     </row>
     <row r="29">
@@ -931,31 +931,31 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C29">
-        <v>31.875</v>
+        <v>31.62203754</v>
       </c>
       <c r="D29">
-        <v>201.17647059</v>
+        <v>335.2018653</v>
       </c>
       <c r="E29">
-        <v>-9.84817212</v>
+        <v>9.51934229</v>
       </c>
       <c r="F29">
-        <v>16.98404363</v>
+        <v>17.03050663</v>
       </c>
       <c r="G29">
-        <v>-3.8152022</v>
+        <v>-4.39817759</v>
       </c>
       <c r="H29">
-        <v>0.49240861</v>
+        <v>-0.47596711</v>
       </c>
       <c r="I29">
-        <v>-0.84920218</v>
+        <v>-0.85152533</v>
       </c>
       <c r="J29">
-        <v>0.19076011</v>
+        <v>0.21990888</v>
       </c>
     </row>
     <row r="30">
@@ -963,31 +963,31 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C30">
-        <v>31.875</v>
+        <v>32.21794052</v>
       </c>
       <c r="D30">
-        <v>222.35294118</v>
+        <v>112.70962935</v>
       </c>
       <c r="E30">
-        <v>-7.80493701</v>
+        <v>-4.11650146</v>
       </c>
       <c r="F30">
-        <v>16.98404363</v>
+        <v>16.9205254</v>
       </c>
       <c r="G30">
-        <v>-7.11514021</v>
+        <v>9.83616979</v>
       </c>
       <c r="H30">
-        <v>0.39024685</v>
+        <v>0.20582507</v>
       </c>
       <c r="I30">
-        <v>-0.84920218</v>
+        <v>-0.84602627</v>
       </c>
       <c r="J30">
-        <v>0.35575701</v>
+        <v>-0.49180849</v>
       </c>
     </row>
     <row r="31">
@@ -995,31 +995,31 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C31">
-        <v>31.875</v>
+        <v>32.80416657</v>
       </c>
       <c r="D31">
-        <v>243.52941176</v>
+        <v>250.2173934</v>
       </c>
       <c r="E31">
-        <v>-4.70760191</v>
+        <v>-3.66726133</v>
       </c>
       <c r="F31">
-        <v>16.98404363</v>
+        <v>16.81054416</v>
       </c>
       <c r="G31">
-        <v>-9.4541391</v>
+        <v>-10.19592072</v>
       </c>
       <c r="H31">
-        <v>0.2353801</v>
+        <v>0.18336307</v>
       </c>
       <c r="I31">
-        <v>-0.84920218</v>
+        <v>-0.84052721</v>
       </c>
       <c r="J31">
-        <v>0.47270696</v>
+        <v>0.50979604</v>
       </c>
     </row>
     <row r="32">
@@ -1027,31 +1027,31 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>31.875</v>
+        <v>33.38123091</v>
       </c>
       <c r="D32">
-        <v>264.70588235</v>
+        <v>27.72515745</v>
       </c>
       <c r="E32">
-        <v>-0.97447909</v>
+        <v>9.74075255</v>
       </c>
       <c r="F32">
-        <v>16.98404363</v>
+        <v>16.70056293</v>
       </c>
       <c r="G32">
-        <v>-10.51630413</v>
+        <v>5.11946655</v>
       </c>
       <c r="H32">
-        <v>0.04872395</v>
+        <v>-0.48703763</v>
       </c>
       <c r="I32">
-        <v>-0.84920218</v>
+        <v>-0.83502815</v>
       </c>
       <c r="J32">
-        <v>0.52581521</v>
+        <v>-0.25597333</v>
       </c>
     </row>
     <row r="33">
@@ -1059,31 +1059,31 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C33">
-        <v>31.875</v>
+        <v>33.94960606</v>
       </c>
       <c r="D33">
-        <v>285.88235294</v>
+        <v>165.2329215</v>
       </c>
       <c r="E33">
-        <v>2.89025254</v>
+        <v>-10.80034937</v>
       </c>
       <c r="F33">
-        <v>16.98404363</v>
+        <v>16.59058169</v>
       </c>
       <c r="G33">
-        <v>-10.158184</v>
+        <v>2.84693743</v>
       </c>
       <c r="H33">
-        <v>-0.14451263</v>
+        <v>0.54001747</v>
       </c>
       <c r="I33">
-        <v>-0.84920218</v>
+        <v>-0.82952908</v>
       </c>
       <c r="J33">
-        <v>0.5079092</v>
+        <v>-0.14234687</v>
       </c>
     </row>
     <row r="34">
@@ -1091,31 +1091,31 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C34">
-        <v>31.875</v>
+        <v>34.50972663</v>
       </c>
       <c r="D34">
-        <v>307.05882353</v>
+        <v>302.74068555</v>
       </c>
       <c r="E34">
-        <v>6.36463954</v>
+        <v>6.12819059</v>
       </c>
       <c r="F34">
-        <v>16.98404363</v>
+        <v>16.48060045</v>
       </c>
       <c r="G34">
-        <v>-8.42814484</v>
+        <v>-9.5307444</v>
       </c>
       <c r="H34">
-        <v>-0.31823198</v>
+        <v>-0.30640953</v>
       </c>
       <c r="I34">
-        <v>-0.84920218</v>
+        <v>-0.82403002</v>
       </c>
       <c r="J34">
-        <v>0.42140724</v>
+        <v>0.47653722</v>
       </c>
     </row>
     <row r="35">
@@ -1123,31 +1123,31 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>31.875</v>
+        <v>35.06199346</v>
       </c>
       <c r="D35">
-        <v>328.23529412</v>
+        <v>80.2484496</v>
       </c>
       <c r="E35">
-        <v>8.97944671</v>
+        <v>1.9460049</v>
       </c>
       <c r="F35">
-        <v>16.98404363</v>
+        <v>16.37061922</v>
       </c>
       <c r="G35">
-        <v>-5.55983802</v>
+        <v>11.32324562</v>
       </c>
       <c r="H35">
-        <v>-0.44897234</v>
+        <v>-0.09730025</v>
       </c>
       <c r="I35">
-        <v>-0.84920218</v>
+        <v>-0.81853096</v>
       </c>
       <c r="J35">
-        <v>0.2779919</v>
+        <v>-0.56616228</v>
       </c>
     </row>
     <row r="36">
@@ -1155,31 +1155,31 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C36">
-        <v>31.875</v>
+        <v>35.60677721</v>
       </c>
       <c r="D36">
-        <v>349.41176471</v>
+        <v>217.75621365</v>
       </c>
       <c r="E36">
-        <v>10.38152984</v>
+        <v>-9.20631895</v>
       </c>
       <c r="F36">
-        <v>16.98404363</v>
+        <v>16.26063798</v>
       </c>
       <c r="G36">
-        <v>-1.94064426</v>
+        <v>-7.12989086</v>
       </c>
       <c r="H36">
-        <v>-0.51907649</v>
+        <v>0.46031595</v>
       </c>
       <c r="I36">
-        <v>-0.84920218</v>
+        <v>-0.8130319</v>
       </c>
       <c r="J36">
-        <v>0.09703221</v>
+        <v>0.35649454</v>
       </c>
     </row>
     <row r="37">
@@ -1187,31 +1187,31 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C37">
-        <v>42.5</v>
+        <v>36.1444214</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>355.2639777</v>
       </c>
       <c r="E37">
-        <v>13.51180415</v>
+        <v>11.75617536</v>
       </c>
       <c r="F37">
-        <v>14.74554674</v>
+        <v>16.15065675</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>-0.9739751</v>
       </c>
       <c r="H37">
-        <v>-0.67559021</v>
+        <v>-0.58780877</v>
       </c>
       <c r="I37">
-        <v>-0.73727734</v>
+        <v>-0.80753284</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>0.04869875</v>
       </c>
     </row>
     <row r="38">
@@ -1219,31 +1219,31 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C38">
-        <v>42.5</v>
+        <v>36.67524515</v>
       </c>
       <c r="D38">
-        <v>17.14285714</v>
+        <v>132.77174175</v>
       </c>
       <c r="E38">
-        <v>12.91151261</v>
+        <v>-8.11199233</v>
       </c>
       <c r="F38">
-        <v>14.74554674</v>
+        <v>16.04067551</v>
       </c>
       <c r="G38">
-        <v>3.98267419</v>
+        <v>8.76882601</v>
       </c>
       <c r="H38">
-        <v>-0.64557563</v>
+        <v>0.40559962</v>
       </c>
       <c r="I38">
-        <v>-0.73727734</v>
+        <v>-0.80203378</v>
       </c>
       <c r="J38">
-        <v>-0.19913371</v>
+        <v>-0.4384413</v>
       </c>
     </row>
     <row r="39">
@@ -1251,31 +1251,31 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>42.5</v>
+        <v>37.19954552</v>
       </c>
       <c r="D39">
-        <v>34.28571429</v>
+        <v>270.2795058</v>
       </c>
       <c r="E39">
-        <v>11.1639765</v>
+        <v>0.05898742</v>
       </c>
       <c r="F39">
-        <v>14.74554674</v>
+        <v>15.93069427</v>
       </c>
       <c r="G39">
-        <v>7.6114703</v>
+        <v>-12.09171205</v>
       </c>
       <c r="H39">
-        <v>-0.55819883</v>
+        <v>-0.00294937</v>
       </c>
       <c r="I39">
-        <v>-0.73727734</v>
+        <v>-0.79653471</v>
       </c>
       <c r="J39">
-        <v>-0.38057351</v>
+        <v>0.6045856</v>
       </c>
     </row>
     <row r="40">
@@ -1283,31 +1283,31 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C40">
-        <v>42.5</v>
+        <v>37.71759963</v>
       </c>
       <c r="D40">
-        <v>51.42857143</v>
+        <v>47.78726985</v>
       </c>
       <c r="E40">
-        <v>8.42447209</v>
+        <v>8.22078448</v>
       </c>
       <c r="F40">
-        <v>14.74554674</v>
+        <v>15.82071304</v>
       </c>
       <c r="G40">
-        <v>10.56395387</v>
+        <v>9.06221504</v>
       </c>
       <c r="H40">
-        <v>-0.4212236</v>
+        <v>-0.41103922</v>
       </c>
       <c r="I40">
-        <v>-0.73727734</v>
+        <v>-0.79103565</v>
       </c>
       <c r="J40">
-        <v>-0.52819769</v>
+        <v>-0.45311075</v>
       </c>
     </row>
     <row r="41">
@@ -1315,31 +1315,31 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="C41">
-        <v>42.5</v>
+        <v>38.22966644</v>
       </c>
       <c r="D41">
-        <v>68.57142857</v>
+        <v>185.2950339</v>
       </c>
       <c r="E41">
-        <v>4.93641637</v>
+        <v>-12.32349083</v>
       </c>
       <c r="F41">
-        <v>14.74554674</v>
+        <v>15.7107318</v>
       </c>
       <c r="G41">
-        <v>12.57778378</v>
+        <v>-1.14213836</v>
       </c>
       <c r="H41">
-        <v>-0.24682082</v>
+        <v>0.61617454</v>
       </c>
       <c r="I41">
-        <v>-0.73727734</v>
+        <v>-0.78553659</v>
       </c>
       <c r="J41">
-        <v>-0.62888919</v>
+        <v>0.05710692</v>
       </c>
     </row>
     <row r="42">
@@ -1347,31 +1347,31 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C42">
-        <v>42.5</v>
+        <v>38.73598841</v>
       </c>
       <c r="D42">
-        <v>85.71428571</v>
+        <v>322.80279795</v>
       </c>
       <c r="E42">
-        <v>1.00973839</v>
+        <v>9.96866634</v>
       </c>
       <c r="F42">
-        <v>14.74554674</v>
+        <v>15.60075057</v>
       </c>
       <c r="G42">
-        <v>13.47402241</v>
+        <v>-7.56586235</v>
       </c>
       <c r="H42">
-        <v>-0.05048692</v>
+        <v>-0.49843332</v>
       </c>
       <c r="I42">
-        <v>-0.73727734</v>
+        <v>-0.78003753</v>
       </c>
       <c r="J42">
-        <v>-0.67370112</v>
+        <v>0.37829312</v>
       </c>
     </row>
     <row r="43">
@@ -1379,31 +1379,31 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C43">
-        <v>42.5</v>
+        <v>39.23679292</v>
       </c>
       <c r="D43">
-        <v>102.85714286</v>
+        <v>100.310562</v>
       </c>
       <c r="E43">
-        <v>-3.00665928</v>
+        <v>-2.26423829</v>
       </c>
       <c r="F43">
-        <v>14.74554674</v>
+        <v>15.49076933</v>
       </c>
       <c r="G43">
-        <v>13.17303501</v>
+        <v>12.44625608</v>
       </c>
       <c r="H43">
-        <v>0.15033296</v>
+        <v>0.11321191</v>
       </c>
       <c r="I43">
-        <v>-0.73727734</v>
+        <v>-0.77453847</v>
       </c>
       <c r="J43">
-        <v>-0.65865175</v>
+        <v>-0.6223128</v>
       </c>
     </row>
     <row r="44">
@@ -1411,31 +1411,31 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C44">
-        <v>42.5</v>
+        <v>39.73229356</v>
       </c>
       <c r="D44">
-        <v>120</v>
+        <v>237.81832605</v>
       </c>
       <c r="E44">
-        <v>-6.75590208</v>
+        <v>-6.80884453</v>
       </c>
       <c r="F44">
-        <v>14.74554674</v>
+        <v>15.3807881</v>
       </c>
       <c r="G44">
-        <v>11.70156565</v>
+        <v>-10.81993502</v>
       </c>
       <c r="H44">
-        <v>0.3377951</v>
+        <v>0.34044223</v>
       </c>
       <c r="I44">
-        <v>-0.73727734</v>
+        <v>-0.7690394</v>
       </c>
       <c r="J44">
-        <v>-0.58507828</v>
+        <v>0.54099675</v>
       </c>
     </row>
     <row r="45">
@@ -1443,31 +1443,31 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="C45">
-        <v>42.5</v>
+        <v>40.2226913</v>
       </c>
       <c r="D45">
-        <v>137.14285714</v>
+        <v>15.3260901</v>
       </c>
       <c r="E45">
-        <v>-9.90485333</v>
+        <v>12.45590133</v>
       </c>
       <c r="F45">
-        <v>14.74554674</v>
+        <v>15.27080686</v>
       </c>
       <c r="G45">
-        <v>9.19036082</v>
+        <v>3.41364615</v>
       </c>
       <c r="H45">
-        <v>0.49524267</v>
+        <v>-0.62279507</v>
       </c>
       <c r="I45">
-        <v>-0.73727734</v>
+        <v>-0.76354034</v>
       </c>
       <c r="J45">
-        <v>-0.45951804</v>
+        <v>-0.17068231</v>
       </c>
     </row>
     <row r="46">
@@ -1475,31 +1475,31 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C46">
-        <v>42.5</v>
+        <v>40.70817548</v>
       </c>
       <c r="D46">
-        <v>154.28571429</v>
+        <v>152.83385415</v>
       </c>
       <c r="E46">
-        <v>-12.17371489</v>
+        <v>-11.60518511</v>
       </c>
       <c r="F46">
-        <v>14.74554674</v>
+        <v>15.16082562</v>
       </c>
       <c r="G46">
-        <v>5.86255211</v>
+        <v>5.95558939</v>
       </c>
       <c r="H46">
-        <v>0.60868574</v>
+        <v>0.58025926</v>
       </c>
       <c r="I46">
-        <v>-0.73727734</v>
+        <v>-0.75804128</v>
       </c>
       <c r="J46">
-        <v>-0.29312761</v>
+        <v>-0.29777947</v>
       </c>
     </row>
     <row r="47">
@@ -1507,31 +1507,31 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C47">
-        <v>42.5</v>
+        <v>41.18892473</v>
       </c>
       <c r="D47">
-        <v>171.42857143</v>
+        <v>290.3416182</v>
       </c>
       <c r="E47">
-        <v>-13.36088846</v>
+        <v>4.57841945</v>
       </c>
       <c r="F47">
-        <v>14.74554674</v>
+        <v>15.05084439</v>
       </c>
       <c r="G47">
-        <v>2.01382991</v>
+        <v>-12.34950034</v>
       </c>
       <c r="H47">
-        <v>0.66804442</v>
+        <v>-0.22892097</v>
       </c>
       <c r="I47">
-        <v>-0.73727734</v>
+        <v>-0.75254222</v>
       </c>
       <c r="J47">
-        <v>-0.1006915</v>
+        <v>0.61747502</v>
       </c>
     </row>
     <row r="48">
@@ -1539,31 +1539,31 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C48">
-        <v>42.5</v>
+        <v>41.66510786</v>
       </c>
       <c r="D48">
-        <v>188.57142857</v>
+        <v>67.84938225</v>
       </c>
       <c r="E48">
-        <v>-13.36088846</v>
+        <v>5.0129747</v>
       </c>
       <c r="F48">
-        <v>14.74554674</v>
+        <v>14.94086315</v>
       </c>
       <c r="G48">
-        <v>-2.01382991</v>
+        <v>12.31424756</v>
       </c>
       <c r="H48">
-        <v>0.66804442</v>
+        <v>-0.25064873</v>
       </c>
       <c r="I48">
-        <v>-0.73727734</v>
+        <v>-0.74704316</v>
       </c>
       <c r="J48">
-        <v>0.1006915</v>
+        <v>-0.61571238</v>
       </c>
     </row>
     <row r="49">
@@ -1571,31 +1571,31 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="C49">
-        <v>42.5</v>
+        <v>42.13688452</v>
       </c>
       <c r="D49">
-        <v>205.71428571</v>
+        <v>205.3571463</v>
       </c>
       <c r="E49">
-        <v>-12.17371489</v>
+        <v>-12.12532896</v>
       </c>
       <c r="F49">
-        <v>14.74554674</v>
+        <v>14.83088192</v>
       </c>
       <c r="G49">
-        <v>-5.86255211</v>
+        <v>-5.74641968</v>
       </c>
       <c r="H49">
-        <v>0.60868574</v>
+        <v>0.60626645</v>
       </c>
       <c r="I49">
-        <v>-0.73727734</v>
+        <v>-0.7415441</v>
       </c>
       <c r="J49">
-        <v>0.29312761</v>
+        <v>0.28732098</v>
       </c>
     </row>
     <row r="50">
@@ -1603,31 +1603,31 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="C50">
-        <v>42.5</v>
+        <v>42.60440597</v>
       </c>
       <c r="D50">
-        <v>222.85714286</v>
+        <v>342.86491035</v>
       </c>
       <c r="E50">
-        <v>-9.90485333</v>
+        <v>12.93770803</v>
       </c>
       <c r="F50">
-        <v>14.74554674</v>
+        <v>14.72090068</v>
       </c>
       <c r="G50">
-        <v>-9.19036082</v>
+        <v>-3.98883366</v>
       </c>
       <c r="H50">
-        <v>0.49524267</v>
+        <v>-0.6468854</v>
       </c>
       <c r="I50">
-        <v>-0.73727734</v>
+        <v>-0.73604503</v>
       </c>
       <c r="J50">
-        <v>0.45951804</v>
+        <v>0.19944168</v>
       </c>
     </row>
     <row r="51">
@@ -1635,31 +1635,31 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C51">
-        <v>42.5</v>
+        <v>43.06781562</v>
       </c>
       <c r="D51">
-        <v>240</v>
+        <v>120.3726744</v>
       </c>
       <c r="E51">
-        <v>-6.75590208</v>
+        <v>-6.90542119</v>
       </c>
       <c r="F51">
-        <v>14.74554674</v>
+        <v>14.61091945</v>
       </c>
       <c r="G51">
-        <v>-11.70156565</v>
+        <v>11.78287703</v>
       </c>
       <c r="H51">
-        <v>0.3377951</v>
+        <v>0.34527106</v>
       </c>
       <c r="I51">
-        <v>-0.73727734</v>
+        <v>-0.73054597</v>
       </c>
       <c r="J51">
-        <v>0.58507828</v>
+        <v>-0.58914385</v>
       </c>
     </row>
     <row r="52">
@@ -1667,31 +1667,31 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C52">
-        <v>42.5</v>
+        <v>43.52724963</v>
       </c>
       <c r="D52">
-        <v>257.14285714</v>
+        <v>257.88043845</v>
       </c>
       <c r="E52">
-        <v>-3.00665928</v>
+        <v>-2.8918819</v>
       </c>
       <c r="F52">
-        <v>14.74554674</v>
+        <v>14.50093821</v>
       </c>
       <c r="G52">
-        <v>-13.17303501</v>
+        <v>-13.46698965</v>
       </c>
       <c r="H52">
-        <v>0.15033296</v>
+        <v>0.14459409</v>
       </c>
       <c r="I52">
-        <v>-0.73727734</v>
+        <v>-0.72504691</v>
       </c>
       <c r="J52">
-        <v>0.65865175</v>
+        <v>0.67334948</v>
       </c>
     </row>
     <row r="53">
@@ -1699,31 +1699,31 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="C53">
-        <v>42.5</v>
+        <v>43.9828374</v>
       </c>
       <c r="D53">
-        <v>274.28571429</v>
+        <v>35.3882025</v>
       </c>
       <c r="E53">
-        <v>1.00973839</v>
+        <v>11.32285003</v>
       </c>
       <c r="F53">
-        <v>14.74554674</v>
+        <v>14.39095697</v>
       </c>
       <c r="G53">
-        <v>-13.47402241</v>
+        <v>8.04322228</v>
       </c>
       <c r="H53">
-        <v>-0.05048692</v>
+        <v>-0.5661425</v>
       </c>
       <c r="I53">
-        <v>-0.73727734</v>
+        <v>-0.71954785</v>
       </c>
       <c r="J53">
-        <v>0.67370112</v>
+        <v>-0.40216111</v>
       </c>
     </row>
     <row r="54">
@@ -1731,31 +1731,31 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="C54">
-        <v>42.5</v>
+        <v>44.43470206</v>
       </c>
       <c r="D54">
-        <v>291.42857143</v>
+        <v>172.89596655</v>
       </c>
       <c r="E54">
-        <v>4.93641637</v>
+        <v>-13.89442942</v>
       </c>
       <c r="F54">
-        <v>14.74554674</v>
+        <v>14.28097574</v>
       </c>
       <c r="G54">
-        <v>-12.57778378</v>
+        <v>1.73163598</v>
       </c>
       <c r="H54">
-        <v>-0.24682082</v>
+        <v>0.69472147</v>
       </c>
       <c r="I54">
-        <v>-0.73727734</v>
+        <v>-0.71404879</v>
       </c>
       <c r="J54">
-        <v>0.62888919</v>
+        <v>-0.0865818</v>
       </c>
     </row>
     <row r="55">
@@ -1763,31 +1763,31 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C55">
-        <v>42.5</v>
+        <v>44.88296084</v>
       </c>
       <c r="D55">
-        <v>308.57142857</v>
+        <v>310.4037306</v>
       </c>
       <c r="E55">
-        <v>8.42447209</v>
+        <v>9.14775706</v>
       </c>
       <c r="F55">
-        <v>14.74554674</v>
+        <v>14.1709945</v>
       </c>
       <c r="G55">
-        <v>-10.56395387</v>
+        <v>-10.74716035</v>
       </c>
       <c r="H55">
-        <v>-0.4212236</v>
+        <v>-0.45738785</v>
       </c>
       <c r="I55">
-        <v>-0.73727734</v>
+        <v>-0.70854973</v>
       </c>
       <c r="J55">
-        <v>0.52819769</v>
+        <v>0.53735802</v>
       </c>
     </row>
     <row r="56">
@@ -1795,31 +1795,31 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="C56">
-        <v>42.5</v>
+        <v>45.32772553</v>
       </c>
       <c r="D56">
-        <v>325.71428571</v>
+        <v>87.91149465</v>
       </c>
       <c r="E56">
-        <v>11.1639765</v>
+        <v>0.5183245</v>
       </c>
       <c r="F56">
-        <v>14.74554674</v>
+        <v>14.06101327</v>
       </c>
       <c r="G56">
-        <v>-7.6114703</v>
+        <v>14.21334745</v>
       </c>
       <c r="H56">
-        <v>-0.55819883</v>
+        <v>-0.02591623</v>
       </c>
       <c r="I56">
-        <v>-0.73727734</v>
+        <v>-0.70305066</v>
       </c>
       <c r="J56">
-        <v>0.38057351</v>
+        <v>-0.71066737</v>
       </c>
     </row>
     <row r="57">
@@ -1827,31 +1827,31 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C57">
-        <v>42.5</v>
+        <v>45.76910277</v>
       </c>
       <c r="D57">
-        <v>342.85714286</v>
+        <v>225.4192587</v>
       </c>
       <c r="E57">
-        <v>12.91151261</v>
+        <v>-10.0589081</v>
       </c>
       <c r="F57">
-        <v>14.74554674</v>
+        <v>13.95103203</v>
       </c>
       <c r="G57">
-        <v>-3.98267419</v>
+        <v>-10.20720692</v>
       </c>
       <c r="H57">
-        <v>-0.64557563</v>
+        <v>0.5029454</v>
       </c>
       <c r="I57">
-        <v>-0.73727734</v>
+        <v>-0.6975516</v>
       </c>
       <c r="J57">
-        <v>0.19913371</v>
+        <v>0.51036035</v>
       </c>
     </row>
     <row r="58">
@@ -1859,31 +1859,31 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="C58">
-        <v>53.125</v>
+        <v>46.20719441</v>
       </c>
       <c r="D58">
-        <v>7.2</v>
+        <v>2.92702275</v>
       </c>
       <c r="E58">
-        <v>15.87277495</v>
+        <v>14.41810799</v>
       </c>
       <c r="F58">
-        <v>12.0014248</v>
+        <v>13.84105079</v>
       </c>
       <c r="G58">
-        <v>2.00519779</v>
+        <v>0.73720755</v>
       </c>
       <c r="H58">
-        <v>-0.79363875</v>
+        <v>-0.7209054</v>
       </c>
       <c r="I58">
-        <v>-0.60007124</v>
+        <v>-0.69205254</v>
       </c>
       <c r="J58">
-        <v>-0.10025989</v>
+        <v>-0.03686038</v>
       </c>
     </row>
     <row r="59">
@@ -1891,31 +1891,31 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="C59">
-        <v>53.125</v>
+        <v>46.64209782</v>
       </c>
       <c r="D59">
-        <v>21.6</v>
+        <v>140.4347868</v>
       </c>
       <c r="E59">
-        <v>14.87543012</v>
+        <v>-11.21011038</v>
       </c>
       <c r="F59">
-        <v>12.0014248</v>
+        <v>13.73106956</v>
       </c>
       <c r="G59">
-        <v>5.88959943</v>
+        <v>9.26235144</v>
       </c>
       <c r="H59">
-        <v>-0.74377151</v>
+        <v>0.56050552</v>
       </c>
       <c r="I59">
-        <v>-0.60007124</v>
+        <v>-0.68655348</v>
       </c>
       <c r="J59">
-        <v>-0.29447997</v>
+        <v>-0.46311757</v>
       </c>
     </row>
     <row r="60">
@@ -1923,31 +1923,31 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C60">
-        <v>53.125</v>
+        <v>47.07390611</v>
       </c>
       <c r="D60">
-        <v>36</v>
+        <v>277.94255085</v>
       </c>
       <c r="E60">
-        <v>12.94340732</v>
+        <v>2.02360023</v>
       </c>
       <c r="F60">
-        <v>12.0014248</v>
+        <v>13.62108832</v>
       </c>
       <c r="G60">
-        <v>9.40393587</v>
+        <v>-14.50417164</v>
       </c>
       <c r="H60">
-        <v>-0.64717037</v>
+        <v>-0.10118001</v>
       </c>
       <c r="I60">
-        <v>-0.60007124</v>
+        <v>-0.68105442</v>
       </c>
       <c r="J60">
-        <v>-0.47019679</v>
+        <v>0.72520858</v>
       </c>
     </row>
     <row r="61">
@@ -1955,31 +1955,31 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="C61">
-        <v>53.125</v>
+        <v>47.50270848</v>
       </c>
       <c r="D61">
-        <v>50.4</v>
+        <v>55.4503149</v>
       </c>
       <c r="E61">
-        <v>10.19810262</v>
+        <v>8.36286672</v>
       </c>
       <c r="F61">
-        <v>12.0014248</v>
+        <v>13.51110709</v>
       </c>
       <c r="G61">
-        <v>12.32738844</v>
+        <v>12.14547016</v>
       </c>
       <c r="H61">
-        <v>-0.50990513</v>
+        <v>-0.41814334</v>
       </c>
       <c r="I61">
-        <v>-0.60007124</v>
+        <v>-0.67555535</v>
       </c>
       <c r="J61">
-        <v>-0.61636942</v>
+        <v>-0.60727351</v>
       </c>
     </row>
     <row r="62">
@@ -1987,31 +1987,31 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="C62">
-        <v>53.125</v>
+        <v>47.92859036</v>
       </c>
       <c r="D62">
-        <v>64.8</v>
+        <v>192.95807895</v>
       </c>
       <c r="E62">
-        <v>6.81201364</v>
+        <v>-14.46813811</v>
       </c>
       <c r="F62">
-        <v>12.0014248</v>
+        <v>13.40112585</v>
       </c>
       <c r="G62">
-        <v>14.47626585</v>
+        <v>-3.32908477</v>
       </c>
       <c r="H62">
-        <v>-0.34060068</v>
+        <v>0.72340691</v>
       </c>
       <c r="I62">
-        <v>-0.60007124</v>
+        <v>-0.67005629</v>
       </c>
       <c r="J62">
-        <v>-0.72381329</v>
+        <v>0.16645424</v>
       </c>
     </row>
     <row r="63">
@@ -2019,31 +2019,31 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="C63">
-        <v>53.125</v>
+        <v>48.35163369</v>
       </c>
       <c r="D63">
-        <v>79.2</v>
+        <v>330.465843</v>
       </c>
       <c r="E63">
-        <v>2.99790078</v>
+        <v>13.00285654</v>
       </c>
       <c r="F63">
-        <v>12.0014248</v>
+        <v>13.29114462</v>
       </c>
       <c r="G63">
-        <v>15.71554624</v>
+        <v>-7.36689871</v>
       </c>
       <c r="H63">
-        <v>-0.14989504</v>
+        <v>-0.65014283</v>
       </c>
       <c r="I63">
-        <v>-0.60007124</v>
+        <v>-0.66455723</v>
       </c>
       <c r="J63">
-        <v>-0.78577731</v>
+        <v>0.36834494</v>
       </c>
     </row>
     <row r="64">
@@ -2051,31 +2051,31 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="C64">
-        <v>53.125</v>
+        <v>48.7719171</v>
       </c>
       <c r="D64">
-        <v>93.6</v>
+        <v>107.97360705</v>
       </c>
       <c r="E64">
-        <v>-1.00458121</v>
+        <v>-4.6415937</v>
       </c>
       <c r="F64">
-        <v>12.0014248</v>
+        <v>13.18116338</v>
       </c>
       <c r="G64">
-        <v>15.96736107</v>
+        <v>14.307779</v>
       </c>
       <c r="H64">
-        <v>0.05022906</v>
+        <v>0.23207968</v>
       </c>
       <c r="I64">
-        <v>-0.60007124</v>
+        <v>-0.65905817</v>
       </c>
       <c r="J64">
-        <v>-0.79836805</v>
+        <v>-0.71538895</v>
       </c>
     </row>
     <row r="65">
@@ -2083,31 +2083,31 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="C65">
-        <v>53.125</v>
+        <v>49.18951608</v>
       </c>
       <c r="D65">
-        <v>108</v>
+        <v>245.4813711</v>
       </c>
       <c r="E65">
-        <v>-4.94394166</v>
+        <v>-6.28190121</v>
       </c>
       <c r="F65">
-        <v>12.0014248</v>
+        <v>13.07118214</v>
       </c>
       <c r="G65">
-        <v>15.21588787</v>
+        <v>-13.77250575</v>
       </c>
       <c r="H65">
-        <v>0.24719708</v>
+        <v>0.31409506</v>
       </c>
       <c r="I65">
-        <v>-0.60007124</v>
+        <v>-0.65355911</v>
       </c>
       <c r="J65">
-        <v>-0.76079439</v>
+        <v>0.68862529</v>
       </c>
     </row>
     <row r="66">
@@ -2115,31 +2115,31 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="C66">
-        <v>53.125</v>
+        <v>49.6045032</v>
       </c>
       <c r="D66">
-        <v>122.4</v>
+        <v>22.98913515</v>
       </c>
       <c r="E66">
-        <v>-8.57265608</v>
+        <v>14.02206024</v>
       </c>
       <c r="F66">
-        <v>12.0014248</v>
+        <v>12.96120091</v>
       </c>
       <c r="G66">
-        <v>13.50834448</v>
+        <v>5.94887364</v>
       </c>
       <c r="H66">
-        <v>0.4286328</v>
+        <v>-0.70110301</v>
       </c>
       <c r="I66">
-        <v>-0.60007124</v>
+        <v>-0.64806005</v>
       </c>
       <c r="J66">
-        <v>-0.67541722</v>
+        <v>-0.29744368</v>
       </c>
     </row>
     <row r="67">
@@ -2147,31 +2147,31 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="C67">
-        <v>53.125</v>
+        <v>50.01694824</v>
       </c>
       <c r="D67">
-        <v>136.8</v>
+        <v>160.4968992</v>
       </c>
       <c r="E67">
-        <v>-11.66271899</v>
+        <v>-14.44541267</v>
       </c>
       <c r="F67">
-        <v>12.0014248</v>
+        <v>12.85121967</v>
       </c>
       <c r="G67">
-        <v>10.95202212</v>
+        <v>5.11626874</v>
       </c>
       <c r="H67">
-        <v>0.58313595</v>
+        <v>0.72227063</v>
       </c>
       <c r="I67">
-        <v>-0.60007124</v>
+        <v>-0.64256098</v>
       </c>
       <c r="J67">
-        <v>-0.54760111</v>
+        <v>-0.25581344</v>
       </c>
     </row>
     <row r="68">
@@ -2179,31 +2179,31 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C68">
-        <v>53.125</v>
+        <v>50.42691834</v>
       </c>
       <c r="D68">
-        <v>151.2</v>
+        <v>298.00466325</v>
       </c>
       <c r="E68">
-        <v>-14.01997037</v>
+        <v>7.23860001</v>
       </c>
       <c r="F68">
-        <v>12.0014248</v>
+        <v>12.74123844</v>
       </c>
       <c r="G68">
-        <v>7.70754394</v>
+        <v>-13.61115399</v>
       </c>
       <c r="H68">
-        <v>0.70099852</v>
+        <v>-0.36193</v>
       </c>
       <c r="I68">
-        <v>-0.60007124</v>
+        <v>-0.63706192</v>
       </c>
       <c r="J68">
-        <v>-0.3853772</v>
+        <v>0.6805577</v>
       </c>
     </row>
     <row r="69">
@@ -2211,31 +2211,31 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="C69">
-        <v>53.125</v>
+        <v>50.83447813</v>
       </c>
       <c r="D69">
-        <v>165.6</v>
+        <v>75.5124273</v>
       </c>
       <c r="E69">
-        <v>-15.49629546</v>
+        <v>3.87925963</v>
       </c>
       <c r="F69">
-        <v>12.0014248</v>
+        <v>12.6312572</v>
       </c>
       <c r="G69">
-        <v>3.97877242</v>
+        <v>15.01341687</v>
       </c>
       <c r="H69">
-        <v>0.77481477</v>
+        <v>-0.19396298</v>
       </c>
       <c r="I69">
-        <v>-0.60007124</v>
+        <v>-0.63156286</v>
       </c>
       <c r="J69">
-        <v>-0.19893862</v>
+        <v>-0.75067084</v>
       </c>
     </row>
     <row r="70">
@@ -2243,31 +2243,31 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>53.125</v>
+        <v>51.23968992</v>
       </c>
       <c r="D70">
-        <v>180</v>
+        <v>213.02019135</v>
       </c>
       <c r="E70">
-        <v>-15.9989313</v>
+        <v>-13.07643971</v>
       </c>
       <c r="F70">
-        <v>12.0014248</v>
+        <v>12.52127596</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>-8.49849237</v>
       </c>
       <c r="H70">
-        <v>0.79994657</v>
+        <v>0.65382199</v>
       </c>
       <c r="I70">
-        <v>-0.60007124</v>
+        <v>-0.6260638</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>0.42492462</v>
       </c>
     </row>
     <row r="71">
@@ -2275,31 +2275,31 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C71">
-        <v>53.125</v>
+        <v>51.64261374</v>
       </c>
       <c r="D71">
-        <v>194.4</v>
+        <v>350.5279554</v>
       </c>
       <c r="E71">
-        <v>-15.49629546</v>
+        <v>15.46928115</v>
       </c>
       <c r="F71">
-        <v>12.0014248</v>
+        <v>12.41129473</v>
       </c>
       <c r="G71">
-        <v>-3.97877242</v>
+        <v>-2.58091146</v>
       </c>
       <c r="H71">
-        <v>0.77481477</v>
+        <v>-0.77346406</v>
       </c>
       <c r="I71">
-        <v>-0.60007124</v>
+        <v>-0.62056474</v>
       </c>
       <c r="J71">
-        <v>0.19893862</v>
+        <v>0.12904557</v>
       </c>
     </row>
     <row r="72">
@@ -2307,31 +2307,31 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="C72">
-        <v>53.125</v>
+        <v>52.04330752</v>
       </c>
       <c r="D72">
-        <v>208.8</v>
+        <v>128.03571945</v>
       </c>
       <c r="E72">
-        <v>-14.01997037</v>
+        <v>-9.71642959</v>
       </c>
       <c r="F72">
-        <v>12.0014248</v>
+        <v>12.30131349</v>
       </c>
       <c r="G72">
-        <v>-7.70754394</v>
+        <v>12.42049445</v>
       </c>
       <c r="H72">
-        <v>0.70099852</v>
+        <v>0.48582148</v>
       </c>
       <c r="I72">
-        <v>-0.60007124</v>
+        <v>-0.61506567</v>
       </c>
       <c r="J72">
-        <v>0.3853772</v>
+        <v>-0.62102472</v>
       </c>
     </row>
     <row r="73">
@@ -2339,31 +2339,31 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="C73">
-        <v>53.125</v>
+        <v>52.44182715</v>
       </c>
       <c r="D73">
-        <v>223.2</v>
+        <v>265.5434835</v>
       </c>
       <c r="E73">
-        <v>-11.66271899</v>
+        <v>-1.23194932</v>
       </c>
       <c r="F73">
-        <v>12.0014248</v>
+        <v>12.19133226</v>
       </c>
       <c r="G73">
-        <v>-10.95202212</v>
+        <v>-15.8067618</v>
       </c>
       <c r="H73">
-        <v>0.58313595</v>
+        <v>0.06159747</v>
       </c>
       <c r="I73">
-        <v>-0.60007124</v>
+        <v>-0.60956661</v>
       </c>
       <c r="J73">
-        <v>0.54760111</v>
+        <v>0.79033809</v>
       </c>
     </row>
     <row r="74">
@@ -2371,31 +2371,31 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>53.125</v>
+        <v>52.83822663</v>
       </c>
       <c r="D74">
-        <v>237.6</v>
+        <v>43.05124755</v>
       </c>
       <c r="E74">
-        <v>-8.57265608</v>
+        <v>11.64707237</v>
       </c>
       <c r="F74">
-        <v>12.0014248</v>
+        <v>12.08135102</v>
       </c>
       <c r="G74">
-        <v>-13.50834448</v>
+        <v>10.88056353</v>
       </c>
       <c r="H74">
-        <v>0.4286328</v>
+        <v>-0.58235362</v>
       </c>
       <c r="I74">
-        <v>-0.60007124</v>
+        <v>-0.60406755</v>
       </c>
       <c r="J74">
-        <v>0.67541722</v>
+        <v>-0.54402818</v>
       </c>
     </row>
     <row r="75">
@@ -2403,31 +2403,31 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C75">
-        <v>53.125</v>
+        <v>53.23255811</v>
       </c>
       <c r="D75">
-        <v>252</v>
+        <v>180.5590116</v>
       </c>
       <c r="E75">
-        <v>-4.94394166</v>
+        <v>-16.02067015</v>
       </c>
       <c r="F75">
-        <v>12.0014248</v>
+        <v>11.97136979</v>
       </c>
       <c r="G75">
-        <v>-15.21588787</v>
+        <v>-0.15631212</v>
       </c>
       <c r="H75">
-        <v>0.24719708</v>
+        <v>0.80103351</v>
       </c>
       <c r="I75">
-        <v>-0.60007124</v>
+        <v>-0.59856849</v>
       </c>
       <c r="J75">
-        <v>0.76079439</v>
+        <v>0.00781561</v>
       </c>
     </row>
     <row r="76">
@@ -2435,31 +2435,31 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="C76">
-        <v>53.125</v>
+        <v>53.62487201</v>
       </c>
       <c r="D76">
-        <v>266.4</v>
+        <v>318.06677565</v>
       </c>
       <c r="E76">
-        <v>-1.00458121</v>
+        <v>11.97943048</v>
       </c>
       <c r="F76">
-        <v>12.0014248</v>
+        <v>11.86138855</v>
       </c>
       <c r="G76">
-        <v>-15.96736107</v>
+        <v>-10.76107369</v>
       </c>
       <c r="H76">
-        <v>0.05022906</v>
+        <v>-0.59897152</v>
       </c>
       <c r="I76">
-        <v>-0.60007124</v>
+        <v>-0.59306943</v>
       </c>
       <c r="J76">
-        <v>0.79836805</v>
+        <v>0.53805368</v>
       </c>
     </row>
     <row r="77">
@@ -2467,31 +2467,31 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="C77">
-        <v>53.125</v>
+        <v>54.01521712</v>
       </c>
       <c r="D77">
-        <v>280.8</v>
+        <v>95.5745397</v>
       </c>
       <c r="E77">
-        <v>2.99790078</v>
+        <v>-1.57207189</v>
       </c>
       <c r="F77">
-        <v>12.0014248</v>
+        <v>11.75140731</v>
       </c>
       <c r="G77">
-        <v>-15.71554624</v>
+        <v>16.10692448</v>
       </c>
       <c r="H77">
-        <v>-0.14989504</v>
+        <v>0.07860359</v>
       </c>
       <c r="I77">
-        <v>-0.60007124</v>
+        <v>-0.58757037</v>
       </c>
       <c r="J77">
-        <v>0.78577731</v>
+        <v>-0.80534622</v>
       </c>
     </row>
     <row r="78">
@@ -2499,31 +2499,31 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="C78">
-        <v>53.125</v>
+        <v>54.40364062</v>
       </c>
       <c r="D78">
-        <v>295.2</v>
+        <v>233.08230375</v>
       </c>
       <c r="E78">
-        <v>6.81201364</v>
+        <v>-9.76850325</v>
       </c>
       <c r="F78">
-        <v>12.0014248</v>
+        <v>11.64142608</v>
       </c>
       <c r="G78">
-        <v>-14.47626585</v>
+        <v>-13.00205919</v>
       </c>
       <c r="H78">
-        <v>-0.34060068</v>
+        <v>0.48842516</v>
       </c>
       <c r="I78">
-        <v>-0.60007124</v>
+        <v>-0.5820713</v>
       </c>
       <c r="J78">
-        <v>0.72381329</v>
+        <v>0.65010296</v>
       </c>
     </row>
     <row r="79">
@@ -2531,31 +2531,31 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="C79">
-        <v>53.125</v>
+        <v>54.79018821</v>
       </c>
       <c r="D79">
-        <v>309.6</v>
+        <v>10.5900678</v>
       </c>
       <c r="E79">
-        <v>10.19810262</v>
+        <v>16.06259215</v>
       </c>
       <c r="F79">
-        <v>12.0014248</v>
+        <v>11.53144484</v>
       </c>
       <c r="G79">
-        <v>-12.32738844</v>
+        <v>3.00315054</v>
       </c>
       <c r="H79">
-        <v>-0.50990513</v>
+        <v>-0.80312961</v>
       </c>
       <c r="I79">
-        <v>-0.60007124</v>
+        <v>-0.57657224</v>
       </c>
       <c r="J79">
-        <v>0.61636942</v>
+        <v>-0.15015753</v>
       </c>
     </row>
     <row r="80">
@@ -2563,31 +2563,31 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="C80">
-        <v>53.125</v>
+        <v>55.17490417</v>
       </c>
       <c r="D80">
-        <v>324</v>
+        <v>148.09783185</v>
       </c>
       <c r="E80">
-        <v>12.94340732</v>
+        <v>-13.9380745</v>
       </c>
       <c r="F80">
-        <v>12.0014248</v>
+        <v>11.42146361</v>
       </c>
       <c r="G80">
-        <v>-9.40393587</v>
+        <v>8.67641909</v>
       </c>
       <c r="H80">
-        <v>-0.64717037</v>
+        <v>0.69690373</v>
       </c>
       <c r="I80">
-        <v>-0.60007124</v>
+        <v>-0.57107318</v>
       </c>
       <c r="J80">
-        <v>0.47019679</v>
+        <v>-0.43382095</v>
       </c>
     </row>
     <row r="81">
@@ -2595,31 +2595,31 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="C81">
-        <v>53.125</v>
+        <v>55.55783137</v>
       </c>
       <c r="D81">
-        <v>338.4</v>
+        <v>285.6055959</v>
       </c>
       <c r="E81">
-        <v>14.87543012</v>
+        <v>4.43710146</v>
       </c>
       <c r="F81">
-        <v>12.0014248</v>
+        <v>11.31148237</v>
       </c>
       <c r="G81">
-        <v>-5.88959943</v>
+        <v>-15.88592135</v>
       </c>
       <c r="H81">
-        <v>-0.74377151</v>
+        <v>-0.22185507</v>
       </c>
       <c r="I81">
-        <v>-0.60007124</v>
+        <v>-0.56557412</v>
       </c>
       <c r="J81">
-        <v>0.29447997</v>
+        <v>0.79429607</v>
       </c>
     </row>
     <row r="82">
@@ -2627,31 +2627,31 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>53.125</v>
+        <v>55.93901142</v>
       </c>
       <c r="D82">
-        <v>352.8</v>
+        <v>63.11335995</v>
       </c>
       <c r="E82">
-        <v>15.87277495</v>
+        <v>7.49287152</v>
       </c>
       <c r="F82">
-        <v>12.0014248</v>
+        <v>11.20150113</v>
       </c>
       <c r="G82">
-        <v>-2.00519779</v>
+        <v>14.7777958</v>
       </c>
       <c r="H82">
-        <v>-0.79363875</v>
+        <v>-0.37464358</v>
       </c>
       <c r="I82">
-        <v>-0.60007124</v>
+        <v>-0.56007506</v>
       </c>
       <c r="J82">
-        <v>0.10025989</v>
+        <v>-0.73888979</v>
       </c>
     </row>
     <row r="83">
@@ -2659,31 +2659,31 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C83">
-        <v>63.75</v>
+        <v>56.31848467</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>200.621124</v>
       </c>
       <c r="E83">
-        <v>17.93745483</v>
+        <v>-15.57636221</v>
       </c>
       <c r="F83">
-        <v>8.8457738</v>
+        <v>11.0915199</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>-5.86132465</v>
       </c>
       <c r="H83">
-        <v>-0.89687274</v>
+        <v>0.77881811</v>
       </c>
       <c r="I83">
-        <v>-0.44228869</v>
+        <v>-0.55457599</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>0.29306623</v>
       </c>
     </row>
     <row r="84">
@@ -2691,31 +2691,31 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="C84">
-        <v>63.75</v>
+        <v>56.69629025</v>
       </c>
       <c r="D84">
-        <v>12.85714286</v>
+        <v>338.12888805</v>
       </c>
       <c r="E84">
-        <v>17.48772539</v>
+        <v>15.51232923</v>
       </c>
       <c r="F84">
-        <v>8.8457738</v>
+        <v>10.98153866</v>
       </c>
       <c r="G84">
-        <v>3.9914592</v>
+        <v>-6.2268331</v>
       </c>
       <c r="H84">
-        <v>-0.87438627</v>
+        <v>-0.77561646</v>
       </c>
       <c r="I84">
-        <v>-0.44228869</v>
+        <v>-0.54907693</v>
       </c>
       <c r="J84">
-        <v>-0.19957296</v>
+        <v>0.31134166</v>
       </c>
     </row>
     <row r="85">
@@ -2723,31 +2723,31 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="C85">
-        <v>63.75</v>
+        <v>57.07246618</v>
       </c>
       <c r="D85">
-        <v>25.71428571</v>
+        <v>115.6366521</v>
       </c>
       <c r="E85">
-        <v>16.16108837</v>
+        <v>-7.26318208</v>
       </c>
       <c r="F85">
-        <v>8.8457738</v>
+        <v>10.87155743</v>
       </c>
       <c r="G85">
-        <v>7.78276997</v>
+        <v>15.13457714</v>
       </c>
       <c r="H85">
-        <v>-0.80805442</v>
+        <v>0.3631591</v>
       </c>
       <c r="I85">
-        <v>-0.44228869</v>
+        <v>-0.54357787</v>
       </c>
       <c r="J85">
-        <v>-0.3891385</v>
+        <v>-0.75672886</v>
       </c>
     </row>
     <row r="86">
@@ -2755,31 +2755,31 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C86">
-        <v>63.75</v>
+        <v>57.44704939</v>
       </c>
       <c r="D86">
-        <v>38.57142857</v>
+        <v>253.14441615</v>
       </c>
       <c r="E86">
-        <v>14.0240669</v>
+        <v>-4.88812033</v>
       </c>
       <c r="F86">
-        <v>8.8457738</v>
+        <v>10.76157619</v>
       </c>
       <c r="G86">
-        <v>11.18382016</v>
+        <v>-16.13365295</v>
       </c>
       <c r="H86">
-        <v>-0.70120335</v>
+        <v>0.24440602</v>
       </c>
       <c r="I86">
-        <v>-0.44228869</v>
+        <v>-0.53807881</v>
       </c>
       <c r="J86">
-        <v>-0.55919101</v>
+        <v>0.80668265</v>
       </c>
     </row>
     <row r="87">
@@ -2787,31 +2787,31 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="C87">
-        <v>63.75</v>
+        <v>57.82007573</v>
       </c>
       <c r="D87">
-        <v>51.42857143</v>
+        <v>30.6521802</v>
       </c>
       <c r="E87">
-        <v>11.18382016</v>
+        <v>14.56244022</v>
       </c>
       <c r="F87">
-        <v>8.8457738</v>
+        <v>10.65159496</v>
       </c>
       <c r="G87">
-        <v>14.0240669</v>
+        <v>8.63011354</v>
       </c>
       <c r="H87">
-        <v>-0.55919101</v>
+        <v>-0.72812201</v>
       </c>
       <c r="I87">
-        <v>-0.44228869</v>
+        <v>-0.53257975</v>
       </c>
       <c r="J87">
-        <v>-0.70120335</v>
+        <v>-0.43150568</v>
       </c>
     </row>
     <row r="88">
@@ -2819,31 +2819,31 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="C88">
-        <v>63.75</v>
+        <v>58.19158008</v>
       </c>
       <c r="D88">
-        <v>64.28571429</v>
+        <v>168.15994425</v>
       </c>
       <c r="E88">
-        <v>7.78276997</v>
+        <v>-16.63469467</v>
       </c>
       <c r="F88">
-        <v>8.8457738</v>
+        <v>10.54161372</v>
       </c>
       <c r="G88">
-        <v>16.16108837</v>
+        <v>3.48730749</v>
       </c>
       <c r="H88">
-        <v>-0.3891385</v>
+        <v>0.83173473</v>
       </c>
       <c r="I88">
-        <v>-0.44228869</v>
+        <v>-0.52708069</v>
       </c>
       <c r="J88">
-        <v>-0.80805442</v>
+        <v>-0.17436537</v>
       </c>
     </row>
     <row r="89">
@@ -2851,31 +2851,31 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C89">
-        <v>63.75</v>
+        <v>58.56159636</v>
       </c>
       <c r="D89">
-        <v>77.14285714</v>
+        <v>305.6677083</v>
       </c>
       <c r="E89">
-        <v>3.9914592</v>
+        <v>9.94975186</v>
       </c>
       <c r="F89">
-        <v>8.8457738</v>
+        <v>10.43163248</v>
       </c>
       <c r="G89">
-        <v>17.48772539</v>
+        <v>-13.8630257</v>
       </c>
       <c r="H89">
-        <v>-0.19957296</v>
+        <v>-0.49748759</v>
       </c>
       <c r="I89">
-        <v>-0.44228869</v>
+        <v>-0.52158162</v>
       </c>
       <c r="J89">
-        <v>-0.87438627</v>
+        <v>0.69315128</v>
       </c>
     </row>
     <row r="90">
@@ -2883,31 +2883,31 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="C90">
-        <v>63.75</v>
+        <v>58.93015755</v>
       </c>
       <c r="D90">
-        <v>90</v>
+        <v>83.17547235</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>2.03563367</v>
       </c>
       <c r="F90">
-        <v>8.8457738</v>
+        <v>10.32165125</v>
       </c>
       <c r="G90">
-        <v>17.93745483</v>
+        <v>17.00940067</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>-0.10178168</v>
       </c>
       <c r="I90">
-        <v>-0.44228869</v>
+        <v>-0.51608256</v>
       </c>
       <c r="J90">
-        <v>-0.89687274</v>
+        <v>-0.85047003</v>
       </c>
     </row>
     <row r="91">
@@ -2915,31 +2915,31 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="C91">
-        <v>63.75</v>
+        <v>59.29729576</v>
       </c>
       <c r="D91">
-        <v>102.85714286</v>
+        <v>220.6832364</v>
       </c>
       <c r="E91">
-        <v>-3.9914592</v>
+        <v>-13.04058563</v>
       </c>
       <c r="F91">
-        <v>8.8457738</v>
+        <v>10.21167001</v>
       </c>
       <c r="G91">
-        <v>17.48772539</v>
+        <v>-11.21003666</v>
       </c>
       <c r="H91">
-        <v>0.19957296</v>
+        <v>0.65202928</v>
       </c>
       <c r="I91">
-        <v>-0.44228869</v>
+        <v>-0.5105835</v>
       </c>
       <c r="J91">
-        <v>-0.87438627</v>
+        <v>0.56050183</v>
       </c>
     </row>
     <row r="92">
@@ -2947,31 +2947,31 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C92">
-        <v>63.75</v>
+        <v>59.66304224</v>
       </c>
       <c r="D92">
-        <v>115.71428571</v>
+        <v>358.19100045</v>
       </c>
       <c r="E92">
-        <v>-7.78276997</v>
+        <v>17.25279583</v>
       </c>
       <c r="F92">
-        <v>8.8457738</v>
+        <v>10.10168878</v>
       </c>
       <c r="G92">
-        <v>16.16108837</v>
+        <v>-0.54490357</v>
       </c>
       <c r="H92">
-        <v>0.3891385</v>
+        <v>-0.86263979</v>
       </c>
       <c r="I92">
-        <v>-0.44228869</v>
+        <v>-0.50508444</v>
       </c>
       <c r="J92">
-        <v>-0.80805442</v>
+        <v>0.02724518</v>
       </c>
     </row>
     <row r="93">
@@ -2979,31 +2979,31 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="C93">
-        <v>63.75</v>
+        <v>60.02742744</v>
       </c>
       <c r="D93">
-        <v>128.57142857</v>
+        <v>135.6987645</v>
       </c>
       <c r="E93">
-        <v>-11.18382016</v>
+        <v>-12.39932544</v>
       </c>
       <c r="F93">
-        <v>8.8457738</v>
+        <v>9.99170754</v>
       </c>
       <c r="G93">
-        <v>14.0240669</v>
+        <v>12.10051689</v>
       </c>
       <c r="H93">
-        <v>0.55919101</v>
+        <v>0.61996627</v>
       </c>
       <c r="I93">
-        <v>-0.44228869</v>
+        <v>-0.49958538</v>
       </c>
       <c r="J93">
-        <v>-0.70120335</v>
+        <v>-0.60502584</v>
       </c>
     </row>
     <row r="94">
@@ -3011,31 +3011,31 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="C94">
-        <v>63.75</v>
+        <v>60.39048104</v>
       </c>
       <c r="D94">
-        <v>141.42857143</v>
+        <v>273.20652855</v>
       </c>
       <c r="E94">
-        <v>-14.0240669</v>
+        <v>0.97261689</v>
       </c>
       <c r="F94">
-        <v>8.8457738</v>
+        <v>9.88172631</v>
       </c>
       <c r="G94">
-        <v>11.18382016</v>
+        <v>-17.361034</v>
       </c>
       <c r="H94">
-        <v>0.70120335</v>
+        <v>-0.04863084</v>
       </c>
       <c r="I94">
-        <v>-0.44228869</v>
+        <v>-0.49408632</v>
       </c>
       <c r="J94">
-        <v>-0.55919101</v>
+        <v>0.8680517</v>
       </c>
     </row>
     <row r="95">
@@ -3043,31 +3043,31 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="C95">
-        <v>63.75</v>
+        <v>60.75223193</v>
       </c>
       <c r="D95">
-        <v>154.28571429</v>
+        <v>50.7142926</v>
       </c>
       <c r="E95">
-        <v>-16.16108837</v>
+        <v>11.04931786</v>
       </c>
       <c r="F95">
-        <v>8.8457738</v>
+        <v>9.77174507</v>
       </c>
       <c r="G95">
-        <v>7.78276997</v>
+        <v>13.50650114</v>
       </c>
       <c r="H95">
-        <v>0.80805442</v>
+        <v>-0.55246589</v>
       </c>
       <c r="I95">
-        <v>-0.44228869</v>
+        <v>-0.48858725</v>
       </c>
       <c r="J95">
-        <v>-0.3891385</v>
+        <v>-0.67532506</v>
       </c>
     </row>
     <row r="96">
@@ -3075,31 +3075,31 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="C96">
-        <v>63.75</v>
+        <v>61.11270831</v>
       </c>
       <c r="D96">
-        <v>167.14285714</v>
+        <v>188.22205665</v>
       </c>
       <c r="E96">
-        <v>-17.48772539</v>
+        <v>-17.33143833</v>
       </c>
       <c r="F96">
-        <v>8.8457738</v>
+        <v>9.66176383</v>
       </c>
       <c r="G96">
-        <v>3.9914592</v>
+        <v>-2.50430927</v>
       </c>
       <c r="H96">
-        <v>0.87438627</v>
+        <v>0.86657192</v>
       </c>
       <c r="I96">
-        <v>-0.44228869</v>
+        <v>-0.48308819</v>
       </c>
       <c r="J96">
-        <v>-0.19957296</v>
+        <v>0.12521546</v>
       </c>
     </row>
     <row r="97">
@@ -3107,31 +3107,31 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="C97">
-        <v>63.75</v>
+        <v>61.47193768</v>
       </c>
       <c r="D97">
-        <v>180</v>
+        <v>325.7298207</v>
       </c>
       <c r="E97">
-        <v>-17.93745483</v>
+        <v>14.52107516</v>
       </c>
       <c r="F97">
-        <v>8.8457738</v>
+        <v>9.5517826</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>-9.89453513</v>
       </c>
       <c r="H97">
-        <v>0.89687274</v>
+        <v>-0.72605376</v>
       </c>
       <c r="I97">
-        <v>-0.44228869</v>
+        <v>-0.47758913</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>0.49472676</v>
       </c>
     </row>
     <row r="98">
@@ -3139,31 +3139,31 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="C98">
-        <v>63.75</v>
+        <v>61.82994687</v>
       </c>
       <c r="D98">
-        <v>192.85714286</v>
+        <v>103.23758475</v>
       </c>
       <c r="E98">
-        <v>-17.48772539</v>
+        <v>-4.03731476</v>
       </c>
       <c r="F98">
-        <v>8.8457738</v>
+        <v>9.44180136</v>
       </c>
       <c r="G98">
-        <v>-3.9914592</v>
+        <v>17.16253118</v>
       </c>
       <c r="H98">
-        <v>0.87438627</v>
+        <v>0.20186574</v>
       </c>
       <c r="I98">
-        <v>-0.44228869</v>
+        <v>-0.47209007</v>
       </c>
       <c r="J98">
-        <v>0.19957296</v>
+        <v>-0.85812656</v>
       </c>
     </row>
     <row r="99">
@@ -3171,31 +3171,31 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="C99">
-        <v>63.75</v>
+        <v>62.18676207</v>
       </c>
       <c r="D99">
-        <v>205.71428571</v>
+        <v>240.7453488</v>
       </c>
       <c r="E99">
-        <v>-16.16108837</v>
+        <v>-8.6447007</v>
       </c>
       <c r="F99">
-        <v>8.8457738</v>
+        <v>9.33182013</v>
       </c>
       <c r="G99">
-        <v>-7.78276997</v>
+        <v>-15.43328491</v>
       </c>
       <c r="H99">
-        <v>0.80805442</v>
+        <v>0.43223503</v>
       </c>
       <c r="I99">
-        <v>-0.44228869</v>
+        <v>-0.46659101</v>
       </c>
       <c r="J99">
-        <v>0.3891385</v>
+        <v>0.77166425</v>
       </c>
     </row>
     <row r="100">
@@ -3203,31 +3203,31 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="C100">
-        <v>63.75</v>
+        <v>62.54240884</v>
       </c>
       <c r="D100">
-        <v>218.57142857</v>
+        <v>18.25311285</v>
       </c>
       <c r="E100">
-        <v>-14.0240669</v>
+        <v>16.85405333</v>
       </c>
       <c r="F100">
-        <v>8.8457738</v>
+        <v>9.22183889</v>
       </c>
       <c r="G100">
-        <v>-11.18382016</v>
+        <v>5.55864856</v>
       </c>
       <c r="H100">
-        <v>0.70120335</v>
+        <v>-0.84270267</v>
       </c>
       <c r="I100">
-        <v>-0.44228869</v>
+        <v>-0.46109194</v>
       </c>
       <c r="J100">
-        <v>0.55919101</v>
+        <v>-0.27793243</v>
       </c>
     </row>
     <row r="101">
@@ -3235,31 +3235,31 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="C101">
-        <v>63.75</v>
+        <v>62.89691216</v>
       </c>
       <c r="D101">
-        <v>231.42857143</v>
+        <v>155.7608769</v>
       </c>
       <c r="E101">
-        <v>-11.18382016</v>
+        <v>-16.23418507</v>
       </c>
       <c r="F101">
-        <v>8.8457738</v>
+        <v>9.11185765</v>
       </c>
       <c r="G101">
-        <v>-14.0240669</v>
+        <v>7.30926023</v>
       </c>
       <c r="H101">
-        <v>0.55919101</v>
+        <v>0.81170925</v>
       </c>
       <c r="I101">
-        <v>-0.44228869</v>
+        <v>-0.45559288</v>
       </c>
       <c r="J101">
-        <v>0.70120335</v>
+        <v>-0.36546301</v>
       </c>
     </row>
     <row r="102">
@@ -3267,31 +3267,31 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="C102">
-        <v>63.75</v>
+        <v>63.25029644</v>
       </c>
       <c r="D102">
-        <v>244.28571429</v>
+        <v>293.26864095</v>
       </c>
       <c r="E102">
-        <v>-7.78276997</v>
+        <v>7.05531574</v>
       </c>
       <c r="F102">
-        <v>8.8457738</v>
+        <v>9.00187642</v>
       </c>
       <c r="G102">
-        <v>-16.16108837</v>
+        <v>-16.40697232</v>
       </c>
       <c r="H102">
-        <v>0.3891385</v>
+        <v>-0.35276579</v>
       </c>
       <c r="I102">
-        <v>-0.44228869</v>
+        <v>-0.45009382</v>
       </c>
       <c r="J102">
-        <v>0.80805442</v>
+        <v>0.82034862</v>
       </c>
     </row>
     <row r="103">
@@ -3299,31 +3299,31 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="C103">
-        <v>63.75</v>
+        <v>63.60258551</v>
       </c>
       <c r="D103">
-        <v>257.14285714</v>
+        <v>70.776405</v>
       </c>
       <c r="E103">
-        <v>-3.9914592</v>
+        <v>5.898493</v>
       </c>
       <c r="F103">
-        <v>8.8457738</v>
+        <v>8.89189518</v>
       </c>
       <c r="G103">
-        <v>-17.48772539</v>
+        <v>16.91573174</v>
       </c>
       <c r="H103">
-        <v>0.19957296</v>
+        <v>-0.29492465</v>
       </c>
       <c r="I103">
-        <v>-0.44228869</v>
+        <v>-0.44459476</v>
       </c>
       <c r="J103">
-        <v>0.87438627</v>
+        <v>-0.84578659</v>
       </c>
     </row>
     <row r="104">
@@ -3331,31 +3331,31 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="C104">
-        <v>63.75</v>
+        <v>63.9538027</v>
       </c>
       <c r="D104">
-        <v>270</v>
+        <v>208.28416905</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>-15.82347987</v>
       </c>
       <c r="F104">
-        <v>8.8457738</v>
+        <v>8.78191395</v>
       </c>
       <c r="G104">
-        <v>-17.93745483</v>
+        <v>-8.5144273</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>0.79117399</v>
       </c>
       <c r="I104">
-        <v>-0.44228869</v>
+        <v>-0.4390957</v>
       </c>
       <c r="J104">
-        <v>0.89687274</v>
+        <v>0.42572136</v>
       </c>
     </row>
     <row r="105">
@@ -3363,31 +3363,31 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="C105">
-        <v>63.75</v>
+        <v>64.30397081</v>
       </c>
       <c r="D105">
-        <v>282.85714286</v>
+        <v>345.7919331</v>
       </c>
       <c r="E105">
-        <v>3.9914592</v>
+        <v>17.47085862</v>
       </c>
       <c r="F105">
-        <v>8.8457738</v>
+        <v>8.67193271</v>
       </c>
       <c r="G105">
-        <v>-17.48772539</v>
+        <v>-4.42342425</v>
       </c>
       <c r="H105">
-        <v>-0.19957296</v>
+        <v>-0.87354293</v>
       </c>
       <c r="I105">
-        <v>-0.44228869</v>
+        <v>-0.43359664</v>
       </c>
       <c r="J105">
-        <v>0.87438627</v>
+        <v>0.22117121</v>
       </c>
     </row>
     <row r="106">
@@ -3395,31 +3395,31 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="C106">
-        <v>63.75</v>
+        <v>64.65311215</v>
       </c>
       <c r="D106">
-        <v>295.71428571</v>
+        <v>123.29969715</v>
       </c>
       <c r="E106">
-        <v>7.78276997</v>
+        <v>-9.92331564</v>
       </c>
       <c r="F106">
-        <v>8.8457738</v>
+        <v>8.56195148</v>
       </c>
       <c r="G106">
-        <v>-16.16108837</v>
+        <v>15.10697831</v>
       </c>
       <c r="H106">
-        <v>-0.3891385</v>
+        <v>0.49616578</v>
       </c>
       <c r="I106">
-        <v>-0.44228869</v>
+        <v>-0.42809757</v>
       </c>
       <c r="J106">
-        <v>0.80805442</v>
+        <v>-0.75534892</v>
       </c>
     </row>
     <row r="107">
@@ -3427,31 +3427,31 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="C107">
-        <v>63.75</v>
+        <v>65.00124855</v>
       </c>
       <c r="D107">
-        <v>308.57142857</v>
+        <v>260.8074612</v>
       </c>
       <c r="E107">
-        <v>11.18382016</v>
+        <v>-2.89573064</v>
       </c>
       <c r="F107">
-        <v>8.8457738</v>
+        <v>8.45197024</v>
       </c>
       <c r="G107">
-        <v>-14.0240669</v>
+        <v>-17.89354473</v>
       </c>
       <c r="H107">
-        <v>-0.55919101</v>
+        <v>0.14478653</v>
       </c>
       <c r="I107">
-        <v>-0.44228869</v>
+        <v>-0.42259851</v>
       </c>
       <c r="J107">
-        <v>0.70120335</v>
+        <v>0.89467724</v>
       </c>
     </row>
     <row r="108">
@@ -3459,31 +3459,31 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C108">
-        <v>63.75</v>
+        <v>65.34840139</v>
       </c>
       <c r="D108">
-        <v>321.42857143</v>
+        <v>38.31522525</v>
       </c>
       <c r="E108">
-        <v>14.0240669</v>
+        <v>14.26205623</v>
       </c>
       <c r="F108">
-        <v>8.8457738</v>
+        <v>8.341989</v>
       </c>
       <c r="G108">
-        <v>-11.18382016</v>
+        <v>11.26964825</v>
       </c>
       <c r="H108">
-        <v>-0.70120335</v>
+        <v>-0.71310281</v>
       </c>
       <c r="I108">
-        <v>-0.44228869</v>
+        <v>-0.41709945</v>
       </c>
       <c r="J108">
-        <v>0.55919101</v>
+        <v>-0.56348241</v>
       </c>
     </row>
     <row r="109">
@@ -3491,31 +3491,31 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="C109">
-        <v>63.75</v>
+        <v>65.69459158</v>
       </c>
       <c r="D109">
-        <v>334.28571429</v>
+        <v>175.8229893</v>
       </c>
       <c r="E109">
-        <v>16.16108837</v>
+        <v>-18.17887292</v>
       </c>
       <c r="F109">
-        <v>8.8457738</v>
+        <v>8.23200777</v>
       </c>
       <c r="G109">
-        <v>-7.78276997</v>
+        <v>1.32763979</v>
       </c>
       <c r="H109">
-        <v>-0.80805442</v>
+        <v>0.90894365</v>
       </c>
       <c r="I109">
-        <v>-0.44228869</v>
+        <v>-0.41160039</v>
       </c>
       <c r="J109">
-        <v>0.3891385</v>
+        <v>-0.06638199</v>
       </c>
     </row>
     <row r="110">
@@ -3523,31 +3523,31 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C110">
-        <v>63.75</v>
+        <v>66.03983964</v>
       </c>
       <c r="D110">
-        <v>347.14285714</v>
+        <v>313.33075335</v>
       </c>
       <c r="E110">
-        <v>17.48772539</v>
+        <v>12.54153859</v>
       </c>
       <c r="F110">
-        <v>8.8457738</v>
+        <v>8.12202653</v>
       </c>
       <c r="G110">
-        <v>-3.9914592</v>
+        <v>-13.29445354</v>
       </c>
       <c r="H110">
-        <v>-0.87438627</v>
+        <v>-0.62707693</v>
       </c>
       <c r="I110">
-        <v>-0.44228869</v>
+        <v>-0.40610133</v>
       </c>
       <c r="J110">
-        <v>0.19957296</v>
+        <v>0.66472268</v>
       </c>
     </row>
     <row r="111">
@@ -3555,31 +3555,31 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="C111">
-        <v>74.375</v>
+        <v>66.38416564</v>
       </c>
       <c r="D111">
-        <v>6</v>
+        <v>90.8385174</v>
       </c>
       <c r="E111">
-        <v>19.15538949</v>
+        <v>-0.26817538</v>
       </c>
       <c r="F111">
-        <v>5.38680108</v>
+        <v>8.0120453</v>
       </c>
       <c r="G111">
-        <v>2.01331256</v>
+        <v>18.32307868</v>
       </c>
       <c r="H111">
-        <v>-0.95776947</v>
+        <v>0.01340877</v>
       </c>
       <c r="I111">
-        <v>-0.26934005</v>
+        <v>-0.40060226</v>
       </c>
       <c r="J111">
-        <v>-0.10066563</v>
+        <v>-0.91615393</v>
       </c>
     </row>
     <row r="112">
@@ -3587,31 +3587,31 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="C112">
-        <v>74.375</v>
+        <v>66.72758928</v>
       </c>
       <c r="D112">
-        <v>18</v>
+        <v>228.34628145</v>
       </c>
       <c r="E112">
-        <v>18.31820706</v>
+        <v>-12.21101616</v>
       </c>
       <c r="F112">
-        <v>5.38680108</v>
+        <v>7.90206406</v>
       </c>
       <c r="G112">
-        <v>5.95194627</v>
+        <v>-13.7276534</v>
       </c>
       <c r="H112">
-        <v>-0.91591035</v>
+        <v>0.61055081</v>
       </c>
       <c r="I112">
-        <v>-0.26934005</v>
+        <v>-0.3951032</v>
       </c>
       <c r="J112">
-        <v>-0.29759731</v>
+        <v>0.68638267</v>
       </c>
     </row>
     <row r="113">
@@ -3619,31 +3619,31 @@
         <v>112</v>
       </c>
       <c r="B113">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="C113">
-        <v>74.375</v>
+        <v>67.07012984</v>
       </c>
       <c r="D113">
-        <v>30</v>
+        <v>5.8540455</v>
       </c>
       <c r="E113">
-        <v>16.68043107</v>
+        <v>18.32358883</v>
       </c>
       <c r="F113">
-        <v>5.38680108</v>
+        <v>7.79208282</v>
       </c>
       <c r="G113">
-        <v>9.63045137</v>
+        <v>1.87870642</v>
       </c>
       <c r="H113">
-        <v>-0.83402155</v>
+        <v>-0.91617944</v>
       </c>
       <c r="I113">
-        <v>-0.26934005</v>
+        <v>-0.38960414</v>
       </c>
       <c r="J113">
-        <v>-0.48152257</v>
+        <v>-0.09393532</v>
       </c>
     </row>
     <row r="114">
@@ -3651,31 +3651,31 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="C114">
-        <v>74.375</v>
+        <v>67.41180627</v>
       </c>
       <c r="D114">
-        <v>42</v>
+        <v>143.36180955</v>
       </c>
       <c r="E114">
-        <v>14.3136402</v>
+        <v>-14.81731522</v>
       </c>
       <c r="F114">
-        <v>5.38680108</v>
+        <v>7.68210159</v>
       </c>
       <c r="G114">
-        <v>12.88805953</v>
+        <v>11.01964087</v>
       </c>
       <c r="H114">
-        <v>-0.71568201</v>
+        <v>0.74086576</v>
       </c>
       <c r="I114">
-        <v>-0.26934005</v>
+        <v>-0.38410508</v>
       </c>
       <c r="J114">
-        <v>-0.64440298</v>
+        <v>-0.55098204</v>
       </c>
     </row>
     <row r="115">
@@ -3683,31 +3683,31 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="C115">
-        <v>74.375</v>
+        <v>67.75263712</v>
       </c>
       <c r="D115">
-        <v>54</v>
+        <v>280.8695736</v>
       </c>
       <c r="E115">
-        <v>11.32127457</v>
+        <v>3.49072241</v>
       </c>
       <c r="F115">
-        <v>5.38680108</v>
+        <v>7.57212035</v>
       </c>
       <c r="G115">
-        <v>15.58239764</v>
+        <v>-18.17904977</v>
       </c>
       <c r="H115">
-        <v>-0.56606373</v>
+        <v>-0.17453612</v>
       </c>
       <c r="I115">
-        <v>-0.26934005</v>
+        <v>-0.37860602</v>
       </c>
       <c r="J115">
-        <v>-0.77911988</v>
+        <v>0.90895249</v>
       </c>
     </row>
     <row r="116">
@@ -3715,31 +3715,31 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="C116">
-        <v>74.375</v>
+        <v>68.09264062</v>
       </c>
       <c r="D116">
-        <v>66</v>
+        <v>58.37733765</v>
       </c>
       <c r="E116">
-        <v>7.83411492</v>
+        <v>9.72921067</v>
       </c>
       <c r="F116">
-        <v>5.38680108</v>
+        <v>7.46213912</v>
       </c>
       <c r="G116">
-        <v>17.5957102</v>
+        <v>15.80059934</v>
       </c>
       <c r="H116">
-        <v>-0.39170575</v>
+        <v>-0.48646053</v>
       </c>
       <c r="I116">
-        <v>-0.26934005</v>
+        <v>-0.37310696</v>
       </c>
       <c r="J116">
-        <v>-0.87978551</v>
+        <v>-0.79002997</v>
       </c>
     </row>
     <row r="117">
@@ -3747,31 +3747,31 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="C117">
-        <v>74.375</v>
+        <v>68.43183464</v>
       </c>
       <c r="D117">
-        <v>78</v>
+        <v>195.8851017</v>
       </c>
       <c r="E117">
-        <v>4.00456685</v>
+        <v>-17.88934494</v>
       </c>
       <c r="F117">
-        <v>5.38680108</v>
+        <v>7.35215788</v>
       </c>
       <c r="G117">
-        <v>18.8400058</v>
+        <v>-5.09088521</v>
       </c>
       <c r="H117">
-        <v>-0.20022834</v>
+        <v>0.89446725</v>
       </c>
       <c r="I117">
-        <v>-0.26934005</v>
+        <v>-0.36760789</v>
       </c>
       <c r="J117">
-        <v>-0.94200029</v>
+        <v>0.25454426</v>
       </c>
     </row>
     <row r="118">
@@ -3779,31 +3779,31 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7</v>
+        <v>116</v>
       </c>
       <c r="C118">
-        <v>74.375</v>
+        <v>68.77023676</v>
       </c>
       <c r="D118">
-        <v>90</v>
+        <v>333.39286575</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>16.6684244</v>
       </c>
       <c r="F118">
-        <v>5.38680108</v>
+        <v>7.24217665</v>
       </c>
       <c r="G118">
-        <v>19.26090273</v>
+        <v>-8.34952127</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>-0.83342122</v>
       </c>
       <c r="I118">
-        <v>-0.26934005</v>
+        <v>-0.36210883</v>
       </c>
       <c r="J118">
-        <v>-0.96304514</v>
+        <v>0.41747606</v>
       </c>
     </row>
     <row r="119">
@@ -3811,31 +3811,31 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="C119">
-        <v>74.375</v>
+        <v>69.10786421</v>
       </c>
       <c r="D119">
-        <v>102</v>
+        <v>110.9006298</v>
       </c>
       <c r="E119">
-        <v>-4.00456685</v>
+        <v>-6.66586587</v>
       </c>
       <c r="F119">
-        <v>5.38680108</v>
+        <v>7.13219541</v>
       </c>
       <c r="G119">
-        <v>18.8400058</v>
+        <v>17.45560142</v>
       </c>
       <c r="H119">
-        <v>0.20022834</v>
+        <v>0.33329329</v>
       </c>
       <c r="I119">
-        <v>-0.26934005</v>
+        <v>-0.35660977</v>
       </c>
       <c r="J119">
-        <v>-0.94200029</v>
+        <v>-0.87278007</v>
       </c>
     </row>
     <row r="120">
@@ -3843,31 +3843,31 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="C120">
-        <v>74.375</v>
+        <v>69.44473393</v>
       </c>
       <c r="D120">
-        <v>114</v>
+        <v>248.40839385</v>
       </c>
       <c r="E120">
-        <v>-7.83411492</v>
+        <v>-6.89119946</v>
       </c>
       <c r="F120">
-        <v>5.38680108</v>
+        <v>7.02221417</v>
       </c>
       <c r="G120">
-        <v>17.5957102</v>
+        <v>-17.41263559</v>
       </c>
       <c r="H120">
-        <v>0.39170575</v>
+        <v>0.34455997</v>
       </c>
       <c r="I120">
-        <v>-0.26934005</v>
+        <v>-0.35111071</v>
       </c>
       <c r="J120">
-        <v>-0.87978551</v>
+        <v>0.87063178</v>
       </c>
     </row>
     <row r="121">
@@ -3875,31 +3875,31 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="C121">
-        <v>74.375</v>
+        <v>69.78086257</v>
       </c>
       <c r="D121">
-        <v>126</v>
+        <v>25.9161579</v>
       </c>
       <c r="E121">
-        <v>-11.32127457</v>
+        <v>16.88018556</v>
       </c>
       <c r="F121">
-        <v>5.38680108</v>
+        <v>6.91223294</v>
       </c>
       <c r="G121">
-        <v>15.58239764</v>
+        <v>8.20246128</v>
       </c>
       <c r="H121">
-        <v>0.56606373</v>
+        <v>-0.84400928</v>
       </c>
       <c r="I121">
-        <v>-0.26934005</v>
+        <v>-0.34561165</v>
       </c>
       <c r="J121">
-        <v>-0.77911988</v>
+        <v>-0.41012306</v>
       </c>
     </row>
     <row r="122">
@@ -3907,31 +3907,31 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="C122">
-        <v>74.375</v>
+        <v>70.11626649</v>
       </c>
       <c r="D122">
-        <v>138</v>
+        <v>163.42392195</v>
       </c>
       <c r="E122">
-        <v>-14.3136402</v>
+        <v>-18.02608</v>
       </c>
       <c r="F122">
-        <v>5.38680108</v>
+        <v>6.8022517</v>
       </c>
       <c r="G122">
-        <v>12.88805953</v>
+        <v>5.36561381</v>
       </c>
       <c r="H122">
-        <v>0.71568201</v>
+        <v>0.901304</v>
       </c>
       <c r="I122">
-        <v>-0.26934005</v>
+        <v>-0.34011259</v>
       </c>
       <c r="J122">
-        <v>-0.64440298</v>
+        <v>-0.26828069</v>
       </c>
     </row>
     <row r="123">
@@ -3939,31 +3939,31 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="C123">
-        <v>74.375</v>
+        <v>70.45096178</v>
       </c>
       <c r="D123">
-        <v>150</v>
+        <v>300.931686</v>
       </c>
       <c r="E123">
-        <v>-16.68043107</v>
+        <v>9.68771</v>
       </c>
       <c r="F123">
-        <v>5.38680108</v>
+        <v>6.69227047</v>
       </c>
       <c r="G123">
-        <v>9.63045137</v>
+        <v>-16.1666877</v>
       </c>
       <c r="H123">
-        <v>0.83402155</v>
+        <v>-0.4843855</v>
       </c>
       <c r="I123">
-        <v>-0.26934005</v>
+        <v>-0.33461352</v>
       </c>
       <c r="J123">
-        <v>-0.48152257</v>
+        <v>0.80833438</v>
       </c>
     </row>
     <row r="124">
@@ -3971,31 +3971,31 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="C124">
-        <v>74.375</v>
+        <v>70.78496427</v>
       </c>
       <c r="D124">
-        <v>162</v>
+        <v>78.43945005</v>
       </c>
       <c r="E124">
-        <v>-18.31820706</v>
+        <v>3.78477874</v>
       </c>
       <c r="F124">
-        <v>5.38680108</v>
+        <v>6.58228923</v>
       </c>
       <c r="G124">
-        <v>5.95194627</v>
+        <v>18.50267328</v>
       </c>
       <c r="H124">
-        <v>0.91591035</v>
+        <v>-0.18923894</v>
       </c>
       <c r="I124">
-        <v>-0.26934005</v>
+        <v>-0.32911446</v>
       </c>
       <c r="J124">
-        <v>-0.29759731</v>
+        <v>-0.92513366</v>
       </c>
     </row>
     <row r="125">
@@ -4003,31 +4003,31 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="C125">
-        <v>74.375</v>
+        <v>71.11828951</v>
       </c>
       <c r="D125">
-        <v>174</v>
+        <v>215.9472141</v>
       </c>
       <c r="E125">
-        <v>-19.15538949</v>
+        <v>-15.319896</v>
       </c>
       <c r="F125">
-        <v>5.38680108</v>
+        <v>6.47230799</v>
       </c>
       <c r="G125">
-        <v>2.01331256</v>
+        <v>-11.10900607</v>
       </c>
       <c r="H125">
-        <v>0.95776947</v>
+        <v>0.7659948</v>
       </c>
       <c r="I125">
-        <v>-0.26934005</v>
+        <v>-0.3236154</v>
       </c>
       <c r="J125">
-        <v>-0.10066563</v>
+        <v>0.5554503</v>
       </c>
     </row>
     <row r="126">
@@ -4035,31 +4035,31 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>7</v>
+        <v>124</v>
       </c>
       <c r="C126">
-        <v>74.375</v>
+        <v>71.45095283</v>
       </c>
       <c r="D126">
-        <v>186</v>
+        <v>353.45497815</v>
       </c>
       <c r="E126">
-        <v>-19.15538949</v>
+        <v>18.83745697</v>
       </c>
       <c r="F126">
-        <v>5.38680108</v>
+        <v>6.36232676</v>
       </c>
       <c r="G126">
-        <v>-2.01331256</v>
+        <v>-2.1612527</v>
       </c>
       <c r="H126">
-        <v>0.95776947</v>
+        <v>-0.94187285</v>
       </c>
       <c r="I126">
-        <v>-0.26934005</v>
+        <v>-0.31811634</v>
       </c>
       <c r="J126">
-        <v>0.10066563</v>
+        <v>0.10806264</v>
       </c>
     </row>
     <row r="127">
@@ -4067,31 +4067,31 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="C127">
-        <v>74.375</v>
+        <v>71.7829693</v>
       </c>
       <c r="D127">
-        <v>198</v>
+        <v>130.9627422</v>
       </c>
       <c r="E127">
-        <v>-18.31820706</v>
+        <v>-12.45421013</v>
       </c>
       <c r="F127">
-        <v>5.38680108</v>
+        <v>6.25234552</v>
       </c>
       <c r="G127">
-        <v>-5.95194627</v>
+        <v>14.34575985</v>
       </c>
       <c r="H127">
-        <v>0.91591035</v>
+        <v>0.62271051</v>
       </c>
       <c r="I127">
-        <v>-0.26934005</v>
+        <v>-0.31261728</v>
       </c>
       <c r="J127">
-        <v>0.29759731</v>
+        <v>-0.71728799</v>
       </c>
     </row>
     <row r="128">
@@ -4099,31 +4099,31 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="C128">
-        <v>74.375</v>
+        <v>72.11435376</v>
       </c>
       <c r="D128">
-        <v>210</v>
+        <v>268.47050625</v>
       </c>
       <c r="E128">
-        <v>-16.68043107</v>
+        <v>-0.50803133</v>
       </c>
       <c r="F128">
-        <v>5.38680108</v>
+        <v>6.14236429</v>
       </c>
       <c r="G128">
-        <v>-9.63045137</v>
+        <v>-19.02664619</v>
       </c>
       <c r="H128">
-        <v>0.83402155</v>
+        <v>0.02540157</v>
       </c>
       <c r="I128">
-        <v>-0.26934005</v>
+        <v>-0.30711821</v>
       </c>
       <c r="J128">
-        <v>0.48152257</v>
+        <v>0.95133231</v>
       </c>
     </row>
     <row r="129">
@@ -4131,31 +4131,31 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C129">
-        <v>74.375</v>
+        <v>72.44512084</v>
       </c>
       <c r="D129">
-        <v>222</v>
+        <v>45.9782703</v>
       </c>
       <c r="E129">
-        <v>-14.3136402</v>
+        <v>13.25134283</v>
       </c>
       <c r="F129">
-        <v>5.38680108</v>
+        <v>6.03238305</v>
       </c>
       <c r="G129">
-        <v>-12.88805953</v>
+        <v>13.71175655</v>
       </c>
       <c r="H129">
-        <v>0.71568201</v>
+        <v>-0.66256714</v>
       </c>
       <c r="I129">
-        <v>-0.26934005</v>
+        <v>-0.30161915</v>
       </c>
       <c r="J129">
-        <v>0.64440298</v>
+        <v>-0.68558783</v>
       </c>
     </row>
     <row r="130">
@@ -4163,31 +4163,31 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="C130">
-        <v>74.375</v>
+        <v>72.77528493</v>
       </c>
       <c r="D130">
-        <v>234</v>
+        <v>183.48603435</v>
       </c>
       <c r="E130">
-        <v>-11.32127457</v>
+        <v>-19.06766706</v>
       </c>
       <c r="F130">
-        <v>5.38680108</v>
+        <v>5.92240182</v>
       </c>
       <c r="G130">
-        <v>-15.58239764</v>
+        <v>-1.16156348</v>
       </c>
       <c r="H130">
-        <v>0.56606373</v>
+        <v>0.95338335</v>
       </c>
       <c r="I130">
-        <v>-0.26934005</v>
+        <v>-0.29612009</v>
       </c>
       <c r="J130">
-        <v>0.77911988</v>
+        <v>0.05807817</v>
       </c>
     </row>
     <row r="131">
@@ -4195,31 +4195,31 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="C131">
-        <v>74.375</v>
+        <v>73.10486022</v>
       </c>
       <c r="D131">
-        <v>246</v>
+        <v>320.9937984</v>
       </c>
       <c r="E131">
-        <v>-7.83411492</v>
+        <v>14.87075586</v>
       </c>
       <c r="F131">
-        <v>5.38680108</v>
+        <v>5.81242058</v>
       </c>
       <c r="G131">
-        <v>-17.5957102</v>
+        <v>-12.04476596</v>
       </c>
       <c r="H131">
-        <v>0.39170575</v>
+        <v>-0.74353779</v>
       </c>
       <c r="I131">
-        <v>-0.26934005</v>
+        <v>-0.29062103</v>
       </c>
       <c r="J131">
-        <v>0.87978551</v>
+        <v>0.6022383</v>
       </c>
     </row>
     <row r="132">
@@ -4227,31 +4227,31 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="C132">
-        <v>74.375</v>
+        <v>73.43386071</v>
       </c>
       <c r="D132">
-        <v>258</v>
+        <v>98.50156245</v>
       </c>
       <c r="E132">
-        <v>-4.00456685</v>
+        <v>-2.83399754</v>
       </c>
       <c r="F132">
-        <v>5.38680108</v>
+        <v>5.70243934</v>
       </c>
       <c r="G132">
-        <v>-18.8400058</v>
+        <v>18.95918362</v>
       </c>
       <c r="H132">
-        <v>0.20022834</v>
+        <v>0.14169988</v>
       </c>
       <c r="I132">
-        <v>-0.26934005</v>
+        <v>-0.28512197</v>
       </c>
       <c r="J132">
-        <v>0.94200029</v>
+        <v>-0.94795918</v>
       </c>
     </row>
     <row r="133">
@@ -4259,31 +4259,31 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>7</v>
+        <v>131</v>
       </c>
       <c r="C133">
-        <v>74.375</v>
+        <v>73.76230018</v>
       </c>
       <c r="D133">
-        <v>270</v>
+        <v>236.0093265</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>-10.73514145</v>
       </c>
       <c r="F133">
-        <v>5.38680108</v>
+        <v>5.59245811</v>
       </c>
       <c r="G133">
-        <v>-19.26090273</v>
+        <v>-15.92109137</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>0.53675707</v>
       </c>
       <c r="I133">
-        <v>-0.26934005</v>
+        <v>-0.27962291</v>
       </c>
       <c r="J133">
-        <v>0.96304514</v>
+        <v>0.79605457</v>
       </c>
     </row>
     <row r="134">
@@ -4291,31 +4291,31 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="C134">
-        <v>74.375</v>
+        <v>74.09019222</v>
       </c>
       <c r="D134">
-        <v>282</v>
+        <v>13.51709055</v>
       </c>
       <c r="E134">
-        <v>4.00456685</v>
+        <v>18.70111398</v>
       </c>
       <c r="F134">
-        <v>5.38680108</v>
+        <v>5.48247687</v>
       </c>
       <c r="G134">
-        <v>-18.8400058</v>
+        <v>4.49564047</v>
       </c>
       <c r="H134">
-        <v>-0.20022834</v>
+        <v>-0.9350557</v>
       </c>
       <c r="I134">
-        <v>-0.26934005</v>
+        <v>-0.27412384</v>
       </c>
       <c r="J134">
-        <v>0.94200029</v>
+        <v>-0.22478202</v>
       </c>
     </row>
     <row r="135">
@@ -4323,31 +4323,31 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="C135">
-        <v>74.375</v>
+        <v>74.41755026</v>
       </c>
       <c r="D135">
-        <v>294</v>
+        <v>151.0248546</v>
       </c>
       <c r="E135">
-        <v>7.83411492</v>
+        <v>-16.85350932</v>
       </c>
       <c r="F135">
-        <v>5.38680108</v>
+        <v>5.37249564</v>
       </c>
       <c r="G135">
-        <v>-17.5957102</v>
+        <v>9.33249774</v>
       </c>
       <c r="H135">
-        <v>-0.39170575</v>
+        <v>0.84267547</v>
       </c>
       <c r="I135">
-        <v>-0.26934005</v>
+        <v>-0.26862478</v>
       </c>
       <c r="J135">
-        <v>0.87978551</v>
+        <v>-0.46662489</v>
       </c>
     </row>
     <row r="136">
@@ -4355,31 +4355,31 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="C136">
-        <v>74.375</v>
+        <v>74.74438753</v>
       </c>
       <c r="D136">
-        <v>306</v>
+        <v>288.53261866</v>
       </c>
       <c r="E136">
-        <v>11.32127457</v>
+        <v>6.13288285</v>
       </c>
       <c r="F136">
-        <v>5.38680108</v>
+        <v>5.2625144</v>
       </c>
       <c r="G136">
-        <v>-15.58239764</v>
+        <v>-18.29463556</v>
       </c>
       <c r="H136">
-        <v>-0.56606373</v>
+        <v>-0.30664414</v>
       </c>
       <c r="I136">
-        <v>-0.26934005</v>
+        <v>-0.26312572</v>
       </c>
       <c r="J136">
-        <v>0.77911988</v>
+        <v>0.91473178</v>
       </c>
     </row>
     <row r="137">
@@ -4387,31 +4387,31 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="C137">
-        <v>74.375</v>
+        <v>75.07071708</v>
       </c>
       <c r="D137">
-        <v>318</v>
+        <v>66.04038271</v>
       </c>
       <c r="E137">
-        <v>14.3136402</v>
+        <v>7.84769638</v>
       </c>
       <c r="F137">
-        <v>5.38680108</v>
+        <v>5.15253317</v>
       </c>
       <c r="G137">
-        <v>-12.88805953</v>
+        <v>17.65970168</v>
       </c>
       <c r="H137">
-        <v>-0.71568201</v>
+        <v>-0.39238482</v>
       </c>
       <c r="I137">
-        <v>-0.26934005</v>
+        <v>-0.25762666</v>
       </c>
       <c r="J137">
-        <v>0.64440298</v>
+        <v>-0.88298508</v>
       </c>
     </row>
     <row r="138">
@@ -4419,31 +4419,31 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C138">
-        <v>74.375</v>
+        <v>75.39655182</v>
       </c>
       <c r="D138">
-        <v>330</v>
+        <v>203.54814676</v>
       </c>
       <c r="E138">
-        <v>16.68043107</v>
+        <v>-17.74217931</v>
       </c>
       <c r="F138">
-        <v>5.38680108</v>
+        <v>5.04255193</v>
       </c>
       <c r="G138">
-        <v>-9.63045137</v>
+        <v>-7.73225345</v>
       </c>
       <c r="H138">
-        <v>-0.83402155</v>
+        <v>0.88710897</v>
       </c>
       <c r="I138">
-        <v>-0.26934005</v>
+        <v>-0.2521276</v>
       </c>
       <c r="J138">
-        <v>0.48152257</v>
+        <v>0.38661267</v>
       </c>
     </row>
     <row r="139">
@@ -4451,31 +4451,31 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>7</v>
+        <v>137</v>
       </c>
       <c r="C139">
-        <v>74.375</v>
+        <v>75.72190449</v>
       </c>
       <c r="D139">
-        <v>342</v>
+        <v>341.05591081</v>
       </c>
       <c r="E139">
-        <v>18.31820706</v>
+        <v>18.3323808</v>
       </c>
       <c r="F139">
-        <v>5.38680108</v>
+        <v>4.93257069</v>
       </c>
       <c r="G139">
-        <v>-5.95194627</v>
+        <v>-6.29234142</v>
       </c>
       <c r="H139">
-        <v>-0.91591035</v>
+        <v>-0.91661904</v>
       </c>
       <c r="I139">
-        <v>-0.26934005</v>
+        <v>-0.24662853</v>
       </c>
       <c r="J139">
-        <v>0.29759731</v>
+        <v>0.31461707</v>
       </c>
     </row>
     <row r="140">
@@ -4483,31 +4483,31 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>7</v>
+        <v>138</v>
       </c>
       <c r="C140">
-        <v>74.375</v>
+        <v>76.04678765</v>
       </c>
       <c r="D140">
-        <v>354</v>
+        <v>118.56367486</v>
       </c>
       <c r="E140">
-        <v>19.15538949</v>
+        <v>-9.28053544</v>
       </c>
       <c r="F140">
-        <v>5.38680108</v>
+        <v>4.82258946</v>
       </c>
       <c r="G140">
-        <v>-2.01331256</v>
+        <v>17.04741308</v>
       </c>
       <c r="H140">
-        <v>-0.95776947</v>
+        <v>0.46402677</v>
       </c>
       <c r="I140">
-        <v>-0.26934005</v>
+        <v>-0.24112947</v>
       </c>
       <c r="J140">
-        <v>0.10066563</v>
+        <v>-0.85237065</v>
       </c>
     </row>
     <row r="141">
@@ -4515,31 +4515,31 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="C141">
-        <v>85</v>
+        <v>76.37121375</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>256.07143891</v>
       </c>
       <c r="E141">
-        <v>19.92389396</v>
+        <v>-4.67868225</v>
       </c>
       <c r="F141">
-        <v>1.74311485</v>
+        <v>4.71260822</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>-18.86534538</v>
       </c>
       <c r="H141">
-        <v>-0.9961947</v>
+        <v>0.23393411</v>
       </c>
       <c r="I141">
-        <v>-0.08715574</v>
+        <v>-0.23563041</v>
       </c>
       <c r="J141">
-        <v>0</v>
+        <v>0.94326727</v>
       </c>
     </row>
     <row r="142">
@@ -4547,31 +4547,31 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="C142">
-        <v>85</v>
+        <v>76.69519505</v>
       </c>
       <c r="D142">
-        <v>11.61290323</v>
+        <v>33.57920296</v>
       </c>
       <c r="E142">
-        <v>19.51605068</v>
+        <v>16.21521411</v>
       </c>
       <c r="F142">
-        <v>1.74311485</v>
+        <v>4.60262699</v>
       </c>
       <c r="G142">
-        <v>4.01065037</v>
+        <v>10.76488068</v>
       </c>
       <c r="H142">
-        <v>-0.97580253</v>
+        <v>-0.81076071</v>
       </c>
       <c r="I142">
-        <v>-0.08715574</v>
+        <v>-0.23013135</v>
       </c>
       <c r="J142">
-        <v>-0.20053252</v>
+        <v>-0.53824403</v>
       </c>
     </row>
     <row r="143">
@@ -4579,31 +4579,31 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="C143">
-        <v>85</v>
+        <v>77.0187437</v>
       </c>
       <c r="D143">
-        <v>23.22580645</v>
+        <v>171.08696701</v>
       </c>
       <c r="E143">
-        <v>18.30921799</v>
+        <v>-19.25353708</v>
       </c>
       <c r="F143">
-        <v>1.74311485</v>
+        <v>4.49264575</v>
       </c>
       <c r="G143">
-        <v>7.85710424</v>
+        <v>3.01951058</v>
       </c>
       <c r="H143">
-        <v>-0.9154609</v>
+        <v>0.96267685</v>
       </c>
       <c r="I143">
-        <v>-0.08715574</v>
+        <v>-0.22463229</v>
       </c>
       <c r="J143">
-        <v>-0.39285521</v>
+        <v>-0.15097553</v>
       </c>
     </row>
     <row r="144">
@@ -4611,31 +4611,31 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="C144">
-        <v>85</v>
+        <v>77.34187172</v>
       </c>
       <c r="D144">
-        <v>34.83870968</v>
+        <v>308.59473106</v>
       </c>
       <c r="E144">
-        <v>16.35280377</v>
+        <v>12.1729209</v>
       </c>
       <c r="F144">
-        <v>1.74311485</v>
+        <v>4.38266451</v>
       </c>
       <c r="G144">
-        <v>11.38188734</v>
+        <v>-15.25163101</v>
       </c>
       <c r="H144">
-        <v>-0.81764019</v>
+        <v>-0.60864605</v>
       </c>
       <c r="I144">
-        <v>-0.08715574</v>
+        <v>-0.21913323</v>
       </c>
       <c r="J144">
-        <v>-0.56909437</v>
+        <v>0.76258155</v>
       </c>
     </row>
     <row r="145">
@@ -4643,31 +4643,31 @@
         <v>144</v>
       </c>
       <c r="B145">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="C145">
-        <v>85</v>
+        <v>77.66459096</v>
       </c>
       <c r="D145">
-        <v>46.4516129</v>
+        <v>86.10249511</v>
       </c>
       <c r="E145">
-        <v>13.72690384</v>
+        <v>1.32805255</v>
       </c>
       <c r="F145">
-        <v>1.74311485</v>
+        <v>4.27268328</v>
       </c>
       <c r="G145">
-        <v>14.44069464</v>
+        <v>19.49308734</v>
       </c>
       <c r="H145">
-        <v>-0.68634519</v>
+        <v>-0.06640263</v>
       </c>
       <c r="I145">
-        <v>-0.08715574</v>
+        <v>-0.21363416</v>
       </c>
       <c r="J145">
-        <v>-0.72203473</v>
+        <v>-0.97465437</v>
       </c>
     </row>
     <row r="146">
@@ -4675,31 +4675,31 @@
         <v>145</v>
       </c>
       <c r="B146">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="C146">
-        <v>85</v>
+        <v>77.98691318</v>
       </c>
       <c r="D146">
-        <v>58.06451613</v>
+        <v>223.61025916</v>
       </c>
       <c r="E146">
-        <v>10.53902285</v>
+        <v>-14.16383545</v>
       </c>
       <c r="F146">
-        <v>1.74311485</v>
+        <v>4.16270204</v>
       </c>
       <c r="G146">
-        <v>16.9082982</v>
+        <v>-13.49287504</v>
       </c>
       <c r="H146">
-        <v>-0.52695114</v>
+        <v>0.70819177</v>
       </c>
       <c r="I146">
-        <v>-0.08715574</v>
+        <v>-0.2081351</v>
       </c>
       <c r="J146">
-        <v>-0.84541491</v>
+        <v>0.67464375</v>
       </c>
     </row>
     <row r="147">
@@ -4707,31 +4707,31 @@
         <v>146</v>
       </c>
       <c r="B147">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="C147">
-        <v>85</v>
+        <v>78.30885001</v>
       </c>
       <c r="D147">
-        <v>69.67741935</v>
+        <v>1.11802321</v>
       </c>
       <c r="E147">
-        <v>6.91967303</v>
+        <v>19.5813539</v>
       </c>
       <c r="F147">
-        <v>1.74311485</v>
+        <v>4.05272081</v>
       </c>
       <c r="G147">
-        <v>18.68367404</v>
+        <v>0.38214311</v>
       </c>
       <c r="H147">
-        <v>-0.34598365</v>
+        <v>-0.9790677</v>
       </c>
       <c r="I147">
-        <v>-0.08715574</v>
+        <v>-0.20263604</v>
       </c>
       <c r="J147">
-        <v>-0.9341837</v>
+        <v>-0.01910716</v>
       </c>
     </row>
     <row r="148">
@@ -4739,31 +4739,31 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="C148">
-        <v>85</v>
+        <v>78.63041295</v>
       </c>
       <c r="D148">
-        <v>81.29032258</v>
+        <v>138.62578726</v>
       </c>
       <c r="E148">
-        <v>3.01703098</v>
+        <v>-14.71365157</v>
       </c>
       <c r="F148">
-        <v>1.74311485</v>
+        <v>3.94273957</v>
       </c>
       <c r="G148">
-        <v>19.69413808</v>
+        <v>12.96006412</v>
       </c>
       <c r="H148">
-        <v>-0.15085155</v>
+        <v>0.73568258</v>
       </c>
       <c r="I148">
-        <v>-0.08715574</v>
+        <v>-0.19713698</v>
       </c>
       <c r="J148">
-        <v>-0.9847069</v>
+        <v>-0.64800321</v>
       </c>
     </row>
     <row r="149">
@@ -4771,31 +4771,31 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="C149">
-        <v>85</v>
+        <v>78.9516134</v>
       </c>
       <c r="D149">
-        <v>92.90322581</v>
+        <v>276.13355131</v>
       </c>
       <c r="E149">
-        <v>-1.00912867</v>
+        <v>2.09731992</v>
       </c>
       <c r="F149">
-        <v>1.74311485</v>
+        <v>3.83275834</v>
       </c>
       <c r="G149">
-        <v>19.89832179</v>
+        <v>-19.51694681</v>
       </c>
       <c r="H149">
-        <v>0.05045643</v>
+        <v>-0.104866</v>
       </c>
       <c r="I149">
-        <v>-0.08715574</v>
+        <v>-0.19163792</v>
       </c>
       <c r="J149">
-        <v>-0.99491609</v>
+        <v>0.97584734</v>
       </c>
     </row>
     <row r="150">
@@ -4803,31 +4803,31 @@
         <v>149</v>
       </c>
       <c r="B150">
-        <v>8</v>
+        <v>148</v>
       </c>
       <c r="C150">
-        <v>85</v>
+        <v>79.27246264</v>
       </c>
       <c r="D150">
-        <v>104.51612903</v>
+        <v>53.64131536</v>
       </c>
       <c r="E150">
-        <v>-4.99397447</v>
+        <v>11.64955125</v>
       </c>
       <c r="F150">
-        <v>1.74311485</v>
+        <v>3.7227771</v>
       </c>
       <c r="G150">
-        <v>19.28786586</v>
+        <v>15.82494506</v>
       </c>
       <c r="H150">
-        <v>0.24969872</v>
+        <v>-0.58247756</v>
       </c>
       <c r="I150">
-        <v>-0.08715574</v>
+        <v>-0.18613885</v>
       </c>
       <c r="J150">
-        <v>-0.96439329</v>
+        <v>-0.79124725</v>
       </c>
     </row>
     <row r="151">
@@ -4835,31 +4835,31 @@
         <v>150</v>
       </c>
       <c r="B151">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="C151">
-        <v>85</v>
+        <v>79.59297184</v>
       </c>
       <c r="D151">
-        <v>116.12903226</v>
+        <v>191.14907941</v>
       </c>
       <c r="E151">
-        <v>-8.77436638</v>
+        <v>-19.29974355</v>
       </c>
       <c r="F151">
-        <v>1.74311485</v>
+        <v>3.61279586</v>
       </c>
       <c r="G151">
-        <v>17.88776244</v>
+        <v>-3.80363049</v>
       </c>
       <c r="H151">
-        <v>0.43871832</v>
+        <v>0.96498718</v>
       </c>
       <c r="I151">
-        <v>-0.08715574</v>
+        <v>-0.18063979</v>
       </c>
       <c r="J151">
-        <v>-0.89438812</v>
+        <v>0.19018152</v>
       </c>
     </row>
     <row r="152">
@@ -4867,31 +4867,31 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="C152">
-        <v>85</v>
+        <v>79.91315209</v>
       </c>
       <c r="D152">
-        <v>127.74193548</v>
+        <v>328.65684346</v>
       </c>
       <c r="E152">
-        <v>-12.19553469</v>
+        <v>16.8173261</v>
       </c>
       <c r="F152">
-        <v>1.74311485</v>
+        <v>3.50281463</v>
       </c>
       <c r="G152">
-        <v>15.75533193</v>
+        <v>-10.24245246</v>
       </c>
       <c r="H152">
-        <v>0.60977673</v>
+        <v>-0.84086631</v>
       </c>
       <c r="I152">
-        <v>-0.08715574</v>
+        <v>-0.17514073</v>
       </c>
       <c r="J152">
-        <v>-0.7877666</v>
+        <v>0.51212262</v>
       </c>
     </row>
     <row r="153">
@@ -4899,31 +4899,31 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="C153">
-        <v>85</v>
+        <v>80.23301437</v>
       </c>
       <c r="D153">
-        <v>139.35483871</v>
+        <v>106.16460751</v>
       </c>
       <c r="E153">
-        <v>-15.11741638</v>
+        <v>-5.48725427</v>
       </c>
       <c r="F153">
-        <v>1.74311485</v>
+        <v>3.39283339</v>
       </c>
       <c r="G153">
-        <v>12.97787628</v>
+        <v>18.93089333</v>
       </c>
       <c r="H153">
-        <v>0.75587082</v>
+        <v>0.27436271</v>
       </c>
       <c r="I153">
-        <v>-0.08715574</v>
+        <v>-0.16964167</v>
       </c>
       <c r="J153">
-        <v>-0.64889381</v>
+        <v>-0.94654467</v>
       </c>
     </row>
     <row r="154">
@@ -4931,31 +4931,31 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="C154">
-        <v>85</v>
+        <v>80.55256956</v>
       </c>
       <c r="D154">
-        <v>150.96774194</v>
+        <v>243.67237156</v>
       </c>
       <c r="E154">
-        <v>-17.42038927</v>
+        <v>-8.74976052</v>
       </c>
       <c r="F154">
-        <v>1.74311485</v>
+        <v>3.28285216</v>
       </c>
       <c r="G154">
-        <v>9.66910484</v>
+        <v>-17.68232373</v>
       </c>
       <c r="H154">
-        <v>0.87101946</v>
+        <v>0.43748803</v>
       </c>
       <c r="I154">
-        <v>-0.08715574</v>
+        <v>-0.16414261</v>
       </c>
       <c r="J154">
-        <v>-0.48345524</v>
+        <v>0.88411619</v>
       </c>
     </row>
     <row r="155">
@@ -4963,31 +4963,31 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>8</v>
+        <v>153</v>
       </c>
       <c r="C155">
-        <v>85</v>
+        <v>80.87182845</v>
       </c>
       <c r="D155">
-        <v>162.58064516</v>
+        <v>21.18013561</v>
       </c>
       <c r="E155">
-        <v>-19.01016937</v>
+        <v>18.41281026</v>
       </c>
       <c r="F155">
-        <v>1.74311485</v>
+        <v>3.17287092</v>
       </c>
       <c r="G155">
-        <v>5.96447912</v>
+        <v>7.1345153</v>
       </c>
       <c r="H155">
-        <v>0.95050847</v>
+        <v>-0.92064051</v>
       </c>
       <c r="I155">
-        <v>-0.08715574</v>
+        <v>-0.15864355</v>
       </c>
       <c r="J155">
-        <v>-0.29822396</v>
+        <v>-0.35672576</v>
       </c>
     </row>
     <row r="156">
@@ -4995,31 +4995,31 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>8</v>
+        <v>154</v>
       </c>
       <c r="C156">
-        <v>85</v>
+        <v>81.19080175</v>
       </c>
       <c r="D156">
-        <v>174.19354839</v>
+        <v>158.68789966</v>
       </c>
       <c r="E156">
-        <v>-19.82167091</v>
+        <v>-18.41249977</v>
       </c>
       <c r="F156">
-        <v>1.74311485</v>
+        <v>3.06288968</v>
       </c>
       <c r="G156">
-        <v>2.01566692</v>
+        <v>7.1832137</v>
       </c>
       <c r="H156">
-        <v>0.99108355</v>
+        <v>0.92062499</v>
       </c>
       <c r="I156">
-        <v>-0.08715574</v>
+        <v>-0.15314448</v>
       </c>
       <c r="J156">
-        <v>-0.10078335</v>
+        <v>-0.35916068</v>
       </c>
     </row>
     <row r="157">
@@ -5027,31 +5027,31 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>8</v>
+        <v>155</v>
       </c>
       <c r="C157">
-        <v>85</v>
+        <v>81.50950009</v>
       </c>
       <c r="D157">
-        <v>185.80645161</v>
+        <v>296.19566371</v>
       </c>
       <c r="E157">
-        <v>-19.82167091</v>
+        <v>8.73199885</v>
       </c>
       <c r="F157">
-        <v>1.74311485</v>
+        <v>2.95290845</v>
       </c>
       <c r="G157">
-        <v>-2.01566692</v>
+        <v>-17.74915569</v>
       </c>
       <c r="H157">
-        <v>0.99108355</v>
+        <v>-0.43659994</v>
       </c>
       <c r="I157">
-        <v>-0.08715574</v>
+        <v>-0.14764542</v>
       </c>
       <c r="J157">
-        <v>0.10078335</v>
+        <v>0.88745778</v>
       </c>
     </row>
     <row r="158">
@@ -5059,31 +5059,31 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="C158">
-        <v>85</v>
+        <v>81.82793402</v>
       </c>
       <c r="D158">
-        <v>197.41935484</v>
+        <v>73.70342776</v>
       </c>
       <c r="E158">
-        <v>-19.01016937</v>
+        <v>5.55519765</v>
       </c>
       <c r="F158">
-        <v>1.74311485</v>
+        <v>2.84292721</v>
       </c>
       <c r="G158">
-        <v>-5.96447912</v>
+        <v>19.00151425</v>
       </c>
       <c r="H158">
-        <v>0.95050847</v>
+        <v>-0.27775988</v>
       </c>
       <c r="I158">
-        <v>-0.08715574</v>
+        <v>-0.14214636</v>
       </c>
       <c r="J158">
-        <v>0.29822396</v>
+        <v>-0.95007571</v>
       </c>
     </row>
     <row r="159">
@@ -5091,31 +5091,31 @@
         <v>158</v>
       </c>
       <c r="B159">
-        <v>8</v>
+        <v>157</v>
       </c>
       <c r="C159">
-        <v>85</v>
+        <v>82.146114</v>
       </c>
       <c r="D159">
-        <v>209.03225806</v>
+        <v>211.21119181</v>
       </c>
       <c r="E159">
-        <v>-17.42038927</v>
+        <v>-16.94480972</v>
       </c>
       <c r="F159">
-        <v>1.74311485</v>
+        <v>2.73294598</v>
       </c>
       <c r="G159">
-        <v>-9.66910484</v>
+        <v>-10.26666596</v>
       </c>
       <c r="H159">
-        <v>0.87101946</v>
+        <v>0.84724049</v>
       </c>
       <c r="I159">
-        <v>-0.08715574</v>
+        <v>-0.1366473</v>
       </c>
       <c r="J159">
-        <v>0.48345524</v>
+        <v>0.5133333</v>
       </c>
     </row>
     <row r="160">
@@ -5123,31 +5123,31 @@
         <v>159</v>
       </c>
       <c r="B160">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="C160">
-        <v>85</v>
+        <v>82.46405043</v>
       </c>
       <c r="D160">
-        <v>220.64516129</v>
+        <v>348.71895586</v>
       </c>
       <c r="E160">
-        <v>-15.11741638</v>
+        <v>19.44418155</v>
       </c>
       <c r="F160">
-        <v>1.74311485</v>
+        <v>2.62296474</v>
       </c>
       <c r="G160">
-        <v>-12.97787628</v>
+        <v>-3.8786415</v>
       </c>
       <c r="H160">
-        <v>0.75587082</v>
+        <v>-0.97220908</v>
       </c>
       <c r="I160">
-        <v>-0.08715574</v>
+        <v>-0.13114824</v>
       </c>
       <c r="J160">
-        <v>0.64889381</v>
+        <v>0.19393208</v>
       </c>
     </row>
     <row r="161">
@@ -5155,31 +5155,31 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="C161">
-        <v>85</v>
+        <v>82.78175363</v>
       </c>
       <c r="D161">
-        <v>232.25806452</v>
+        <v>126.22671991</v>
       </c>
       <c r="E161">
-        <v>-12.19553469</v>
+        <v>-11.72596485</v>
       </c>
       <c r="F161">
-        <v>1.74311485</v>
+        <v>2.51298351</v>
       </c>
       <c r="G161">
-        <v>-15.75533193</v>
+        <v>16.00583213</v>
       </c>
       <c r="H161">
-        <v>0.60977673</v>
+        <v>0.58629824</v>
       </c>
       <c r="I161">
-        <v>-0.08715574</v>
+        <v>-0.12564918</v>
       </c>
       <c r="J161">
-        <v>0.7877666</v>
+        <v>-0.80029161</v>
       </c>
     </row>
     <row r="162">
@@ -5187,31 +5187,31 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="C162">
-        <v>85</v>
+        <v>83.09923387</v>
       </c>
       <c r="D162">
-        <v>243.87096774</v>
+        <v>263.73448396</v>
       </c>
       <c r="E162">
-        <v>-8.77436638</v>
+        <v>-2.16690914</v>
       </c>
       <c r="F162">
-        <v>1.74311485</v>
+        <v>2.40300227</v>
       </c>
       <c r="G162">
-        <v>-17.88776244</v>
+        <v>-19.73651653</v>
       </c>
       <c r="H162">
-        <v>0.43871832</v>
+        <v>0.10834546</v>
       </c>
       <c r="I162">
-        <v>-0.08715574</v>
+        <v>-0.12015011</v>
       </c>
       <c r="J162">
-        <v>0.89438812</v>
+        <v>0.98682583</v>
       </c>
     </row>
     <row r="163">
@@ -5219,31 +5219,31 @@
         <v>162</v>
       </c>
       <c r="B163">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="C163">
-        <v>85</v>
+        <v>83.41650134</v>
       </c>
       <c r="D163">
-        <v>255.48387097</v>
+        <v>41.24224801</v>
       </c>
       <c r="E163">
-        <v>-4.99397447</v>
+        <v>14.93941317</v>
       </c>
       <c r="F163">
-        <v>1.74311485</v>
+        <v>2.29302103</v>
       </c>
       <c r="G163">
-        <v>-19.28786586</v>
+        <v>13.09793834</v>
       </c>
       <c r="H163">
-        <v>0.24969872</v>
+        <v>-0.74697066</v>
       </c>
       <c r="I163">
-        <v>-0.08715574</v>
+        <v>-0.11465105</v>
       </c>
       <c r="J163">
-        <v>0.96439329</v>
+        <v>-0.65489692</v>
       </c>
     </row>
     <row r="164">
@@ -5251,31 +5251,31 @@
         <v>163</v>
       </c>
       <c r="B164">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="C164">
-        <v>85</v>
+        <v>83.73356618</v>
       </c>
       <c r="D164">
-        <v>267.09677419</v>
+        <v>178.75001206</v>
       </c>
       <c r="E164">
-        <v>-1.00912867</v>
+        <v>-19.8757705</v>
       </c>
       <c r="F164">
-        <v>1.74311485</v>
+        <v>2.1830398</v>
       </c>
       <c r="G164">
-        <v>-19.89832179</v>
+        <v>0.43368667</v>
       </c>
       <c r="H164">
-        <v>0.05045643</v>
+        <v>0.99378853</v>
       </c>
       <c r="I164">
-        <v>-0.08715574</v>
+        <v>-0.10915199</v>
       </c>
       <c r="J164">
-        <v>0.99491609</v>
+        <v>-0.02168433</v>
       </c>
     </row>
     <row r="165">
@@ -5283,31 +5283,31 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>8</v>
+        <v>163</v>
       </c>
       <c r="C165">
-        <v>85</v>
+        <v>84.05043846</v>
       </c>
       <c r="D165">
-        <v>278.70967742</v>
+        <v>316.25777611</v>
       </c>
       <c r="E165">
-        <v>3.01703098</v>
+        <v>14.37132616</v>
       </c>
       <c r="F165">
-        <v>1.74311485</v>
+        <v>2.07305856</v>
       </c>
       <c r="G165">
-        <v>-19.69413808</v>
+        <v>-13.75381447</v>
       </c>
       <c r="H165">
-        <v>-0.15085155</v>
+        <v>-0.71856631</v>
       </c>
       <c r="I165">
-        <v>-0.08715574</v>
+        <v>-0.10365293</v>
       </c>
       <c r="J165">
-        <v>0.9847069</v>
+        <v>0.68769072</v>
       </c>
     </row>
     <row r="166">
@@ -5315,31 +5315,31 @@
         <v>165</v>
       </c>
       <c r="B166">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="C166">
-        <v>85</v>
+        <v>84.36712822</v>
       </c>
       <c r="D166">
-        <v>290.32258065</v>
+        <v>93.76554016</v>
       </c>
       <c r="E166">
-        <v>6.91967303</v>
+        <v>-1.30713302</v>
       </c>
       <c r="F166">
-        <v>1.74311485</v>
+        <v>1.96307733</v>
       </c>
       <c r="G166">
-        <v>-18.68367404</v>
+        <v>19.86045646</v>
       </c>
       <c r="H166">
-        <v>-0.34598365</v>
+        <v>0.06535665</v>
       </c>
       <c r="I166">
-        <v>-0.08715574</v>
+        <v>-0.09815387</v>
       </c>
       <c r="J166">
-        <v>0.9341837</v>
+        <v>-0.99302282</v>
       </c>
     </row>
     <row r="167">
@@ -5347,159 +5347,31 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>8</v>
+        <v>165</v>
       </c>
       <c r="C167">
-        <v>85</v>
+        <v>84.68364542</v>
       </c>
       <c r="D167">
-        <v>301.93548387</v>
+        <v>231.27330421</v>
       </c>
       <c r="E167">
-        <v>10.53902285</v>
+        <v>-12.45830077</v>
       </c>
       <c r="F167">
-        <v>1.74311485</v>
+        <v>1.85309609</v>
       </c>
       <c r="G167">
-        <v>-16.9082982</v>
+        <v>-15.53566146</v>
       </c>
       <c r="H167">
-        <v>-0.52695114</v>
+        <v>0.62291504</v>
       </c>
       <c r="I167">
-        <v>-0.08715574</v>
+        <v>-0.0926548</v>
       </c>
       <c r="J167">
-        <v>0.84541491</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168">
-        <v>167</v>
-      </c>
-      <c r="B168">
-        <v>8</v>
-      </c>
-      <c r="C168">
-        <v>85</v>
-      </c>
-      <c r="D168">
-        <v>313.5483871</v>
-      </c>
-      <c r="E168">
-        <v>13.72690384</v>
-      </c>
-      <c r="F168">
-        <v>1.74311485</v>
-      </c>
-      <c r="G168">
-        <v>-14.44069464</v>
-      </c>
-      <c r="H168">
-        <v>-0.68634519</v>
-      </c>
-      <c r="I168">
-        <v>-0.08715574</v>
-      </c>
-      <c r="J168">
-        <v>0.72203473</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169">
-        <v>168</v>
-      </c>
-      <c r="B169">
-        <v>8</v>
-      </c>
-      <c r="C169">
-        <v>85</v>
-      </c>
-      <c r="D169">
-        <v>325.16129032</v>
-      </c>
-      <c r="E169">
-        <v>16.35280377</v>
-      </c>
-      <c r="F169">
-        <v>1.74311485</v>
-      </c>
-      <c r="G169">
-        <v>-11.38188734</v>
-      </c>
-      <c r="H169">
-        <v>-0.81764019</v>
-      </c>
-      <c r="I169">
-        <v>-0.08715574</v>
-      </c>
-      <c r="J169">
-        <v>0.56909437</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170">
-        <v>169</v>
-      </c>
-      <c r="B170">
-        <v>8</v>
-      </c>
-      <c r="C170">
-        <v>85</v>
-      </c>
-      <c r="D170">
-        <v>336.77419355</v>
-      </c>
-      <c r="E170">
-        <v>18.30921799</v>
-      </c>
-      <c r="F170">
-        <v>1.74311485</v>
-      </c>
-      <c r="G170">
-        <v>-7.85710424</v>
-      </c>
-      <c r="H170">
-        <v>-0.9154609</v>
-      </c>
-      <c r="I170">
-        <v>-0.08715574</v>
-      </c>
-      <c r="J170">
-        <v>0.39285521</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171">
-        <v>170</v>
-      </c>
-      <c r="B171">
-        <v>8</v>
-      </c>
-      <c r="C171">
-        <v>85</v>
-      </c>
-      <c r="D171">
-        <v>348.38709677</v>
-      </c>
-      <c r="E171">
-        <v>19.51605068</v>
-      </c>
-      <c r="F171">
-        <v>1.74311485</v>
-      </c>
-      <c r="G171">
-        <v>-4.01065037</v>
-      </c>
-      <c r="H171">
-        <v>-0.97580253</v>
-      </c>
-      <c r="I171">
-        <v>-0.08715574</v>
-      </c>
-      <c r="J171">
-        <v>0.20053252</v>
+        <v>0.77678307</v>
       </c>
     </row>
   </sheetData>

--- a/pin_points_with_normals.xlsx
+++ b/pin_points_with_normals.xlsx
@@ -102,25 +102,25 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>6.01147643</v>
+        <v>11.4591559</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2.09455331</v>
+        <v>3.97338662</v>
       </c>
       <c r="F3">
-        <v>19.89001876</v>
+        <v>19.60133156</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>-0.10472767</v>
+        <v>-0.19866933</v>
       </c>
       <c r="I3">
-        <v>-0.99450094</v>
+        <v>-0.98006658</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -131,31 +131,31 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>8.50542008</v>
+        <v>11.4591559</v>
       </c>
       <c r="D4">
-        <v>137.50776405</v>
+        <v>60</v>
       </c>
       <c r="E4">
-        <v>-2.18118094</v>
+        <v>1.98669331</v>
       </c>
       <c r="F4">
-        <v>19.78003753</v>
+        <v>19.60133156</v>
       </c>
       <c r="G4">
-        <v>1.99814041</v>
+        <v>3.44105375</v>
       </c>
       <c r="H4">
-        <v>0.10905905</v>
+        <v>-0.09933467</v>
       </c>
       <c r="I4">
-        <v>-0.98900188</v>
+        <v>-0.98006658</v>
       </c>
       <c r="J4">
-        <v>-0.09990702</v>
+        <v>-0.17205269</v>
       </c>
     </row>
     <row r="5">
@@ -163,31 +163,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>10.42176856</v>
+        <v>11.4591559</v>
       </c>
       <c r="D5">
-        <v>275.0155281</v>
+        <v>120</v>
       </c>
       <c r="E5">
-        <v>0.31629372</v>
+        <v>-1.98669331</v>
       </c>
       <c r="F5">
-        <v>19.67005629</v>
+        <v>19.60133156</v>
       </c>
       <c r="G5">
-        <v>-3.60400385</v>
+        <v>3.44105375</v>
       </c>
       <c r="H5">
-        <v>-0.01581469</v>
+        <v>0.09933467</v>
       </c>
       <c r="I5">
-        <v>-0.98350281</v>
+        <v>-0.98006658</v>
       </c>
       <c r="J5">
-        <v>0.18020019</v>
+        <v>-0.17205269</v>
       </c>
     </row>
     <row r="6">
@@ -195,31 +195,31 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>12.03957694</v>
+        <v>11.4591559</v>
       </c>
       <c r="D6">
-        <v>52.52329215</v>
+        <v>180</v>
       </c>
       <c r="E6">
-        <v>2.53825232</v>
+        <v>-3.97338662</v>
       </c>
       <c r="F6">
-        <v>19.56007506</v>
+        <v>19.60133156</v>
       </c>
       <c r="G6">
-        <v>3.31070067</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>-0.12691262</v>
+        <v>0.19866933</v>
       </c>
       <c r="I6">
-        <v>-0.97800375</v>
+        <v>-0.98006658</v>
       </c>
       <c r="J6">
-        <v>-0.16553503</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -227,31 +227,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>13.46688263</v>
+        <v>11.4591559</v>
       </c>
       <c r="D7">
-        <v>190.0310562</v>
+        <v>240</v>
       </c>
       <c r="E7">
-        <v>-4.58646629</v>
+        <v>-1.98669331</v>
       </c>
       <c r="F7">
-        <v>19.45009382</v>
+        <v>19.60133156</v>
       </c>
       <c r="G7">
-        <v>-0.81128131</v>
+        <v>-3.44105375</v>
       </c>
       <c r="H7">
-        <v>0.22932331</v>
+        <v>0.09933467</v>
       </c>
       <c r="I7">
-        <v>-0.97250469</v>
+        <v>-0.98006658</v>
       </c>
       <c r="J7">
-        <v>0.04056407</v>
+        <v>0.17205269</v>
       </c>
     </row>
     <row r="8">
@@ -259,31 +259,31 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>14.75906858</v>
+        <v>11.4591559</v>
       </c>
       <c r="D8">
-        <v>327.53882025</v>
+        <v>300</v>
       </c>
       <c r="E8">
-        <v>4.2990177</v>
+        <v>1.98669331</v>
       </c>
       <c r="F8">
-        <v>19.34011259</v>
+        <v>19.60133156</v>
       </c>
       <c r="G8">
-        <v>-2.73468316</v>
+        <v>-3.44105375</v>
       </c>
       <c r="H8">
-        <v>-0.21495089</v>
+        <v>-0.09933467</v>
       </c>
       <c r="I8">
-        <v>-0.96700563</v>
+        <v>-0.98006658</v>
       </c>
       <c r="J8">
-        <v>0.13673416</v>
+        <v>0.17205269</v>
       </c>
     </row>
     <row r="9">
@@ -291,31 +291,31 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>15.94902031</v>
+        <v>16.48287513</v>
       </c>
       <c r="D9">
-        <v>105.0465843</v>
+        <v>68.75388203</v>
       </c>
       <c r="E9">
-        <v>-1.42669155</v>
+        <v>2.05632353</v>
       </c>
       <c r="F9">
-        <v>19.23013135</v>
+        <v>19.1780916</v>
       </c>
       <c r="G9">
-        <v>5.30722145</v>
+        <v>5.28888798</v>
       </c>
       <c r="H9">
-        <v>0.07133458</v>
+        <v>-0.10281618</v>
       </c>
       <c r="I9">
-        <v>-0.96150657</v>
+        <v>-0.95890458</v>
       </c>
       <c r="J9">
-        <v>-0.26536107</v>
+        <v>-0.2644444</v>
       </c>
     </row>
     <row r="10">
@@ -323,31 +323,31 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>17.05815531</v>
+        <v>17.55941927</v>
       </c>
       <c r="D10">
-        <v>242.55434835</v>
+        <v>206.26164608</v>
       </c>
       <c r="E10">
-        <v>-2.70406966</v>
+        <v>-5.41109251</v>
       </c>
       <c r="F10">
-        <v>19.12015011</v>
+        <v>19.06809175</v>
       </c>
       <c r="G10">
-        <v>-5.20652158</v>
+        <v>-2.66982301</v>
       </c>
       <c r="H10">
-        <v>0.13520348</v>
+        <v>0.27055463</v>
       </c>
       <c r="I10">
-        <v>-0.95600751</v>
+        <v>-0.95340459</v>
       </c>
       <c r="J10">
-        <v>0.26032608</v>
+        <v>0.13349115</v>
       </c>
     </row>
     <row r="11">
@@ -355,31 +355,31 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>18.10134398</v>
+        <v>18.57552112</v>
       </c>
       <c r="D11">
-        <v>20.0621124</v>
+        <v>343.76941013</v>
       </c>
       <c r="E11">
-        <v>5.83691859</v>
+        <v>6.11716492</v>
       </c>
       <c r="F11">
-        <v>19.01016888</v>
+        <v>18.9580919</v>
       </c>
       <c r="G11">
-        <v>2.13163331</v>
+        <v>-1.78074283</v>
       </c>
       <c r="H11">
-        <v>-0.29184593</v>
+        <v>-0.30585825</v>
       </c>
       <c r="I11">
-        <v>-0.95050844</v>
+        <v>-0.94790459</v>
       </c>
       <c r="J11">
-        <v>-0.10658167</v>
+        <v>0.08903714</v>
       </c>
     </row>
     <row r="12">
@@ -387,31 +387,31 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>19.0894089</v>
+        <v>19.5406198</v>
       </c>
       <c r="D12">
-        <v>157.56987645</v>
+        <v>121.27717418</v>
       </c>
       <c r="E12">
-        <v>-6.04601894</v>
+        <v>-3.47304631</v>
       </c>
       <c r="F12">
-        <v>18.90018764</v>
+        <v>18.84809204</v>
       </c>
       <c r="G12">
-        <v>2.49570873</v>
+        <v>5.71728744</v>
       </c>
       <c r="H12">
-        <v>0.30230095</v>
+        <v>0.17365232</v>
       </c>
       <c r="I12">
-        <v>-0.94500938</v>
+        <v>-0.9424046</v>
       </c>
       <c r="J12">
-        <v>-0.12478544</v>
+        <v>-0.28586437</v>
       </c>
     </row>
     <row r="13">
@@ -419,31 +419,31 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>20.03051695</v>
+        <v>20.46194102</v>
       </c>
       <c r="D13">
-        <v>295.0776405</v>
+        <v>258.78493823</v>
       </c>
       <c r="E13">
-        <v>2.90351965</v>
+        <v>-1.35983167</v>
       </c>
       <c r="F13">
-        <v>18.79020641</v>
+        <v>18.73809219</v>
       </c>
       <c r="G13">
-        <v>-6.20465284</v>
+        <v>-6.85818919</v>
       </c>
       <c r="H13">
-        <v>-0.14517598</v>
+        <v>0.06799158</v>
       </c>
       <c r="I13">
-        <v>-0.93951032</v>
+        <v>-0.93690461</v>
       </c>
       <c r="J13">
-        <v>0.31023264</v>
+        <v>0.34290946</v>
       </c>
     </row>
     <row r="14">
@@ -451,31 +451,31 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>20.93101046</v>
+        <v>21.34516161</v>
       </c>
       <c r="D14">
-        <v>72.58540455</v>
+        <v>36.29270228</v>
       </c>
       <c r="E14">
-        <v>2.13834473</v>
+        <v>5.86747295</v>
       </c>
       <c r="F14">
-        <v>18.68022517</v>
+        <v>18.62809234</v>
       </c>
       <c r="G14">
-        <v>6.81737995</v>
+        <v>4.30893689</v>
       </c>
       <c r="H14">
-        <v>-0.10691724</v>
+        <v>-0.29337365</v>
       </c>
       <c r="I14">
-        <v>-0.93401126</v>
+        <v>-0.93140462</v>
       </c>
       <c r="J14">
-        <v>-0.340869</v>
+        <v>-0.21544684</v>
       </c>
     </row>
     <row r="15">
@@ -483,31 +483,31 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>21.79593122</v>
+        <v>22.19483771</v>
       </c>
       <c r="D15">
-        <v>210.0931686</v>
+        <v>173.80046633</v>
       </c>
       <c r="E15">
-        <v>-6.42509131</v>
+        <v>-7.51096362</v>
       </c>
       <c r="F15">
-        <v>18.57024393</v>
+        <v>18.51809248</v>
       </c>
       <c r="G15">
-        <v>-3.72347175</v>
+        <v>0.81588991</v>
       </c>
       <c r="H15">
-        <v>0.32125457</v>
+        <v>0.37554818</v>
       </c>
       <c r="I15">
-        <v>-0.9285122</v>
+        <v>-0.92590462</v>
       </c>
       <c r="J15">
-        <v>0.18617359</v>
+        <v>-0.0407945</v>
       </c>
     </row>
     <row r="16">
@@ -515,31 +515,31 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>22.62936552</v>
+        <v>23.01469185</v>
       </c>
       <c r="D16">
-        <v>347.60093265</v>
+        <v>311.30823038</v>
       </c>
       <c r="E16">
-        <v>7.51588028</v>
+        <v>5.16162324</v>
       </c>
       <c r="F16">
-        <v>18.4602627</v>
+        <v>18.40809263</v>
       </c>
       <c r="G16">
-        <v>-1.6523452</v>
+        <v>-5.87365059</v>
       </c>
       <c r="H16">
-        <v>-0.37579401</v>
+        <v>-0.25808116</v>
       </c>
       <c r="I16">
-        <v>-0.92301313</v>
+        <v>-0.92040463</v>
       </c>
       <c r="J16">
-        <v>0.08261726</v>
+        <v>0.29368253</v>
       </c>
     </row>
     <row r="17">
@@ -547,31 +547,31 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>23.43467981</v>
+        <v>23.80781188</v>
       </c>
       <c r="D17">
-        <v>125.1086967</v>
+        <v>88.81599443</v>
       </c>
       <c r="E17">
-        <v>-4.57461759</v>
+        <v>0.1668233</v>
       </c>
       <c r="F17">
-        <v>18.35028146</v>
+        <v>18.29809278</v>
       </c>
       <c r="G17">
-        <v>6.50692278</v>
+        <v>8.07167707</v>
       </c>
       <c r="H17">
-        <v>0.22873088</v>
+        <v>-0.00834117</v>
       </c>
       <c r="I17">
-        <v>-0.91751407</v>
+        <v>-0.91490464</v>
       </c>
       <c r="J17">
-        <v>-0.32534614</v>
+        <v>-0.40358385</v>
       </c>
     </row>
     <row r="18">
@@ -579,31 +579,31 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>24.21468653</v>
+        <v>24.57679274</v>
       </c>
       <c r="D18">
-        <v>262.61646075</v>
+        <v>226.32375848</v>
       </c>
       <c r="E18">
-        <v>-1.05419072</v>
+        <v>-5.74443811</v>
       </c>
       <c r="F18">
-        <v>18.24030023</v>
+        <v>18.18809292</v>
       </c>
       <c r="G18">
-        <v>-8.13511706</v>
+        <v>-6.01620367</v>
       </c>
       <c r="H18">
-        <v>0.05270954</v>
+        <v>0.28722191</v>
       </c>
       <c r="I18">
-        <v>-0.91201501</v>
+        <v>-0.90940465</v>
       </c>
       <c r="J18">
-        <v>0.40675585</v>
+        <v>0.30081018</v>
       </c>
     </row>
     <row r="19">
@@ -611,31 +611,31 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>24.97176378</v>
+        <v>25.32384002</v>
       </c>
       <c r="D19">
-        <v>40.1242248</v>
+        <v>3.83152253</v>
       </c>
       <c r="E19">
-        <v>6.45626131</v>
+        <v>8.53555912</v>
       </c>
       <c r="F19">
-        <v>18.13031899</v>
+        <v>18.07809307</v>
       </c>
       <c r="G19">
-        <v>5.44134387</v>
+        <v>0.57164813</v>
       </c>
       <c r="H19">
-        <v>-0.32281307</v>
+        <v>-0.42677796</v>
       </c>
       <c r="I19">
-        <v>-0.90651595</v>
+        <v>-0.90390465</v>
       </c>
       <c r="J19">
-        <v>-0.27206719</v>
+        <v>-0.02858241</v>
       </c>
     </row>
     <row r="20">
@@ -643,31 +643,31 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C20">
-        <v>25.7079438</v>
+        <v>26.05084703</v>
       </c>
       <c r="D20">
-        <v>177.63198885</v>
+        <v>141.33928658</v>
       </c>
       <c r="E20">
-        <v>-8.66827165</v>
+        <v>-6.85857466</v>
       </c>
       <c r="F20">
-        <v>18.02033776</v>
+        <v>17.96809322</v>
       </c>
       <c r="G20">
-        <v>0.35846025</v>
+        <v>5.48703743</v>
       </c>
       <c r="H20">
-        <v>0.43341358</v>
+        <v>0.34292873</v>
       </c>
       <c r="I20">
-        <v>-0.90101689</v>
+        <v>-0.89840466</v>
       </c>
       <c r="J20">
-        <v>-0.01792301</v>
+        <v>-0.27435187</v>
       </c>
     </row>
     <row r="21">
@@ -675,31 +675,31 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>26.42497944</v>
+        <v>26.75945341</v>
       </c>
       <c r="D21">
-        <v>315.1397529</v>
+        <v>278.84705063</v>
       </c>
       <c r="E21">
-        <v>6.30894532</v>
+        <v>1.38493173</v>
       </c>
       <c r="F21">
-        <v>17.91035652</v>
+        <v>17.85809336</v>
       </c>
       <c r="G21">
-        <v>-6.27824324</v>
+        <v>-8.89777869</v>
       </c>
       <c r="H21">
-        <v>-0.31544727</v>
+        <v>-0.06924659</v>
       </c>
       <c r="I21">
-        <v>-0.89551783</v>
+        <v>-0.89290467</v>
       </c>
       <c r="J21">
-        <v>0.31391216</v>
+        <v>0.44488893</v>
       </c>
     </row>
     <row r="22">
@@ -707,31 +707,31 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>27.12439512</v>
+        <v>27.45109023</v>
       </c>
       <c r="D22">
-        <v>92.64751695</v>
+        <v>56.35481468</v>
       </c>
       <c r="E22">
-        <v>-0.42119568</v>
+        <v>5.10822798</v>
       </c>
       <c r="F22">
-        <v>17.80037528</v>
+        <v>17.74809351</v>
       </c>
       <c r="G22">
-        <v>9.10874492</v>
+        <v>7.67536212</v>
       </c>
       <c r="H22">
-        <v>0.02105978</v>
+        <v>-0.2554114</v>
       </c>
       <c r="I22">
-        <v>-0.89001876</v>
+        <v>-0.88740468</v>
       </c>
       <c r="J22">
-        <v>-0.45543725</v>
+        <v>-0.38376811</v>
       </c>
     </row>
     <row r="23">
@@ -739,31 +739,31 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C23">
-        <v>27.80752645</v>
+        <v>28.12701534</v>
       </c>
       <c r="D23">
-        <v>230.155281</v>
+        <v>193.86257873</v>
       </c>
       <c r="E23">
-        <v>-5.97785266</v>
+        <v>-9.15393126</v>
       </c>
       <c r="F23">
-        <v>17.69039405</v>
+        <v>17.63809366</v>
       </c>
       <c r="G23">
-        <v>-7.16346536</v>
+        <v>-2.25902517</v>
       </c>
       <c r="H23">
-        <v>0.29889263</v>
+        <v>0.45769656</v>
       </c>
       <c r="I23">
-        <v>-0.8845197</v>
+        <v>-0.88190468</v>
       </c>
       <c r="J23">
-        <v>0.35817327</v>
+        <v>0.11295126</v>
       </c>
     </row>
     <row r="24">
@@ -771,31 +771,31 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C24">
-        <v>28.47555137</v>
+        <v>28.78834134</v>
       </c>
       <c r="D24">
-        <v>7.66304505</v>
+        <v>331.37034278</v>
       </c>
       <c r="E24">
-        <v>9.45051518</v>
+        <v>8.45391158</v>
       </c>
       <c r="F24">
-        <v>17.58041281</v>
+        <v>17.5280938</v>
       </c>
       <c r="G24">
-        <v>1.27155345</v>
+        <v>-4.61490049</v>
       </c>
       <c r="H24">
-        <v>-0.47252576</v>
+        <v>-0.42269558</v>
       </c>
       <c r="I24">
-        <v>-0.87902064</v>
+        <v>-0.87640469</v>
       </c>
       <c r="J24">
-        <v>-0.06357767</v>
+        <v>0.23074502</v>
       </c>
     </row>
     <row r="25">
@@ -803,31 +803,31 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C25">
-        <v>29.12951505</v>
+        <v>29.43605803</v>
       </c>
       <c r="D25">
-        <v>145.1708091</v>
+        <v>108.87810683</v>
       </c>
       <c r="E25">
-        <v>-7.99163751</v>
+        <v>-3.18024337</v>
       </c>
       <c r="F25">
-        <v>17.47043158</v>
+        <v>17.41809395</v>
       </c>
       <c r="G25">
-        <v>5.56037323</v>
+        <v>9.30032555</v>
       </c>
       <c r="H25">
-        <v>0.39958188</v>
+        <v>0.15901217</v>
       </c>
       <c r="I25">
-        <v>-0.87352158</v>
+        <v>-0.8709047</v>
       </c>
       <c r="J25">
-        <v>-0.27801866</v>
+        <v>-0.46501628</v>
       </c>
     </row>
     <row r="26">
@@ -835,31 +835,31 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C26">
-        <v>29.77034991</v>
+        <v>30.07105058</v>
       </c>
       <c r="D26">
-        <v>282.67857315</v>
+        <v>246.38587088</v>
       </c>
       <c r="E26">
-        <v>2.179559</v>
+        <v>-4.01435065</v>
       </c>
       <c r="F26">
-        <v>17.36045034</v>
+        <v>17.3080941</v>
       </c>
       <c r="G26">
-        <v>-9.6883583</v>
+        <v>-9.18231276</v>
       </c>
       <c r="H26">
-        <v>-0.10897795</v>
+        <v>0.20071753</v>
       </c>
       <c r="I26">
-        <v>-0.86802252</v>
+        <v>-0.8654047</v>
       </c>
       <c r="J26">
-        <v>0.48441791</v>
+        <v>0.45911564</v>
       </c>
     </row>
     <row r="27">
@@ -867,31 +867,31 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C27">
-        <v>30.39889196</v>
+        <v>30.69411434</v>
       </c>
       <c r="D27">
-        <v>60.1863372</v>
+        <v>23.89363493</v>
       </c>
       <c r="E27">
-        <v>5.03164033</v>
+        <v>9.33416195</v>
       </c>
       <c r="F27">
-        <v>17.2504691</v>
+        <v>17.19809424</v>
       </c>
       <c r="G27">
-        <v>8.78088328</v>
+        <v>4.13509071</v>
       </c>
       <c r="H27">
-        <v>-0.25158202</v>
+        <v>-0.4667081</v>
       </c>
       <c r="I27">
-        <v>-0.86252346</v>
+        <v>-0.85990471</v>
       </c>
       <c r="J27">
-        <v>-0.43904416</v>
+        <v>-0.20675454</v>
       </c>
     </row>
     <row r="28">
@@ -899,31 +899,31 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C28">
-        <v>31.01589415</v>
+        <v>31.30596715</v>
       </c>
       <c r="D28">
-        <v>197.69410125</v>
+        <v>161.40139898</v>
       </c>
       <c r="E28">
-        <v>-9.81799138</v>
+        <v>-9.84944375</v>
       </c>
       <c r="F28">
-        <v>17.14048787</v>
+        <v>17.08809439</v>
       </c>
       <c r="G28">
-        <v>-3.13220703</v>
+        <v>3.31443631</v>
       </c>
       <c r="H28">
-        <v>0.49089957</v>
+        <v>0.49247219</v>
       </c>
       <c r="I28">
-        <v>-0.85702439</v>
+        <v>-0.85440472</v>
       </c>
       <c r="J28">
-        <v>0.15661035</v>
+        <v>-0.16572182</v>
       </c>
     </row>
     <row r="29">
@@ -931,31 +931,31 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C29">
-        <v>31.62203754</v>
+        <v>31.90725947</v>
       </c>
       <c r="D29">
-        <v>335.2018653</v>
+        <v>298.90916303</v>
       </c>
       <c r="E29">
-        <v>9.51934229</v>
+        <v>5.11021837</v>
       </c>
       <c r="F29">
-        <v>17.03050663</v>
+        <v>16.97809454</v>
       </c>
       <c r="G29">
-        <v>-4.39817759</v>
+        <v>-9.25364653</v>
       </c>
       <c r="H29">
-        <v>-0.47596711</v>
+        <v>-0.25551092</v>
       </c>
       <c r="I29">
-        <v>-0.85152533</v>
+        <v>-0.84890473</v>
       </c>
       <c r="J29">
-        <v>0.21990888</v>
+        <v>0.46268233</v>
       </c>
     </row>
     <row r="30">
@@ -963,31 +963,31 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>32.21794052</v>
+        <v>32.49858295</v>
       </c>
       <c r="D30">
-        <v>112.70962935</v>
+        <v>76.41692708</v>
       </c>
       <c r="E30">
-        <v>-4.11650146</v>
+        <v>2.52365151</v>
       </c>
       <c r="F30">
-        <v>16.9205254</v>
+        <v>16.86809468</v>
       </c>
       <c r="G30">
-        <v>9.83616979</v>
+        <v>10.44502584</v>
       </c>
       <c r="H30">
-        <v>0.20582507</v>
+        <v>-0.12618258</v>
       </c>
       <c r="I30">
-        <v>-0.84602627</v>
+        <v>-0.84340473</v>
       </c>
       <c r="J30">
-        <v>-0.49180849</v>
+        <v>-0.52225129</v>
       </c>
     </row>
     <row r="31">
@@ -995,31 +995,31 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C31">
-        <v>32.80416657</v>
+        <v>33.08047759</v>
       </c>
       <c r="D31">
-        <v>250.2173934</v>
+        <v>213.92469113</v>
       </c>
       <c r="E31">
-        <v>-3.66726133</v>
+        <v>-9.05806325</v>
       </c>
       <c r="F31">
-        <v>16.81054416</v>
+        <v>16.75809483</v>
       </c>
       <c r="G31">
-        <v>-10.19592072</v>
+        <v>-6.09243365</v>
       </c>
       <c r="H31">
-        <v>0.18336307</v>
+        <v>0.45290316</v>
       </c>
       <c r="I31">
-        <v>-0.84052721</v>
+        <v>-0.83790474</v>
       </c>
       <c r="J31">
-        <v>0.50979604</v>
+        <v>0.30462168</v>
       </c>
     </row>
     <row r="32">
@@ -1027,31 +1027,31 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C32">
-        <v>33.38123091</v>
+        <v>33.65343785</v>
       </c>
       <c r="D32">
-        <v>27.72515745</v>
+        <v>351.43245518</v>
       </c>
       <c r="E32">
-        <v>9.74075255</v>
+        <v>10.95968286</v>
       </c>
       <c r="F32">
-        <v>16.70056293</v>
+        <v>16.64809498</v>
       </c>
       <c r="G32">
-        <v>5.11946655</v>
+        <v>-1.65114664</v>
       </c>
       <c r="H32">
-        <v>-0.48703763</v>
+        <v>-0.54798414</v>
       </c>
       <c r="I32">
-        <v>-0.83502815</v>
+        <v>-0.83240475</v>
       </c>
       <c r="J32">
-        <v>-0.25597333</v>
+        <v>0.08255733</v>
       </c>
     </row>
     <row r="33">
@@ -1059,31 +1059,31 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C33">
-        <v>33.94960606</v>
+        <v>34.21791784</v>
       </c>
       <c r="D33">
-        <v>165.2329215</v>
+        <v>128.94021923</v>
       </c>
       <c r="E33">
-        <v>-10.80034937</v>
+        <v>-7.06874237</v>
       </c>
       <c r="F33">
-        <v>16.59058169</v>
+        <v>16.53809512</v>
       </c>
       <c r="G33">
-        <v>2.84693743</v>
+        <v>8.74781636</v>
       </c>
       <c r="H33">
-        <v>0.54001747</v>
+        <v>0.35343712</v>
       </c>
       <c r="I33">
-        <v>-0.82952908</v>
+        <v>-0.82690476</v>
       </c>
       <c r="J33">
-        <v>-0.14234687</v>
+        <v>-0.43739082</v>
       </c>
     </row>
     <row r="34">
@@ -1091,31 +1091,31 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C34">
-        <v>34.50972663</v>
+        <v>34.7743358</v>
       </c>
       <c r="D34">
-        <v>302.74068555</v>
+        <v>266.44798328</v>
       </c>
       <c r="E34">
-        <v>6.12819059</v>
+        <v>-0.70671175</v>
       </c>
       <c r="F34">
-        <v>16.48060045</v>
+        <v>16.42809527</v>
       </c>
       <c r="G34">
-        <v>-9.5307444</v>
+        <v>-11.38500085</v>
       </c>
       <c r="H34">
-        <v>-0.30640953</v>
+        <v>0.03533559</v>
       </c>
       <c r="I34">
-        <v>-0.82403002</v>
+        <v>-0.82140476</v>
       </c>
       <c r="J34">
-        <v>0.47653722</v>
+        <v>0.56925004</v>
       </c>
     </row>
     <row r="35">
@@ -1123,31 +1123,31 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C35">
-        <v>35.06199346</v>
+        <v>35.32307795</v>
       </c>
       <c r="D35">
-        <v>80.2484496</v>
+        <v>43.95574733</v>
       </c>
       <c r="E35">
-        <v>1.9460049</v>
+        <v>8.32445017</v>
       </c>
       <c r="F35">
-        <v>16.37061922</v>
+        <v>16.31809542</v>
       </c>
       <c r="G35">
-        <v>11.32324562</v>
+        <v>8.02641211</v>
       </c>
       <c r="H35">
-        <v>-0.09730025</v>
+        <v>-0.41622251</v>
       </c>
       <c r="I35">
-        <v>-0.81853096</v>
+        <v>-0.81590477</v>
       </c>
       <c r="J35">
-        <v>-0.56616228</v>
+        <v>-0.40132061</v>
       </c>
     </row>
     <row r="36">
@@ -1155,31 +1155,31 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C36">
-        <v>35.60677721</v>
+        <v>35.86450179</v>
       </c>
       <c r="D36">
-        <v>217.75621365</v>
+        <v>181.46351138</v>
       </c>
       <c r="E36">
-        <v>-9.20631895</v>
+        <v>-11.71358519</v>
       </c>
       <c r="F36">
-        <v>16.26063798</v>
+        <v>16.20809556</v>
       </c>
       <c r="G36">
-        <v>-7.12989086</v>
+        <v>-0.29926627</v>
       </c>
       <c r="H36">
-        <v>0.46031595</v>
+        <v>0.58567926</v>
       </c>
       <c r="I36">
-        <v>-0.8130319</v>
+        <v>-0.81040478</v>
       </c>
       <c r="J36">
-        <v>0.35649454</v>
+        <v>0.01496331</v>
       </c>
     </row>
     <row r="37">
@@ -1187,31 +1187,31 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C37">
-        <v>36.1444214</v>
+        <v>36.39893906</v>
       </c>
       <c r="D37">
-        <v>355.2639777</v>
+        <v>318.97127543</v>
       </c>
       <c r="E37">
-        <v>11.75617536</v>
+        <v>8.95304878</v>
       </c>
       <c r="F37">
-        <v>16.15065675</v>
+        <v>16.09809571</v>
       </c>
       <c r="G37">
-        <v>-0.9739751</v>
+        <v>-7.7906503</v>
       </c>
       <c r="H37">
-        <v>-0.58780877</v>
+        <v>-0.44765244</v>
       </c>
       <c r="I37">
-        <v>-0.80753284</v>
+        <v>-0.80490479</v>
       </c>
       <c r="J37">
-        <v>0.04869875</v>
+        <v>0.38953251</v>
       </c>
     </row>
     <row r="38">
@@ -1219,31 +1219,31 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C38">
-        <v>36.67524515</v>
+        <v>36.92669821</v>
       </c>
       <c r="D38">
-        <v>132.77174175</v>
+        <v>96.47903948</v>
       </c>
       <c r="E38">
-        <v>-8.11199233</v>
+        <v>-1.3558659</v>
       </c>
       <c r="F38">
-        <v>16.04067551</v>
+        <v>15.98809586</v>
       </c>
       <c r="G38">
-        <v>8.76882601</v>
+        <v>11.93911297</v>
       </c>
       <c r="H38">
-        <v>0.40559962</v>
+        <v>0.06779329</v>
       </c>
       <c r="I38">
-        <v>-0.80203378</v>
+        <v>-0.79940479</v>
       </c>
       <c r="J38">
-        <v>-0.4384413</v>
+        <v>-0.59695565</v>
       </c>
     </row>
     <row r="39">
@@ -1251,31 +1251,31 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C39">
-        <v>37.19954552</v>
+        <v>37.44806668</v>
       </c>
       <c r="D39">
-        <v>270.2795058</v>
+        <v>233.98680353</v>
       </c>
       <c r="E39">
-        <v>0.05898742</v>
+        <v>-7.15022911</v>
       </c>
       <c r="F39">
-        <v>15.93069427</v>
+        <v>15.878096</v>
       </c>
       <c r="G39">
-        <v>-12.09171205</v>
+        <v>-9.83668089</v>
       </c>
       <c r="H39">
-        <v>-0.00294937</v>
+        <v>0.35751146</v>
       </c>
       <c r="I39">
-        <v>-0.79653471</v>
+        <v>-0.7939048</v>
       </c>
       <c r="J39">
-        <v>0.6045856</v>
+        <v>0.49183404</v>
       </c>
     </row>
     <row r="40">
@@ -1283,31 +1283,31 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C40">
-        <v>37.71759963</v>
+        <v>37.96331282</v>
       </c>
       <c r="D40">
-        <v>47.78726985</v>
+        <v>11.49456758</v>
       </c>
       <c r="E40">
-        <v>8.22078448</v>
+        <v>12.05637896</v>
       </c>
       <c r="F40">
-        <v>15.82071304</v>
+        <v>15.76809615</v>
       </c>
       <c r="G40">
-        <v>9.06221504</v>
+        <v>2.45170762</v>
       </c>
       <c r="H40">
-        <v>-0.41103922</v>
+        <v>-0.60281895</v>
       </c>
       <c r="I40">
-        <v>-0.79103565</v>
+        <v>-0.78840481</v>
       </c>
       <c r="J40">
-        <v>-0.45311075</v>
+        <v>-0.12258538</v>
       </c>
     </row>
     <row r="41">
@@ -1315,31 +1315,31 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C41">
-        <v>38.22966644</v>
+        <v>38.47268764</v>
       </c>
       <c r="D41">
-        <v>185.2950339</v>
+        <v>149.00233163</v>
       </c>
       <c r="E41">
-        <v>-12.32349083</v>
+        <v>-10.66584786</v>
       </c>
       <c r="F41">
-        <v>15.7107318</v>
+        <v>15.6580963</v>
       </c>
       <c r="G41">
-        <v>-1.14213836</v>
+        <v>6.40809721</v>
       </c>
       <c r="H41">
-        <v>0.61617454</v>
+        <v>0.53329239</v>
       </c>
       <c r="I41">
-        <v>-0.78553659</v>
+        <v>-0.78290481</v>
       </c>
       <c r="J41">
-        <v>0.05710692</v>
+        <v>-0.32040486</v>
       </c>
     </row>
     <row r="42">
@@ -1347,31 +1347,31 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C42">
-        <v>38.73598841</v>
+        <v>38.97642632</v>
       </c>
       <c r="D42">
-        <v>322.80279795</v>
+        <v>286.51009568</v>
       </c>
       <c r="E42">
-        <v>9.96866634</v>
+        <v>3.57504169</v>
       </c>
       <c r="F42">
-        <v>15.60075057</v>
+        <v>15.54809644</v>
       </c>
       <c r="G42">
-        <v>-7.56586235</v>
+        <v>-12.06133384</v>
       </c>
       <c r="H42">
-        <v>-0.49843332</v>
+        <v>-0.17875208</v>
       </c>
       <c r="I42">
-        <v>-0.78003753</v>
+        <v>-0.77740482</v>
       </c>
       <c r="J42">
-        <v>0.37829312</v>
+        <v>0.60306669</v>
       </c>
     </row>
     <row r="43">
@@ -1379,31 +1379,31 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C43">
-        <v>39.23679292</v>
+        <v>39.47474963</v>
       </c>
       <c r="D43">
-        <v>100.310562</v>
+        <v>64.01785973</v>
       </c>
       <c r="E43">
-        <v>-2.26423829</v>
+        <v>5.57022233</v>
       </c>
       <c r="F43">
-        <v>15.49076933</v>
+        <v>15.43809659</v>
       </c>
       <c r="G43">
-        <v>12.44625608</v>
+        <v>11.42968927</v>
       </c>
       <c r="H43">
-        <v>0.11321191</v>
+        <v>-0.27851112</v>
       </c>
       <c r="I43">
-        <v>-0.77453847</v>
+        <v>-0.77190483</v>
       </c>
       <c r="J43">
-        <v>-0.6223128</v>
+        <v>-0.57148446</v>
       </c>
     </row>
     <row r="44">
@@ -1411,31 +1411,31 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C44">
-        <v>39.73229356</v>
+        <v>39.96786506</v>
       </c>
       <c r="D44">
-        <v>237.81832605</v>
+        <v>201.52562378</v>
       </c>
       <c r="E44">
-        <v>-6.80884453</v>
+        <v>-11.95111391</v>
       </c>
       <c r="F44">
-        <v>15.3807881</v>
+        <v>15.32809674</v>
       </c>
       <c r="G44">
-        <v>-10.81993502</v>
+        <v>-4.71384415</v>
       </c>
       <c r="H44">
-        <v>0.34044223</v>
+        <v>0.5975557</v>
       </c>
       <c r="I44">
-        <v>-0.7690394</v>
+        <v>-0.76640484</v>
       </c>
       <c r="J44">
-        <v>0.54099675</v>
+        <v>0.23569221</v>
       </c>
     </row>
     <row r="45">
@@ -1443,31 +1443,31 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C45">
-        <v>40.2226913</v>
+        <v>40.45596799</v>
       </c>
       <c r="D45">
-        <v>15.3260901</v>
+        <v>339.03338783</v>
       </c>
       <c r="E45">
-        <v>12.45590133</v>
+        <v>12.11803292</v>
       </c>
       <c r="F45">
-        <v>15.27080686</v>
+        <v>15.21809688</v>
       </c>
       <c r="G45">
-        <v>3.41364615</v>
+        <v>-4.64357679</v>
       </c>
       <c r="H45">
-        <v>-0.62279507</v>
+        <v>-0.60590165</v>
       </c>
       <c r="I45">
-        <v>-0.76354034</v>
+        <v>-0.76090484</v>
       </c>
       <c r="J45">
-        <v>-0.17068231</v>
+        <v>0.23217884</v>
       </c>
     </row>
     <row r="46">
@@ -1475,31 +1475,31 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C46">
-        <v>40.70817548</v>
+        <v>40.93924262</v>
       </c>
       <c r="D46">
-        <v>152.83385415</v>
+        <v>116.54115188</v>
       </c>
       <c r="E46">
-        <v>-11.60518511</v>
+        <v>-5.85591904</v>
       </c>
       <c r="F46">
-        <v>15.16082562</v>
+        <v>15.10809703</v>
       </c>
       <c r="G46">
-        <v>5.95558939</v>
+        <v>11.72406143</v>
       </c>
       <c r="H46">
-        <v>0.58025926</v>
+        <v>0.29279595</v>
       </c>
       <c r="I46">
-        <v>-0.75804128</v>
+        <v>-0.75540485</v>
       </c>
       <c r="J46">
-        <v>-0.29777947</v>
+        <v>-0.58620307</v>
       </c>
     </row>
     <row r="47">
@@ -1507,31 +1507,31 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C47">
-        <v>41.18892473</v>
+        <v>41.41786286</v>
       </c>
       <c r="D47">
-        <v>290.3416182</v>
+        <v>254.04891593</v>
       </c>
       <c r="E47">
-        <v>4.57841945</v>
+        <v>-3.63607455</v>
       </c>
       <c r="F47">
-        <v>15.05084439</v>
+        <v>14.99809718</v>
       </c>
       <c r="G47">
-        <v>-12.34950034</v>
+        <v>-12.72147959</v>
       </c>
       <c r="H47">
-        <v>-0.22892097</v>
+        <v>0.18180373</v>
       </c>
       <c r="I47">
-        <v>-0.75254222</v>
+        <v>-0.74990486</v>
       </c>
       <c r="J47">
-        <v>0.61747502</v>
+        <v>0.63607398</v>
       </c>
     </row>
     <row r="48">
@@ -1539,31 +1539,31 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C48">
-        <v>41.66510786</v>
+        <v>41.89199312</v>
       </c>
       <c r="D48">
-        <v>67.84938225</v>
+        <v>31.55667998</v>
       </c>
       <c r="E48">
-        <v>5.0129747</v>
+        <v>11.37973502</v>
       </c>
       <c r="F48">
-        <v>14.94086315</v>
+        <v>14.88809732</v>
       </c>
       <c r="G48">
-        <v>12.31424756</v>
+        <v>6.98900486</v>
       </c>
       <c r="H48">
-        <v>-0.25064873</v>
+        <v>-0.56898675</v>
       </c>
       <c r="I48">
-        <v>-0.74704316</v>
+        <v>-0.74440487</v>
       </c>
       <c r="J48">
-        <v>-0.61571238</v>
+        <v>-0.34945024</v>
       </c>
     </row>
     <row r="49">
@@ -1571,31 +1571,31 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C49">
-        <v>42.13688452</v>
+        <v>42.36178903</v>
       </c>
       <c r="D49">
-        <v>205.3571463</v>
+        <v>169.06444403</v>
       </c>
       <c r="E49">
-        <v>-12.12532896</v>
+        <v>-13.23148329</v>
       </c>
       <c r="F49">
-        <v>14.83088192</v>
+        <v>14.77809747</v>
       </c>
       <c r="G49">
-        <v>-5.74641968</v>
+        <v>2.55649863</v>
       </c>
       <c r="H49">
-        <v>0.60626645</v>
+        <v>0.66157416</v>
       </c>
       <c r="I49">
-        <v>-0.7415441</v>
+        <v>-0.73890487</v>
       </c>
       <c r="J49">
-        <v>0.28732098</v>
+        <v>-0.12782493</v>
       </c>
     </row>
     <row r="50">
@@ -1603,31 +1603,31 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C50">
-        <v>42.60440597</v>
+        <v>42.82739808</v>
       </c>
       <c r="D50">
-        <v>342.86491035</v>
+        <v>306.57220808</v>
       </c>
       <c r="E50">
-        <v>12.93770803</v>
+        <v>8.10088366</v>
       </c>
       <c r="F50">
-        <v>14.72090068</v>
+        <v>14.66809762</v>
       </c>
       <c r="G50">
-        <v>-3.98883366</v>
+        <v>-10.91891003</v>
       </c>
       <c r="H50">
-        <v>-0.6468854</v>
+        <v>-0.40504418</v>
       </c>
       <c r="I50">
-        <v>-0.73604503</v>
+        <v>-0.73340488</v>
       </c>
       <c r="J50">
-        <v>0.19944168</v>
+        <v>0.5459455</v>
       </c>
     </row>
     <row r="51">
@@ -1635,31 +1635,31 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C51">
-        <v>43.06781562</v>
+        <v>43.2889602</v>
       </c>
       <c r="D51">
-        <v>120.3726744</v>
+        <v>84.07997213</v>
       </c>
       <c r="E51">
-        <v>-6.90542119</v>
+        <v>1.41441998</v>
       </c>
       <c r="F51">
-        <v>14.61091945</v>
+        <v>14.55809776</v>
       </c>
       <c r="G51">
-        <v>11.78287703</v>
+        <v>13.64042542</v>
       </c>
       <c r="H51">
-        <v>0.34527106</v>
+        <v>-0.070721</v>
       </c>
       <c r="I51">
-        <v>-0.73054597</v>
+        <v>-0.72790489</v>
       </c>
       <c r="J51">
-        <v>-0.58914385</v>
+        <v>-0.68202127</v>
       </c>
     </row>
     <row r="52">
@@ -1667,31 +1667,31 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C52">
-        <v>43.52724963</v>
+        <v>43.74660833</v>
       </c>
       <c r="D52">
-        <v>257.88043845</v>
+        <v>221.58773618</v>
       </c>
       <c r="E52">
-        <v>-2.8918819</v>
+        <v>-10.34356836</v>
       </c>
       <c r="F52">
-        <v>14.50093821</v>
+        <v>14.44809791</v>
       </c>
       <c r="G52">
-        <v>-13.46698965</v>
+        <v>-9.17949129</v>
       </c>
       <c r="H52">
-        <v>0.14459409</v>
+        <v>0.51717842</v>
       </c>
       <c r="I52">
-        <v>-0.72504691</v>
+        <v>-0.7224049</v>
       </c>
       <c r="J52">
-        <v>0.67334948</v>
+        <v>0.45897456</v>
       </c>
     </row>
     <row r="53">
@@ -1699,31 +1699,31 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C53">
-        <v>43.9828374</v>
+        <v>44.20046884</v>
       </c>
       <c r="D53">
-        <v>35.3882025</v>
+        <v>359.09550023</v>
       </c>
       <c r="E53">
-        <v>11.32285003</v>
+        <v>13.94168198</v>
       </c>
       <c r="F53">
-        <v>14.39095697</v>
+        <v>14.33809806</v>
       </c>
       <c r="G53">
-        <v>8.04322228</v>
+        <v>-0.22010864</v>
       </c>
       <c r="H53">
-        <v>-0.5661425</v>
+        <v>-0.6970841</v>
       </c>
       <c r="I53">
-        <v>-0.71954785</v>
+        <v>-0.7169049</v>
       </c>
       <c r="J53">
-        <v>-0.40216111</v>
+        <v>0.01100543</v>
       </c>
     </row>
     <row r="54">
@@ -1731,31 +1731,31 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C54">
-        <v>44.43470206</v>
+        <v>44.65066206</v>
       </c>
       <c r="D54">
-        <v>172.89596655</v>
+        <v>136.60326428</v>
       </c>
       <c r="E54">
-        <v>-13.89442942</v>
+        <v>-10.21302752</v>
       </c>
       <c r="F54">
-        <v>14.28097574</v>
+        <v>14.2280982</v>
       </c>
       <c r="G54">
-        <v>1.73163598</v>
+        <v>9.65687788</v>
       </c>
       <c r="H54">
-        <v>0.69472147</v>
+        <v>0.51065138</v>
       </c>
       <c r="I54">
-        <v>-0.71404879</v>
+        <v>-0.71140491</v>
       </c>
       <c r="J54">
-        <v>-0.0865818</v>
+        <v>-0.48284389</v>
       </c>
     </row>
     <row r="55">
@@ -1763,31 +1763,31 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C55">
-        <v>44.88296084</v>
+        <v>45.0973026</v>
       </c>
       <c r="D55">
-        <v>310.4037306</v>
+        <v>274.11102833</v>
       </c>
       <c r="E55">
-        <v>9.14775706</v>
+        <v>1.01556195</v>
       </c>
       <c r="F55">
-        <v>14.1709945</v>
+        <v>14.11809835</v>
       </c>
       <c r="G55">
-        <v>-10.74716035</v>
+        <v>-14.12968269</v>
       </c>
       <c r="H55">
-        <v>-0.45738785</v>
+        <v>-0.0507781</v>
       </c>
       <c r="I55">
-        <v>-0.70854973</v>
+        <v>-0.70590492</v>
       </c>
       <c r="J55">
-        <v>0.53735802</v>
+        <v>0.70648413</v>
       </c>
     </row>
     <row r="56">
@@ -1795,31 +1795,31 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C56">
-        <v>45.32772553</v>
+        <v>45.54049979</v>
       </c>
       <c r="D56">
-        <v>87.91149465</v>
+        <v>51.61879238</v>
       </c>
       <c r="E56">
-        <v>0.5183245</v>
+        <v>8.86316155</v>
       </c>
       <c r="F56">
-        <v>14.06101327</v>
+        <v>14.0080985</v>
       </c>
       <c r="G56">
-        <v>14.21334745</v>
+        <v>11.19006451</v>
       </c>
       <c r="H56">
-        <v>-0.02591623</v>
+        <v>-0.44315808</v>
       </c>
       <c r="I56">
-        <v>-0.70305066</v>
+        <v>-0.70040492</v>
       </c>
       <c r="J56">
-        <v>-0.71066737</v>
+        <v>-0.55950323</v>
       </c>
     </row>
     <row r="57">
@@ -1827,31 +1827,31 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C57">
-        <v>45.76910277</v>
+        <v>45.98035798</v>
       </c>
       <c r="D57">
-        <v>225.4192587</v>
+        <v>189.12655643</v>
       </c>
       <c r="E57">
-        <v>-10.0589081</v>
+        <v>-14.19996149</v>
       </c>
       <c r="F57">
-        <v>13.95103203</v>
+        <v>13.89809864</v>
       </c>
       <c r="G57">
-        <v>-10.20720692</v>
+        <v>-2.28121632</v>
       </c>
       <c r="H57">
-        <v>0.5029454</v>
+        <v>0.70999807</v>
       </c>
       <c r="I57">
-        <v>-0.6975516</v>
+        <v>-0.69490493</v>
       </c>
       <c r="J57">
-        <v>0.51036035</v>
+        <v>0.11406082</v>
       </c>
     </row>
     <row r="58">
@@ -1859,31 +1859,31 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C58">
-        <v>46.20719441</v>
+        <v>46.41697688</v>
       </c>
       <c r="D58">
-        <v>2.92702275</v>
+        <v>326.63432048</v>
       </c>
       <c r="E58">
-        <v>14.41810799</v>
+        <v>12.09965284</v>
       </c>
       <c r="F58">
-        <v>13.84105079</v>
+        <v>13.78809879</v>
       </c>
       <c r="G58">
-        <v>0.73720755</v>
+        <v>-7.96785623</v>
       </c>
       <c r="H58">
-        <v>-0.7209054</v>
+        <v>-0.60498264</v>
       </c>
       <c r="I58">
-        <v>-0.69205254</v>
+        <v>-0.68940494</v>
       </c>
       <c r="J58">
-        <v>-0.03686038</v>
+        <v>0.39839281</v>
       </c>
     </row>
     <row r="59">
@@ -1891,31 +1891,31 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C59">
-        <v>46.64209782</v>
+        <v>46.85045183</v>
       </c>
       <c r="D59">
-        <v>140.4347868</v>
+        <v>104.14208453</v>
       </c>
       <c r="E59">
-        <v>-11.21011038</v>
+        <v>-3.56508329</v>
       </c>
       <c r="F59">
-        <v>13.73106956</v>
+        <v>13.67809894</v>
       </c>
       <c r="G59">
-        <v>9.26235144</v>
+        <v>14.14919752</v>
       </c>
       <c r="H59">
-        <v>0.56050552</v>
+        <v>0.17825416</v>
       </c>
       <c r="I59">
-        <v>-0.68655348</v>
+        <v>-0.68390495</v>
       </c>
       <c r="J59">
-        <v>-0.46311757</v>
+        <v>-0.70745988</v>
       </c>
     </row>
     <row r="60">
@@ -1923,31 +1923,31 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C60">
-        <v>47.07390611</v>
+        <v>47.28087407</v>
       </c>
       <c r="D60">
-        <v>277.94255085</v>
+        <v>241.64984858</v>
       </c>
       <c r="E60">
-        <v>2.02360023</v>
+        <v>-6.97746169</v>
       </c>
       <c r="F60">
-        <v>13.62108832</v>
+        <v>13.56809908</v>
       </c>
       <c r="G60">
-        <v>-14.50417164</v>
+        <v>-12.93142357</v>
       </c>
       <c r="H60">
-        <v>-0.10118001</v>
+        <v>0.34887308</v>
       </c>
       <c r="I60">
-        <v>-0.68105442</v>
+        <v>-0.67840495</v>
       </c>
       <c r="J60">
-        <v>0.72520858</v>
+        <v>0.64657118</v>
       </c>
     </row>
     <row r="61">
@@ -1955,31 +1955,31 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C61">
-        <v>47.50270848</v>
+        <v>47.708331</v>
       </c>
       <c r="D61">
-        <v>55.4503149</v>
+        <v>19.15761263</v>
       </c>
       <c r="E61">
-        <v>8.36286672</v>
+        <v>13.97524636</v>
       </c>
       <c r="F61">
-        <v>13.51110709</v>
+        <v>13.45809923</v>
       </c>
       <c r="G61">
-        <v>12.14547016</v>
+        <v>4.85510601</v>
       </c>
       <c r="H61">
-        <v>-0.41814334</v>
+        <v>-0.69876232</v>
       </c>
       <c r="I61">
-        <v>-0.67555535</v>
+        <v>-0.67290496</v>
       </c>
       <c r="J61">
-        <v>-0.60727351</v>
+        <v>-0.2427553</v>
       </c>
     </row>
     <row r="62">
@@ -1987,31 +1987,31 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C62">
-        <v>47.92859036</v>
+        <v>48.13290638</v>
       </c>
       <c r="D62">
-        <v>192.95807895</v>
+        <v>156.66537668</v>
       </c>
       <c r="E62">
-        <v>-14.46813811</v>
+        <v>-13.67568562</v>
       </c>
       <c r="F62">
-        <v>13.40112585</v>
+        <v>13.34809938</v>
       </c>
       <c r="G62">
-        <v>-3.32908477</v>
+        <v>5.89948014</v>
       </c>
       <c r="H62">
-        <v>0.72340691</v>
+        <v>0.68378428</v>
       </c>
       <c r="I62">
-        <v>-0.67005629</v>
+        <v>-0.66740497</v>
       </c>
       <c r="J62">
-        <v>0.16645424</v>
+        <v>-0.29497401</v>
       </c>
     </row>
     <row r="63">
@@ -2019,31 +2019,31 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C63">
-        <v>48.35163369</v>
+        <v>48.55468057</v>
       </c>
       <c r="D63">
-        <v>330.465843</v>
+        <v>294.17314073</v>
       </c>
       <c r="E63">
-        <v>13.00285654</v>
+        <v>6.13905479</v>
       </c>
       <c r="F63">
-        <v>13.29114462</v>
+        <v>13.23809952</v>
       </c>
       <c r="G63">
-        <v>-7.36689871</v>
+        <v>-13.67716079</v>
       </c>
       <c r="H63">
-        <v>-0.65014283</v>
+        <v>-0.30695274</v>
       </c>
       <c r="I63">
-        <v>-0.66455723</v>
+        <v>-0.66190498</v>
       </c>
       <c r="J63">
-        <v>0.36834494</v>
+        <v>0.68385804</v>
       </c>
     </row>
     <row r="64">
@@ -2051,31 +2051,31 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C64">
-        <v>48.7719171</v>
+        <v>48.97373071</v>
       </c>
       <c r="D64">
-        <v>107.97360705</v>
+        <v>71.68090478</v>
       </c>
       <c r="E64">
-        <v>-4.6415937</v>
+        <v>4.74234678</v>
       </c>
       <c r="F64">
-        <v>13.18116338</v>
+        <v>13.12809967</v>
       </c>
       <c r="G64">
-        <v>14.307779</v>
+        <v>14.32351724</v>
       </c>
       <c r="H64">
-        <v>0.23207968</v>
+        <v>-0.23711734</v>
       </c>
       <c r="I64">
-        <v>-0.65905817</v>
+        <v>-0.65640498</v>
       </c>
       <c r="J64">
-        <v>-0.71538895</v>
+        <v>-0.71617586</v>
       </c>
     </row>
     <row r="65">
@@ -2083,31 +2083,31 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C65">
-        <v>49.18951608</v>
+        <v>49.39013089</v>
       </c>
       <c r="D65">
-        <v>245.4813711</v>
+        <v>209.18866883</v>
       </c>
       <c r="E65">
-        <v>-6.28190121</v>
+        <v>-13.25520119</v>
       </c>
       <c r="F65">
-        <v>13.07118214</v>
+        <v>13.01809982</v>
       </c>
       <c r="G65">
-        <v>-13.77250575</v>
+        <v>-7.4046417</v>
       </c>
       <c r="H65">
-        <v>0.31409506</v>
+        <v>0.66276006</v>
       </c>
       <c r="I65">
-        <v>-0.65355911</v>
+        <v>-0.65090499</v>
       </c>
       <c r="J65">
-        <v>0.68862529</v>
+        <v>0.37023208</v>
       </c>
     </row>
     <row r="66">
@@ -2115,31 +2115,31 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C66">
-        <v>49.6045032</v>
+        <v>49.80395236</v>
       </c>
       <c r="D66">
-        <v>22.98913515</v>
+        <v>346.69643288</v>
       </c>
       <c r="E66">
-        <v>14.02206024</v>
+        <v>14.86685091</v>
       </c>
       <c r="F66">
-        <v>12.96120091</v>
+        <v>12.90809996</v>
       </c>
       <c r="G66">
-        <v>5.94887364</v>
+        <v>-3.51535195</v>
       </c>
       <c r="H66">
-        <v>-0.70110301</v>
+        <v>-0.74334255</v>
       </c>
       <c r="I66">
-        <v>-0.64806005</v>
+        <v>-0.645405</v>
       </c>
       <c r="J66">
-        <v>-0.29744368</v>
+        <v>0.1757676</v>
       </c>
     </row>
     <row r="67">
@@ -2147,31 +2147,31 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C67">
-        <v>50.01694824</v>
+        <v>50.21526363</v>
       </c>
       <c r="D67">
-        <v>160.4968992</v>
+        <v>124.20419693</v>
       </c>
       <c r="E67">
-        <v>-14.44541267</v>
+        <v>-8.63963574</v>
       </c>
       <c r="F67">
-        <v>12.85121967</v>
+        <v>12.79810011</v>
       </c>
       <c r="G67">
-        <v>5.11626874</v>
+        <v>12.71083505</v>
       </c>
       <c r="H67">
-        <v>0.72227063</v>
+        <v>0.43198179</v>
       </c>
       <c r="I67">
-        <v>-0.64256098</v>
+        <v>-0.63990501</v>
       </c>
       <c r="J67">
-        <v>-0.25581344</v>
+        <v>-0.63554175</v>
       </c>
     </row>
     <row r="68">
@@ -2179,31 +2179,31 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C68">
-        <v>50.42691834</v>
+        <v>50.62413066</v>
       </c>
       <c r="D68">
-        <v>298.00466325</v>
+        <v>261.71196098</v>
       </c>
       <c r="E68">
-        <v>7.23860001</v>
+        <v>-2.2285556</v>
       </c>
       <c r="F68">
-        <v>12.74123844</v>
+        <v>12.68810026</v>
       </c>
       <c r="G68">
-        <v>-13.61115399</v>
+        <v>-15.29855064</v>
       </c>
       <c r="H68">
-        <v>-0.36193</v>
+        <v>0.11142778</v>
       </c>
       <c r="I68">
-        <v>-0.63706192</v>
+        <v>-0.63440501</v>
       </c>
       <c r="J68">
-        <v>0.6805577</v>
+        <v>0.76492753</v>
       </c>
     </row>
     <row r="69">
@@ -2211,31 +2211,31 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C69">
-        <v>50.83447813</v>
+        <v>51.03061696</v>
       </c>
       <c r="D69">
-        <v>75.5124273</v>
+        <v>39.21972503</v>
       </c>
       <c r="E69">
-        <v>3.87925963</v>
+        <v>12.04672586</v>
       </c>
       <c r="F69">
-        <v>12.6312572</v>
+        <v>12.5781004</v>
       </c>
       <c r="G69">
-        <v>15.01341687</v>
+        <v>9.83197774</v>
       </c>
       <c r="H69">
-        <v>-0.19396298</v>
+        <v>-0.60233629</v>
       </c>
       <c r="I69">
-        <v>-0.63156286</v>
+        <v>-0.62890502</v>
       </c>
       <c r="J69">
-        <v>-0.75067084</v>
+        <v>-0.49159889</v>
       </c>
     </row>
     <row r="70">
@@ -2243,31 +2243,31 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C70">
-        <v>51.23968992</v>
+        <v>51.43478377</v>
       </c>
       <c r="D70">
-        <v>213.02019135</v>
+        <v>176.72748908</v>
       </c>
       <c r="E70">
-        <v>-13.07643971</v>
+        <v>-15.61248105</v>
       </c>
       <c r="F70">
-        <v>12.52127596</v>
+        <v>12.46810055</v>
       </c>
       <c r="G70">
-        <v>-8.49849237</v>
+        <v>0.89269482</v>
       </c>
       <c r="H70">
-        <v>0.65382199</v>
+        <v>0.78062405</v>
       </c>
       <c r="I70">
-        <v>-0.6260638</v>
+        <v>-0.62340503</v>
       </c>
       <c r="J70">
-        <v>0.42492462</v>
+        <v>-0.04463474</v>
       </c>
     </row>
     <row r="71">
@@ -2275,31 +2275,31 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C71">
-        <v>51.64261374</v>
+        <v>51.8366901</v>
       </c>
       <c r="D71">
-        <v>350.5279554</v>
+        <v>314.23525313</v>
       </c>
       <c r="E71">
-        <v>15.46928115</v>
+        <v>10.96989371</v>
       </c>
       <c r="F71">
-        <v>12.41129473</v>
+        <v>12.3581007</v>
       </c>
       <c r="G71">
-        <v>-2.58091146</v>
+        <v>-11.2667111</v>
       </c>
       <c r="H71">
-        <v>-0.77346406</v>
+        <v>-0.54849469</v>
       </c>
       <c r="I71">
-        <v>-0.62056474</v>
+        <v>-0.61790503</v>
       </c>
       <c r="J71">
-        <v>0.12904557</v>
+        <v>0.56333556</v>
       </c>
     </row>
     <row r="72">
@@ -2307,31 +2307,31 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C72">
-        <v>52.04330752</v>
+        <v>52.23639293</v>
       </c>
       <c r="D72">
-        <v>128.03571945</v>
+        <v>91.74301718</v>
       </c>
       <c r="E72">
-        <v>-9.71642959</v>
+        <v>-0.48091484</v>
       </c>
       <c r="F72">
-        <v>12.30131349</v>
+        <v>12.24810084</v>
       </c>
       <c r="G72">
-        <v>12.42049445</v>
+        <v>15.80356753</v>
       </c>
       <c r="H72">
-        <v>0.48582148</v>
+        <v>0.02404574</v>
       </c>
       <c r="I72">
-        <v>-0.61506567</v>
+        <v>-0.61240504</v>
       </c>
       <c r="J72">
-        <v>-0.62102472</v>
+        <v>-0.79017838</v>
       </c>
     </row>
     <row r="73">
@@ -2339,31 +2339,31 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C73">
-        <v>52.44182715</v>
+        <v>52.63394724</v>
       </c>
       <c r="D73">
-        <v>265.5434835</v>
+        <v>229.25078123</v>
       </c>
       <c r="E73">
-        <v>-1.23194932</v>
+        <v>-10.37576991</v>
       </c>
       <c r="F73">
-        <v>12.19133226</v>
+        <v>12.13810099</v>
       </c>
       <c r="G73">
-        <v>-15.8067618</v>
+        <v>-12.04200577</v>
       </c>
       <c r="H73">
-        <v>0.06159747</v>
+        <v>0.5187885</v>
       </c>
       <c r="I73">
-        <v>-0.60956661</v>
+        <v>-0.60690505</v>
       </c>
       <c r="J73">
-        <v>0.79033809</v>
+        <v>0.60210029</v>
       </c>
     </row>
     <row r="74">
@@ -2371,31 +2371,31 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C74">
-        <v>52.83822663</v>
+        <v>53.02940615</v>
       </c>
       <c r="D74">
-        <v>43.05124755</v>
+        <v>6.75854528</v>
       </c>
       <c r="E74">
-        <v>11.64707237</v>
+        <v>15.86784692</v>
       </c>
       <c r="F74">
-        <v>12.08135102</v>
+        <v>12.02810114</v>
       </c>
       <c r="G74">
-        <v>10.88056353</v>
+        <v>1.88048322</v>
       </c>
       <c r="H74">
-        <v>-0.58235362</v>
+        <v>-0.79339235</v>
       </c>
       <c r="I74">
-        <v>-0.60406755</v>
+        <v>-0.60140506</v>
       </c>
       <c r="J74">
-        <v>-0.54402818</v>
+        <v>-0.09402416</v>
       </c>
     </row>
     <row r="75">
@@ -2403,31 +2403,31 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C75">
-        <v>53.23255811</v>
+        <v>53.422821</v>
       </c>
       <c r="D75">
-        <v>180.5590116</v>
+        <v>144.26630933</v>
       </c>
       <c r="E75">
-        <v>-16.02067015</v>
+        <v>-13.03743963</v>
       </c>
       <c r="F75">
-        <v>11.97136979</v>
+        <v>11.91810128</v>
       </c>
       <c r="G75">
-        <v>-0.15631212</v>
+        <v>9.37998026</v>
       </c>
       <c r="H75">
-        <v>0.80103351</v>
+        <v>0.65187198</v>
       </c>
       <c r="I75">
-        <v>-0.59856849</v>
+        <v>-0.59590506</v>
       </c>
       <c r="J75">
-        <v>0.00781561</v>
+        <v>-0.46899901</v>
       </c>
     </row>
     <row r="76">
@@ -2435,31 +2435,31 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C76">
-        <v>53.62487201</v>
+        <v>53.81424142</v>
       </c>
       <c r="D76">
-        <v>318.06677565</v>
+        <v>281.77407338</v>
       </c>
       <c r="E76">
-        <v>11.97943048</v>
+        <v>3.29385388</v>
       </c>
       <c r="F76">
-        <v>11.86138855</v>
+        <v>11.80810143</v>
       </c>
       <c r="G76">
-        <v>-10.76107369</v>
+        <v>-15.80250826</v>
       </c>
       <c r="H76">
-        <v>-0.59897152</v>
+        <v>-0.16469269</v>
       </c>
       <c r="I76">
-        <v>-0.59306943</v>
+        <v>-0.59040507</v>
       </c>
       <c r="J76">
-        <v>0.53805368</v>
+        <v>0.79012541</v>
       </c>
     </row>
     <row r="77">
@@ -2467,31 +2467,31 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C77">
-        <v>54.01521712</v>
+        <v>54.20371545</v>
       </c>
       <c r="D77">
-        <v>95.5745397</v>
+        <v>59.28183743</v>
       </c>
       <c r="E77">
-        <v>-1.57207189</v>
+        <v>8.28646631</v>
       </c>
       <c r="F77">
-        <v>11.75140731</v>
+        <v>11.69810158</v>
       </c>
       <c r="G77">
-        <v>16.10692448</v>
+        <v>13.94592756</v>
       </c>
       <c r="H77">
-        <v>0.07860359</v>
+        <v>-0.41432332</v>
       </c>
       <c r="I77">
-        <v>-0.58757037</v>
+        <v>-0.58490508</v>
       </c>
       <c r="J77">
-        <v>-0.80534622</v>
+        <v>-0.69729638</v>
       </c>
     </row>
     <row r="78">
@@ -2499,31 +2499,31 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C78">
-        <v>54.40364062</v>
+        <v>54.59128955</v>
       </c>
       <c r="D78">
-        <v>233.08230375</v>
+        <v>196.78960148</v>
       </c>
       <c r="E78">
-        <v>-9.76850325</v>
+        <v>-15.60592313</v>
       </c>
       <c r="F78">
-        <v>11.64142608</v>
+        <v>11.58810172</v>
       </c>
       <c r="G78">
-        <v>-13.00205919</v>
+        <v>-4.70861568</v>
       </c>
       <c r="H78">
-        <v>0.48842516</v>
+        <v>0.78029616</v>
       </c>
       <c r="I78">
-        <v>-0.5820713</v>
+        <v>-0.57940509</v>
       </c>
       <c r="J78">
-        <v>0.65010296</v>
+        <v>0.23543078</v>
       </c>
     </row>
     <row r="79">
@@ -2531,31 +2531,31 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C79">
-        <v>54.79018821</v>
+        <v>54.97700876</v>
       </c>
       <c r="D79">
-        <v>10.5900678</v>
+        <v>334.29736553</v>
       </c>
       <c r="E79">
-        <v>16.06259215</v>
+        <v>14.75790605</v>
       </c>
       <c r="F79">
-        <v>11.53144484</v>
+        <v>11.47810187</v>
       </c>
       <c r="G79">
-        <v>3.00315054</v>
+        <v>-7.1033363</v>
       </c>
       <c r="H79">
-        <v>-0.80312961</v>
+        <v>-0.7378953</v>
       </c>
       <c r="I79">
-        <v>-0.57657224</v>
+        <v>-0.57390509</v>
       </c>
       <c r="J79">
-        <v>-0.15015753</v>
+        <v>0.35516681</v>
       </c>
     </row>
     <row r="80">
@@ -2563,31 +2563,31 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C80">
-        <v>55.17490417</v>
+        <v>55.36091669</v>
       </c>
       <c r="D80">
-        <v>148.09783185</v>
+        <v>111.80512958</v>
       </c>
       <c r="E80">
-        <v>-13.9380745</v>
+        <v>-6.11221687</v>
       </c>
       <c r="F80">
-        <v>11.42146361</v>
+        <v>11.36810202</v>
       </c>
       <c r="G80">
-        <v>8.67641909</v>
+        <v>15.27766545</v>
       </c>
       <c r="H80">
-        <v>0.69690373</v>
+        <v>0.30561084</v>
       </c>
       <c r="I80">
-        <v>-0.57107318</v>
+        <v>-0.5684051</v>
       </c>
       <c r="J80">
-        <v>-0.43382095</v>
+        <v>-0.76388327</v>
       </c>
     </row>
     <row r="81">
@@ -2595,31 +2595,31 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C81">
-        <v>55.55783137</v>
+        <v>55.74305561</v>
       </c>
       <c r="D81">
-        <v>285.6055959</v>
+        <v>249.31289363</v>
       </c>
       <c r="E81">
-        <v>4.43710146</v>
+        <v>-5.83961142</v>
       </c>
       <c r="F81">
-        <v>11.31148237</v>
+        <v>11.25810216</v>
       </c>
       <c r="G81">
-        <v>-15.88592135</v>
+        <v>-15.46460714</v>
       </c>
       <c r="H81">
-        <v>-0.22185507</v>
+        <v>0.29198057</v>
       </c>
       <c r="I81">
-        <v>-0.56557412</v>
+        <v>-0.56290511</v>
       </c>
       <c r="J81">
-        <v>0.79429607</v>
+        <v>0.77323036</v>
       </c>
     </row>
     <row r="82">
@@ -2627,31 +2627,31 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C82">
-        <v>55.93901142</v>
+        <v>56.12346653</v>
       </c>
       <c r="D82">
-        <v>63.11335995</v>
+        <v>26.82065768</v>
       </c>
       <c r="E82">
-        <v>7.49287152</v>
+        <v>14.81852034</v>
       </c>
       <c r="F82">
-        <v>11.20150113</v>
+        <v>11.14810231</v>
       </c>
       <c r="G82">
-        <v>14.7777958</v>
+        <v>7.49208047</v>
       </c>
       <c r="H82">
-        <v>-0.37464358</v>
+        <v>-0.74092602</v>
       </c>
       <c r="I82">
-        <v>-0.56007506</v>
+        <v>-0.55740512</v>
       </c>
       <c r="J82">
-        <v>-0.73888979</v>
+        <v>-0.37460402</v>
       </c>
     </row>
     <row r="83">
@@ -2659,31 +2659,31 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C83">
-        <v>56.31848467</v>
+        <v>56.50218922</v>
       </c>
       <c r="D83">
-        <v>200.621124</v>
+        <v>164.32842173</v>
       </c>
       <c r="E83">
-        <v>-15.57636221</v>
+        <v>-16.05814277</v>
       </c>
       <c r="F83">
-        <v>11.0915199</v>
+        <v>11.03810246</v>
       </c>
       <c r="G83">
-        <v>-5.86132465</v>
+        <v>4.50514651</v>
       </c>
       <c r="H83">
-        <v>0.77881811</v>
+        <v>0.80290714</v>
       </c>
       <c r="I83">
-        <v>-0.55457599</v>
+        <v>-0.55190512</v>
       </c>
       <c r="J83">
-        <v>0.29306623</v>
+        <v>-0.22525733</v>
       </c>
     </row>
     <row r="84">
@@ -2691,31 +2691,31 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C84">
-        <v>56.69629025</v>
+        <v>56.87926229</v>
       </c>
       <c r="D84">
-        <v>338.12888805</v>
+        <v>301.83618578</v>
       </c>
       <c r="E84">
-        <v>15.51232923</v>
+        <v>8.83572013</v>
       </c>
       <c r="F84">
-        <v>10.98153866</v>
+        <v>10.9281026</v>
       </c>
       <c r="G84">
-        <v>-6.2268331</v>
+        <v>-14.23048219</v>
       </c>
       <c r="H84">
-        <v>-0.77561646</v>
+        <v>-0.44178601</v>
       </c>
       <c r="I84">
-        <v>-0.54907693</v>
+        <v>-0.54640513</v>
       </c>
       <c r="J84">
-        <v>0.31134166</v>
+        <v>0.71152411</v>
       </c>
     </row>
     <row r="85">
@@ -2723,31 +2723,31 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C85">
-        <v>57.07246618</v>
+        <v>57.25472324</v>
       </c>
       <c r="D85">
-        <v>115.6366521</v>
+        <v>79.34394983</v>
       </c>
       <c r="E85">
-        <v>-7.26318208</v>
+        <v>3.11054298</v>
       </c>
       <c r="F85">
-        <v>10.87155743</v>
+        <v>10.81810275</v>
       </c>
       <c r="G85">
-        <v>15.13457714</v>
+        <v>16.53158115</v>
       </c>
       <c r="H85">
-        <v>0.3631591</v>
+        <v>-0.15552715</v>
       </c>
       <c r="I85">
-        <v>-0.54357787</v>
+        <v>-0.54090514</v>
       </c>
       <c r="J85">
-        <v>-0.75672886</v>
+        <v>-0.82657906</v>
       </c>
     </row>
     <row r="86">
@@ -2755,31 +2755,31 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C86">
-        <v>57.44704939</v>
+        <v>57.62860849</v>
       </c>
       <c r="D86">
-        <v>253.14441615</v>
+        <v>216.85171388</v>
       </c>
       <c r="E86">
-        <v>-4.88812033</v>
+        <v>-13.51674172</v>
       </c>
       <c r="F86">
-        <v>10.76157619</v>
+        <v>10.7081029</v>
       </c>
       <c r="G86">
-        <v>-16.13365295</v>
+        <v>-10.13085513</v>
       </c>
       <c r="H86">
-        <v>0.24440602</v>
+        <v>0.67583709</v>
       </c>
       <c r="I86">
-        <v>-0.53807881</v>
+        <v>-0.53540514</v>
       </c>
       <c r="J86">
-        <v>0.80668265</v>
+        <v>0.50654276</v>
       </c>
     </row>
     <row r="87">
@@ -2787,31 +2787,31 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C87">
-        <v>57.82007573</v>
+        <v>58.00095343</v>
       </c>
       <c r="D87">
-        <v>30.6521802</v>
+        <v>354.35947793</v>
       </c>
       <c r="E87">
-        <v>14.56244022</v>
+        <v>16.87901476</v>
       </c>
       <c r="F87">
-        <v>10.65159496</v>
+        <v>10.59810304</v>
       </c>
       <c r="G87">
-        <v>8.63011354</v>
+        <v>-1.66705505</v>
       </c>
       <c r="H87">
-        <v>-0.72812201</v>
+        <v>-0.84395074</v>
       </c>
       <c r="I87">
-        <v>-0.53257975</v>
+        <v>-0.52990515</v>
       </c>
       <c r="J87">
-        <v>-0.43150568</v>
+        <v>0.08335275</v>
       </c>
     </row>
     <row r="88">
@@ -2819,31 +2819,31 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C88">
-        <v>58.19158008</v>
+        <v>58.37179248</v>
       </c>
       <c r="D88">
-        <v>168.15994425</v>
+        <v>131.86724198</v>
       </c>
       <c r="E88">
-        <v>-16.63469467</v>
+        <v>-11.36552387</v>
       </c>
       <c r="F88">
-        <v>10.54161372</v>
+        <v>10.48810319</v>
       </c>
       <c r="G88">
-        <v>3.48730749</v>
+        <v>12.6816623</v>
       </c>
       <c r="H88">
-        <v>0.83173473</v>
+        <v>0.56827619</v>
       </c>
       <c r="I88">
-        <v>-0.52708069</v>
+        <v>-0.52440516</v>
       </c>
       <c r="J88">
-        <v>-0.17436537</v>
+        <v>-0.63408311</v>
       </c>
     </row>
     <row r="89">
@@ -2851,31 +2851,31 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C89">
-        <v>58.56159636</v>
+        <v>58.74115912</v>
       </c>
       <c r="D89">
-        <v>305.6677083</v>
+        <v>269.37500603</v>
       </c>
       <c r="E89">
-        <v>9.94975186</v>
+        <v>-0.18648987</v>
       </c>
       <c r="F89">
-        <v>10.43163248</v>
+        <v>10.37810334</v>
       </c>
       <c r="G89">
-        <v>-13.8630257</v>
+        <v>-17.09561911</v>
       </c>
       <c r="H89">
-        <v>-0.49748759</v>
+        <v>0.00932449</v>
       </c>
       <c r="I89">
-        <v>-0.52158162</v>
+        <v>-0.51890517</v>
       </c>
       <c r="J89">
-        <v>0.69315128</v>
+        <v>0.85478096</v>
       </c>
     </row>
     <row r="90">
@@ -2883,31 +2883,31 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C90">
-        <v>58.93015755</v>
+        <v>59.10908593</v>
       </c>
       <c r="D90">
-        <v>83.17547235</v>
+        <v>46.88277008</v>
       </c>
       <c r="E90">
-        <v>2.03563367</v>
+        <v>11.73074565</v>
       </c>
       <c r="F90">
-        <v>10.32165125</v>
+        <v>10.26810349</v>
       </c>
       <c r="G90">
-        <v>17.00940067</v>
+        <v>12.5281945</v>
       </c>
       <c r="H90">
-        <v>-0.10178168</v>
+        <v>-0.58653728</v>
       </c>
       <c r="I90">
-        <v>-0.51608256</v>
+        <v>-0.51340517</v>
       </c>
       <c r="J90">
-        <v>-0.85047003</v>
+        <v>-0.62640972</v>
       </c>
     </row>
     <row r="91">
@@ -2915,31 +2915,31 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C91">
-        <v>59.29729576</v>
+        <v>59.47560459</v>
       </c>
       <c r="D91">
-        <v>220.6832364</v>
+        <v>184.39053413</v>
       </c>
       <c r="E91">
-        <v>-13.04058563</v>
+        <v>-17.17770183</v>
       </c>
       <c r="F91">
-        <v>10.21167001</v>
+        <v>10.15810363</v>
       </c>
       <c r="G91">
-        <v>-11.21003666</v>
+        <v>-1.31889742</v>
       </c>
       <c r="H91">
-        <v>0.65202928</v>
+        <v>0.85888509</v>
       </c>
       <c r="I91">
-        <v>-0.5105835</v>
+        <v>-0.50790518</v>
       </c>
       <c r="J91">
-        <v>0.56050183</v>
+        <v>0.06594487</v>
       </c>
     </row>
     <row r="92">
@@ -2947,31 +2947,31 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C92">
-        <v>59.66304224</v>
+        <v>59.840746</v>
       </c>
       <c r="D92">
-        <v>358.19100045</v>
+        <v>321.89829818</v>
       </c>
       <c r="E92">
-        <v>17.25279583</v>
+        <v>13.60787193</v>
       </c>
       <c r="F92">
-        <v>10.10168878</v>
+        <v>10.04810378</v>
       </c>
       <c r="G92">
-        <v>-0.54490357</v>
+        <v>-10.67058723</v>
       </c>
       <c r="H92">
-        <v>-0.86263979</v>
+        <v>-0.6803936</v>
       </c>
       <c r="I92">
-        <v>-0.50508444</v>
+        <v>-0.50240519</v>
       </c>
       <c r="J92">
-        <v>0.02724518</v>
+        <v>0.53352936</v>
       </c>
     </row>
     <row r="93">
@@ -2979,31 +2979,31 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C93">
-        <v>60.02742744</v>
+        <v>60.20454021</v>
       </c>
       <c r="D93">
-        <v>135.6987645</v>
+        <v>99.40606223</v>
       </c>
       <c r="E93">
-        <v>-12.39932544</v>
+        <v>-2.83651289</v>
       </c>
       <c r="F93">
-        <v>9.99170754</v>
+        <v>9.93810393</v>
       </c>
       <c r="G93">
-        <v>12.10051689</v>
+        <v>17.12274175</v>
       </c>
       <c r="H93">
-        <v>0.61996627</v>
+        <v>0.14182564</v>
       </c>
       <c r="I93">
-        <v>-0.49958538</v>
+        <v>-0.4969052</v>
       </c>
       <c r="J93">
-        <v>-0.60502584</v>
+        <v>-0.85613709</v>
       </c>
     </row>
     <row r="94">
@@ -3011,31 +3011,31 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C94">
-        <v>60.39048104</v>
+        <v>60.56701656</v>
       </c>
       <c r="D94">
-        <v>273.20652855</v>
+        <v>236.91382628</v>
       </c>
       <c r="E94">
-        <v>0.97261689</v>
+        <v>-9.50882178</v>
       </c>
       <c r="F94">
-        <v>9.88172631</v>
+        <v>9.82810407</v>
       </c>
       <c r="G94">
-        <v>-17.361034</v>
+        <v>-14.59420017</v>
       </c>
       <c r="H94">
-        <v>-0.04863084</v>
+        <v>0.47544109</v>
       </c>
       <c r="I94">
-        <v>-0.49408632</v>
+        <v>-0.4914052</v>
       </c>
       <c r="J94">
-        <v>0.8680517</v>
+        <v>0.72971001</v>
       </c>
     </row>
     <row r="95">
@@ -3043,31 +3043,31 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C95">
-        <v>60.75223193</v>
+        <v>60.9282036</v>
       </c>
       <c r="D95">
-        <v>50.7142926</v>
+        <v>14.42159033</v>
       </c>
       <c r="E95">
-        <v>11.04931786</v>
+        <v>16.92941739</v>
       </c>
       <c r="F95">
-        <v>9.77174507</v>
+        <v>9.71810422</v>
       </c>
       <c r="G95">
-        <v>13.50650114</v>
+        <v>4.35353619</v>
       </c>
       <c r="H95">
-        <v>-0.55246589</v>
+        <v>-0.84647087</v>
       </c>
       <c r="I95">
-        <v>-0.48858725</v>
+        <v>-0.48590521</v>
       </c>
       <c r="J95">
-        <v>-0.67532506</v>
+        <v>-0.21767681</v>
       </c>
     </row>
     <row r="96">
@@ -3075,31 +3075,31 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C96">
-        <v>61.11270831</v>
+        <v>61.2881292</v>
       </c>
       <c r="D96">
-        <v>188.22205665</v>
+        <v>151.92935438</v>
       </c>
       <c r="E96">
-        <v>-17.33143833</v>
+        <v>-15.47755909</v>
       </c>
       <c r="F96">
-        <v>9.66176383</v>
+        <v>9.60810437</v>
       </c>
       <c r="G96">
-        <v>-2.50430927</v>
+        <v>8.25405931</v>
       </c>
       <c r="H96">
-        <v>0.86657192</v>
+        <v>0.77387795</v>
       </c>
       <c r="I96">
-        <v>-0.48308819</v>
+        <v>-0.48040522</v>
       </c>
       <c r="J96">
-        <v>0.12521546</v>
+        <v>-0.41270297</v>
       </c>
     </row>
     <row r="97">
@@ -3107,31 +3107,31 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C97">
-        <v>61.47193768</v>
+        <v>61.64682054</v>
       </c>
       <c r="D97">
-        <v>325.7298207</v>
+        <v>289.43711843</v>
       </c>
       <c r="E97">
-        <v>14.52107516</v>
+        <v>5.85703518</v>
       </c>
       <c r="F97">
-        <v>9.5517826</v>
+        <v>9.49810451</v>
       </c>
       <c r="G97">
-        <v>-9.89453513</v>
+        <v>-16.59762482</v>
       </c>
       <c r="H97">
-        <v>-0.72605376</v>
+        <v>-0.29285176</v>
       </c>
       <c r="I97">
-        <v>-0.47758913</v>
+        <v>-0.47490523</v>
       </c>
       <c r="J97">
-        <v>0.49472676</v>
+        <v>0.82988124</v>
       </c>
     </row>
     <row r="98">
@@ -3139,31 +3139,31 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C98">
-        <v>61.82994687</v>
+        <v>62.00430416</v>
       </c>
       <c r="D98">
-        <v>103.23758475</v>
+        <v>66.94488248</v>
       </c>
       <c r="E98">
-        <v>-4.03731476</v>
+        <v>6.91581237</v>
       </c>
       <c r="F98">
-        <v>9.44180136</v>
+        <v>9.38810466</v>
       </c>
       <c r="G98">
-        <v>17.16253118</v>
+        <v>16.24915475</v>
       </c>
       <c r="H98">
-        <v>0.20186574</v>
+        <v>-0.34579062</v>
       </c>
       <c r="I98">
-        <v>-0.47209007</v>
+        <v>-0.46940523</v>
       </c>
       <c r="J98">
-        <v>-0.85812656</v>
+        <v>-0.81245774</v>
       </c>
     </row>
     <row r="99">
@@ -3171,31 +3171,31 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C99">
-        <v>62.18676207</v>
+        <v>62.36060594</v>
       </c>
       <c r="D99">
-        <v>240.7453488</v>
+        <v>204.45264653</v>
       </c>
       <c r="E99">
-        <v>-8.6447007</v>
+        <v>-16.12848461</v>
       </c>
       <c r="F99">
-        <v>9.33182013</v>
+        <v>9.27810481</v>
       </c>
       <c r="G99">
-        <v>-15.43328491</v>
+        <v>-7.33408177</v>
       </c>
       <c r="H99">
-        <v>0.43223503</v>
+        <v>0.80642423</v>
       </c>
       <c r="I99">
-        <v>-0.46659101</v>
+        <v>-0.46390524</v>
       </c>
       <c r="J99">
-        <v>0.77166425</v>
+        <v>0.36670409</v>
       </c>
     </row>
     <row r="100">
@@ -3203,31 +3203,31 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C100">
-        <v>62.54240884</v>
+        <v>62.71575117</v>
       </c>
       <c r="D100">
-        <v>18.25311285</v>
+        <v>341.96041058</v>
       </c>
       <c r="E100">
-        <v>16.85405333</v>
+        <v>16.90110255</v>
       </c>
       <c r="F100">
-        <v>9.22183889</v>
+        <v>9.16810495</v>
       </c>
       <c r="G100">
-        <v>5.55864856</v>
+        <v>-5.50441498</v>
       </c>
       <c r="H100">
-        <v>-0.84270267</v>
+        <v>-0.84505513</v>
       </c>
       <c r="I100">
-        <v>-0.46109194</v>
+        <v>-0.45840525</v>
       </c>
       <c r="J100">
-        <v>-0.27793243</v>
+        <v>0.27522075</v>
       </c>
     </row>
     <row r="101">
@@ -3235,31 +3235,31 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C101">
-        <v>62.89691216</v>
+        <v>63.06976456</v>
       </c>
       <c r="D101">
-        <v>155.7608769</v>
+        <v>119.46817463</v>
       </c>
       <c r="E101">
-        <v>-16.23418507</v>
+        <v>-8.77186795</v>
       </c>
       <c r="F101">
-        <v>9.11185765</v>
+        <v>9.0581051</v>
       </c>
       <c r="G101">
-        <v>7.30926023</v>
+        <v>15.52433782</v>
       </c>
       <c r="H101">
-        <v>0.81170925</v>
+        <v>0.4385934</v>
       </c>
       <c r="I101">
-        <v>-0.45559288</v>
+        <v>-0.45290525</v>
       </c>
       <c r="J101">
-        <v>-0.36546301</v>
+        <v>-0.77621689</v>
       </c>
     </row>
     <row r="102">
@@ -3267,31 +3267,31 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C102">
-        <v>63.25029644</v>
+        <v>63.42267025</v>
       </c>
       <c r="D102">
-        <v>293.26864095</v>
+        <v>256.97593868</v>
       </c>
       <c r="E102">
-        <v>7.05531574</v>
+        <v>-4.03093412</v>
       </c>
       <c r="F102">
-        <v>9.00187642</v>
+        <v>8.94810525</v>
       </c>
       <c r="G102">
-        <v>-16.40697232</v>
+        <v>-17.42650231</v>
       </c>
       <c r="H102">
-        <v>-0.35276579</v>
+        <v>0.20154671</v>
       </c>
       <c r="I102">
-        <v>-0.45009382</v>
+        <v>-0.44740526</v>
       </c>
       <c r="J102">
-        <v>0.82034862</v>
+        <v>0.87132512</v>
       </c>
     </row>
     <row r="103">
@@ -3299,31 +3299,31 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C103">
-        <v>63.60258551</v>
+        <v>63.77449184</v>
       </c>
       <c r="D103">
-        <v>70.776405</v>
+        <v>34.48370273</v>
       </c>
       <c r="E103">
-        <v>5.898493</v>
+        <v>14.78873105</v>
       </c>
       <c r="F103">
-        <v>8.89189518</v>
+        <v>8.83810539</v>
       </c>
       <c r="G103">
-        <v>16.91573174</v>
+        <v>10.15782097</v>
       </c>
       <c r="H103">
-        <v>-0.29492465</v>
+        <v>-0.73943655</v>
       </c>
       <c r="I103">
-        <v>-0.44459476</v>
+        <v>-0.44190527</v>
       </c>
       <c r="J103">
-        <v>-0.84578659</v>
+        <v>-0.50789105</v>
       </c>
     </row>
     <row r="104">
@@ -3331,31 +3331,31 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C104">
-        <v>63.9538027</v>
+        <v>64.12525241</v>
       </c>
       <c r="D104">
-        <v>208.28416905</v>
+        <v>171.99146678</v>
       </c>
       <c r="E104">
-        <v>-15.82347987</v>
+        <v>-17.8195048</v>
       </c>
       <c r="F104">
-        <v>8.78191395</v>
+        <v>8.72810554</v>
       </c>
       <c r="G104">
-        <v>-8.5144273</v>
+        <v>2.50707446</v>
       </c>
       <c r="H104">
-        <v>0.79117399</v>
+        <v>0.89097524</v>
       </c>
       <c r="I104">
-        <v>-0.4390957</v>
+        <v>-0.43640528</v>
       </c>
       <c r="J104">
-        <v>0.42572136</v>
+        <v>-0.12535372</v>
       </c>
     </row>
     <row r="105">
@@ -3363,31 +3363,31 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C105">
-        <v>64.30397081</v>
+        <v>64.47497452</v>
       </c>
       <c r="D105">
-        <v>345.7919331</v>
+        <v>309.49923083</v>
       </c>
       <c r="E105">
-        <v>17.47085862</v>
+        <v>11.47971665</v>
       </c>
       <c r="F105">
-        <v>8.67193271</v>
+        <v>8.61810569</v>
       </c>
       <c r="G105">
-        <v>-4.42342425</v>
+        <v>-13.92639078</v>
       </c>
       <c r="H105">
-        <v>-0.87354293</v>
+        <v>-0.57398583</v>
       </c>
       <c r="I105">
-        <v>-0.43359664</v>
+        <v>-0.43090528</v>
       </c>
       <c r="J105">
-        <v>0.22117121</v>
+        <v>0.69631954</v>
       </c>
     </row>
     <row r="106">
@@ -3395,31 +3395,31 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C106">
-        <v>64.65311215</v>
+        <v>64.82368026</v>
       </c>
       <c r="D106">
-        <v>123.29969715</v>
+        <v>87.00699488</v>
       </c>
       <c r="E106">
-        <v>-9.92331564</v>
+        <v>0.94507719</v>
       </c>
       <c r="F106">
-        <v>8.56195148</v>
+        <v>8.50810583</v>
       </c>
       <c r="G106">
-        <v>15.10697831</v>
+        <v>18.07536899</v>
       </c>
       <c r="H106">
-        <v>0.49616578</v>
+        <v>-0.04725386</v>
       </c>
       <c r="I106">
-        <v>-0.42809757</v>
+        <v>-0.42540529</v>
       </c>
       <c r="J106">
-        <v>-0.75534892</v>
+        <v>-0.90376845</v>
       </c>
     </row>
     <row r="107">
@@ -3427,31 +3427,31 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C107">
-        <v>65.00124855</v>
+        <v>65.17139124</v>
       </c>
       <c r="D107">
-        <v>260.8074612</v>
+        <v>224.51475893</v>
       </c>
       <c r="E107">
-        <v>-2.89573064</v>
+        <v>-12.94318698</v>
       </c>
       <c r="F107">
-        <v>8.45197024</v>
+        <v>8.39810598</v>
       </c>
       <c r="G107">
-        <v>-17.89354473</v>
+        <v>-12.72578983</v>
       </c>
       <c r="H107">
-        <v>0.14478653</v>
+        <v>0.64715935</v>
       </c>
       <c r="I107">
-        <v>-0.42259851</v>
+        <v>-0.4199053</v>
       </c>
       <c r="J107">
-        <v>0.89467724</v>
+        <v>0.63628949</v>
       </c>
     </row>
     <row r="108">
@@ -3459,31 +3459,31 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C108">
-        <v>65.34840139</v>
+        <v>65.51812863</v>
       </c>
       <c r="D108">
-        <v>38.31522525</v>
+        <v>2.02252298</v>
       </c>
       <c r="E108">
-        <v>14.26205623</v>
+        <v>18.19050953</v>
       </c>
       <c r="F108">
-        <v>8.341989</v>
+        <v>8.28810613</v>
       </c>
       <c r="G108">
-        <v>11.26964825</v>
+        <v>0.6423861</v>
       </c>
       <c r="H108">
-        <v>-0.71310281</v>
+        <v>-0.90952548</v>
       </c>
       <c r="I108">
-        <v>-0.41709945</v>
+        <v>-0.41440531</v>
       </c>
       <c r="J108">
-        <v>-0.56348241</v>
+        <v>-0.03211931</v>
       </c>
     </row>
     <row r="109">
@@ -3491,31 +3491,31 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C109">
-        <v>65.69459158</v>
+        <v>65.86391315</v>
       </c>
       <c r="D109">
-        <v>175.8229893</v>
+        <v>139.53028703</v>
       </c>
       <c r="E109">
-        <v>-18.17887292</v>
+        <v>-13.88484097</v>
       </c>
       <c r="F109">
-        <v>8.23200777</v>
+        <v>8.17810627</v>
       </c>
       <c r="G109">
-        <v>1.32763979</v>
+        <v>11.84608665</v>
       </c>
       <c r="H109">
-        <v>0.90894365</v>
+        <v>0.69424205</v>
       </c>
       <c r="I109">
-        <v>-0.41160039</v>
+        <v>-0.40890531</v>
       </c>
       <c r="J109">
-        <v>-0.06638199</v>
+        <v>-0.59230433</v>
       </c>
     </row>
     <row r="110">
@@ -3523,31 +3523,31 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C110">
-        <v>66.03983964</v>
+        <v>66.20876512</v>
       </c>
       <c r="D110">
-        <v>313.33075335</v>
+        <v>277.03805108</v>
       </c>
       <c r="E110">
-        <v>12.54153859</v>
+        <v>2.24232366</v>
       </c>
       <c r="F110">
-        <v>8.12202653</v>
+        <v>8.06810642</v>
       </c>
       <c r="G110">
-        <v>-13.29445354</v>
+        <v>-18.16253406</v>
       </c>
       <c r="H110">
-        <v>-0.62707693</v>
+        <v>-0.11211618</v>
       </c>
       <c r="I110">
-        <v>-0.40610133</v>
+        <v>-0.40340532</v>
       </c>
       <c r="J110">
-        <v>0.66472268</v>
+        <v>0.9081267</v>
       </c>
     </row>
     <row r="111">
@@ -3555,31 +3555,31 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C111">
-        <v>66.38416564</v>
+        <v>66.55270442</v>
       </c>
       <c r="D111">
-        <v>90.8385174</v>
+        <v>54.54581513</v>
       </c>
       <c r="E111">
-        <v>-0.26817538</v>
+        <v>10.64309733</v>
       </c>
       <c r="F111">
-        <v>8.0120453</v>
+        <v>7.95810657</v>
       </c>
       <c r="G111">
-        <v>18.32307868</v>
+        <v>14.94633798</v>
       </c>
       <c r="H111">
-        <v>0.01340877</v>
+        <v>-0.53215487</v>
       </c>
       <c r="I111">
-        <v>-0.40060226</v>
+        <v>-0.39790533</v>
       </c>
       <c r="J111">
-        <v>-0.91615393</v>
+        <v>-0.7473169</v>
       </c>
     </row>
     <row r="112">
@@ -3587,31 +3587,31 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C112">
-        <v>66.72758928</v>
+        <v>66.89575056</v>
       </c>
       <c r="D112">
-        <v>228.34628145</v>
+        <v>192.05357918</v>
       </c>
       <c r="E112">
-        <v>-12.21101616</v>
+        <v>-17.99027003</v>
       </c>
       <c r="F112">
-        <v>7.90206406</v>
+        <v>7.84810671</v>
       </c>
       <c r="G112">
-        <v>-13.7276534</v>
+        <v>-3.84153682</v>
       </c>
       <c r="H112">
-        <v>0.61055081</v>
+        <v>0.8995135</v>
       </c>
       <c r="I112">
-        <v>-0.3951032</v>
+        <v>-0.39240534</v>
       </c>
       <c r="J112">
-        <v>0.68638267</v>
+        <v>0.19207684</v>
       </c>
     </row>
     <row r="113">
@@ -3619,31 +3619,31 @@
         <v>112</v>
       </c>
       <c r="B113">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C113">
-        <v>67.07012984</v>
+        <v>67.23792267</v>
       </c>
       <c r="D113">
-        <v>5.8540455</v>
+        <v>329.56134323</v>
       </c>
       <c r="E113">
-        <v>18.32358883</v>
+        <v>15.90051225</v>
       </c>
       <c r="F113">
-        <v>7.79208282</v>
+        <v>7.73810686</v>
       </c>
       <c r="G113">
-        <v>1.87870642</v>
+        <v>-9.3432014</v>
       </c>
       <c r="H113">
-        <v>-0.91617944</v>
+        <v>-0.79502561</v>
       </c>
       <c r="I113">
-        <v>-0.38960414</v>
+        <v>-0.38690534</v>
       </c>
       <c r="J113">
-        <v>-0.09393532</v>
+        <v>0.46716007</v>
       </c>
     </row>
     <row r="114">
@@ -3651,31 +3651,31 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C114">
-        <v>67.41180627</v>
+        <v>67.57923951</v>
       </c>
       <c r="D114">
-        <v>143.36180955</v>
+        <v>107.06910728</v>
       </c>
       <c r="E114">
-        <v>-14.81731522</v>
+        <v>-5.42673542</v>
       </c>
       <c r="F114">
-        <v>7.68210159</v>
+        <v>7.62810701</v>
       </c>
       <c r="G114">
-        <v>11.01964087</v>
+        <v>17.67378076</v>
       </c>
       <c r="H114">
-        <v>0.74086576</v>
+        <v>0.27133677</v>
       </c>
       <c r="I114">
-        <v>-0.38410508</v>
+        <v>-0.38140535</v>
       </c>
       <c r="J114">
-        <v>-0.55098204</v>
+        <v>-0.88368904</v>
       </c>
     </row>
     <row r="115">
@@ -3683,31 +3683,31 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C115">
-        <v>67.75263712</v>
+        <v>67.91971948</v>
       </c>
       <c r="D115">
-        <v>280.8695736</v>
+        <v>244.57687133</v>
       </c>
       <c r="E115">
-        <v>3.49072241</v>
+        <v>-7.95628146</v>
       </c>
       <c r="F115">
-        <v>7.57212035</v>
+        <v>7.51810715</v>
       </c>
       <c r="G115">
-        <v>-18.17904977</v>
+        <v>-16.73844826</v>
       </c>
       <c r="H115">
-        <v>-0.17453612</v>
+        <v>0.39781407</v>
       </c>
       <c r="I115">
-        <v>-0.37860602</v>
+        <v>-0.37590536</v>
       </c>
       <c r="J115">
-        <v>0.90895249</v>
+        <v>0.83692241</v>
       </c>
     </row>
     <row r="116">
@@ -3715,31 +3715,31 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C116">
-        <v>68.09264062</v>
+        <v>68.25938064</v>
       </c>
       <c r="D116">
-        <v>58.37733765</v>
+        <v>22.08463538</v>
       </c>
       <c r="E116">
-        <v>9.72921067</v>
+        <v>17.21437051</v>
       </c>
       <c r="F116">
-        <v>7.46213912</v>
+        <v>7.4081073</v>
       </c>
       <c r="G116">
-        <v>15.80059934</v>
+        <v>6.98465419</v>
       </c>
       <c r="H116">
-        <v>-0.48646053</v>
+        <v>-0.86071853</v>
       </c>
       <c r="I116">
-        <v>-0.37310696</v>
+        <v>-0.37040536</v>
       </c>
       <c r="J116">
-        <v>-0.79002997</v>
+        <v>-0.34923271</v>
       </c>
     </row>
     <row r="117">
@@ -3747,31 +3747,31 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C117">
-        <v>68.43183464</v>
+        <v>68.59824073</v>
       </c>
       <c r="D117">
-        <v>195.8851017</v>
+        <v>159.59239943</v>
       </c>
       <c r="E117">
-        <v>-17.88934494</v>
+        <v>-17.45216574</v>
       </c>
       <c r="F117">
-        <v>7.35215788</v>
+        <v>7.29810745</v>
       </c>
       <c r="G117">
-        <v>-5.09088521</v>
+        <v>6.4930377</v>
       </c>
       <c r="H117">
-        <v>0.89446725</v>
+        <v>0.87260829</v>
       </c>
       <c r="I117">
-        <v>-0.36760789</v>
+        <v>-0.36490537</v>
       </c>
       <c r="J117">
-        <v>0.25454426</v>
+        <v>-0.32465189</v>
       </c>
     </row>
     <row r="118">
@@ -3779,31 +3779,31 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C118">
-        <v>68.77023676</v>
+        <v>68.93631715</v>
       </c>
       <c r="D118">
-        <v>333.39286575</v>
+        <v>297.10016348</v>
       </c>
       <c r="E118">
-        <v>16.6684244</v>
+        <v>8.5021693</v>
       </c>
       <c r="F118">
-        <v>7.24217665</v>
+        <v>7.18810759</v>
       </c>
       <c r="G118">
-        <v>-8.34952127</v>
+        <v>-16.61457873</v>
       </c>
       <c r="H118">
-        <v>-0.83342122</v>
+        <v>-0.42510847</v>
       </c>
       <c r="I118">
-        <v>-0.36210883</v>
+        <v>-0.35940538</v>
       </c>
       <c r="J118">
-        <v>0.41747606</v>
+        <v>0.83072894</v>
       </c>
     </row>
     <row r="119">
@@ -3811,31 +3811,31 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C119">
-        <v>69.10786421</v>
+        <v>69.27362701</v>
       </c>
       <c r="D119">
-        <v>110.9006298</v>
+        <v>74.60792753</v>
       </c>
       <c r="E119">
-        <v>-6.66586587</v>
+        <v>4.96489778</v>
       </c>
       <c r="F119">
-        <v>7.13219541</v>
+        <v>7.07810774</v>
       </c>
       <c r="G119">
-        <v>17.45560142</v>
+        <v>18.03469381</v>
       </c>
       <c r="H119">
-        <v>0.33329329</v>
+        <v>-0.24824489</v>
       </c>
       <c r="I119">
-        <v>-0.35660977</v>
+        <v>-0.35390539</v>
       </c>
       <c r="J119">
-        <v>-0.87278007</v>
+        <v>-0.90173469</v>
       </c>
     </row>
     <row r="120">
@@ -3843,31 +3843,31 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C120">
-        <v>69.44473393</v>
+        <v>69.61018711</v>
       </c>
       <c r="D120">
-        <v>248.40839385</v>
+        <v>212.11569158</v>
       </c>
       <c r="E120">
-        <v>-6.89119946</v>
+        <v>-15.87816326</v>
       </c>
       <c r="F120">
-        <v>7.02221417</v>
+        <v>6.96810789</v>
       </c>
       <c r="G120">
-        <v>-17.41263559</v>
+        <v>-9.9664138</v>
       </c>
       <c r="H120">
-        <v>0.34455997</v>
+        <v>0.79390816</v>
       </c>
       <c r="I120">
-        <v>-0.35111071</v>
+        <v>-0.34840539</v>
       </c>
       <c r="J120">
-        <v>0.87063178</v>
+        <v>0.49832069</v>
       </c>
     </row>
     <row r="121">
@@ -3875,31 +3875,31 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C121">
-        <v>69.78086257</v>
+        <v>69.94601397</v>
       </c>
       <c r="D121">
-        <v>25.9161579</v>
+        <v>349.62345563</v>
       </c>
       <c r="E121">
-        <v>16.88018556</v>
+        <v>18.48013634</v>
       </c>
       <c r="F121">
-        <v>6.91223294</v>
+        <v>6.85810803</v>
       </c>
       <c r="G121">
-        <v>8.20246128</v>
+        <v>-3.3839201</v>
       </c>
       <c r="H121">
-        <v>-0.84400928</v>
+        <v>-0.92400682</v>
       </c>
       <c r="I121">
-        <v>-0.34561165</v>
+        <v>-0.3429054</v>
       </c>
       <c r="J121">
-        <v>-0.41012306</v>
+        <v>0.169196</v>
       </c>
     </row>
     <row r="122">
@@ -3907,31 +3907,31 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C122">
-        <v>70.11626649</v>
+        <v>70.28112382</v>
       </c>
       <c r="D122">
-        <v>163.42392195</v>
+        <v>127.13121968</v>
       </c>
       <c r="E122">
-        <v>-18.02608</v>
+        <v>-11.36489111</v>
       </c>
       <c r="F122">
-        <v>6.8022517</v>
+        <v>6.74810818</v>
       </c>
       <c r="G122">
-        <v>5.36561381</v>
+        <v>15.01007282</v>
       </c>
       <c r="H122">
-        <v>0.901304</v>
+        <v>0.56824456</v>
       </c>
       <c r="I122">
-        <v>-0.34011259</v>
+        <v>-0.33740541</v>
       </c>
       <c r="J122">
-        <v>-0.26828069</v>
+        <v>-0.75050364</v>
       </c>
     </row>
     <row r="123">
@@ -3939,31 +3939,31 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C123">
-        <v>70.45096178</v>
+        <v>70.61553262</v>
       </c>
       <c r="D123">
-        <v>300.931686</v>
+        <v>264.63898373</v>
       </c>
       <c r="E123">
-        <v>9.68771</v>
+        <v>-1.76269135</v>
       </c>
       <c r="F123">
-        <v>6.69227047</v>
+        <v>6.63810833</v>
       </c>
       <c r="G123">
-        <v>-16.1666877</v>
+        <v>-18.78372799</v>
       </c>
       <c r="H123">
-        <v>-0.4843855</v>
+        <v>0.08813457</v>
       </c>
       <c r="I123">
-        <v>-0.33461352</v>
+        <v>-0.33190542</v>
       </c>
       <c r="J123">
-        <v>0.80833438</v>
+        <v>0.9391864</v>
       </c>
     </row>
     <row r="124">
@@ -3971,31 +3971,31 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C124">
-        <v>70.78496427</v>
+        <v>70.94925609</v>
       </c>
       <c r="D124">
-        <v>78.43945005</v>
+        <v>42.14674778</v>
       </c>
       <c r="E124">
-        <v>3.78477874</v>
+        <v>14.01640896</v>
       </c>
       <c r="F124">
-        <v>6.58228923</v>
+        <v>6.52810847</v>
       </c>
       <c r="G124">
-        <v>18.50267328</v>
+        <v>12.68558551</v>
       </c>
       <c r="H124">
-        <v>-0.18923894</v>
+        <v>-0.70082045</v>
       </c>
       <c r="I124">
-        <v>-0.32911446</v>
+        <v>-0.32640542</v>
       </c>
       <c r="J124">
-        <v>-0.92513366</v>
+        <v>-0.63427928</v>
       </c>
     </row>
     <row r="125">
@@ -4003,31 +4003,31 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C125">
-        <v>71.11828951</v>
+        <v>71.28230965</v>
       </c>
       <c r="D125">
-        <v>215.9472141</v>
+        <v>179.65451183</v>
       </c>
       <c r="E125">
-        <v>-15.319896</v>
+        <v>-18.94188047</v>
       </c>
       <c r="F125">
-        <v>6.47230799</v>
+        <v>6.41810862</v>
       </c>
       <c r="G125">
-        <v>-11.10900607</v>
+        <v>0.11421914</v>
       </c>
       <c r="H125">
-        <v>0.7659948</v>
+        <v>0.94709402</v>
       </c>
       <c r="I125">
-        <v>-0.3236154</v>
+        <v>-0.32090543</v>
       </c>
       <c r="J125">
-        <v>0.5554503</v>
+        <v>-0.00571096</v>
       </c>
     </row>
     <row r="126">
@@ -4035,31 +4035,31 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C126">
-        <v>71.45095283</v>
+        <v>71.61470854</v>
       </c>
       <c r="D126">
-        <v>353.45497815</v>
+        <v>317.16227588</v>
       </c>
       <c r="E126">
-        <v>18.83745697</v>
+        <v>13.91706863</v>
       </c>
       <c r="F126">
-        <v>6.36232676</v>
+        <v>6.30810877</v>
       </c>
       <c r="G126">
-        <v>-2.1612527</v>
+        <v>-12.90437773</v>
       </c>
       <c r="H126">
-        <v>-0.94187285</v>
+        <v>-0.69585343</v>
       </c>
       <c r="I126">
-        <v>-0.31811634</v>
+        <v>-0.31540544</v>
       </c>
       <c r="J126">
-        <v>0.10806264</v>
+        <v>0.64521889</v>
       </c>
     </row>
     <row r="127">
@@ -4067,31 +4067,31 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C127">
-        <v>71.7829693</v>
+        <v>71.9464677</v>
       </c>
       <c r="D127">
-        <v>130.9627422</v>
+        <v>94.67003993</v>
       </c>
       <c r="E127">
-        <v>-12.45421013</v>
+        <v>-1.54817929</v>
       </c>
       <c r="F127">
-        <v>6.25234552</v>
+        <v>6.19810891</v>
       </c>
       <c r="G127">
-        <v>14.34575985</v>
+        <v>18.95221852</v>
       </c>
       <c r="H127">
-        <v>0.62271051</v>
+        <v>0.07740896</v>
       </c>
       <c r="I127">
-        <v>-0.31261728</v>
+        <v>-0.30990545</v>
       </c>
       <c r="J127">
-        <v>-0.71728799</v>
+        <v>-0.94761093</v>
       </c>
     </row>
     <row r="128">
@@ -4099,31 +4099,31 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C128">
-        <v>72.11435376</v>
+        <v>72.27760188</v>
       </c>
       <c r="D128">
-        <v>268.47050625</v>
+        <v>232.17780398</v>
       </c>
       <c r="E128">
-        <v>-0.50803133</v>
+        <v>-11.68223163</v>
       </c>
       <c r="F128">
-        <v>6.14236429</v>
+        <v>6.08810906</v>
       </c>
       <c r="G128">
-        <v>-19.02664619</v>
+        <v>-15.048601</v>
       </c>
       <c r="H128">
-        <v>0.02540157</v>
+        <v>0.58411158</v>
       </c>
       <c r="I128">
-        <v>-0.30711821</v>
+        <v>-0.30440545</v>
       </c>
       <c r="J128">
-        <v>0.95133231</v>
+        <v>0.75243005</v>
       </c>
     </row>
     <row r="129">
@@ -4131,31 +4131,31 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C129">
-        <v>72.44512084</v>
+        <v>72.6081256</v>
       </c>
       <c r="D129">
-        <v>45.9782703</v>
+        <v>9.68556803</v>
       </c>
       <c r="E129">
-        <v>13.25134283</v>
+        <v>18.81360532</v>
       </c>
       <c r="F129">
-        <v>6.03238305</v>
+        <v>5.97810921</v>
       </c>
       <c r="G129">
-        <v>13.71175655</v>
+        <v>3.21099133</v>
       </c>
       <c r="H129">
-        <v>-0.66256714</v>
+        <v>-0.94068027</v>
       </c>
       <c r="I129">
-        <v>-0.30161915</v>
+        <v>-0.29890546</v>
       </c>
       <c r="J129">
-        <v>-0.68558783</v>
+        <v>-0.16054957</v>
       </c>
     </row>
     <row r="130">
@@ -4163,31 +4163,31 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C130">
-        <v>72.77528493</v>
+        <v>72.93805316</v>
       </c>
       <c r="D130">
-        <v>183.48603435</v>
+        <v>147.19333208</v>
       </c>
       <c r="E130">
-        <v>-19.06766706</v>
+        <v>-16.0702278</v>
       </c>
       <c r="F130">
-        <v>5.92240182</v>
+        <v>5.86810935</v>
       </c>
       <c r="G130">
-        <v>-1.16156348</v>
+        <v>10.35920224</v>
       </c>
       <c r="H130">
-        <v>0.95338335</v>
+        <v>0.80351139</v>
       </c>
       <c r="I130">
-        <v>-0.29612009</v>
+        <v>-0.29340547</v>
       </c>
       <c r="J130">
-        <v>0.05807817</v>
+        <v>-0.51796011</v>
       </c>
     </row>
     <row r="131">
@@ -4195,31 +4195,31 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C131">
-        <v>73.10486022</v>
+        <v>73.26739866</v>
       </c>
       <c r="D131">
-        <v>320.9937984</v>
+        <v>284.70109613</v>
       </c>
       <c r="E131">
-        <v>14.87075586</v>
+        <v>4.86062516</v>
       </c>
       <c r="F131">
-        <v>5.81242058</v>
+        <v>5.7581095</v>
       </c>
       <c r="G131">
-        <v>-12.04476596</v>
+        <v>-18.52615713</v>
       </c>
       <c r="H131">
-        <v>-0.74353779</v>
+        <v>-0.24303126</v>
       </c>
       <c r="I131">
-        <v>-0.29062103</v>
+        <v>-0.28790548</v>
       </c>
       <c r="J131">
-        <v>0.6022383</v>
+        <v>0.92630786</v>
       </c>
     </row>
     <row r="132">
@@ -4227,31 +4227,31 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C132">
-        <v>73.43386071</v>
+        <v>73.59617599</v>
       </c>
       <c r="D132">
-        <v>98.50156245</v>
+        <v>62.20886018</v>
       </c>
       <c r="E132">
-        <v>-2.83399754</v>
+        <v>8.94542408</v>
       </c>
       <c r="F132">
-        <v>5.70243934</v>
+        <v>5.64810965</v>
       </c>
       <c r="G132">
-        <v>18.95918362</v>
+        <v>16.97286792</v>
       </c>
       <c r="H132">
-        <v>0.14169988</v>
+        <v>-0.4472712</v>
       </c>
       <c r="I132">
-        <v>-0.28512197</v>
+        <v>-0.28240548</v>
       </c>
       <c r="J132">
-        <v>-0.94795918</v>
+        <v>-0.8486434</v>
       </c>
     </row>
     <row r="133">
@@ -4259,31 +4259,31 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C133">
-        <v>73.76230018</v>
+        <v>73.92439885</v>
       </c>
       <c r="D133">
-        <v>236.0093265</v>
+        <v>199.71662423</v>
       </c>
       <c r="E133">
-        <v>-10.73514145</v>
+        <v>-18.09124701</v>
       </c>
       <c r="F133">
-        <v>5.59245811</v>
+        <v>5.53810979</v>
       </c>
       <c r="G133">
-        <v>-15.92109137</v>
+        <v>-6.48352692</v>
       </c>
       <c r="H133">
-        <v>0.53675707</v>
+        <v>0.90456235</v>
       </c>
       <c r="I133">
-        <v>-0.27962291</v>
+        <v>-0.27690549</v>
       </c>
       <c r="J133">
-        <v>0.79605457</v>
+        <v>0.32417635</v>
       </c>
     </row>
     <row r="134">
@@ -4291,31 +4291,31 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C134">
-        <v>74.09019222</v>
+        <v>74.25208076</v>
       </c>
       <c r="D134">
-        <v>13.51709055</v>
+        <v>337.22438828</v>
       </c>
       <c r="E134">
-        <v>18.70111398</v>
+        <v>17.74839562</v>
       </c>
       <c r="F134">
-        <v>5.48247687</v>
+        <v>5.42810994</v>
       </c>
       <c r="G134">
-        <v>4.49564047</v>
+        <v>-7.45185047</v>
       </c>
       <c r="H134">
-        <v>-0.9350557</v>
+        <v>-0.88741978</v>
       </c>
       <c r="I134">
-        <v>-0.27412384</v>
+        <v>-0.2714055</v>
       </c>
       <c r="J134">
-        <v>-0.22478202</v>
+        <v>0.37259252</v>
       </c>
     </row>
     <row r="135">
@@ -4323,31 +4323,31 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C135">
-        <v>74.41755026</v>
+        <v>74.57923505</v>
       </c>
       <c r="D135">
-        <v>151.0248546</v>
+        <v>114.73215233</v>
       </c>
       <c r="E135">
-        <v>-16.85350932</v>
+        <v>-8.06629774</v>
       </c>
       <c r="F135">
-        <v>5.37249564</v>
+        <v>5.31811009</v>
       </c>
       <c r="G135">
-        <v>9.33249774</v>
+        <v>17.51149753</v>
       </c>
       <c r="H135">
-        <v>0.84267547</v>
+        <v>0.40331489</v>
       </c>
       <c r="I135">
-        <v>-0.26862478</v>
+        <v>-0.2659055</v>
       </c>
       <c r="J135">
-        <v>-0.46662489</v>
+        <v>-0.87557488</v>
       </c>
     </row>
     <row r="136">
@@ -4355,31 +4355,31 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C136">
-        <v>74.74438753</v>
+        <v>74.90587487</v>
       </c>
       <c r="D136">
-        <v>288.53261866</v>
+        <v>252.23991638</v>
       </c>
       <c r="E136">
-        <v>6.13288285</v>
+        <v>-5.89016211</v>
       </c>
       <c r="F136">
-        <v>5.2625144</v>
+        <v>5.20811023</v>
       </c>
       <c r="G136">
-        <v>-18.29463556</v>
+        <v>-18.38971392</v>
       </c>
       <c r="H136">
-        <v>-0.30664414</v>
+        <v>0.29450811</v>
       </c>
       <c r="I136">
-        <v>-0.26312572</v>
+        <v>-0.26040551</v>
       </c>
       <c r="J136">
-        <v>0.91473178</v>
+        <v>0.9194857</v>
       </c>
     </row>
     <row r="137">
@@ -4387,31 +4387,31 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C137">
-        <v>75.07071708</v>
+        <v>75.23201322</v>
       </c>
       <c r="D137">
-        <v>66.04038271</v>
+        <v>29.74768043</v>
       </c>
       <c r="E137">
-        <v>7.84769638</v>
+        <v>16.79076257</v>
       </c>
       <c r="F137">
-        <v>5.15253317</v>
+        <v>5.09811038</v>
       </c>
       <c r="G137">
-        <v>17.65970168</v>
+        <v>9.59580965</v>
       </c>
       <c r="H137">
-        <v>-0.39238482</v>
+        <v>-0.83953813</v>
       </c>
       <c r="I137">
-        <v>-0.25762666</v>
+        <v>-0.25490552</v>
       </c>
       <c r="J137">
-        <v>-0.88298508</v>
+        <v>-0.47979048</v>
       </c>
     </row>
     <row r="138">
@@ -4419,31 +4419,31 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C138">
-        <v>75.39655182</v>
+        <v>75.5576629</v>
       </c>
       <c r="D138">
-        <v>203.54814676</v>
+        <v>167.25544448</v>
       </c>
       <c r="E138">
-        <v>-17.74217931</v>
+        <v>-18.89081927</v>
       </c>
       <c r="F138">
-        <v>5.04255193</v>
+        <v>4.98811053</v>
       </c>
       <c r="G138">
-        <v>-7.73225345</v>
+        <v>4.27266904</v>
       </c>
       <c r="H138">
-        <v>0.88710897</v>
+        <v>0.94454096</v>
       </c>
       <c r="I138">
-        <v>-0.2521276</v>
+        <v>-0.24940553</v>
       </c>
       <c r="J138">
-        <v>0.38661267</v>
+        <v>-0.21363345</v>
       </c>
     </row>
     <row r="139">
@@ -4451,31 +4451,31 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C139">
-        <v>75.72190449</v>
+        <v>75.8828366</v>
       </c>
       <c r="D139">
-        <v>341.05591081</v>
+        <v>304.76320853</v>
       </c>
       <c r="E139">
-        <v>18.3323808</v>
+        <v>11.05931937</v>
       </c>
       <c r="F139">
-        <v>4.93257069</v>
+        <v>4.87811067</v>
       </c>
       <c r="G139">
-        <v>-6.29234142</v>
+        <v>-15.93409839</v>
       </c>
       <c r="H139">
-        <v>-0.91661904</v>
+        <v>-0.55296597</v>
       </c>
       <c r="I139">
-        <v>-0.24662853</v>
+        <v>-0.24390553</v>
       </c>
       <c r="J139">
-        <v>0.31461707</v>
+        <v>0.79670492</v>
       </c>
     </row>
     <row r="140">
@@ -4483,31 +4483,31 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C140">
-        <v>76.04678765</v>
+        <v>76.2075468</v>
       </c>
       <c r="D140">
-        <v>118.56367486</v>
+        <v>82.27097258</v>
       </c>
       <c r="E140">
-        <v>-9.28053544</v>
+        <v>2.61220698</v>
       </c>
       <c r="F140">
-        <v>4.82258946</v>
+        <v>4.76811082</v>
       </c>
       <c r="G140">
-        <v>17.04741308</v>
+        <v>19.24685673</v>
       </c>
       <c r="H140">
-        <v>0.46402677</v>
+        <v>-0.13061035</v>
       </c>
       <c r="I140">
-        <v>-0.24112947</v>
+        <v>-0.23840554</v>
       </c>
       <c r="J140">
-        <v>-0.85237065</v>
+        <v>-0.96234284</v>
       </c>
     </row>
     <row r="141">
@@ -4515,31 +4515,31 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C141">
-        <v>76.37121375</v>
+        <v>76.53180589</v>
       </c>
       <c r="D141">
-        <v>256.07143891</v>
+        <v>219.77873663</v>
       </c>
       <c r="E141">
-        <v>-4.67868225</v>
+        <v>-14.94772411</v>
       </c>
       <c r="F141">
-        <v>4.71260822</v>
+        <v>4.65811097</v>
       </c>
       <c r="G141">
-        <v>-18.86534538</v>
+        <v>-12.44457898</v>
       </c>
       <c r="H141">
-        <v>0.23393411</v>
+        <v>0.74738621</v>
       </c>
       <c r="I141">
-        <v>-0.23563041</v>
+        <v>-0.23290555</v>
       </c>
       <c r="J141">
-        <v>0.94326727</v>
+        <v>0.62222895</v>
       </c>
     </row>
     <row r="142">
@@ -4547,31 +4547,31 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C142">
-        <v>76.69519505</v>
+        <v>76.85562607</v>
       </c>
       <c r="D142">
-        <v>33.57920296</v>
+        <v>357.28650068</v>
       </c>
       <c r="E142">
-        <v>16.21521411</v>
+        <v>19.45416531</v>
       </c>
       <c r="F142">
-        <v>4.60262699</v>
+        <v>4.54811111</v>
       </c>
       <c r="G142">
-        <v>10.76488068</v>
+        <v>-0.92202894</v>
       </c>
       <c r="H142">
-        <v>-0.81076071</v>
+        <v>-0.97270827</v>
       </c>
       <c r="I142">
-        <v>-0.23013135</v>
+        <v>-0.22740556</v>
       </c>
       <c r="J142">
-        <v>-0.53824403</v>
+        <v>0.04610145</v>
       </c>
     </row>
     <row r="143">
@@ -4579,31 +4579,31 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C143">
-        <v>77.0187437</v>
+        <v>77.17901943</v>
       </c>
       <c r="D143">
-        <v>171.08696701</v>
+        <v>134.79426473</v>
       </c>
       <c r="E143">
-        <v>-19.25353708</v>
+        <v>-13.73994248</v>
       </c>
       <c r="F143">
-        <v>4.49264575</v>
+        <v>4.43811126</v>
       </c>
       <c r="G143">
-        <v>3.01951058</v>
+        <v>13.83897211</v>
       </c>
       <c r="H143">
-        <v>0.96267685</v>
+        <v>0.68699712</v>
       </c>
       <c r="I143">
-        <v>-0.22463229</v>
+        <v>-0.22190556</v>
       </c>
       <c r="J143">
-        <v>-0.15097553</v>
+        <v>-0.69194861</v>
       </c>
     </row>
     <row r="144">
@@ -4611,31 +4611,31 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C144">
-        <v>77.34187172</v>
+        <v>77.5019979</v>
       </c>
       <c r="D144">
-        <v>308.59473106</v>
+        <v>272.30202878</v>
       </c>
       <c r="E144">
-        <v>12.1729209</v>
+        <v>0.78430707</v>
       </c>
       <c r="F144">
-        <v>4.38266451</v>
+        <v>4.32811141</v>
       </c>
       <c r="G144">
-        <v>-15.25163101</v>
+        <v>-19.51031302</v>
       </c>
       <c r="H144">
-        <v>-0.60864605</v>
+        <v>-0.03921535</v>
       </c>
       <c r="I144">
-        <v>-0.21913323</v>
+        <v>-0.21640557</v>
       </c>
       <c r="J144">
-        <v>0.76258155</v>
+        <v>0.97551565</v>
       </c>
     </row>
     <row r="145">
@@ -4643,31 +4643,31 @@
         <v>144</v>
       </c>
       <c r="B145">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C145">
-        <v>77.66459096</v>
+        <v>77.82457332</v>
       </c>
       <c r="D145">
-        <v>86.10249511</v>
+        <v>49.80979283</v>
       </c>
       <c r="E145">
-        <v>1.32805255</v>
+        <v>12.61622854</v>
       </c>
       <c r="F145">
-        <v>4.27268328</v>
+        <v>4.21811155</v>
       </c>
       <c r="G145">
-        <v>19.49308734</v>
+        <v>14.93446726</v>
       </c>
       <c r="H145">
-        <v>-0.06640263</v>
+        <v>-0.63081143</v>
       </c>
       <c r="I145">
-        <v>-0.21363416</v>
+        <v>-0.21090558</v>
       </c>
       <c r="J145">
-        <v>-0.97465437</v>
+        <v>-0.74672336</v>
       </c>
     </row>
     <row r="146">
@@ -4675,31 +4675,31 @@
         <v>145</v>
       </c>
       <c r="B146">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C146">
-        <v>77.98691318</v>
+        <v>78.14675736</v>
       </c>
       <c r="D146">
-        <v>223.61025916</v>
+        <v>187.31755688</v>
       </c>
       <c r="E146">
-        <v>-14.16383545</v>
+        <v>-19.41412126</v>
       </c>
       <c r="F146">
-        <v>4.16270204</v>
+        <v>4.1081117</v>
       </c>
       <c r="G146">
-        <v>-13.49287504</v>
+        <v>-2.49305313</v>
       </c>
       <c r="H146">
-        <v>0.70819177</v>
+        <v>0.97070606</v>
       </c>
       <c r="I146">
-        <v>-0.2081351</v>
+        <v>-0.20540559</v>
       </c>
       <c r="J146">
-        <v>0.67464375</v>
+        <v>0.12465266</v>
       </c>
     </row>
     <row r="147">
@@ -4707,31 +4707,31 @@
         <v>146</v>
       </c>
       <c r="B147">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C147">
-        <v>78.30885001</v>
+        <v>78.46856161</v>
       </c>
       <c r="D147">
-        <v>1.11802321</v>
+        <v>324.82532093</v>
       </c>
       <c r="E147">
-        <v>19.5813539</v>
+        <v>16.01800973</v>
       </c>
       <c r="F147">
-        <v>4.05272081</v>
+        <v>3.99811185</v>
       </c>
       <c r="G147">
-        <v>0.38214311</v>
+        <v>-11.28886469</v>
       </c>
       <c r="H147">
-        <v>-0.9790677</v>
+        <v>-0.80090049</v>
       </c>
       <c r="I147">
-        <v>-0.20263604</v>
+        <v>-0.19990559</v>
       </c>
       <c r="J147">
-        <v>-0.01910716</v>
+        <v>0.56444323</v>
       </c>
     </row>
     <row r="148">
@@ -4739,31 +4739,31 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C148">
-        <v>78.63041295</v>
+        <v>78.78999752</v>
       </c>
       <c r="D148">
-        <v>138.62578726</v>
+        <v>102.33308498</v>
       </c>
       <c r="E148">
-        <v>-14.71365157</v>
+        <v>-4.19038834</v>
       </c>
       <c r="F148">
-        <v>3.94273957</v>
+        <v>3.88811199</v>
       </c>
       <c r="G148">
-        <v>12.96006412</v>
+        <v>19.16567846</v>
       </c>
       <c r="H148">
-        <v>0.73568258</v>
+        <v>0.20951942</v>
       </c>
       <c r="I148">
-        <v>-0.19713698</v>
+        <v>-0.1944056</v>
       </c>
       <c r="J148">
-        <v>-0.64800321</v>
+        <v>-0.95828392</v>
       </c>
     </row>
     <row r="149">
@@ -4771,31 +4771,31 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C149">
-        <v>78.9516134</v>
+        <v>79.11107643</v>
       </c>
       <c r="D149">
-        <v>276.13355131</v>
+        <v>239.84084903</v>
       </c>
       <c r="E149">
-        <v>2.09731992</v>
+        <v>-9.86715965</v>
       </c>
       <c r="F149">
-        <v>3.83275834</v>
+        <v>3.77811214</v>
       </c>
       <c r="G149">
-        <v>-19.51694681</v>
+        <v>-16.98131412</v>
       </c>
       <c r="H149">
-        <v>-0.104866</v>
+        <v>0.49335798</v>
       </c>
       <c r="I149">
-        <v>-0.19163792</v>
+        <v>-0.18890561</v>
       </c>
       <c r="J149">
-        <v>0.97584734</v>
+        <v>0.84906571</v>
       </c>
     </row>
     <row r="150">
@@ -4803,31 +4803,31 @@
         <v>149</v>
       </c>
       <c r="B150">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C150">
-        <v>79.27246264</v>
+        <v>79.43180958</v>
       </c>
       <c r="D150">
-        <v>53.64131536</v>
+        <v>17.34861308</v>
       </c>
       <c r="E150">
-        <v>11.64955125</v>
+        <v>18.76634267</v>
       </c>
       <c r="F150">
-        <v>3.7227771</v>
+        <v>3.66811229</v>
       </c>
       <c r="G150">
-        <v>15.82494506</v>
+        <v>5.86253658</v>
       </c>
       <c r="H150">
-        <v>-0.58247756</v>
+        <v>-0.93831713</v>
       </c>
       <c r="I150">
-        <v>-0.18613885</v>
+        <v>-0.18340561</v>
       </c>
       <c r="J150">
-        <v>-0.79124725</v>
+        <v>-0.29312683</v>
       </c>
     </row>
     <row r="151">
@@ -4835,31 +4835,31 @@
         <v>150</v>
       </c>
       <c r="B151">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C151">
-        <v>79.59297184</v>
+        <v>79.7522081</v>
       </c>
       <c r="D151">
-        <v>191.14907941</v>
+        <v>154.85637713</v>
       </c>
       <c r="E151">
-        <v>-19.29974355</v>
+        <v>-17.81609373</v>
       </c>
       <c r="F151">
-        <v>3.61279586</v>
+        <v>3.55811243</v>
       </c>
       <c r="G151">
-        <v>-3.80363049</v>
+        <v>8.36221502</v>
       </c>
       <c r="H151">
-        <v>0.96498718</v>
+        <v>0.89080469</v>
       </c>
       <c r="I151">
-        <v>-0.18063979</v>
+        <v>-0.17790562</v>
       </c>
       <c r="J151">
-        <v>0.19018152</v>
+        <v>-0.41811075</v>
       </c>
     </row>
     <row r="152">
@@ -4867,31 +4867,31 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C152">
-        <v>79.91315209</v>
+        <v>80.07228303</v>
       </c>
       <c r="D152">
-        <v>328.65684346</v>
+        <v>292.36414118</v>
       </c>
       <c r="E152">
-        <v>16.8173261</v>
+        <v>7.49588407</v>
       </c>
       <c r="F152">
-        <v>3.50281463</v>
+        <v>3.44811258</v>
       </c>
       <c r="G152">
-        <v>-10.24245246</v>
+        <v>-18.21873326</v>
       </c>
       <c r="H152">
-        <v>-0.84086631</v>
+        <v>-0.3747942</v>
       </c>
       <c r="I152">
-        <v>-0.17514073</v>
+        <v>-0.17240563</v>
       </c>
       <c r="J152">
-        <v>0.51212262</v>
+        <v>0.91093666</v>
       </c>
     </row>
     <row r="153">
@@ -4899,31 +4899,31 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C153">
-        <v>80.23301437</v>
+        <v>80.39204531</v>
       </c>
       <c r="D153">
-        <v>106.16460751</v>
+        <v>69.87190523</v>
       </c>
       <c r="E153">
-        <v>-5.48725427</v>
+        <v>6.78586236</v>
       </c>
       <c r="F153">
-        <v>3.39283339</v>
+        <v>3.33811273</v>
       </c>
       <c r="G153">
-        <v>18.93089333</v>
+        <v>18.51510398</v>
       </c>
       <c r="H153">
-        <v>0.27436271</v>
+        <v>-0.33929312</v>
       </c>
       <c r="I153">
-        <v>-0.16964167</v>
+        <v>-0.16690564</v>
       </c>
       <c r="J153">
-        <v>-0.94654467</v>
+        <v>-0.9257552</v>
       </c>
     </row>
     <row r="154">
@@ -4931,31 +4931,31 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C154">
-        <v>80.55256956</v>
+        <v>80.71150578</v>
       </c>
       <c r="D154">
-        <v>243.67237156</v>
+        <v>207.37966928</v>
       </c>
       <c r="E154">
-        <v>-8.74976052</v>
+        <v>-17.52671164</v>
       </c>
       <c r="F154">
-        <v>3.28285216</v>
+        <v>3.22811287</v>
       </c>
       <c r="G154">
-        <v>-17.68232373</v>
+        <v>-9.0770957</v>
       </c>
       <c r="H154">
-        <v>0.43748803</v>
+        <v>0.87633558</v>
       </c>
       <c r="I154">
-        <v>-0.16414261</v>
+        <v>-0.16140564</v>
       </c>
       <c r="J154">
-        <v>0.88411619</v>
+        <v>0.45385479</v>
       </c>
     </row>
     <row r="155">
@@ -4963,31 +4963,31 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C155">
-        <v>80.87182845</v>
+        <v>81.03067519</v>
       </c>
       <c r="D155">
-        <v>21.18013561</v>
+        <v>344.88743333</v>
       </c>
       <c r="E155">
-        <v>18.41281026</v>
+        <v>19.07220648</v>
       </c>
       <c r="F155">
-        <v>3.17287092</v>
+        <v>3.11811302</v>
       </c>
       <c r="G155">
-        <v>7.1345153</v>
+        <v>-5.15056416</v>
       </c>
       <c r="H155">
-        <v>-0.92064051</v>
+        <v>-0.95361032</v>
       </c>
       <c r="I155">
-        <v>-0.15864355</v>
+        <v>-0.15590565</v>
       </c>
       <c r="J155">
-        <v>-0.35672576</v>
+        <v>0.25752821</v>
       </c>
     </row>
     <row r="156">
@@ -4995,31 +4995,31 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C156">
-        <v>81.19080175</v>
+        <v>81.34956422</v>
       </c>
       <c r="D156">
-        <v>158.68789966</v>
+        <v>122.39519738</v>
       </c>
       <c r="E156">
-        <v>-18.41249977</v>
+        <v>-10.59322912</v>
       </c>
       <c r="F156">
-        <v>3.06288968</v>
+        <v>3.00811317</v>
       </c>
       <c r="G156">
-        <v>7.1832137</v>
+        <v>16.69535121</v>
       </c>
       <c r="H156">
-        <v>0.92062499</v>
+        <v>0.52966146</v>
       </c>
       <c r="I156">
-        <v>-0.15314448</v>
+        <v>-0.15040566</v>
       </c>
       <c r="J156">
-        <v>-0.35916068</v>
+        <v>-0.83476756</v>
       </c>
     </row>
     <row r="157">
@@ -5027,31 +5027,31 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C157">
-        <v>81.50950009</v>
+        <v>81.66818346</v>
       </c>
       <c r="D157">
-        <v>296.19566371</v>
+        <v>259.90296143</v>
       </c>
       <c r="E157">
-        <v>8.73199885</v>
+        <v>-3.46930929</v>
       </c>
       <c r="F157">
-        <v>2.95290845</v>
+        <v>2.89811331</v>
       </c>
       <c r="G157">
-        <v>-17.74915569</v>
+        <v>-19.48242367</v>
       </c>
       <c r="H157">
-        <v>-0.43659994</v>
+        <v>0.17346546</v>
       </c>
       <c r="I157">
-        <v>-0.14764542</v>
+        <v>-0.14490567</v>
       </c>
       <c r="J157">
-        <v>0.88745778</v>
+        <v>0.97412118</v>
       </c>
     </row>
     <row r="158">
@@ -5059,31 +5059,31 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C158">
-        <v>81.82793402</v>
+        <v>81.98654342</v>
       </c>
       <c r="D158">
-        <v>73.70342776</v>
+        <v>37.41072548</v>
       </c>
       <c r="E158">
-        <v>5.55519765</v>
+        <v>15.73089685</v>
       </c>
       <c r="F158">
-        <v>2.84292721</v>
+        <v>2.78811346</v>
       </c>
       <c r="G158">
-        <v>19.00151425</v>
+        <v>12.03184556</v>
       </c>
       <c r="H158">
-        <v>-0.27775988</v>
+        <v>-0.78654484</v>
       </c>
       <c r="I158">
-        <v>-0.14214636</v>
+        <v>-0.13940567</v>
       </c>
       <c r="J158">
-        <v>-0.95007571</v>
+        <v>-0.60159228</v>
       </c>
     </row>
     <row r="159">
@@ -5091,31 +5091,31 @@
         <v>158</v>
       </c>
       <c r="B159">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C159">
-        <v>82.146114</v>
+        <v>82.30465454</v>
       </c>
       <c r="D159">
-        <v>211.21119181</v>
+        <v>174.91848953</v>
       </c>
       <c r="E159">
-        <v>-16.94480972</v>
+        <v>-19.74198354</v>
       </c>
       <c r="F159">
-        <v>2.73294598</v>
+        <v>2.67811361</v>
       </c>
       <c r="G159">
-        <v>-10.26666596</v>
+        <v>1.75550373</v>
       </c>
       <c r="H159">
-        <v>0.84724049</v>
+        <v>0.98709918</v>
       </c>
       <c r="I159">
-        <v>-0.1366473</v>
+        <v>-0.13390568</v>
       </c>
       <c r="J159">
-        <v>0.5133333</v>
+        <v>-0.08777519</v>
       </c>
     </row>
     <row r="160">
@@ -5123,31 +5123,31 @@
         <v>159</v>
       </c>
       <c r="B160">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C160">
-        <v>82.46405043</v>
+        <v>82.62252719</v>
       </c>
       <c r="D160">
-        <v>348.71895586</v>
+        <v>312.42625358</v>
       </c>
       <c r="E160">
-        <v>19.44418155</v>
+        <v>13.38111648</v>
       </c>
       <c r="F160">
-        <v>2.62296474</v>
+        <v>2.56811375</v>
       </c>
       <c r="G160">
-        <v>-3.8786415</v>
+        <v>-14.64071424</v>
       </c>
       <c r="H160">
-        <v>-0.97220908</v>
+        <v>-0.66905582</v>
       </c>
       <c r="I160">
-        <v>-0.13114824</v>
+        <v>-0.12840569</v>
       </c>
       <c r="J160">
-        <v>0.19393208</v>
+        <v>0.73203571</v>
       </c>
     </row>
     <row r="161">
@@ -5155,31 +5155,31 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C161">
-        <v>82.78175363</v>
+        <v>82.94017165</v>
       </c>
       <c r="D161">
-        <v>126.22671991</v>
+        <v>89.93401763</v>
       </c>
       <c r="E161">
-        <v>-11.72596485</v>
+        <v>0.02285756</v>
       </c>
       <c r="F161">
-        <v>2.51298351</v>
+        <v>2.4581139</v>
       </c>
       <c r="G161">
-        <v>16.00583213</v>
+        <v>19.84835393</v>
       </c>
       <c r="H161">
-        <v>0.58629824</v>
+        <v>-0.00114288</v>
       </c>
       <c r="I161">
-        <v>-0.12564918</v>
+        <v>-0.1229057</v>
       </c>
       <c r="J161">
-        <v>-0.80029161</v>
+        <v>-0.9924177</v>
       </c>
     </row>
     <row r="162">
@@ -5187,31 +5187,31 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C162">
-        <v>83.09923387</v>
+        <v>83.25759818</v>
       </c>
       <c r="D162">
-        <v>263.73448396</v>
+        <v>227.44178168</v>
       </c>
       <c r="E162">
-        <v>-2.16690914</v>
+        <v>-13.43322941</v>
       </c>
       <c r="F162">
-        <v>2.40300227</v>
+        <v>2.34811405</v>
       </c>
       <c r="G162">
-        <v>-19.73651653</v>
+        <v>-14.62992509</v>
       </c>
       <c r="H162">
-        <v>0.10834546</v>
+        <v>0.67166147</v>
       </c>
       <c r="I162">
-        <v>-0.12015011</v>
+        <v>-0.1174057</v>
       </c>
       <c r="J162">
-        <v>0.98682583</v>
+        <v>0.73149625</v>
       </c>
     </row>
     <row r="163">
@@ -5219,31 +5219,31 @@
         <v>162</v>
       </c>
       <c r="B163">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C163">
-        <v>83.41650134</v>
+        <v>83.57481693</v>
       </c>
       <c r="D163">
-        <v>41.24224801</v>
+        <v>4.94954573</v>
       </c>
       <c r="E163">
-        <v>14.93941317</v>
+        <v>19.80026624</v>
       </c>
       <c r="F163">
-        <v>2.29302103</v>
+        <v>2.23811419</v>
       </c>
       <c r="G163">
-        <v>13.09793834</v>
+        <v>1.71473074</v>
       </c>
       <c r="H163">
-        <v>-0.74697066</v>
+        <v>-0.99001331</v>
       </c>
       <c r="I163">
-        <v>-0.11465105</v>
+        <v>-0.11190571</v>
       </c>
       <c r="J163">
-        <v>-0.65489692</v>
+        <v>-0.08573654</v>
       </c>
     </row>
     <row r="164">
@@ -5251,31 +5251,31 @@
         <v>163</v>
       </c>
       <c r="B164">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C164">
-        <v>83.73356618</v>
+        <v>83.89183802</v>
       </c>
       <c r="D164">
-        <v>178.75001206</v>
+        <v>142.45730978</v>
       </c>
       <c r="E164">
-        <v>-19.8757705</v>
+        <v>-15.76796178</v>
       </c>
       <c r="F164">
-        <v>2.1830398</v>
+        <v>2.12811434</v>
       </c>
       <c r="G164">
-        <v>0.43368667</v>
+        <v>12.11785916</v>
       </c>
       <c r="H164">
-        <v>0.99378853</v>
+        <v>0.78839809</v>
       </c>
       <c r="I164">
-        <v>-0.10915199</v>
+        <v>-0.10640572</v>
       </c>
       <c r="J164">
-        <v>-0.02168433</v>
+        <v>-0.60589296</v>
       </c>
     </row>
     <row r="165">
@@ -5283,31 +5283,31 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C165">
-        <v>84.05043846</v>
+        <v>84.20867151</v>
       </c>
       <c r="D165">
-        <v>316.25777611</v>
+        <v>279.96507383</v>
       </c>
       <c r="E165">
-        <v>14.37132616</v>
+        <v>3.44329184</v>
       </c>
       <c r="F165">
-        <v>2.07305856</v>
+        <v>2.01811449</v>
       </c>
       <c r="G165">
-        <v>-13.75381447</v>
+        <v>-19.59772832</v>
       </c>
       <c r="H165">
-        <v>-0.71856631</v>
+        <v>-0.17216459</v>
       </c>
       <c r="I165">
-        <v>-0.10365293</v>
+        <v>-0.10090572</v>
       </c>
       <c r="J165">
-        <v>0.68769072</v>
+        <v>0.97988642</v>
       </c>
     </row>
     <row r="166">
@@ -5315,31 +5315,31 @@
         <v>165</v>
       </c>
       <c r="B166">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C166">
-        <v>84.36712822</v>
+        <v>84.5253274</v>
       </c>
       <c r="D166">
-        <v>93.76554016</v>
+        <v>57.47283788</v>
       </c>
       <c r="E166">
-        <v>-1.30713302</v>
+        <v>10.70493282</v>
       </c>
       <c r="F166">
-        <v>1.96307733</v>
+        <v>1.90811463</v>
       </c>
       <c r="G166">
-        <v>19.86045646</v>
+        <v>16.78581281</v>
       </c>
       <c r="H166">
-        <v>0.06535665</v>
+        <v>-0.53524664</v>
       </c>
       <c r="I166">
-        <v>-0.09815387</v>
+        <v>-0.09540573</v>
       </c>
       <c r="J166">
-        <v>-0.99302282</v>
+        <v>-0.83929064</v>
       </c>
     </row>
     <row r="167">
@@ -5347,31 +5347,31 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C167">
-        <v>84.68364542</v>
+        <v>84.84181565</v>
       </c>
       <c r="D167">
-        <v>231.27330421</v>
+        <v>194.98060193</v>
       </c>
       <c r="E167">
-        <v>-12.45830077</v>
+        <v>-19.24202624</v>
       </c>
       <c r="F167">
-        <v>1.85309609</v>
+        <v>1.79811478</v>
       </c>
       <c r="G167">
-        <v>-15.53566146</v>
+        <v>-5.14890371</v>
       </c>
       <c r="H167">
-        <v>0.62291504</v>
+        <v>0.96210131</v>
       </c>
       <c r="I167">
-        <v>-0.0926548</v>
+        <v>-0.08990574</v>
       </c>
       <c r="J167">
-        <v>0.77678307</v>
+        <v>0.25744519</v>
       </c>
     </row>
   </sheetData>

--- a/pin_points_with_normals.xlsx
+++ b/pin_points_with_normals.xlsx
@@ -102,25 +102,25 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>11.4591559</v>
+        <v>9.85487408</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3.97338662</v>
+        <v>3.42306358</v>
       </c>
       <c r="F3">
-        <v>19.60133156</v>
+        <v>19.70488863</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>-0.19866933</v>
+        <v>-0.17115318</v>
       </c>
       <c r="I3">
-        <v>-0.98006658</v>
+        <v>-0.98524443</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -131,31 +131,31 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>11.4591559</v>
+        <v>11.53536255</v>
       </c>
       <c r="D4">
-        <v>60</v>
+        <v>137.50776405</v>
       </c>
       <c r="E4">
-        <v>1.98669331</v>
+        <v>-2.94907289</v>
       </c>
       <c r="F4">
-        <v>19.60133156</v>
+        <v>19.59602939</v>
       </c>
       <c r="G4">
-        <v>3.44105375</v>
+        <v>2.70159235</v>
       </c>
       <c r="H4">
-        <v>-0.09933467</v>
+        <v>0.14745364</v>
       </c>
       <c r="I4">
-        <v>-0.98006658</v>
+        <v>-0.97980147</v>
       </c>
       <c r="J4">
-        <v>-0.17205269</v>
+        <v>-0.13507962</v>
       </c>
     </row>
     <row r="5">
@@ -163,31 +163,31 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>11.4591559</v>
+        <v>13.00294328</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>275.0155281</v>
       </c>
       <c r="E5">
-        <v>-1.98669331</v>
+        <v>0.3934177</v>
       </c>
       <c r="F5">
-        <v>19.60133156</v>
+        <v>19.48717016</v>
       </c>
       <c r="G5">
-        <v>3.44105375</v>
+        <v>-4.48279175</v>
       </c>
       <c r="H5">
-        <v>0.09933467</v>
+        <v>-0.01967088</v>
       </c>
       <c r="I5">
-        <v>-0.98006658</v>
+        <v>-0.97435851</v>
       </c>
       <c r="J5">
-        <v>-0.17205269</v>
+        <v>0.22413959</v>
       </c>
     </row>
     <row r="6">
@@ -195,31 +195,31 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>11.4591559</v>
+        <v>14.32322131</v>
       </c>
       <c r="D6">
-        <v>180</v>
+        <v>52.52329215</v>
       </c>
       <c r="E6">
-        <v>-3.97338662</v>
+        <v>3.01045476</v>
       </c>
       <c r="F6">
-        <v>19.60133156</v>
+        <v>19.37831092</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.92660515</v>
       </c>
       <c r="H6">
-        <v>0.19866933</v>
+        <v>-0.15052274</v>
       </c>
       <c r="I6">
-        <v>-0.98006658</v>
+        <v>-0.96891555</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>-0.19633026</v>
       </c>
     </row>
     <row r="7">
@@ -227,31 +227,31 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>11.4591559</v>
+        <v>15.53381105</v>
       </c>
       <c r="D7">
-        <v>240</v>
+        <v>190.0310562</v>
       </c>
       <c r="E7">
-        <v>-1.98669331</v>
+        <v>-5.27426292</v>
       </c>
       <c r="F7">
-        <v>19.60133156</v>
+        <v>19.26945169</v>
       </c>
       <c r="G7">
-        <v>-3.44105375</v>
+        <v>-0.93294285</v>
       </c>
       <c r="H7">
-        <v>0.09933467</v>
+        <v>0.26371315</v>
       </c>
       <c r="I7">
-        <v>-0.98006658</v>
+        <v>-0.96347258</v>
       </c>
       <c r="J7">
-        <v>0.17205269</v>
+        <v>0.04664714</v>
       </c>
     </row>
     <row r="8">
@@ -259,31 +259,31 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>11.4591559</v>
+        <v>16.65865182</v>
       </c>
       <c r="D8">
-        <v>300</v>
+        <v>327.53882025</v>
       </c>
       <c r="E8">
-        <v>1.98669331</v>
+        <v>4.83757346</v>
       </c>
       <c r="F8">
-        <v>19.60133156</v>
+        <v>19.16059245</v>
       </c>
       <c r="G8">
-        <v>-3.44105375</v>
+        <v>-3.07726826</v>
       </c>
       <c r="H8">
-        <v>-0.09933467</v>
+        <v>-0.24187867</v>
       </c>
       <c r="I8">
-        <v>-0.98006658</v>
+        <v>-0.95802962</v>
       </c>
       <c r="J8">
-        <v>0.17205269</v>
+        <v>0.15386341</v>
       </c>
     </row>
     <row r="9">
@@ -291,31 +291,31 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>16.48287513</v>
+        <v>17.71409467</v>
       </c>
       <c r="D9">
-        <v>68.75388203</v>
+        <v>105.0465843</v>
       </c>
       <c r="E9">
-        <v>2.05632353</v>
+        <v>-1.57978256</v>
       </c>
       <c r="F9">
-        <v>19.1780916</v>
+        <v>19.05173322</v>
       </c>
       <c r="G9">
-        <v>5.28888798</v>
+        <v>5.87671239</v>
       </c>
       <c r="H9">
-        <v>-0.10281618</v>
+        <v>0.07898913</v>
       </c>
       <c r="I9">
-        <v>-0.95890458</v>
+        <v>-0.95258666</v>
       </c>
       <c r="J9">
-        <v>-0.2644444</v>
+        <v>-0.29383562</v>
       </c>
     </row>
     <row r="10">
@@ -323,31 +323,31 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>17.55941927</v>
+        <v>18.71189443</v>
       </c>
       <c r="D10">
-        <v>206.26164608</v>
+        <v>242.55434835</v>
       </c>
       <c r="E10">
-        <v>-5.41109251</v>
+        <v>-2.95726816</v>
       </c>
       <c r="F10">
-        <v>19.06809175</v>
+        <v>18.94287398</v>
       </c>
       <c r="G10">
-        <v>-2.66982301</v>
+        <v>-5.6940399</v>
       </c>
       <c r="H10">
-        <v>0.27055463</v>
+        <v>0.14786341</v>
       </c>
       <c r="I10">
-        <v>-0.95340459</v>
+        <v>-0.9471437</v>
       </c>
       <c r="J10">
-        <v>0.13349115</v>
+        <v>0.28470199</v>
       </c>
     </row>
     <row r="11">
@@ -355,31 +355,31 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>18.57552112</v>
+        <v>19.66083701</v>
       </c>
       <c r="D11">
-        <v>343.76941013</v>
+        <v>20.0621124</v>
       </c>
       <c r="E11">
-        <v>6.11716492</v>
+        <v>6.32072424</v>
       </c>
       <c r="F11">
-        <v>18.9580919</v>
+        <v>18.83401475</v>
       </c>
       <c r="G11">
-        <v>-1.78074283</v>
+        <v>2.30831836</v>
       </c>
       <c r="H11">
-        <v>-0.30585825</v>
+        <v>-0.31603621</v>
       </c>
       <c r="I11">
-        <v>-0.94790459</v>
+        <v>-0.94170074</v>
       </c>
       <c r="J11">
-        <v>0.08903714</v>
+        <v>-0.11541592</v>
       </c>
     </row>
     <row r="12">
@@ -387,31 +387,31 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>19.5406198</v>
+        <v>20.56769334</v>
       </c>
       <c r="D12">
-        <v>121.27717418</v>
+        <v>157.56987645</v>
       </c>
       <c r="E12">
-        <v>-3.47304631</v>
+        <v>-6.49470678</v>
       </c>
       <c r="F12">
-        <v>18.84809204</v>
+        <v>18.72515551</v>
       </c>
       <c r="G12">
-        <v>5.71728744</v>
+        <v>2.68092055</v>
       </c>
       <c r="H12">
-        <v>0.17365232</v>
+        <v>0.32473534</v>
       </c>
       <c r="I12">
-        <v>-0.9424046</v>
+        <v>-0.93625778</v>
       </c>
       <c r="J12">
-        <v>-0.28586437</v>
+        <v>-0.13404603</v>
       </c>
     </row>
     <row r="13">
@@ -419,31 +419,31 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>20.46194102</v>
+        <v>21.43781218</v>
       </c>
       <c r="D13">
-        <v>258.78493823</v>
+        <v>295.0776405</v>
       </c>
       <c r="E13">
-        <v>-1.35983167</v>
+        <v>3.09823922</v>
       </c>
       <c r="F13">
-        <v>18.73809219</v>
+        <v>18.61629628</v>
       </c>
       <c r="G13">
-        <v>-6.85818919</v>
+        <v>-6.62075726</v>
       </c>
       <c r="H13">
-        <v>0.06799158</v>
+        <v>-0.15491196</v>
       </c>
       <c r="I13">
-        <v>-0.93690461</v>
+        <v>-0.93081481</v>
       </c>
       <c r="J13">
-        <v>0.34290946</v>
+        <v>0.33103786</v>
       </c>
     </row>
     <row r="14">
@@ -451,31 +451,31 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>21.34516161</v>
+        <v>22.27550595</v>
       </c>
       <c r="D14">
-        <v>36.29270228</v>
+        <v>72.58540455</v>
       </c>
       <c r="E14">
-        <v>5.86747295</v>
+        <v>2.2689344</v>
       </c>
       <c r="F14">
-        <v>18.62809234</v>
+        <v>18.50743704</v>
       </c>
       <c r="G14">
-        <v>4.30893689</v>
+        <v>7.2337204</v>
       </c>
       <c r="H14">
-        <v>-0.29337365</v>
+        <v>-0.11344672</v>
       </c>
       <c r="I14">
-        <v>-0.93140462</v>
+        <v>-0.92537185</v>
       </c>
       <c r="J14">
-        <v>-0.21544684</v>
+        <v>-0.36168602</v>
       </c>
     </row>
     <row r="15">
@@ -483,31 +483,31 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>22.19483771</v>
+        <v>23.08431161</v>
       </c>
       <c r="D15">
-        <v>173.80046633</v>
+        <v>210.0931686</v>
       </c>
       <c r="E15">
-        <v>-7.51096362</v>
+        <v>-6.78473093</v>
       </c>
       <c r="F15">
-        <v>18.51809248</v>
+        <v>18.39857781</v>
       </c>
       <c r="G15">
-        <v>0.81588991</v>
+        <v>-3.93189025</v>
       </c>
       <c r="H15">
-        <v>0.37554818</v>
+        <v>0.33923655</v>
       </c>
       <c r="I15">
-        <v>-0.92590462</v>
+        <v>-0.91992889</v>
       </c>
       <c r="J15">
-        <v>-0.0407945</v>
+        <v>0.19659451</v>
       </c>
     </row>
     <row r="16">
@@ -515,31 +515,31 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>23.01469185</v>
+        <v>23.86717274</v>
       </c>
       <c r="D16">
-        <v>311.30823038</v>
+        <v>347.60093265</v>
       </c>
       <c r="E16">
-        <v>5.16162324</v>
+        <v>7.90360618</v>
       </c>
       <c r="F16">
-        <v>18.40809263</v>
+        <v>18.28971857</v>
       </c>
       <c r="G16">
-        <v>-5.87365059</v>
+        <v>-1.73758565</v>
       </c>
       <c r="H16">
-        <v>-0.25808116</v>
+        <v>-0.39518031</v>
       </c>
       <c r="I16">
-        <v>-0.92040463</v>
+        <v>-0.91448593</v>
       </c>
       <c r="J16">
-        <v>0.29368253</v>
+        <v>0.08687928</v>
       </c>
     </row>
     <row r="17">
@@ -547,31 +547,31 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>23.80781188</v>
+        <v>24.62657013</v>
       </c>
       <c r="D17">
-        <v>88.81599443</v>
+        <v>125.1086967</v>
       </c>
       <c r="E17">
-        <v>0.1668233</v>
+        <v>-4.79315619</v>
       </c>
       <c r="F17">
-        <v>18.29809278</v>
+        <v>18.18085934</v>
       </c>
       <c r="G17">
-        <v>8.07167707</v>
+        <v>6.81777145</v>
       </c>
       <c r="H17">
-        <v>-0.00834117</v>
+        <v>0.23965781</v>
       </c>
       <c r="I17">
-        <v>-0.91490464</v>
+        <v>-0.90904297</v>
       </c>
       <c r="J17">
-        <v>-0.40358385</v>
+        <v>-0.34088857</v>
       </c>
     </row>
     <row r="18">
@@ -579,31 +579,31 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>24.57679274</v>
+        <v>25.36461759</v>
       </c>
       <c r="D18">
-        <v>226.32375848</v>
+        <v>262.61646075</v>
       </c>
       <c r="E18">
-        <v>-5.74443811</v>
+        <v>-1.10102101</v>
       </c>
       <c r="F18">
-        <v>18.18809292</v>
+        <v>18.0720001</v>
       </c>
       <c r="G18">
-        <v>-6.01620367</v>
+        <v>-8.49650311</v>
       </c>
       <c r="H18">
-        <v>0.28722191</v>
+        <v>0.05505105</v>
       </c>
       <c r="I18">
-        <v>-0.90940465</v>
+        <v>-0.90360001</v>
       </c>
       <c r="J18">
-        <v>0.30081018</v>
+        <v>0.42482516</v>
       </c>
     </row>
     <row r="19">
@@ -611,31 +611,31 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>25.32384002</v>
+        <v>26.08313364</v>
       </c>
       <c r="D19">
-        <v>3.83152253</v>
+        <v>40.1242248</v>
       </c>
       <c r="E19">
-        <v>8.53555912</v>
+        <v>6.72393781</v>
       </c>
       <c r="F19">
-        <v>18.07809307</v>
+        <v>17.96314087</v>
       </c>
       <c r="G19">
-        <v>0.57164813</v>
+        <v>5.66694191</v>
       </c>
       <c r="H19">
-        <v>-0.42677796</v>
+        <v>-0.33619689</v>
       </c>
       <c r="I19">
-        <v>-0.90390465</v>
+        <v>-0.89815704</v>
       </c>
       <c r="J19">
-        <v>-0.02858241</v>
+        <v>-0.2833471</v>
       </c>
     </row>
     <row r="20">
@@ -643,31 +643,31 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C20">
-        <v>26.05084703</v>
+        <v>26.78369623</v>
       </c>
       <c r="D20">
-        <v>141.33928658</v>
+        <v>177.63198885</v>
       </c>
       <c r="E20">
-        <v>-6.85857466</v>
+        <v>-9.0047745</v>
       </c>
       <c r="F20">
-        <v>17.96809322</v>
+        <v>17.85428163</v>
       </c>
       <c r="G20">
-        <v>5.48703743</v>
+        <v>0.3723757</v>
       </c>
       <c r="H20">
-        <v>0.34292873</v>
+        <v>0.45023872</v>
       </c>
       <c r="I20">
-        <v>-0.89840466</v>
+        <v>-0.89271408</v>
       </c>
       <c r="J20">
-        <v>-0.27435187</v>
+        <v>-0.01861878</v>
       </c>
     </row>
     <row r="21">
@@ -675,31 +675,31 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>26.75945341</v>
+        <v>27.467685</v>
       </c>
       <c r="D21">
-        <v>278.84705063</v>
+        <v>315.1397529</v>
       </c>
       <c r="E21">
-        <v>1.38493173</v>
+        <v>6.53892672</v>
       </c>
       <c r="F21">
-        <v>17.85809336</v>
+        <v>17.7454224</v>
       </c>
       <c r="G21">
-        <v>-8.89777869</v>
+        <v>-6.50710545</v>
       </c>
       <c r="H21">
-        <v>-0.06924659</v>
+        <v>-0.32694634</v>
       </c>
       <c r="I21">
-        <v>-0.89290467</v>
+        <v>-0.88727112</v>
       </c>
       <c r="J21">
-        <v>0.44488893</v>
+        <v>0.32535527</v>
       </c>
     </row>
     <row r="22">
@@ -707,31 +707,31 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>27.45109023</v>
+        <v>28.13631449</v>
       </c>
       <c r="D22">
-        <v>56.35481468</v>
+        <v>92.64751695</v>
       </c>
       <c r="E22">
-        <v>5.10822798</v>
+        <v>-0.43565082</v>
       </c>
       <c r="F22">
-        <v>17.74809351</v>
+        <v>17.63656316</v>
       </c>
       <c r="G22">
-        <v>7.67536212</v>
+        <v>9.42135066</v>
       </c>
       <c r="H22">
-        <v>-0.2554114</v>
+        <v>0.02178254</v>
       </c>
       <c r="I22">
-        <v>-0.88740468</v>
+        <v>-0.88182816</v>
       </c>
       <c r="J22">
-        <v>-0.38376811</v>
+        <v>-0.47106753</v>
       </c>
     </row>
     <row r="23">
@@ -739,31 +739,31 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C23">
-        <v>28.12701534</v>
+        <v>28.79066054</v>
       </c>
       <c r="D23">
-        <v>193.86257873</v>
+        <v>230.155281</v>
       </c>
       <c r="E23">
-        <v>-9.15393126</v>
+        <v>-6.17144921</v>
       </c>
       <c r="F23">
-        <v>17.63809366</v>
+        <v>17.52770393</v>
       </c>
       <c r="G23">
-        <v>-2.25902517</v>
+        <v>-7.39545872</v>
       </c>
       <c r="H23">
-        <v>0.45769656</v>
+        <v>0.30857246</v>
       </c>
       <c r="I23">
-        <v>-0.88190468</v>
+        <v>-0.8763852</v>
       </c>
       <c r="J23">
-        <v>0.11295126</v>
+        <v>0.36977294</v>
       </c>
     </row>
     <row r="24">
@@ -771,31 +771,31 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C24">
-        <v>28.78834134</v>
+        <v>29.43168149</v>
       </c>
       <c r="D24">
-        <v>331.37034278</v>
+        <v>7.66304505</v>
       </c>
       <c r="E24">
-        <v>8.45391158</v>
+        <v>9.73994105</v>
       </c>
       <c r="F24">
-        <v>17.5280938</v>
+        <v>17.41884469</v>
       </c>
       <c r="G24">
-        <v>-4.61490049</v>
+        <v>1.31049529</v>
       </c>
       <c r="H24">
-        <v>-0.42269558</v>
+        <v>-0.48699705</v>
       </c>
       <c r="I24">
-        <v>-0.87640469</v>
+        <v>-0.87094223</v>
       </c>
       <c r="J24">
-        <v>0.23074502</v>
+        <v>-0.06552476</v>
       </c>
     </row>
     <row r="25">
@@ -803,31 +803,31 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>29.43605803</v>
+        <v>30.06023534</v>
       </c>
       <c r="D25">
-        <v>108.87810683</v>
+        <v>145.1708091</v>
       </c>
       <c r="E25">
-        <v>-3.18024337</v>
+        <v>-8.22352595</v>
       </c>
       <c r="F25">
-        <v>17.41809395</v>
+        <v>17.30998546</v>
       </c>
       <c r="G25">
-        <v>9.30032555</v>
+        <v>5.72171516</v>
       </c>
       <c r="H25">
-        <v>0.15901217</v>
+        <v>0.4111763</v>
       </c>
       <c r="I25">
-        <v>-0.8709047</v>
+        <v>-0.86549927</v>
       </c>
       <c r="J25">
-        <v>-0.46501628</v>
+        <v>-0.28608576</v>
       </c>
     </row>
     <row r="26">
@@ -835,31 +835,31 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>30.07105058</v>
+        <v>30.67709392</v>
       </c>
       <c r="D26">
-        <v>246.38587088</v>
+        <v>282.67857315</v>
       </c>
       <c r="E26">
-        <v>-4.01435065</v>
+        <v>2.23958403</v>
       </c>
       <c r="F26">
-        <v>17.3080941</v>
+        <v>17.20112622</v>
       </c>
       <c r="G26">
-        <v>-9.18231276</v>
+        <v>-9.95517554</v>
       </c>
       <c r="H26">
-        <v>0.20071753</v>
+        <v>-0.1119792</v>
       </c>
       <c r="I26">
-        <v>-0.8654047</v>
+        <v>-0.86005631</v>
       </c>
       <c r="J26">
-        <v>0.45911564</v>
+        <v>0.49775878</v>
       </c>
     </row>
     <row r="27">
@@ -867,31 +867,31 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>30.69411434</v>
+        <v>31.2829545</v>
       </c>
       <c r="D27">
-        <v>23.89363493</v>
+        <v>60.1863372</v>
       </c>
       <c r="E27">
-        <v>9.33416195</v>
+        <v>5.16337142</v>
       </c>
       <c r="F27">
-        <v>17.19809424</v>
+        <v>17.09226699</v>
       </c>
       <c r="G27">
-        <v>4.13509071</v>
+        <v>9.0107716</v>
       </c>
       <c r="H27">
-        <v>-0.4667081</v>
+        <v>-0.25816857</v>
       </c>
       <c r="I27">
-        <v>-0.85990471</v>
+        <v>-0.85461335</v>
       </c>
       <c r="J27">
-        <v>-0.20675454</v>
+        <v>-0.45053858</v>
       </c>
     </row>
     <row r="28">
@@ -899,31 +899,31 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>31.30596715</v>
+        <v>31.8784495</v>
       </c>
       <c r="D28">
-        <v>161.40139898</v>
+        <v>197.69410125</v>
       </c>
       <c r="E28">
-        <v>-9.84944375</v>
+        <v>-10.06270268</v>
       </c>
       <c r="F28">
-        <v>17.08809439</v>
+        <v>16.98340775</v>
       </c>
       <c r="G28">
-        <v>3.31443631</v>
+        <v>-3.21027661</v>
       </c>
       <c r="H28">
-        <v>0.49247219</v>
+        <v>0.50313513</v>
       </c>
       <c r="I28">
-        <v>-0.85440472</v>
+        <v>-0.84917039</v>
       </c>
       <c r="J28">
-        <v>-0.16572182</v>
+        <v>0.16051383</v>
       </c>
     </row>
     <row r="29">
@@ -931,31 +931,31 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C29">
-        <v>31.90725947</v>
+        <v>32.46415465</v>
       </c>
       <c r="D29">
-        <v>298.90916303</v>
+        <v>335.2018653</v>
       </c>
       <c r="E29">
-        <v>5.11021837</v>
+        <v>9.74553473</v>
       </c>
       <c r="F29">
-        <v>16.97809454</v>
+        <v>16.87454852</v>
       </c>
       <c r="G29">
-        <v>-9.25364653</v>
+        <v>-4.50268423</v>
       </c>
       <c r="H29">
-        <v>-0.25551092</v>
+        <v>-0.48727674</v>
       </c>
       <c r="I29">
-        <v>-0.84890473</v>
+        <v>-0.84372743</v>
       </c>
       <c r="J29">
-        <v>0.46268233</v>
+        <v>0.22513421</v>
       </c>
     </row>
     <row r="30">
@@ -963,31 +963,31 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C30">
-        <v>32.49858295</v>
+        <v>33.04059581</v>
       </c>
       <c r="D30">
-        <v>76.41692708</v>
+        <v>112.70962935</v>
       </c>
       <c r="E30">
-        <v>2.52365151</v>
+        <v>-4.20986578</v>
       </c>
       <c r="F30">
-        <v>16.86809468</v>
+        <v>16.76568928</v>
       </c>
       <c r="G30">
-        <v>10.44502584</v>
+        <v>10.05925907</v>
       </c>
       <c r="H30">
-        <v>-0.12618258</v>
+        <v>0.21049329</v>
       </c>
       <c r="I30">
-        <v>-0.84340473</v>
+        <v>-0.83828446</v>
       </c>
       <c r="J30">
-        <v>-0.52225129</v>
+        <v>-0.50296295</v>
       </c>
     </row>
     <row r="31">
@@ -995,31 +995,31 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C31">
-        <v>33.08047759</v>
+        <v>33.60825488</v>
       </c>
       <c r="D31">
-        <v>213.92469113</v>
+        <v>250.2173934</v>
       </c>
       <c r="E31">
-        <v>-9.05806325</v>
+        <v>-3.74674489</v>
       </c>
       <c r="F31">
-        <v>16.75809483</v>
+        <v>16.65683005</v>
       </c>
       <c r="G31">
-        <v>-6.09243365</v>
+        <v>-10.41690528</v>
       </c>
       <c r="H31">
-        <v>0.45290316</v>
+        <v>0.18733724</v>
       </c>
       <c r="I31">
-        <v>-0.83790474</v>
+        <v>-0.8328415</v>
       </c>
       <c r="J31">
-        <v>0.30462168</v>
+        <v>0.52084526</v>
       </c>
     </row>
     <row r="32">
@@ -1027,31 +1027,31 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>33.65343785</v>
+        <v>34.16757471</v>
       </c>
       <c r="D32">
-        <v>351.43245518</v>
+        <v>27.72515745</v>
       </c>
       <c r="E32">
-        <v>10.95968286</v>
+        <v>9.94271721</v>
       </c>
       <c r="F32">
-        <v>16.64809498</v>
+        <v>16.54797081</v>
       </c>
       <c r="G32">
-        <v>-1.65114664</v>
+        <v>5.22561351</v>
       </c>
       <c r="H32">
-        <v>-0.54798414</v>
+        <v>-0.49713586</v>
       </c>
       <c r="I32">
-        <v>-0.83240475</v>
+        <v>-0.82739854</v>
       </c>
       <c r="J32">
-        <v>0.08255733</v>
+        <v>-0.26128068</v>
       </c>
     </row>
     <row r="33">
@@ -1059,31 +1059,31 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C33">
-        <v>34.21791784</v>
+        <v>34.71896346</v>
       </c>
       <c r="D33">
-        <v>128.94021923</v>
+        <v>165.2329215</v>
       </c>
       <c r="E33">
-        <v>-7.06874237</v>
+        <v>-11.0147863</v>
       </c>
       <c r="F33">
-        <v>16.53809512</v>
+        <v>16.43911158</v>
       </c>
       <c r="G33">
-        <v>8.74781636</v>
+        <v>2.90346232</v>
       </c>
       <c r="H33">
-        <v>0.35343712</v>
+        <v>0.55073931</v>
       </c>
       <c r="I33">
-        <v>-0.82690476</v>
+        <v>-0.82195558</v>
       </c>
       <c r="J33">
-        <v>-0.43739082</v>
+        <v>-0.14517312</v>
       </c>
     </row>
     <row r="34">
@@ -1091,31 +1091,31 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C34">
-        <v>34.7743358</v>
+        <v>35.26279824</v>
       </c>
       <c r="D34">
-        <v>266.44798328</v>
+        <v>302.74068555</v>
       </c>
       <c r="E34">
-        <v>-0.70671175</v>
+        <v>6.24481096</v>
       </c>
       <c r="F34">
-        <v>16.42809527</v>
+        <v>16.33025234</v>
       </c>
       <c r="G34">
-        <v>-11.38500085</v>
+        <v>-9.71211586</v>
       </c>
       <c r="H34">
-        <v>0.03533559</v>
+        <v>-0.31224055</v>
       </c>
       <c r="I34">
-        <v>-0.82140476</v>
+        <v>-0.81651262</v>
       </c>
       <c r="J34">
-        <v>0.56925004</v>
+        <v>0.48560579</v>
       </c>
     </row>
     <row r="35">
@@ -1123,31 +1123,31 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>35.32307795</v>
+        <v>35.79942834</v>
       </c>
       <c r="D35">
-        <v>43.95574733</v>
+        <v>80.2484496</v>
       </c>
       <c r="E35">
-        <v>8.32445017</v>
+        <v>1.98153043</v>
       </c>
       <c r="F35">
-        <v>16.31809542</v>
+        <v>16.22139311</v>
       </c>
       <c r="G35">
-        <v>8.02641211</v>
+        <v>11.52995849</v>
       </c>
       <c r="H35">
-        <v>-0.41622251</v>
+        <v>-0.09907652</v>
       </c>
       <c r="I35">
-        <v>-0.81590477</v>
+        <v>-0.81106966</v>
       </c>
       <c r="J35">
-        <v>-0.40132061</v>
+        <v>-0.57649792</v>
       </c>
     </row>
     <row r="36">
@@ -1155,31 +1155,31 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C36">
-        <v>35.86450179</v>
+        <v>36.32917802</v>
       </c>
       <c r="D36">
-        <v>181.46351138</v>
+        <v>217.75621365</v>
       </c>
       <c r="E36">
-        <v>-11.71358519</v>
+        <v>-9.36767533</v>
       </c>
       <c r="F36">
-        <v>16.20809556</v>
+        <v>16.11253387</v>
       </c>
       <c r="G36">
-        <v>-0.29926627</v>
+        <v>-7.25485431</v>
       </c>
       <c r="H36">
-        <v>0.58567926</v>
+        <v>0.46838377</v>
       </c>
       <c r="I36">
-        <v>-0.81040478</v>
+        <v>-0.80562669</v>
       </c>
       <c r="J36">
-        <v>0.01496331</v>
+        <v>0.36274272</v>
       </c>
     </row>
     <row r="37">
@@ -1187,31 +1187,31 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C37">
-        <v>36.39893906</v>
+        <v>36.85234897</v>
       </c>
       <c r="D37">
-        <v>318.97127543</v>
+        <v>355.2639777</v>
       </c>
       <c r="E37">
-        <v>8.95304878</v>
+        <v>11.95414375</v>
       </c>
       <c r="F37">
-        <v>16.09809571</v>
+        <v>16.00367464</v>
       </c>
       <c r="G37">
-        <v>-7.7906503</v>
+        <v>-0.99037637</v>
       </c>
       <c r="H37">
-        <v>-0.44765244</v>
+        <v>-0.59770719</v>
       </c>
       <c r="I37">
-        <v>-0.80490479</v>
+        <v>-0.80018373</v>
       </c>
       <c r="J37">
-        <v>0.38953251</v>
+        <v>0.04951882</v>
       </c>
     </row>
     <row r="38">
@@ -1219,31 +1219,31 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C38">
-        <v>36.92669821</v>
+        <v>37.36922242</v>
       </c>
       <c r="D38">
-        <v>96.47903948</v>
+        <v>132.77174175</v>
       </c>
       <c r="E38">
-        <v>-1.3558659</v>
+        <v>-8.24333083</v>
       </c>
       <c r="F38">
-        <v>15.98809586</v>
+        <v>15.8948154</v>
       </c>
       <c r="G38">
-        <v>11.93911297</v>
+        <v>8.91079908</v>
       </c>
       <c r="H38">
-        <v>0.06779329</v>
+        <v>0.41216654</v>
       </c>
       <c r="I38">
-        <v>-0.79940479</v>
+        <v>-0.79474077</v>
       </c>
       <c r="J38">
-        <v>-0.59695565</v>
+        <v>-0.44553995</v>
       </c>
     </row>
     <row r="39">
@@ -1251,31 +1251,31 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C39">
-        <v>37.44806668</v>
+        <v>37.88006107</v>
       </c>
       <c r="D39">
-        <v>233.98680353</v>
+        <v>270.2795058</v>
       </c>
       <c r="E39">
-        <v>-7.15022911</v>
+        <v>0.05990627</v>
       </c>
       <c r="F39">
-        <v>15.878096</v>
+        <v>15.78595617</v>
       </c>
       <c r="G39">
-        <v>-9.83668089</v>
+        <v>-12.28006511</v>
       </c>
       <c r="H39">
-        <v>0.35751146</v>
+        <v>-0.00299531</v>
       </c>
       <c r="I39">
-        <v>-0.7939048</v>
+        <v>-0.78929781</v>
       </c>
       <c r="J39">
-        <v>0.49183404</v>
+        <v>0.61400326</v>
       </c>
     </row>
     <row r="40">
@@ -1283,31 +1283,31 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C40">
-        <v>37.96331282</v>
+        <v>38.38511073</v>
       </c>
       <c r="D40">
-        <v>11.49456758</v>
+        <v>47.78726985</v>
       </c>
       <c r="E40">
-        <v>12.05637896</v>
+        <v>8.34406265</v>
       </c>
       <c r="F40">
-        <v>15.76809615</v>
+        <v>15.67709693</v>
       </c>
       <c r="G40">
-        <v>2.45170762</v>
+        <v>9.19811123</v>
       </c>
       <c r="H40">
-        <v>-0.60281895</v>
+        <v>-0.41720313</v>
       </c>
       <c r="I40">
-        <v>-0.78840481</v>
+        <v>-0.78385485</v>
       </c>
       <c r="J40">
-        <v>-0.12258538</v>
+        <v>-0.45990556</v>
       </c>
     </row>
     <row r="41">
@@ -1315,31 +1315,31 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C41">
-        <v>38.47268764</v>
+        <v>38.88460182</v>
       </c>
       <c r="D41">
-        <v>149.00233163</v>
+        <v>185.2950339</v>
       </c>
       <c r="E41">
-        <v>-10.66584786</v>
+        <v>-12.50150138</v>
       </c>
       <c r="F41">
-        <v>15.6580963</v>
+        <v>15.5682377</v>
       </c>
       <c r="G41">
-        <v>6.40809721</v>
+        <v>-1.15863634</v>
       </c>
       <c r="H41">
-        <v>0.53329239</v>
+        <v>0.62507507</v>
       </c>
       <c r="I41">
-        <v>-0.78290481</v>
+        <v>-0.77841188</v>
       </c>
       <c r="J41">
-        <v>-0.32040486</v>
+        <v>0.05793182</v>
       </c>
     </row>
     <row r="42">
@@ -1347,31 +1347,31 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C42">
-        <v>38.97642632</v>
+        <v>39.37875069</v>
       </c>
       <c r="D42">
-        <v>286.51009568</v>
+        <v>322.80279795</v>
       </c>
       <c r="E42">
-        <v>3.57504169</v>
+        <v>10.10744535</v>
       </c>
       <c r="F42">
-        <v>15.54809644</v>
+        <v>15.45937846</v>
       </c>
       <c r="G42">
-        <v>-12.06133384</v>
+        <v>-7.67119066</v>
       </c>
       <c r="H42">
-        <v>-0.17875208</v>
+        <v>-0.50537227</v>
       </c>
       <c r="I42">
-        <v>-0.77740482</v>
+        <v>-0.77296892</v>
       </c>
       <c r="J42">
-        <v>0.60306669</v>
+        <v>0.38355953</v>
       </c>
     </row>
     <row r="43">
@@ -1379,31 +1379,31 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C43">
-        <v>39.47474963</v>
+        <v>39.8677608</v>
       </c>
       <c r="D43">
-        <v>64.01785973</v>
+        <v>100.310562</v>
       </c>
       <c r="E43">
-        <v>5.57022233</v>
+        <v>-2.29463347</v>
       </c>
       <c r="F43">
-        <v>15.43809659</v>
+        <v>15.35051923</v>
       </c>
       <c r="G43">
-        <v>11.42968927</v>
+        <v>12.61333488</v>
       </c>
       <c r="H43">
-        <v>-0.27851112</v>
+        <v>0.11473167</v>
       </c>
       <c r="I43">
-        <v>-0.77190483</v>
+        <v>-0.76752596</v>
       </c>
       <c r="J43">
-        <v>-0.57148446</v>
+        <v>-0.63066674</v>
       </c>
     </row>
     <row r="44">
@@ -1411,31 +1411,31 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C44">
-        <v>39.96786506</v>
+        <v>40.35182376</v>
       </c>
       <c r="D44">
-        <v>201.52562378</v>
+        <v>237.81832605</v>
       </c>
       <c r="E44">
-        <v>-11.95111391</v>
+        <v>-6.89702242</v>
       </c>
       <c r="F44">
-        <v>15.32809674</v>
+        <v>15.24165999</v>
       </c>
       <c r="G44">
-        <v>-4.71384415</v>
+        <v>-10.96005851</v>
       </c>
       <c r="H44">
-        <v>0.5975557</v>
+        <v>0.34485112</v>
       </c>
       <c r="I44">
-        <v>-0.76640484</v>
+        <v>-0.762083</v>
       </c>
       <c r="J44">
-        <v>0.23569221</v>
+        <v>0.54800293</v>
       </c>
     </row>
     <row r="45">
@@ -1443,31 +1443,31 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C45">
-        <v>40.45596799</v>
+        <v>40.83112027</v>
       </c>
       <c r="D45">
-        <v>339.03338783</v>
+        <v>15.3260901</v>
       </c>
       <c r="E45">
-        <v>12.11803292</v>
+        <v>12.61159121</v>
       </c>
       <c r="F45">
-        <v>15.21809688</v>
+        <v>15.13280076</v>
       </c>
       <c r="G45">
-        <v>-4.64357679</v>
+        <v>3.45631429</v>
       </c>
       <c r="H45">
-        <v>-0.60590165</v>
+        <v>-0.63057956</v>
       </c>
       <c r="I45">
-        <v>-0.76090484</v>
+        <v>-0.75664004</v>
       </c>
       <c r="J45">
-        <v>0.23217884</v>
+        <v>-0.17281571</v>
       </c>
     </row>
     <row r="46">
@@ -1475,31 +1475,31 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C46">
-        <v>40.93924262</v>
+        <v>41.30582102</v>
       </c>
       <c r="D46">
-        <v>116.54115188</v>
+        <v>152.83385415</v>
       </c>
       <c r="E46">
-        <v>-5.85591904</v>
+        <v>-11.74524692</v>
       </c>
       <c r="F46">
-        <v>15.10809703</v>
+        <v>15.02394152</v>
       </c>
       <c r="G46">
-        <v>11.72406143</v>
+        <v>6.0274668</v>
       </c>
       <c r="H46">
-        <v>0.29279595</v>
+        <v>0.58726235</v>
       </c>
       <c r="I46">
-        <v>-0.75540485</v>
+        <v>-0.75119708</v>
       </c>
       <c r="J46">
-        <v>-0.58620307</v>
+        <v>-0.30137334</v>
       </c>
     </row>
     <row r="47">
@@ -1507,31 +1507,31 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C47">
-        <v>41.41786286</v>
+        <v>41.77608741</v>
       </c>
       <c r="D47">
-        <v>254.04891593</v>
+        <v>290.3416182</v>
       </c>
       <c r="E47">
-        <v>-3.63607455</v>
+        <v>4.63179448</v>
       </c>
       <c r="F47">
-        <v>14.99809718</v>
+        <v>14.91508229</v>
       </c>
       <c r="G47">
-        <v>-12.72147959</v>
+        <v>-12.49347031</v>
       </c>
       <c r="H47">
-        <v>0.18180373</v>
+        <v>-0.23158972</v>
       </c>
       <c r="I47">
-        <v>-0.74990486</v>
+        <v>-0.74575411</v>
       </c>
       <c r="J47">
-        <v>0.63607398</v>
+        <v>0.62467352</v>
       </c>
     </row>
     <row r="48">
@@ -1539,31 +1539,31 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C48">
-        <v>41.89199312</v>
+        <v>42.24207226</v>
       </c>
       <c r="D48">
-        <v>31.55667998</v>
+        <v>67.84938225</v>
       </c>
       <c r="E48">
-        <v>11.37973502</v>
+        <v>5.06944693</v>
       </c>
       <c r="F48">
-        <v>14.88809732</v>
+        <v>14.80622305</v>
       </c>
       <c r="G48">
-        <v>6.98900486</v>
+        <v>12.4529702</v>
       </c>
       <c r="H48">
-        <v>-0.56898675</v>
+        <v>-0.25347235</v>
       </c>
       <c r="I48">
-        <v>-0.74440487</v>
+        <v>-0.74031115</v>
       </c>
       <c r="J48">
-        <v>-0.34945024</v>
+        <v>-0.62264851</v>
       </c>
     </row>
     <row r="49">
@@ -1571,31 +1571,31 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C49">
-        <v>42.36178903</v>
+        <v>42.70392042</v>
       </c>
       <c r="D49">
-        <v>169.06444403</v>
+        <v>205.3571463</v>
       </c>
       <c r="E49">
-        <v>-13.23148329</v>
+        <v>-12.25736795</v>
       </c>
       <c r="F49">
-        <v>14.77809747</v>
+        <v>14.69736382</v>
       </c>
       <c r="G49">
-        <v>2.55649863</v>
+        <v>-5.80899542</v>
       </c>
       <c r="H49">
-        <v>0.66157416</v>
+        <v>0.6128684</v>
       </c>
       <c r="I49">
-        <v>-0.73890487</v>
+        <v>-0.73486819</v>
       </c>
       <c r="J49">
-        <v>-0.12782493</v>
+        <v>0.29044977</v>
       </c>
     </row>
     <row r="50">
@@ -1603,31 +1603,31 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C50">
-        <v>42.82739808</v>
+        <v>43.1617694</v>
       </c>
       <c r="D50">
-        <v>306.57220808</v>
+        <v>342.86491035</v>
       </c>
       <c r="E50">
-        <v>8.10088366</v>
+        <v>13.07393974</v>
       </c>
       <c r="F50">
-        <v>14.66809762</v>
+        <v>14.58850458</v>
       </c>
       <c r="G50">
-        <v>-10.91891003</v>
+        <v>-4.03083536</v>
       </c>
       <c r="H50">
-        <v>-0.40504418</v>
+        <v>-0.65369699</v>
       </c>
       <c r="I50">
-        <v>-0.73340488</v>
+        <v>-0.72942523</v>
       </c>
       <c r="J50">
-        <v>0.5459455</v>
+        <v>0.20154177</v>
       </c>
     </row>
     <row r="51">
@@ -1635,31 +1635,31 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C51">
-        <v>43.2889602</v>
+        <v>43.61574981</v>
       </c>
       <c r="D51">
-        <v>84.07997213</v>
+        <v>120.3726744</v>
       </c>
       <c r="E51">
-        <v>1.41441998</v>
+        <v>-6.97575392</v>
       </c>
       <c r="F51">
-        <v>14.55809776</v>
+        <v>14.47964535</v>
       </c>
       <c r="G51">
-        <v>13.64042542</v>
+        <v>11.90288737</v>
       </c>
       <c r="H51">
-        <v>-0.070721</v>
+        <v>0.3487877</v>
       </c>
       <c r="I51">
-        <v>-0.72790489</v>
+        <v>-0.72398227</v>
       </c>
       <c r="J51">
-        <v>-0.68202127</v>
+        <v>-0.59514437</v>
       </c>
     </row>
     <row r="52">
@@ -1667,31 +1667,31 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C52">
-        <v>43.74660833</v>
+        <v>44.06598589</v>
       </c>
       <c r="D52">
-        <v>221.58773618</v>
+        <v>257.88043845</v>
       </c>
       <c r="E52">
-        <v>-10.34356836</v>
+        <v>-2.92038028</v>
       </c>
       <c r="F52">
-        <v>14.44809791</v>
+        <v>14.37078611</v>
       </c>
       <c r="G52">
-        <v>-9.17949129</v>
+        <v>-13.59970167</v>
       </c>
       <c r="H52">
-        <v>0.51717842</v>
+        <v>0.14601901</v>
       </c>
       <c r="I52">
-        <v>-0.7224049</v>
+        <v>-0.71853931</v>
       </c>
       <c r="J52">
-        <v>0.45897456</v>
+        <v>0.67998508</v>
       </c>
     </row>
     <row r="53">
@@ -1699,31 +1699,31 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C53">
-        <v>44.20046884</v>
+        <v>44.51259592</v>
       </c>
       <c r="D53">
-        <v>359.09550023</v>
+        <v>35.3882025</v>
       </c>
       <c r="E53">
-        <v>13.94168198</v>
+        <v>11.43084063</v>
       </c>
       <c r="F53">
-        <v>14.33809806</v>
+        <v>14.26192688</v>
       </c>
       <c r="G53">
-        <v>-0.22010864</v>
+        <v>8.11993375</v>
       </c>
       <c r="H53">
-        <v>-0.6970841</v>
+        <v>-0.57154203</v>
       </c>
       <c r="I53">
-        <v>-0.7169049</v>
+        <v>-0.71309634</v>
       </c>
       <c r="J53">
-        <v>0.01100543</v>
+        <v>-0.40599669</v>
       </c>
     </row>
     <row r="54">
@@ -1731,31 +1731,31 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C54">
-        <v>44.65066206</v>
+        <v>44.95569263</v>
       </c>
       <c r="D54">
-        <v>136.60326428</v>
+        <v>172.89596655</v>
       </c>
       <c r="E54">
-        <v>-10.21302752</v>
+        <v>-14.02271327</v>
       </c>
       <c r="F54">
-        <v>14.2280982</v>
+        <v>14.15306764</v>
       </c>
       <c r="G54">
-        <v>9.65687788</v>
+        <v>1.74762375</v>
       </c>
       <c r="H54">
-        <v>0.51065138</v>
+        <v>0.70113566</v>
       </c>
       <c r="I54">
-        <v>-0.71140491</v>
+        <v>-0.70765338</v>
       </c>
       <c r="J54">
-        <v>-0.48284389</v>
+        <v>-0.08738119</v>
       </c>
     </row>
     <row r="55">
@@ -1763,31 +1763,31 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C55">
-        <v>45.0973026</v>
+        <v>45.39538354</v>
       </c>
       <c r="D55">
-        <v>274.11102833</v>
+        <v>310.4037306</v>
       </c>
       <c r="E55">
-        <v>1.01556195</v>
+        <v>9.22953768</v>
       </c>
       <c r="F55">
-        <v>14.11809835</v>
+        <v>14.04420841</v>
       </c>
       <c r="G55">
-        <v>-14.12968269</v>
+        <v>-10.84323957</v>
       </c>
       <c r="H55">
-        <v>-0.0507781</v>
+        <v>-0.46147688</v>
       </c>
       <c r="I55">
-        <v>-0.70590492</v>
+        <v>-0.70221042</v>
       </c>
       <c r="J55">
-        <v>0.70648413</v>
+        <v>0.54216198</v>
       </c>
     </row>
     <row r="56">
@@ -1795,31 +1795,31 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C56">
-        <v>45.54049979</v>
+        <v>45.83177132</v>
       </c>
       <c r="D56">
-        <v>51.61879238</v>
+        <v>87.91149465</v>
       </c>
       <c r="E56">
-        <v>8.86316155</v>
+        <v>0.52281236</v>
       </c>
       <c r="F56">
-        <v>14.0080985</v>
+        <v>13.93534917</v>
       </c>
       <c r="G56">
-        <v>11.19006451</v>
+        <v>14.33641206</v>
       </c>
       <c r="H56">
-        <v>-0.44315808</v>
+        <v>-0.02614062</v>
       </c>
       <c r="I56">
-        <v>-0.70040492</v>
+        <v>-0.69676746</v>
       </c>
       <c r="J56">
-        <v>-0.55950323</v>
+        <v>-0.7168206</v>
       </c>
     </row>
     <row r="57">
@@ -1827,31 +1827,31 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C57">
-        <v>45.98035798</v>
+        <v>46.26495407</v>
       </c>
       <c r="D57">
-        <v>189.12655643</v>
+        <v>225.4192587</v>
       </c>
       <c r="E57">
-        <v>-14.19996149</v>
+        <v>-10.14327629</v>
       </c>
       <c r="F57">
-        <v>13.89809864</v>
+        <v>13.82648994</v>
       </c>
       <c r="G57">
-        <v>-2.28121632</v>
+        <v>-10.29281896</v>
       </c>
       <c r="H57">
-        <v>0.70999807</v>
+        <v>0.50716381</v>
       </c>
       <c r="I57">
-        <v>-0.69490493</v>
+        <v>-0.6913245</v>
       </c>
       <c r="J57">
-        <v>0.11406082</v>
+        <v>0.51464095</v>
       </c>
     </row>
     <row r="58">
@@ -1859,31 +1859,31 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C58">
-        <v>46.41697688</v>
+        <v>46.69502562</v>
       </c>
       <c r="D58">
-        <v>326.63432048</v>
+        <v>2.92702275</v>
       </c>
       <c r="E58">
-        <v>12.09965284</v>
+        <v>14.53527654</v>
       </c>
       <c r="F58">
-        <v>13.78809879</v>
+        <v>13.7176307</v>
       </c>
       <c r="G58">
-        <v>-7.96785623</v>
+        <v>0.74319846</v>
       </c>
       <c r="H58">
-        <v>-0.60498264</v>
+        <v>-0.72676383</v>
       </c>
       <c r="I58">
-        <v>-0.68940494</v>
+        <v>-0.68588154</v>
       </c>
       <c r="J58">
-        <v>0.39839281</v>
+        <v>-0.03715992</v>
       </c>
     </row>
     <row r="59">
@@ -1891,31 +1891,31 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C59">
-        <v>46.85045183</v>
+        <v>47.12207578</v>
       </c>
       <c r="D59">
-        <v>104.14208453</v>
+        <v>140.4347868</v>
       </c>
       <c r="E59">
-        <v>-3.56508329</v>
+        <v>-11.29839098</v>
       </c>
       <c r="F59">
-        <v>13.67809894</v>
+        <v>13.60877147</v>
       </c>
       <c r="G59">
-        <v>14.14919752</v>
+        <v>9.33529327</v>
       </c>
       <c r="H59">
-        <v>0.17825416</v>
+        <v>0.56491955</v>
       </c>
       <c r="I59">
-        <v>-0.68390495</v>
+        <v>-0.68043857</v>
       </c>
       <c r="J59">
-        <v>-0.70745988</v>
+        <v>-0.46676466</v>
       </c>
     </row>
     <row r="60">
@@ -1923,31 +1923,31 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C60">
-        <v>47.28087407</v>
+        <v>47.54619058</v>
       </c>
       <c r="D60">
-        <v>241.64984858</v>
+        <v>277.94255085</v>
       </c>
       <c r="E60">
-        <v>-6.97746169</v>
+        <v>2.03904583</v>
       </c>
       <c r="F60">
-        <v>13.56809908</v>
+        <v>13.49991223</v>
       </c>
       <c r="G60">
-        <v>-12.93142357</v>
+        <v>-14.6148781</v>
       </c>
       <c r="H60">
-        <v>0.34887308</v>
+        <v>-0.10195229</v>
       </c>
       <c r="I60">
-        <v>-0.67840495</v>
+        <v>-0.67499561</v>
       </c>
       <c r="J60">
-        <v>0.64657118</v>
+        <v>0.7307439</v>
       </c>
     </row>
     <row r="61">
@@ -1955,31 +1955,31 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C61">
-        <v>47.708331</v>
+        <v>47.96745251</v>
       </c>
       <c r="D61">
-        <v>19.15761263</v>
+        <v>55.4503149</v>
       </c>
       <c r="E61">
-        <v>13.97524636</v>
+        <v>8.42474329</v>
       </c>
       <c r="F61">
-        <v>13.45809923</v>
+        <v>13.391053</v>
       </c>
       <c r="G61">
-        <v>4.85510601</v>
+        <v>12.23533408</v>
       </c>
       <c r="H61">
-        <v>-0.69876232</v>
+        <v>-0.42123716</v>
       </c>
       <c r="I61">
-        <v>-0.67290496</v>
+        <v>-0.66955265</v>
       </c>
       <c r="J61">
-        <v>-0.2427553</v>
+        <v>-0.6117667</v>
       </c>
     </row>
     <row r="62">
@@ -1987,31 +1987,31 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C62">
-        <v>48.13290638</v>
+        <v>48.3859407</v>
       </c>
       <c r="D62">
-        <v>156.66537668</v>
+        <v>192.95807895</v>
       </c>
       <c r="E62">
-        <v>-13.67568562</v>
+        <v>-14.57192338</v>
       </c>
       <c r="F62">
-        <v>13.34809938</v>
+        <v>13.28219376</v>
       </c>
       <c r="G62">
-        <v>5.89948014</v>
+        <v>-3.35296552</v>
       </c>
       <c r="H62">
-        <v>0.68378428</v>
+        <v>0.72859617</v>
       </c>
       <c r="I62">
-        <v>-0.66740497</v>
+        <v>-0.66410969</v>
       </c>
       <c r="J62">
-        <v>-0.29497401</v>
+        <v>0.16764828</v>
       </c>
     </row>
     <row r="63">
@@ -2019,31 +2019,31 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63">
-        <v>48.55468057</v>
+        <v>48.80173113</v>
       </c>
       <c r="D63">
-        <v>294.17314073</v>
+        <v>330.465843</v>
       </c>
       <c r="E63">
-        <v>6.13905479</v>
+        <v>13.09329845</v>
       </c>
       <c r="F63">
-        <v>13.23809952</v>
+        <v>13.17333453</v>
       </c>
       <c r="G63">
-        <v>-13.67716079</v>
+        <v>-7.41813947</v>
       </c>
       <c r="H63">
-        <v>-0.30695274</v>
+        <v>-0.65466492</v>
       </c>
       <c r="I63">
-        <v>-0.66190498</v>
+        <v>-0.65866673</v>
       </c>
       <c r="J63">
-        <v>0.68385804</v>
+        <v>0.37090697</v>
       </c>
     </row>
     <row r="64">
@@ -2051,31 +2051,31 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C64">
-        <v>48.97373071</v>
+        <v>49.2148968</v>
       </c>
       <c r="D64">
-        <v>71.68090478</v>
+        <v>107.97360705</v>
       </c>
       <c r="E64">
-        <v>4.74234678</v>
+        <v>-4.6729018</v>
       </c>
       <c r="F64">
-        <v>13.12809967</v>
+        <v>13.06447529</v>
       </c>
       <c r="G64">
-        <v>14.32351724</v>
+        <v>14.40428666</v>
       </c>
       <c r="H64">
-        <v>-0.23711734</v>
+        <v>0.23364509</v>
       </c>
       <c r="I64">
-        <v>-0.65640498</v>
+        <v>-0.65322376</v>
       </c>
       <c r="J64">
-        <v>-0.71617586</v>
+        <v>-0.72021433</v>
       </c>
     </row>
     <row r="65">
@@ -2083,31 +2083,31 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C65">
-        <v>49.39013089</v>
+        <v>49.62550787</v>
       </c>
       <c r="D65">
-        <v>209.18866883</v>
+        <v>245.4813711</v>
       </c>
       <c r="E65">
-        <v>-13.25520119</v>
+        <v>-6.32299585</v>
       </c>
       <c r="F65">
-        <v>13.01809982</v>
+        <v>12.95561606</v>
       </c>
       <c r="G65">
-        <v>-7.4046417</v>
+        <v>-13.86260207</v>
       </c>
       <c r="H65">
-        <v>0.66276006</v>
+        <v>0.31614979</v>
       </c>
       <c r="I65">
-        <v>-0.65090499</v>
+        <v>-0.6477808</v>
       </c>
       <c r="J65">
-        <v>0.37023208</v>
+        <v>0.6931301</v>
       </c>
     </row>
     <row r="66">
@@ -2115,31 +2115,31 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C66">
-        <v>49.80395236</v>
+        <v>50.03363186</v>
       </c>
       <c r="D66">
-        <v>346.69643288</v>
+        <v>22.98913515</v>
       </c>
       <c r="E66">
-        <v>14.86685091</v>
+        <v>14.11103188</v>
       </c>
       <c r="F66">
-        <v>12.90809996</v>
+        <v>12.84675682</v>
       </c>
       <c r="G66">
-        <v>-3.51535195</v>
+        <v>5.98661995</v>
       </c>
       <c r="H66">
-        <v>-0.74334255</v>
+        <v>-0.70555159</v>
       </c>
       <c r="I66">
-        <v>-0.645405</v>
+        <v>-0.64233784</v>
       </c>
       <c r="J66">
-        <v>0.1757676</v>
+        <v>-0.299331</v>
       </c>
     </row>
     <row r="67">
@@ -2147,31 +2147,31 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C67">
-        <v>50.21526363</v>
+        <v>50.43933377</v>
       </c>
       <c r="D67">
-        <v>124.20419693</v>
+        <v>160.4968992</v>
       </c>
       <c r="E67">
-        <v>-8.63963574</v>
+        <v>-14.53432293</v>
       </c>
       <c r="F67">
-        <v>12.79810011</v>
+        <v>12.73789759</v>
       </c>
       <c r="G67">
-        <v>12.71083505</v>
+        <v>5.14775893</v>
       </c>
       <c r="H67">
-        <v>0.43198179</v>
+        <v>0.72671615</v>
       </c>
       <c r="I67">
-        <v>-0.63990501</v>
+        <v>-0.63689488</v>
       </c>
       <c r="J67">
-        <v>-0.63554175</v>
+        <v>-0.25738795</v>
       </c>
     </row>
     <row r="68">
@@ -2179,31 +2179,31 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C68">
-        <v>50.62413066</v>
+        <v>50.8426762</v>
       </c>
       <c r="D68">
-        <v>261.71196098</v>
+        <v>298.00466325</v>
       </c>
       <c r="E68">
-        <v>-2.2285556</v>
+        <v>7.2818206</v>
       </c>
       <c r="F68">
-        <v>12.68810026</v>
+        <v>12.62903835</v>
       </c>
       <c r="G68">
-        <v>-15.29855064</v>
+        <v>-13.69242415</v>
       </c>
       <c r="H68">
-        <v>0.11142778</v>
+        <v>-0.36409103</v>
       </c>
       <c r="I68">
-        <v>-0.63440501</v>
+        <v>-0.63145192</v>
       </c>
       <c r="J68">
-        <v>0.76492753</v>
+        <v>0.68462121</v>
       </c>
     </row>
     <row r="69">
@@ -2211,31 +2211,31 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C69">
-        <v>51.03061696</v>
+        <v>51.24371949</v>
       </c>
       <c r="D69">
-        <v>39.21972503</v>
+        <v>75.5124273</v>
       </c>
       <c r="E69">
-        <v>12.04672586</v>
+        <v>3.90173086</v>
       </c>
       <c r="F69">
-        <v>12.5781004</v>
+        <v>12.52017912</v>
       </c>
       <c r="G69">
-        <v>9.83197774</v>
+        <v>15.10038447</v>
       </c>
       <c r="H69">
-        <v>-0.60233629</v>
+        <v>-0.19508654</v>
       </c>
       <c r="I69">
-        <v>-0.62890502</v>
+        <v>-0.62600896</v>
       </c>
       <c r="J69">
-        <v>-0.49159889</v>
+        <v>-0.75501922</v>
       </c>
     </row>
     <row r="70">
@@ -2243,31 +2243,31 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C70">
-        <v>51.43478377</v>
+        <v>51.64252185</v>
       </c>
       <c r="D70">
-        <v>176.72748908</v>
+        <v>213.02019135</v>
       </c>
       <c r="E70">
-        <v>-15.61248105</v>
+        <v>-13.14993044</v>
       </c>
       <c r="F70">
-        <v>12.46810055</v>
+        <v>12.41131988</v>
       </c>
       <c r="G70">
-        <v>0.89269482</v>
+        <v>-8.54625464</v>
       </c>
       <c r="H70">
-        <v>0.78062405</v>
+        <v>0.65749652</v>
       </c>
       <c r="I70">
-        <v>-0.62340503</v>
+        <v>-0.62056599</v>
       </c>
       <c r="J70">
-        <v>-0.04463474</v>
+        <v>0.42731273</v>
       </c>
     </row>
     <row r="71">
@@ -2275,31 +2275,31 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C71">
-        <v>51.8366901</v>
+        <v>52.03913942</v>
       </c>
       <c r="D71">
-        <v>314.23525313</v>
+        <v>350.5279554</v>
       </c>
       <c r="E71">
-        <v>10.96989371</v>
+        <v>15.55363351</v>
       </c>
       <c r="F71">
-        <v>12.3581007</v>
+        <v>12.30246065</v>
       </c>
       <c r="G71">
-        <v>-11.2667111</v>
+        <v>-2.5949849</v>
       </c>
       <c r="H71">
-        <v>-0.54849469</v>
+        <v>-0.77768168</v>
       </c>
       <c r="I71">
-        <v>-0.61790503</v>
+        <v>-0.61512303</v>
       </c>
       <c r="J71">
-        <v>0.56333556</v>
+        <v>0.12974925</v>
       </c>
     </row>
     <row r="72">
@@ -2307,31 +2307,31 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C72">
-        <v>52.23639293</v>
+        <v>52.43362642</v>
       </c>
       <c r="D72">
-        <v>91.74301718</v>
+        <v>128.03571945</v>
       </c>
       <c r="E72">
-        <v>-0.48091484</v>
+        <v>-9.76783784</v>
       </c>
       <c r="F72">
-        <v>12.24810084</v>
+        <v>12.19360141</v>
       </c>
       <c r="G72">
-        <v>15.80356753</v>
+        <v>12.48620953</v>
       </c>
       <c r="H72">
-        <v>0.02404574</v>
+        <v>0.48839189</v>
       </c>
       <c r="I72">
-        <v>-0.61240504</v>
+        <v>-0.60968007</v>
       </c>
       <c r="J72">
-        <v>-0.79017838</v>
+        <v>-0.62431048</v>
       </c>
     </row>
     <row r="73">
@@ -2339,31 +2339,31 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C73">
-        <v>52.63394724</v>
+        <v>52.82603523</v>
       </c>
       <c r="D73">
-        <v>229.25078123</v>
+        <v>265.5434835</v>
       </c>
       <c r="E73">
-        <v>-10.37576991</v>
+        <v>-1.23827386</v>
       </c>
       <c r="F73">
-        <v>12.13810099</v>
+        <v>12.08474218</v>
       </c>
       <c r="G73">
-        <v>-12.04200577</v>
+        <v>-15.88791001</v>
       </c>
       <c r="H73">
-        <v>0.5187885</v>
+        <v>0.06191369</v>
       </c>
       <c r="I73">
-        <v>-0.60690505</v>
+        <v>-0.60423711</v>
       </c>
       <c r="J73">
-        <v>0.60210029</v>
+        <v>0.7943955</v>
       </c>
     </row>
     <row r="74">
@@ -2371,31 +2371,31 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C74">
-        <v>53.02940615</v>
+        <v>53.21641648</v>
       </c>
       <c r="D74">
-        <v>6.75854528</v>
+        <v>43.05124755</v>
       </c>
       <c r="E74">
-        <v>15.86784692</v>
+        <v>11.70509126</v>
       </c>
       <c r="F74">
-        <v>12.02810114</v>
+        <v>11.97588294</v>
       </c>
       <c r="G74">
-        <v>1.88048322</v>
+        <v>10.93476412</v>
       </c>
       <c r="H74">
-        <v>-0.79339235</v>
+        <v>-0.58525456</v>
       </c>
       <c r="I74">
-        <v>-0.60140506</v>
+        <v>-0.59879415</v>
       </c>
       <c r="J74">
-        <v>-0.09402416</v>
+        <v>-0.54673821</v>
       </c>
     </row>
     <row r="75">
@@ -2403,31 +2403,31 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C75">
-        <v>53.422821</v>
+        <v>53.60481911</v>
       </c>
       <c r="D75">
-        <v>144.26630933</v>
+        <v>180.5590116</v>
       </c>
       <c r="E75">
-        <v>-13.03743963</v>
+        <v>-16.0981079</v>
       </c>
       <c r="F75">
-        <v>11.91810128</v>
+        <v>11.86702371</v>
       </c>
       <c r="G75">
-        <v>9.37998026</v>
+        <v>-0.15706767</v>
       </c>
       <c r="H75">
-        <v>0.65187198</v>
+        <v>0.8049054</v>
       </c>
       <c r="I75">
-        <v>-0.59590506</v>
+        <v>-0.59335119</v>
       </c>
       <c r="J75">
-        <v>-0.46899901</v>
+        <v>0.00785338</v>
       </c>
     </row>
     <row r="76">
@@ -2435,31 +2435,31 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C76">
-        <v>53.81424142</v>
+        <v>53.99129051</v>
       </c>
       <c r="D76">
-        <v>281.77407338</v>
+        <v>318.06677565</v>
       </c>
       <c r="E76">
-        <v>3.29385388</v>
+        <v>12.03561628</v>
       </c>
       <c r="F76">
-        <v>11.80810143</v>
+        <v>11.75816447</v>
       </c>
       <c r="G76">
-        <v>-15.80250826</v>
+        <v>-10.81154517</v>
       </c>
       <c r="H76">
-        <v>-0.16469269</v>
+        <v>-0.60178081</v>
       </c>
       <c r="I76">
-        <v>-0.59040507</v>
+        <v>-0.58790822</v>
       </c>
       <c r="J76">
-        <v>0.79012541</v>
+        <v>0.54057726</v>
       </c>
     </row>
     <row r="77">
@@ -2467,31 +2467,31 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C77">
-        <v>54.20371545</v>
+        <v>54.37587651</v>
       </c>
       <c r="D77">
-        <v>59.28183743</v>
+        <v>95.5745397</v>
       </c>
       <c r="E77">
-        <v>8.28646631</v>
+        <v>-1.57922633</v>
       </c>
       <c r="F77">
-        <v>11.69810158</v>
+        <v>11.64930524</v>
       </c>
       <c r="G77">
-        <v>13.94592756</v>
+        <v>16.18022656</v>
       </c>
       <c r="H77">
-        <v>-0.41432332</v>
+        <v>0.07896132</v>
       </c>
       <c r="I77">
-        <v>-0.58490508</v>
+        <v>-0.58246526</v>
       </c>
       <c r="J77">
-        <v>-0.69729638</v>
+        <v>-0.80901133</v>
       </c>
     </row>
     <row r="78">
@@ -2499,31 +2499,31 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C78">
-        <v>54.59128955</v>
+        <v>54.75862153</v>
       </c>
       <c r="D78">
-        <v>196.78960148</v>
+        <v>233.08230375</v>
       </c>
       <c r="E78">
-        <v>-15.60592313</v>
+        <v>-9.81163888</v>
       </c>
       <c r="F78">
-        <v>11.58810172</v>
+        <v>11.540446</v>
       </c>
       <c r="G78">
-        <v>-4.70861568</v>
+        <v>-13.05947352</v>
       </c>
       <c r="H78">
-        <v>0.78029616</v>
+        <v>0.49058194</v>
       </c>
       <c r="I78">
-        <v>-0.57940509</v>
+        <v>-0.5770223</v>
       </c>
       <c r="J78">
-        <v>0.23543078</v>
+        <v>0.65297368</v>
       </c>
     </row>
     <row r="79">
@@ -2531,31 +2531,31 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C79">
-        <v>54.97700876</v>
+        <v>55.13956859</v>
       </c>
       <c r="D79">
-        <v>334.29736553</v>
+        <v>10.5900678</v>
       </c>
       <c r="E79">
-        <v>14.75790605</v>
+        <v>16.13141228</v>
       </c>
       <c r="F79">
-        <v>11.47810187</v>
+        <v>11.43158677</v>
       </c>
       <c r="G79">
-        <v>-7.1033363</v>
+        <v>3.01601753</v>
       </c>
       <c r="H79">
-        <v>-0.7378953</v>
+        <v>-0.80657061</v>
       </c>
       <c r="I79">
-        <v>-0.57390509</v>
+        <v>-0.57157934</v>
       </c>
       <c r="J79">
-        <v>0.35516681</v>
+        <v>-0.15080088</v>
       </c>
     </row>
     <row r="80">
@@ -2563,31 +2563,31 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C80">
-        <v>55.36091669</v>
+        <v>55.51875941</v>
       </c>
       <c r="D80">
-        <v>111.80512958</v>
+        <v>148.09783185</v>
       </c>
       <c r="E80">
-        <v>-6.11221687</v>
+        <v>-13.99601441</v>
       </c>
       <c r="F80">
-        <v>11.36810202</v>
+        <v>11.32272753</v>
       </c>
       <c r="G80">
-        <v>15.27766545</v>
+        <v>8.71248655</v>
       </c>
       <c r="H80">
-        <v>0.30561084</v>
+        <v>0.69980072</v>
       </c>
       <c r="I80">
-        <v>-0.5684051</v>
+        <v>-0.56613638</v>
       </c>
       <c r="J80">
-        <v>-0.76388327</v>
+        <v>-0.43562433</v>
       </c>
     </row>
     <row r="81">
@@ -2595,31 +2595,31 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C81">
-        <v>55.74305561</v>
+        <v>55.89623442</v>
       </c>
       <c r="D81">
-        <v>249.31289363</v>
+        <v>285.6055959</v>
       </c>
       <c r="E81">
-        <v>-5.83961142</v>
+        <v>4.45499636</v>
       </c>
       <c r="F81">
-        <v>11.25810216</v>
+        <v>11.2138683</v>
       </c>
       <c r="G81">
-        <v>-15.46460714</v>
+        <v>-15.94998951</v>
       </c>
       <c r="H81">
-        <v>0.29198057</v>
+        <v>-0.22274982</v>
       </c>
       <c r="I81">
-        <v>-0.56290511</v>
+        <v>-0.56069341</v>
       </c>
       <c r="J81">
-        <v>0.77323036</v>
+        <v>0.79749948</v>
       </c>
     </row>
     <row r="82">
@@ -2627,31 +2627,31 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C82">
-        <v>56.12346653</v>
+        <v>56.2720329</v>
       </c>
       <c r="D82">
-        <v>26.82065768</v>
+        <v>63.11335995</v>
       </c>
       <c r="E82">
-        <v>14.81852034</v>
+        <v>7.52218779</v>
       </c>
       <c r="F82">
-        <v>11.14810231</v>
+        <v>11.10500906</v>
       </c>
       <c r="G82">
-        <v>7.49208047</v>
+        <v>14.83561474</v>
       </c>
       <c r="H82">
-        <v>-0.74092602</v>
+        <v>-0.37610939</v>
       </c>
       <c r="I82">
-        <v>-0.55740512</v>
+        <v>-0.55525045</v>
       </c>
       <c r="J82">
-        <v>-0.37460402</v>
+        <v>-0.74178074</v>
       </c>
     </row>
     <row r="83">
@@ -2659,31 +2659,31 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C83">
-        <v>56.50218922</v>
+        <v>56.64619292</v>
       </c>
       <c r="D83">
-        <v>164.32842173</v>
+        <v>200.621124</v>
       </c>
       <c r="E83">
-        <v>-16.05814277</v>
+        <v>-15.63548148</v>
       </c>
       <c r="F83">
-        <v>11.03810246</v>
+        <v>10.99614983</v>
       </c>
       <c r="G83">
-        <v>4.50514651</v>
+        <v>-5.883571</v>
       </c>
       <c r="H83">
-        <v>0.80290714</v>
+        <v>0.78177407</v>
       </c>
       <c r="I83">
-        <v>-0.55190512</v>
+        <v>-0.54980749</v>
       </c>
       <c r="J83">
-        <v>-0.22525733</v>
+        <v>0.29417855</v>
       </c>
     </row>
     <row r="84">
@@ -2691,31 +2691,31 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C84">
-        <v>56.87926229</v>
+        <v>57.0187515</v>
       </c>
       <c r="D84">
-        <v>301.83618578</v>
+        <v>338.12888805</v>
       </c>
       <c r="E84">
-        <v>8.83572013</v>
+        <v>15.56943906</v>
       </c>
       <c r="F84">
-        <v>10.9281026</v>
+        <v>10.88729059</v>
       </c>
       <c r="G84">
-        <v>-14.23048219</v>
+        <v>-6.24975767</v>
       </c>
       <c r="H84">
-        <v>-0.44178601</v>
+        <v>-0.77847195</v>
       </c>
       <c r="I84">
-        <v>-0.54640513</v>
+        <v>-0.54436453</v>
       </c>
       <c r="J84">
-        <v>0.71152411</v>
+        <v>0.31248788</v>
       </c>
     </row>
     <row r="85">
@@ -2723,31 +2723,31 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C85">
-        <v>57.25472324</v>
+        <v>57.38974456</v>
       </c>
       <c r="D85">
-        <v>79.34394983</v>
+        <v>115.6366521</v>
       </c>
       <c r="E85">
-        <v>3.11054298</v>
+        <v>-7.28911766</v>
       </c>
       <c r="F85">
-        <v>10.81810275</v>
+        <v>10.77843136</v>
       </c>
       <c r="G85">
-        <v>16.53158115</v>
+        <v>15.18862012</v>
       </c>
       <c r="H85">
-        <v>-0.15552715</v>
+        <v>0.36445588</v>
       </c>
       <c r="I85">
-        <v>-0.54090514</v>
+        <v>-0.53892157</v>
       </c>
       <c r="J85">
-        <v>-0.82657906</v>
+        <v>-0.75943101</v>
       </c>
     </row>
     <row r="86">
@@ -2755,31 +2755,31 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C86">
-        <v>57.62860849</v>
+        <v>57.75920705</v>
       </c>
       <c r="D86">
-        <v>216.85171388</v>
+        <v>253.14441615</v>
       </c>
       <c r="E86">
-        <v>-13.51674172</v>
+        <v>-4.90504836</v>
       </c>
       <c r="F86">
-        <v>10.7081029</v>
+        <v>10.66957212</v>
       </c>
       <c r="G86">
-        <v>-10.13085513</v>
+        <v>-16.18952536</v>
       </c>
       <c r="H86">
-        <v>0.67583709</v>
+        <v>0.24525242</v>
       </c>
       <c r="I86">
-        <v>-0.53540514</v>
+        <v>-0.53347861</v>
       </c>
       <c r="J86">
-        <v>0.50654276</v>
+        <v>0.80947627</v>
       </c>
     </row>
     <row r="87">
@@ -2787,31 +2787,31 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C87">
-        <v>58.00095343</v>
+        <v>58.12717294</v>
       </c>
       <c r="D87">
-        <v>354.35947793</v>
+        <v>30.6521802</v>
       </c>
       <c r="E87">
-        <v>16.87901476</v>
+        <v>14.61134497</v>
       </c>
       <c r="F87">
-        <v>10.59810304</v>
+        <v>10.56071289</v>
       </c>
       <c r="G87">
-        <v>-1.66705505</v>
+        <v>8.65909588</v>
       </c>
       <c r="H87">
-        <v>-0.84395074</v>
+        <v>-0.73056725</v>
       </c>
       <c r="I87">
-        <v>-0.52990515</v>
+        <v>-0.52803564</v>
       </c>
       <c r="J87">
-        <v>0.08335275</v>
+        <v>-0.43295479</v>
       </c>
     </row>
     <row r="88">
@@ -2819,31 +2819,31 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C88">
-        <v>58.37179248</v>
+        <v>58.49367524</v>
       </c>
       <c r="D88">
-        <v>131.86724198</v>
+        <v>168.15994425</v>
       </c>
       <c r="E88">
-        <v>-11.36552387</v>
+        <v>-16.6888619</v>
       </c>
       <c r="F88">
-        <v>10.48810319</v>
+        <v>10.45185365</v>
       </c>
       <c r="G88">
-        <v>12.6816623</v>
+        <v>3.49866314</v>
       </c>
       <c r="H88">
-        <v>0.56827619</v>
+        <v>0.83444309</v>
       </c>
       <c r="I88">
-        <v>-0.52440516</v>
+        <v>-0.52259268</v>
       </c>
       <c r="J88">
-        <v>-0.63408311</v>
+        <v>-0.17493316</v>
       </c>
     </row>
     <row r="89">
@@ -2851,31 +2851,31 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C89">
-        <v>58.74115912</v>
+        <v>58.85874612</v>
       </c>
       <c r="D89">
-        <v>269.37500603</v>
+        <v>305.6677083</v>
       </c>
       <c r="E89">
-        <v>-0.18648987</v>
+        <v>9.98116329</v>
       </c>
       <c r="F89">
-        <v>10.37810334</v>
+        <v>10.34299442</v>
       </c>
       <c r="G89">
-        <v>-17.09561911</v>
+        <v>-13.90679136</v>
       </c>
       <c r="H89">
-        <v>0.00932449</v>
+        <v>-0.49905816</v>
       </c>
       <c r="I89">
-        <v>-0.51890517</v>
+        <v>-0.51714972</v>
       </c>
       <c r="J89">
-        <v>0.85478096</v>
+        <v>0.69533957</v>
       </c>
     </row>
     <row r="90">
@@ -2883,31 +2883,31 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C90">
-        <v>59.10908593</v>
+        <v>59.22241687</v>
       </c>
       <c r="D90">
-        <v>46.88277008</v>
+        <v>83.17547235</v>
       </c>
       <c r="E90">
-        <v>11.73074565</v>
+        <v>2.04186346</v>
       </c>
       <c r="F90">
-        <v>10.26810349</v>
+        <v>10.23413518</v>
       </c>
       <c r="G90">
-        <v>12.5281945</v>
+        <v>17.0614557</v>
       </c>
       <c r="H90">
-        <v>-0.58653728</v>
+        <v>-0.10209317</v>
       </c>
       <c r="I90">
-        <v>-0.51340517</v>
+        <v>-0.51170676</v>
       </c>
       <c r="J90">
-        <v>-0.62640972</v>
+        <v>-0.85307279</v>
       </c>
     </row>
     <row r="91">
@@ -2915,31 +2915,31 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C91">
-        <v>59.47560459</v>
+        <v>59.58471796</v>
       </c>
       <c r="D91">
-        <v>184.39053413</v>
+        <v>220.6832364</v>
       </c>
       <c r="E91">
-        <v>-17.17770183</v>
+        <v>-13.0792677</v>
       </c>
       <c r="F91">
-        <v>10.15810363</v>
+        <v>10.12527595</v>
       </c>
       <c r="G91">
-        <v>-1.31889742</v>
+        <v>-11.24328881</v>
       </c>
       <c r="H91">
-        <v>0.85888509</v>
+        <v>0.65396339</v>
       </c>
       <c r="I91">
-        <v>-0.50790518</v>
+        <v>-0.5062638</v>
       </c>
       <c r="J91">
-        <v>0.06594487</v>
+        <v>0.56216444</v>
       </c>
     </row>
     <row r="92">
@@ -2947,31 +2947,31 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C92">
-        <v>59.840746</v>
+        <v>59.94567908</v>
       </c>
       <c r="D92">
-        <v>321.89829818</v>
+        <v>358.19100045</v>
       </c>
       <c r="E92">
-        <v>13.60787193</v>
+        <v>17.30239194</v>
       </c>
       <c r="F92">
-        <v>10.04810378</v>
+        <v>10.01641671</v>
       </c>
       <c r="G92">
-        <v>-10.67058723</v>
+        <v>-0.54646999</v>
       </c>
       <c r="H92">
-        <v>-0.6803936</v>
+        <v>-0.8651196</v>
       </c>
       <c r="I92">
-        <v>-0.50240519</v>
+        <v>-0.50082084</v>
       </c>
       <c r="J92">
-        <v>0.53352936</v>
+        <v>0.0273235</v>
       </c>
     </row>
     <row r="93">
@@ -2979,31 +2979,31 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C93">
-        <v>60.20454021</v>
+        <v>60.30532915</v>
       </c>
       <c r="D93">
-        <v>99.40606223</v>
+        <v>135.6987645</v>
       </c>
       <c r="E93">
-        <v>-2.83651289</v>
+        <v>-12.43386318</v>
       </c>
       <c r="F93">
-        <v>9.93810393</v>
+        <v>9.90755748</v>
       </c>
       <c r="G93">
-        <v>17.12274175</v>
+        <v>12.13422231</v>
       </c>
       <c r="H93">
-        <v>0.14182564</v>
+        <v>0.62169316</v>
       </c>
       <c r="I93">
-        <v>-0.4969052</v>
+        <v>-0.49537787</v>
       </c>
       <c r="J93">
-        <v>-0.85613709</v>
+        <v>-0.60671112</v>
       </c>
     </row>
     <row r="94">
@@ -3011,31 +3011,31 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C94">
-        <v>60.56701656</v>
+        <v>60.66369637</v>
       </c>
       <c r="D94">
-        <v>236.91382628</v>
+        <v>273.20652855</v>
       </c>
       <c r="E94">
-        <v>-9.50882178</v>
+        <v>0.97524155</v>
       </c>
       <c r="F94">
-        <v>9.82810407</v>
+        <v>9.79869824</v>
       </c>
       <c r="G94">
-        <v>-14.59420017</v>
+        <v>-17.40788375</v>
       </c>
       <c r="H94">
-        <v>0.47544109</v>
+        <v>-0.04876208</v>
       </c>
       <c r="I94">
-        <v>-0.4914052</v>
+        <v>-0.48993491</v>
       </c>
       <c r="J94">
-        <v>0.72971001</v>
+        <v>0.87039419</v>
       </c>
     </row>
     <row r="95">
@@ -3043,31 +3043,31 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C95">
-        <v>60.9282036</v>
+        <v>61.02080826</v>
       </c>
       <c r="D95">
-        <v>14.42159033</v>
+        <v>50.7142926</v>
       </c>
       <c r="E95">
-        <v>16.92941739</v>
+        <v>11.07819982</v>
       </c>
       <c r="F95">
-        <v>9.71810422</v>
+        <v>9.68983901</v>
       </c>
       <c r="G95">
-        <v>4.35353619</v>
+        <v>13.54180596</v>
       </c>
       <c r="H95">
-        <v>-0.84647087</v>
+        <v>-0.55390999</v>
       </c>
       <c r="I95">
-        <v>-0.48590521</v>
+        <v>-0.48449195</v>
       </c>
       <c r="J95">
-        <v>-0.21767681</v>
+        <v>-0.6770903</v>
       </c>
     </row>
     <row r="96">
@@ -3075,31 +3075,31 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C96">
-        <v>61.2881292</v>
+        <v>61.37669163</v>
       </c>
       <c r="D96">
-        <v>151.92935438</v>
+        <v>188.22205665</v>
       </c>
       <c r="E96">
-        <v>-15.47755909</v>
+        <v>-17.37531206</v>
       </c>
       <c r="F96">
-        <v>9.60810437</v>
+        <v>9.58097977</v>
       </c>
       <c r="G96">
-        <v>8.25405931</v>
+        <v>-2.51064881</v>
       </c>
       <c r="H96">
-        <v>0.77387795</v>
+        <v>0.8687656</v>
       </c>
       <c r="I96">
-        <v>-0.48040522</v>
+        <v>-0.47904899</v>
       </c>
       <c r="J96">
-        <v>-0.41270297</v>
+        <v>0.12553244</v>
       </c>
     </row>
     <row r="97">
@@ -3107,31 +3107,31 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C97">
-        <v>61.64682054</v>
+        <v>61.73137268</v>
       </c>
       <c r="D97">
-        <v>289.43711843</v>
+        <v>325.7298207</v>
       </c>
       <c r="E97">
-        <v>5.85703518</v>
+        <v>14.55666796</v>
       </c>
       <c r="F97">
-        <v>9.49810451</v>
+        <v>9.47212054</v>
       </c>
       <c r="G97">
-        <v>-16.59762482</v>
+        <v>-9.91878775</v>
       </c>
       <c r="H97">
-        <v>-0.29285176</v>
+        <v>-0.7278334</v>
       </c>
       <c r="I97">
-        <v>-0.47490523</v>
+        <v>-0.47360603</v>
       </c>
       <c r="J97">
-        <v>0.82988124</v>
+        <v>0.49593939</v>
       </c>
     </row>
     <row r="98">
@@ -3139,31 +3139,31 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C98">
-        <v>62.00430416</v>
+        <v>62.08487696</v>
       </c>
       <c r="D98">
-        <v>66.94488248</v>
+        <v>103.23758475</v>
       </c>
       <c r="E98">
-        <v>6.91581237</v>
+        <v>-4.04689463</v>
       </c>
       <c r="F98">
-        <v>9.38810466</v>
+        <v>9.3632613</v>
       </c>
       <c r="G98">
-        <v>16.24915475</v>
+        <v>17.20325497</v>
       </c>
       <c r="H98">
-        <v>-0.34579062</v>
+        <v>0.20234473</v>
       </c>
       <c r="I98">
-        <v>-0.46940523</v>
+        <v>-0.46816307</v>
       </c>
       <c r="J98">
-        <v>-0.81245774</v>
+        <v>-0.86016275</v>
       </c>
     </row>
     <row r="99">
@@ -3171,31 +3171,31 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C99">
-        <v>62.36060594</v>
+        <v>62.43722943</v>
       </c>
       <c r="D99">
-        <v>204.45264653</v>
+        <v>240.7453488</v>
       </c>
       <c r="E99">
-        <v>-16.12848461</v>
+        <v>-8.66455367</v>
       </c>
       <c r="F99">
-        <v>9.27810481</v>
+        <v>9.25440207</v>
       </c>
       <c r="G99">
-        <v>-7.33408177</v>
+        <v>-15.4687282</v>
       </c>
       <c r="H99">
-        <v>0.80642423</v>
+        <v>0.43322768</v>
       </c>
       <c r="I99">
-        <v>-0.46390524</v>
+        <v>-0.4627201</v>
       </c>
       <c r="J99">
-        <v>0.36670409</v>
+        <v>0.77343641</v>
       </c>
     </row>
     <row r="100">
@@ -3203,31 +3203,31 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C100">
-        <v>62.71575117</v>
+        <v>62.78845448</v>
       </c>
       <c r="D100">
-        <v>341.96041058</v>
+        <v>18.25311285</v>
       </c>
       <c r="E100">
-        <v>16.90110255</v>
+        <v>16.89150655</v>
       </c>
       <c r="F100">
-        <v>9.16810495</v>
+        <v>9.14554283</v>
       </c>
       <c r="G100">
-        <v>-5.50441498</v>
+        <v>5.57100104</v>
       </c>
       <c r="H100">
-        <v>-0.84505513</v>
+        <v>-0.84457533</v>
       </c>
       <c r="I100">
-        <v>-0.45840525</v>
+        <v>-0.45727714</v>
       </c>
       <c r="J100">
-        <v>0.27522075</v>
+        <v>-0.27855005</v>
       </c>
     </row>
     <row r="101">
@@ -3235,31 +3235,31 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C101">
-        <v>63.06976456</v>
+        <v>63.13857594</v>
       </c>
       <c r="D101">
-        <v>119.46817463</v>
+        <v>155.7608769</v>
       </c>
       <c r="E101">
-        <v>-8.77186795</v>
+        <v>-16.26908463</v>
       </c>
       <c r="F101">
-        <v>9.0581051</v>
+        <v>9.0366836</v>
       </c>
       <c r="G101">
-        <v>15.52433782</v>
+        <v>7.32497336</v>
       </c>
       <c r="H101">
-        <v>0.4385934</v>
+        <v>0.81345423</v>
       </c>
       <c r="I101">
-        <v>-0.45290525</v>
+        <v>-0.45183418</v>
       </c>
       <c r="J101">
-        <v>-0.77621689</v>
+        <v>-0.36624867</v>
       </c>
     </row>
     <row r="102">
@@ -3267,31 +3267,31 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C102">
-        <v>63.42267025</v>
+        <v>63.48761709</v>
       </c>
       <c r="D102">
-        <v>256.97593868</v>
+        <v>293.26864095</v>
       </c>
       <c r="E102">
-        <v>-4.03093412</v>
+        <v>7.06998474</v>
       </c>
       <c r="F102">
-        <v>8.94810525</v>
+        <v>8.92782436</v>
       </c>
       <c r="G102">
-        <v>-17.42650231</v>
+        <v>-16.44108475</v>
       </c>
       <c r="H102">
-        <v>0.20154671</v>
+        <v>-0.35349924</v>
       </c>
       <c r="I102">
-        <v>-0.44740526</v>
+        <v>-0.44639122</v>
       </c>
       <c r="J102">
-        <v>0.87132512</v>
+        <v>0.82205424</v>
       </c>
     </row>
     <row r="103">
@@ -3299,31 +3299,31 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C103">
-        <v>63.77449184</v>
+        <v>63.83560071</v>
       </c>
       <c r="D103">
-        <v>34.48370273</v>
+        <v>70.776405</v>
       </c>
       <c r="E103">
-        <v>14.78873105</v>
+        <v>5.91035082</v>
       </c>
       <c r="F103">
-        <v>8.83810539</v>
+        <v>8.81896513</v>
       </c>
       <c r="G103">
-        <v>10.15782097</v>
+        <v>16.94973767</v>
       </c>
       <c r="H103">
-        <v>-0.73943655</v>
+        <v>-0.29551754</v>
       </c>
       <c r="I103">
-        <v>-0.44190527</v>
+        <v>-0.44094826</v>
       </c>
       <c r="J103">
-        <v>-0.50789105</v>
+        <v>-0.84748688</v>
       </c>
     </row>
     <row r="104">
@@ -3331,31 +3331,31 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C104">
-        <v>64.12525241</v>
+        <v>64.18254908</v>
       </c>
       <c r="D104">
-        <v>171.99146678</v>
+        <v>208.28416905</v>
       </c>
       <c r="E104">
-        <v>-17.8195048</v>
+        <v>-15.85422844</v>
       </c>
       <c r="F104">
-        <v>8.72810554</v>
+        <v>8.71010589</v>
       </c>
       <c r="G104">
-        <v>2.50707446</v>
+        <v>-8.53097274</v>
       </c>
       <c r="H104">
-        <v>0.89097524</v>
+        <v>0.79271142</v>
       </c>
       <c r="I104">
-        <v>-0.43640528</v>
+        <v>-0.43550529</v>
       </c>
       <c r="J104">
-        <v>-0.12535372</v>
+        <v>0.42654864</v>
       </c>
     </row>
     <row r="105">
@@ -3363,31 +3363,31 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C105">
-        <v>64.47497452</v>
+        <v>64.52848399</v>
       </c>
       <c r="D105">
-        <v>309.49923083</v>
+        <v>345.7919331</v>
       </c>
       <c r="E105">
-        <v>11.47971665</v>
+        <v>17.50366588</v>
       </c>
       <c r="F105">
-        <v>8.61810569</v>
+        <v>8.60124666</v>
       </c>
       <c r="G105">
-        <v>-13.92639078</v>
+        <v>-4.43173067</v>
       </c>
       <c r="H105">
-        <v>-0.57398583</v>
+        <v>-0.87518329</v>
       </c>
       <c r="I105">
-        <v>-0.43090528</v>
+        <v>-0.43006233</v>
       </c>
       <c r="J105">
-        <v>0.69631954</v>
+        <v>0.22158653</v>
       </c>
     </row>
     <row r="106">
@@ -3395,31 +3395,31 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C106">
-        <v>64.82368026</v>
+        <v>64.87342677</v>
       </c>
       <c r="D106">
-        <v>87.00699488</v>
+        <v>123.29969715</v>
       </c>
       <c r="E106">
-        <v>0.94507719</v>
+        <v>-9.94131732</v>
       </c>
       <c r="F106">
-        <v>8.50810583</v>
+        <v>8.49238742</v>
       </c>
       <c r="G106">
-        <v>18.07536899</v>
+        <v>15.13438356</v>
       </c>
       <c r="H106">
-        <v>-0.04725386</v>
+        <v>0.49706587</v>
       </c>
       <c r="I106">
-        <v>-0.42540529</v>
+        <v>-0.42461937</v>
       </c>
       <c r="J106">
-        <v>-0.90376845</v>
+        <v>-0.75671918</v>
       </c>
     </row>
     <row r="107">
@@ -3427,31 +3427,31 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C107">
-        <v>65.17139124</v>
+        <v>65.21739831</v>
       </c>
       <c r="D107">
-        <v>224.51475893</v>
+        <v>260.8074612</v>
       </c>
       <c r="E107">
-        <v>-12.94318698</v>
+        <v>-2.90080377</v>
       </c>
       <c r="F107">
-        <v>8.39810598</v>
+        <v>8.38352819</v>
       </c>
       <c r="G107">
-        <v>-12.72578983</v>
+        <v>-17.9248931</v>
       </c>
       <c r="H107">
-        <v>0.64715935</v>
+        <v>0.14504019</v>
       </c>
       <c r="I107">
-        <v>-0.4199053</v>
+        <v>-0.41917641</v>
       </c>
       <c r="J107">
-        <v>0.63628949</v>
+        <v>0.89624465</v>
       </c>
     </row>
     <row r="108">
@@ -3459,31 +3459,31 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C108">
-        <v>65.51812863</v>
+        <v>65.56041906</v>
       </c>
       <c r="D108">
-        <v>2.02252298</v>
+        <v>38.31522525</v>
       </c>
       <c r="E108">
-        <v>18.19050953</v>
+        <v>14.28617851</v>
       </c>
       <c r="F108">
-        <v>8.28810613</v>
+        <v>8.27466895</v>
       </c>
       <c r="G108">
-        <v>0.6423861</v>
+        <v>11.28870928</v>
       </c>
       <c r="H108">
-        <v>-0.90952548</v>
+        <v>-0.71430893</v>
       </c>
       <c r="I108">
-        <v>-0.41440531</v>
+        <v>-0.41373345</v>
       </c>
       <c r="J108">
-        <v>-0.03211931</v>
+        <v>-0.56443546</v>
       </c>
     </row>
     <row r="109">
@@ -3491,31 +3491,31 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C109">
-        <v>65.86391315</v>
+        <v>65.90250905</v>
       </c>
       <c r="D109">
-        <v>139.53028703</v>
+        <v>175.8229893</v>
       </c>
       <c r="E109">
-        <v>-13.88484097</v>
+        <v>-18.20854649</v>
       </c>
       <c r="F109">
-        <v>8.17810627</v>
+        <v>8.16580972</v>
       </c>
       <c r="G109">
-        <v>11.84608665</v>
+        <v>1.32980691</v>
       </c>
       <c r="H109">
-        <v>0.69424205</v>
+        <v>0.91042732</v>
       </c>
       <c r="I109">
-        <v>-0.40890531</v>
+        <v>-0.40829049</v>
       </c>
       <c r="J109">
-        <v>-0.59230433</v>
+        <v>-0.06649035</v>
       </c>
     </row>
     <row r="110">
@@ -3523,31 +3523,31 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C110">
-        <v>66.20876512</v>
+        <v>66.24368792</v>
       </c>
       <c r="D110">
-        <v>277.03805108</v>
+        <v>313.33075335</v>
       </c>
       <c r="E110">
-        <v>2.24232366</v>
+        <v>12.56128837</v>
       </c>
       <c r="F110">
-        <v>8.06810642</v>
+        <v>8.05695048</v>
       </c>
       <c r="G110">
-        <v>-18.16253406</v>
+        <v>-13.31538897</v>
       </c>
       <c r="H110">
-        <v>-0.11211618</v>
+        <v>-0.62806442</v>
       </c>
       <c r="I110">
-        <v>-0.40340532</v>
+        <v>-0.40284752</v>
       </c>
       <c r="J110">
-        <v>0.9081267</v>
+        <v>0.66576945</v>
       </c>
     </row>
     <row r="111">
@@ -3555,31 +3555,31 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C111">
-        <v>66.55270442</v>
+        <v>66.58397491</v>
       </c>
       <c r="D111">
-        <v>54.54581513</v>
+        <v>90.8385174</v>
       </c>
       <c r="E111">
-        <v>10.64309733</v>
+        <v>-0.26858264</v>
       </c>
       <c r="F111">
-        <v>7.95810657</v>
+        <v>7.94809125</v>
       </c>
       <c r="G111">
-        <v>14.94633798</v>
+        <v>18.35090485</v>
       </c>
       <c r="H111">
-        <v>-0.53215487</v>
+        <v>0.01342913</v>
       </c>
       <c r="I111">
-        <v>-0.39790533</v>
+        <v>-0.39740456</v>
       </c>
       <c r="J111">
-        <v>-0.7473169</v>
+        <v>-0.91754524</v>
       </c>
     </row>
     <row r="112">
@@ -3587,31 +3587,31 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C112">
-        <v>66.89575056</v>
+        <v>66.92338889</v>
       </c>
       <c r="D112">
-        <v>192.05357918</v>
+        <v>228.34628145</v>
       </c>
       <c r="E112">
-        <v>-17.99027003</v>
+        <v>-12.22889248</v>
       </c>
       <c r="F112">
-        <v>7.84810671</v>
+        <v>7.83923201</v>
       </c>
       <c r="G112">
-        <v>-3.84153682</v>
+        <v>-13.74775</v>
       </c>
       <c r="H112">
-        <v>0.8995135</v>
+        <v>0.61144462</v>
       </c>
       <c r="I112">
-        <v>-0.39240534</v>
+        <v>-0.3919616</v>
       </c>
       <c r="J112">
-        <v>0.19207684</v>
+        <v>0.6873875</v>
       </c>
     </row>
     <row r="113">
@@ -3619,31 +3619,31 @@
         <v>112</v>
       </c>
       <c r="B113">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C113">
-        <v>67.23792267</v>
+        <v>67.26194837</v>
       </c>
       <c r="D113">
-        <v>329.56134323</v>
+        <v>5.8540455</v>
       </c>
       <c r="E113">
-        <v>15.90051225</v>
+        <v>18.34943689</v>
       </c>
       <c r="F113">
-        <v>7.73810686</v>
+        <v>7.73037278</v>
       </c>
       <c r="G113">
-        <v>-9.3432014</v>
+        <v>1.8813566</v>
       </c>
       <c r="H113">
-        <v>-0.79502561</v>
+        <v>-0.91747184</v>
       </c>
       <c r="I113">
-        <v>-0.38690534</v>
+        <v>-0.38651864</v>
       </c>
       <c r="J113">
-        <v>0.46716007</v>
+        <v>-0.09406783</v>
       </c>
     </row>
     <row r="114">
@@ -3651,31 +3651,31 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C114">
-        <v>67.57923951</v>
+        <v>67.5996715</v>
       </c>
       <c r="D114">
-        <v>107.06910728</v>
+        <v>143.36180955</v>
       </c>
       <c r="E114">
-        <v>-5.42673542</v>
+        <v>-14.83744735</v>
       </c>
       <c r="F114">
-        <v>7.62810701</v>
+        <v>7.62151354</v>
       </c>
       <c r="G114">
-        <v>17.67378076</v>
+        <v>11.03461315</v>
       </c>
       <c r="H114">
-        <v>0.27133677</v>
+        <v>0.74187237</v>
       </c>
       <c r="I114">
-        <v>-0.38140535</v>
+        <v>-0.38107568</v>
       </c>
       <c r="J114">
-        <v>-0.88368904</v>
+        <v>-0.55173066</v>
       </c>
     </row>
     <row r="115">
@@ -3683,31 +3683,31 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C115">
-        <v>67.91971948</v>
+        <v>67.93657609</v>
       </c>
       <c r="D115">
-        <v>244.57687133</v>
+        <v>280.8695736</v>
       </c>
       <c r="E115">
-        <v>-7.95628146</v>
+        <v>3.49528848</v>
       </c>
       <c r="F115">
-        <v>7.51810715</v>
+        <v>7.51265431</v>
       </c>
       <c r="G115">
-        <v>-16.73844826</v>
+        <v>-18.202829</v>
       </c>
       <c r="H115">
-        <v>0.39781407</v>
+        <v>-0.17476442</v>
       </c>
       <c r="I115">
-        <v>-0.37590536</v>
+        <v>-0.37563272</v>
       </c>
       <c r="J115">
-        <v>0.83692241</v>
+        <v>0.91014145</v>
       </c>
     </row>
     <row r="116">
@@ -3715,31 +3715,31 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C116">
-        <v>68.25938064</v>
+        <v>68.27267964</v>
       </c>
       <c r="D116">
-        <v>22.08463538</v>
+        <v>58.37733765</v>
       </c>
       <c r="E116">
-        <v>17.21437051</v>
+        <v>9.74145698</v>
       </c>
       <c r="F116">
-        <v>7.4081073</v>
+        <v>7.40379507</v>
       </c>
       <c r="G116">
-        <v>6.98465419</v>
+        <v>15.82048781</v>
       </c>
       <c r="H116">
-        <v>-0.86071853</v>
+        <v>-0.48707285</v>
       </c>
       <c r="I116">
-        <v>-0.37040536</v>
+        <v>-0.37018975</v>
       </c>
       <c r="J116">
-        <v>-0.34923271</v>
+        <v>-0.79102439</v>
       </c>
     </row>
     <row r="117">
@@ -3747,31 +3747,31 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C117">
-        <v>68.59824073</v>
+        <v>68.60799932</v>
       </c>
       <c r="D117">
-        <v>159.59239943</v>
+        <v>195.8851017</v>
       </c>
       <c r="E117">
-        <v>-17.45216574</v>
+        <v>-17.91100244</v>
       </c>
       <c r="F117">
-        <v>7.29810745</v>
+        <v>7.29493584</v>
       </c>
       <c r="G117">
-        <v>6.4930377</v>
+        <v>-5.09704843</v>
       </c>
       <c r="H117">
-        <v>0.87260829</v>
+        <v>0.89555012</v>
       </c>
       <c r="I117">
-        <v>-0.36490537</v>
+        <v>-0.36474679</v>
       </c>
       <c r="J117">
-        <v>-0.32465189</v>
+        <v>0.25485242</v>
       </c>
     </row>
     <row r="118">
@@ -3779,31 +3779,31 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C118">
-        <v>68.93631715</v>
+        <v>68.94255199</v>
       </c>
       <c r="D118">
-        <v>297.10016348</v>
+        <v>333.39286575</v>
       </c>
       <c r="E118">
-        <v>8.5021693</v>
+        <v>16.687823</v>
       </c>
       <c r="F118">
-        <v>7.18810759</v>
+        <v>7.1860766</v>
       </c>
       <c r="G118">
-        <v>-16.61457873</v>
+        <v>-8.35923839</v>
       </c>
       <c r="H118">
-        <v>-0.42510847</v>
+        <v>-0.83439115</v>
       </c>
       <c r="I118">
-        <v>-0.35940538</v>
+        <v>-0.35930383</v>
       </c>
       <c r="J118">
-        <v>0.83072894</v>
+        <v>0.41796192</v>
       </c>
     </row>
     <row r="119">
@@ -3811,31 +3811,31 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C119">
-        <v>69.27362701</v>
+        <v>69.27635421</v>
       </c>
       <c r="D119">
-        <v>74.60792753</v>
+        <v>110.9006298</v>
       </c>
       <c r="E119">
-        <v>4.96489778</v>
+        <v>-6.67331936</v>
       </c>
       <c r="F119">
-        <v>7.07810774</v>
+        <v>7.07721737</v>
       </c>
       <c r="G119">
-        <v>18.03469381</v>
+        <v>17.47511954</v>
       </c>
       <c r="H119">
-        <v>-0.24824489</v>
+        <v>0.33366597</v>
       </c>
       <c r="I119">
-        <v>-0.35390539</v>
+        <v>-0.35386087</v>
       </c>
       <c r="J119">
-        <v>-0.90173469</v>
+        <v>-0.87375598</v>
       </c>
     </row>
     <row r="120">
@@ -3843,31 +3843,31 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C120">
-        <v>69.61018711</v>
+        <v>69.60942229</v>
       </c>
       <c r="D120">
-        <v>212.11569158</v>
+        <v>248.40839385</v>
       </c>
       <c r="E120">
-        <v>-15.87816326</v>
+        <v>-6.89859858</v>
       </c>
       <c r="F120">
-        <v>6.96810789</v>
+        <v>6.96835813</v>
       </c>
       <c r="G120">
-        <v>-9.9664138</v>
+        <v>-17.43133163</v>
       </c>
       <c r="H120">
-        <v>0.79390816</v>
+        <v>0.34492993</v>
       </c>
       <c r="I120">
-        <v>-0.34840539</v>
+        <v>-0.34841791</v>
       </c>
       <c r="J120">
-        <v>0.49832069</v>
+        <v>0.87156658</v>
       </c>
     </row>
     <row r="121">
@@ -3875,31 +3875,31 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C121">
-        <v>69.94601397</v>
+        <v>69.9417722</v>
       </c>
       <c r="D121">
-        <v>349.62345563</v>
+        <v>25.9161579</v>
       </c>
       <c r="E121">
-        <v>18.48013634</v>
+        <v>16.8975791</v>
       </c>
       <c r="F121">
-        <v>6.85810803</v>
+        <v>6.8594989</v>
       </c>
       <c r="G121">
-        <v>-3.3839201</v>
+        <v>8.21091319</v>
       </c>
       <c r="H121">
-        <v>-0.92400682</v>
+        <v>-0.84487895</v>
       </c>
       <c r="I121">
-        <v>-0.3429054</v>
+        <v>-0.34297494</v>
       </c>
       <c r="J121">
-        <v>0.169196</v>
+        <v>-0.41054566</v>
       </c>
     </row>
     <row r="122">
@@ -3907,31 +3907,31 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C122">
-        <v>70.28112382</v>
+        <v>70.2734197</v>
       </c>
       <c r="D122">
-        <v>127.13121968</v>
+        <v>163.42392195</v>
       </c>
       <c r="E122">
-        <v>-11.36489111</v>
+        <v>-18.0438943</v>
       </c>
       <c r="F122">
-        <v>6.74810818</v>
+        <v>6.75063966</v>
       </c>
       <c r="G122">
-        <v>15.01007282</v>
+        <v>5.37091638</v>
       </c>
       <c r="H122">
-        <v>0.56824456</v>
+        <v>0.90219471</v>
       </c>
       <c r="I122">
-        <v>-0.33740541</v>
+        <v>-0.33753198</v>
       </c>
       <c r="J122">
-        <v>-0.75050364</v>
+        <v>-0.26854582</v>
       </c>
     </row>
     <row r="123">
@@ -3939,31 +3939,31 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C123">
-        <v>70.61553262</v>
+        <v>70.60438027</v>
       </c>
       <c r="D123">
-        <v>264.63898373</v>
+        <v>300.931686</v>
       </c>
       <c r="E123">
-        <v>-1.76269135</v>
+        <v>9.69688622</v>
       </c>
       <c r="F123">
-        <v>6.63810833</v>
+        <v>6.64178043</v>
       </c>
       <c r="G123">
-        <v>-18.78372799</v>
+        <v>-16.18200082</v>
       </c>
       <c r="H123">
-        <v>0.08813457</v>
+        <v>-0.48484431</v>
       </c>
       <c r="I123">
-        <v>-0.33190542</v>
+        <v>-0.33208902</v>
       </c>
       <c r="J123">
-        <v>0.9391864</v>
+        <v>0.80910004</v>
       </c>
     </row>
     <row r="124">
@@ -3971,31 +3971,31 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C124">
-        <v>70.94925609</v>
+        <v>70.93466912</v>
       </c>
       <c r="D124">
-        <v>42.14674778</v>
+        <v>78.43945005</v>
       </c>
       <c r="E124">
-        <v>14.01640896</v>
+        <v>3.78821245</v>
       </c>
       <c r="F124">
-        <v>6.52810847</v>
+        <v>6.53292119</v>
       </c>
       <c r="G124">
-        <v>12.68558551</v>
+        <v>18.51945969</v>
       </c>
       <c r="H124">
-        <v>-0.70082045</v>
+        <v>-0.18941062</v>
       </c>
       <c r="I124">
-        <v>-0.32640542</v>
+        <v>-0.32664606</v>
       </c>
       <c r="J124">
-        <v>-0.63427928</v>
+        <v>-0.92597298</v>
       </c>
     </row>
     <row r="125">
@@ -4003,31 +4003,31 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C125">
-        <v>71.28230965</v>
+        <v>71.26430124</v>
       </c>
       <c r="D125">
-        <v>179.65451183</v>
+        <v>215.9472141</v>
       </c>
       <c r="E125">
-        <v>-18.94188047</v>
+        <v>-15.33319904</v>
       </c>
       <c r="F125">
-        <v>6.41810862</v>
+        <v>6.42406196</v>
       </c>
       <c r="G125">
-        <v>0.11421914</v>
+        <v>-11.11865258</v>
       </c>
       <c r="H125">
-        <v>0.94709402</v>
+        <v>0.76665995</v>
       </c>
       <c r="I125">
-        <v>-0.32090543</v>
+        <v>-0.3212031</v>
       </c>
       <c r="J125">
-        <v>-0.00571096</v>
+        <v>0.55593263</v>
       </c>
     </row>
     <row r="126">
@@ -4035,31 +4035,31 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C126">
-        <v>71.61470854</v>
+        <v>71.59329139</v>
       </c>
       <c r="D126">
-        <v>317.16227588</v>
+        <v>353.45497815</v>
       </c>
       <c r="E126">
-        <v>13.91706863</v>
+        <v>18.85310159</v>
       </c>
       <c r="F126">
-        <v>6.30810877</v>
+        <v>6.31520272</v>
       </c>
       <c r="G126">
-        <v>-12.90437773</v>
+        <v>-2.16304763</v>
       </c>
       <c r="H126">
-        <v>-0.69585343</v>
+        <v>-0.94265508</v>
       </c>
       <c r="I126">
-        <v>-0.31540544</v>
+        <v>-0.31576014</v>
       </c>
       <c r="J126">
-        <v>0.64521889</v>
+        <v>0.10815238</v>
       </c>
     </row>
     <row r="127">
@@ -4067,31 +4067,31 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C127">
-        <v>71.9464677</v>
+        <v>71.92165407</v>
       </c>
       <c r="D127">
-        <v>94.67003993</v>
+        <v>130.9627422</v>
       </c>
       <c r="E127">
-        <v>-1.54817929</v>
+        <v>-12.46409489</v>
       </c>
       <c r="F127">
-        <v>6.19810891</v>
+        <v>6.20634349</v>
       </c>
       <c r="G127">
-        <v>18.95221852</v>
+        <v>14.35714592</v>
       </c>
       <c r="H127">
-        <v>0.07740896</v>
+        <v>0.62320474</v>
       </c>
       <c r="I127">
-        <v>-0.30990545</v>
+        <v>-0.31031717</v>
       </c>
       <c r="J127">
-        <v>-0.94761093</v>
+        <v>-0.7178573</v>
       </c>
     </row>
     <row r="128">
@@ -4099,31 +4099,31 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C128">
-        <v>72.27760188</v>
+        <v>72.2494036</v>
       </c>
       <c r="D128">
-        <v>232.17780398</v>
+        <v>268.47050625</v>
       </c>
       <c r="E128">
-        <v>-11.68223163</v>
+        <v>-0.50841635</v>
       </c>
       <c r="F128">
-        <v>6.08810906</v>
+        <v>6.09748425</v>
       </c>
       <c r="G128">
-        <v>-15.048601</v>
+        <v>-19.04106611</v>
       </c>
       <c r="H128">
-        <v>0.58411158</v>
+        <v>0.02542082</v>
       </c>
       <c r="I128">
-        <v>-0.30440545</v>
+        <v>-0.30487421</v>
       </c>
       <c r="J128">
-        <v>0.75243005</v>
+        <v>0.95205331</v>
       </c>
     </row>
     <row r="129">
@@ -4131,31 +4131,31 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C129">
-        <v>72.6081256</v>
+        <v>72.57655405</v>
       </c>
       <c r="D129">
-        <v>9.68556803</v>
+        <v>45.9782703</v>
       </c>
       <c r="E129">
-        <v>18.81360532</v>
+        <v>13.26092438</v>
       </c>
       <c r="F129">
-        <v>5.97810921</v>
+        <v>5.98862502</v>
       </c>
       <c r="G129">
-        <v>3.21099133</v>
+        <v>13.721671</v>
       </c>
       <c r="H129">
-        <v>-0.94068027</v>
+        <v>-0.66304622</v>
       </c>
       <c r="I129">
-        <v>-0.29890546</v>
+        <v>-0.29943125</v>
       </c>
       <c r="J129">
-        <v>-0.16054957</v>
+        <v>-0.68608355</v>
       </c>
     </row>
     <row r="130">
@@ -4163,31 +4163,31 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C130">
-        <v>72.93805316</v>
+        <v>72.90311932</v>
       </c>
       <c r="D130">
-        <v>147.19333208</v>
+        <v>183.48603435</v>
       </c>
       <c r="E130">
-        <v>-16.0702278</v>
+        <v>-19.08080879</v>
       </c>
       <c r="F130">
-        <v>5.86810935</v>
+        <v>5.87976578</v>
       </c>
       <c r="G130">
-        <v>10.35920224</v>
+        <v>-1.16236405</v>
       </c>
       <c r="H130">
-        <v>0.80351139</v>
+        <v>0.95404044</v>
       </c>
       <c r="I130">
-        <v>-0.29340547</v>
+        <v>-0.29398829</v>
       </c>
       <c r="J130">
-        <v>-0.51796011</v>
+        <v>0.0581182</v>
       </c>
     </row>
     <row r="131">
@@ -4195,31 +4195,31 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C131">
-        <v>73.26739866</v>
+        <v>73.22911307</v>
       </c>
       <c r="D131">
-        <v>284.70109613</v>
+        <v>320.9937984</v>
       </c>
       <c r="E131">
-        <v>4.86062516</v>
+        <v>14.88051591</v>
       </c>
       <c r="F131">
-        <v>5.7581095</v>
+        <v>5.77090655</v>
       </c>
       <c r="G131">
-        <v>-18.52615713</v>
+        <v>-12.05267124</v>
       </c>
       <c r="H131">
-        <v>-0.24303126</v>
+        <v>-0.7440258</v>
       </c>
       <c r="I131">
-        <v>-0.28790548</v>
+        <v>-0.28854533</v>
       </c>
       <c r="J131">
-        <v>0.92630786</v>
+        <v>0.60263356</v>
       </c>
     </row>
     <row r="132">
@@ -4227,31 +4227,31 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C132">
-        <v>73.59617599</v>
+        <v>73.55454881</v>
       </c>
       <c r="D132">
-        <v>62.20886018</v>
+        <v>98.50156245</v>
       </c>
       <c r="E132">
-        <v>8.94542408</v>
+        <v>-2.83576701</v>
       </c>
       <c r="F132">
-        <v>5.64810965</v>
+        <v>5.66204731</v>
       </c>
       <c r="G132">
-        <v>16.97286792</v>
+        <v>18.97102121</v>
       </c>
       <c r="H132">
-        <v>-0.4472712</v>
+        <v>0.14178835</v>
       </c>
       <c r="I132">
-        <v>-0.28240548</v>
+        <v>-0.28310237</v>
       </c>
       <c r="J132">
-        <v>-0.8486434</v>
+        <v>-0.94855106</v>
       </c>
     </row>
     <row r="133">
@@ -4259,31 +4259,31 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C133">
-        <v>73.92439885</v>
+        <v>73.87943983</v>
       </c>
       <c r="D133">
-        <v>199.71662423</v>
+        <v>236.0093265</v>
       </c>
       <c r="E133">
-        <v>-18.09124701</v>
+        <v>-10.74151107</v>
       </c>
       <c r="F133">
-        <v>5.53810979</v>
+        <v>5.55318808</v>
       </c>
       <c r="G133">
-        <v>-6.48352692</v>
+        <v>-15.93053803</v>
       </c>
       <c r="H133">
-        <v>0.90456235</v>
+        <v>0.53707555</v>
       </c>
       <c r="I133">
-        <v>-0.27690549</v>
+        <v>-0.2776594</v>
       </c>
       <c r="J133">
-        <v>0.32417635</v>
+        <v>0.7965269</v>
       </c>
     </row>
     <row r="134">
@@ -4291,31 +4291,31 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C134">
-        <v>74.25208076</v>
+        <v>74.20379926</v>
       </c>
       <c r="D134">
-        <v>337.22438828</v>
+        <v>13.51709055</v>
       </c>
       <c r="E134">
-        <v>17.74839562</v>
+        <v>18.71164684</v>
       </c>
       <c r="F134">
-        <v>5.42810994</v>
+        <v>5.44432884</v>
       </c>
       <c r="G134">
-        <v>-7.45185047</v>
+        <v>4.49817251</v>
       </c>
       <c r="H134">
-        <v>-0.88741978</v>
+        <v>-0.93558234</v>
       </c>
       <c r="I134">
-        <v>-0.2714055</v>
+        <v>-0.27221644</v>
       </c>
       <c r="J134">
-        <v>0.37259252</v>
+        <v>-0.22490863</v>
       </c>
     </row>
     <row r="135">
@@ -4323,31 +4323,31 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C135">
-        <v>74.57923505</v>
+        <v>74.52764003</v>
       </c>
       <c r="D135">
-        <v>114.73215233</v>
+        <v>151.0248546</v>
       </c>
       <c r="E135">
-        <v>-8.06629774</v>
+        <v>-16.86250896</v>
       </c>
       <c r="F135">
-        <v>5.31811009</v>
+        <v>5.33546961</v>
       </c>
       <c r="G135">
-        <v>17.51149753</v>
+        <v>9.33748122</v>
       </c>
       <c r="H135">
-        <v>0.40331489</v>
+        <v>0.84312545</v>
       </c>
       <c r="I135">
-        <v>-0.2659055</v>
+        <v>-0.26677348</v>
       </c>
       <c r="J135">
-        <v>-0.87557488</v>
+        <v>-0.46687406</v>
       </c>
     </row>
     <row r="136">
@@ -4355,31 +4355,31 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C136">
-        <v>74.90587487</v>
+        <v>74.85097493</v>
       </c>
       <c r="D136">
-        <v>252.23991638</v>
+        <v>288.53261866</v>
       </c>
       <c r="E136">
-        <v>-5.89016211</v>
+        <v>6.13598389</v>
       </c>
       <c r="F136">
-        <v>5.20811023</v>
+        <v>5.22661037</v>
       </c>
       <c r="G136">
-        <v>-18.38971392</v>
+        <v>-18.30388608</v>
       </c>
       <c r="H136">
-        <v>0.29450811</v>
+        <v>-0.30679919</v>
       </c>
       <c r="I136">
-        <v>-0.26040551</v>
+        <v>-0.26133052</v>
       </c>
       <c r="J136">
-        <v>0.9194857</v>
+        <v>0.9151943</v>
       </c>
     </row>
     <row r="137">
@@ -4387,31 +4387,31 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C137">
-        <v>75.23201322</v>
+        <v>75.17381657</v>
       </c>
       <c r="D137">
-        <v>29.74768043</v>
+        <v>66.04038271</v>
       </c>
       <c r="E137">
-        <v>16.79076257</v>
+        <v>7.8514488</v>
       </c>
       <c r="F137">
-        <v>5.09811038</v>
+        <v>5.11775114</v>
       </c>
       <c r="G137">
-        <v>9.59580965</v>
+        <v>17.66814577</v>
       </c>
       <c r="H137">
-        <v>-0.83953813</v>
+        <v>-0.39257244</v>
       </c>
       <c r="I137">
-        <v>-0.25490552</v>
+        <v>-0.25588756</v>
       </c>
       <c r="J137">
-        <v>-0.47979048</v>
+        <v>-0.88340729</v>
       </c>
     </row>
     <row r="138">
@@ -4419,31 +4419,31 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C138">
-        <v>75.5576629</v>
+        <v>75.49617741</v>
       </c>
       <c r="D138">
-        <v>167.25544448</v>
+        <v>203.54814676</v>
       </c>
       <c r="E138">
-        <v>-18.89081927</v>
+        <v>-17.75019029</v>
       </c>
       <c r="F138">
-        <v>4.98811053</v>
+        <v>5.0088919</v>
       </c>
       <c r="G138">
-        <v>4.27266904</v>
+        <v>-7.73574473</v>
       </c>
       <c r="H138">
-        <v>0.94454096</v>
+        <v>0.88750951</v>
       </c>
       <c r="I138">
-        <v>-0.24940553</v>
+        <v>-0.2504446</v>
       </c>
       <c r="J138">
-        <v>-0.21363345</v>
+        <v>0.38678724</v>
       </c>
     </row>
     <row r="139">
@@ -4451,31 +4451,31 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C139">
-        <v>75.8828366</v>
+        <v>75.81806974</v>
       </c>
       <c r="D139">
-        <v>304.76320853</v>
+        <v>341.05591081</v>
       </c>
       <c r="E139">
-        <v>11.05931937</v>
+        <v>18.34018539</v>
       </c>
       <c r="F139">
-        <v>4.87811067</v>
+        <v>4.90003267</v>
       </c>
       <c r="G139">
-        <v>-15.93409839</v>
+        <v>-6.29502024</v>
       </c>
       <c r="H139">
-        <v>-0.55296597</v>
+        <v>-0.91700927</v>
       </c>
       <c r="I139">
-        <v>-0.24390553</v>
+        <v>-0.24500163</v>
       </c>
       <c r="J139">
-        <v>0.79670492</v>
+        <v>0.31475101</v>
       </c>
     </row>
     <row r="140">
@@ -4483,31 +4483,31 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C140">
-        <v>76.2075468</v>
+        <v>76.13950572</v>
       </c>
       <c r="D140">
-        <v>82.27097258</v>
+        <v>118.56367486</v>
       </c>
       <c r="E140">
-        <v>2.61220698</v>
+        <v>-9.2842547</v>
       </c>
       <c r="F140">
-        <v>4.76811082</v>
+        <v>4.79117343</v>
       </c>
       <c r="G140">
-        <v>19.24685673</v>
+        <v>17.05424498</v>
       </c>
       <c r="H140">
-        <v>-0.13061035</v>
+        <v>0.46421273</v>
       </c>
       <c r="I140">
-        <v>-0.23840554</v>
+        <v>-0.23955867</v>
       </c>
       <c r="J140">
-        <v>-0.96234284</v>
+        <v>-0.85271225</v>
       </c>
     </row>
     <row r="141">
@@ -4515,31 +4515,31 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C141">
-        <v>76.53180589</v>
+        <v>76.46049735</v>
       </c>
       <c r="D141">
-        <v>219.77873663</v>
+        <v>256.07143891</v>
       </c>
       <c r="E141">
-        <v>-14.94772411</v>
+        <v>-4.68044427</v>
       </c>
       <c r="F141">
-        <v>4.65811097</v>
+        <v>4.6823142</v>
       </c>
       <c r="G141">
-        <v>-12.44457898</v>
+        <v>-18.87245016</v>
       </c>
       <c r="H141">
-        <v>0.74738621</v>
+        <v>0.23402221</v>
       </c>
       <c r="I141">
-        <v>-0.23290555</v>
+        <v>-0.23411571</v>
       </c>
       <c r="J141">
-        <v>0.62222895</v>
+        <v>0.94362251</v>
       </c>
     </row>
     <row r="142">
@@ -4547,31 +4547,31 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C142">
-        <v>76.85562607</v>
+        <v>76.78105652</v>
       </c>
       <c r="D142">
-        <v>357.28650068</v>
+        <v>33.57920296</v>
       </c>
       <c r="E142">
-        <v>19.45416531</v>
+        <v>16.22094223</v>
       </c>
       <c r="F142">
-        <v>4.54811111</v>
+        <v>4.57345496</v>
       </c>
       <c r="G142">
-        <v>-0.92202894</v>
+        <v>10.76868343</v>
       </c>
       <c r="H142">
-        <v>-0.97270827</v>
+        <v>-0.81104711</v>
       </c>
       <c r="I142">
-        <v>-0.22740556</v>
+        <v>-0.22867275</v>
       </c>
       <c r="J142">
-        <v>0.04610145</v>
+        <v>-0.53843417</v>
       </c>
     </row>
     <row r="143">
@@ -4579,31 +4579,31 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C143">
-        <v>77.17901943</v>
+        <v>77.10119495</v>
       </c>
       <c r="D143">
-        <v>134.79426473</v>
+        <v>171.08696701</v>
       </c>
       <c r="E143">
-        <v>-13.73994248</v>
+        <v>-19.25990419</v>
       </c>
       <c r="F143">
-        <v>4.43811126</v>
+        <v>4.46459573</v>
       </c>
       <c r="G143">
-        <v>13.83897211</v>
+        <v>3.02050913</v>
       </c>
       <c r="H143">
-        <v>0.68699712</v>
+        <v>0.96299521</v>
       </c>
       <c r="I143">
-        <v>-0.22190556</v>
+        <v>-0.22322979</v>
       </c>
       <c r="J143">
-        <v>-0.69194861</v>
+        <v>-0.15102546</v>
       </c>
     </row>
     <row r="144">
@@ -4611,31 +4611,31 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C144">
-        <v>77.5019979</v>
+        <v>77.42092426</v>
       </c>
       <c r="D144">
-        <v>272.30202878</v>
+        <v>308.59473106</v>
       </c>
       <c r="E144">
-        <v>0.78430707</v>
+        <v>12.17668141</v>
       </c>
       <c r="F144">
-        <v>4.32811141</v>
+        <v>4.35573649</v>
       </c>
       <c r="G144">
-        <v>-19.51031302</v>
+        <v>-15.2563426</v>
       </c>
       <c r="H144">
-        <v>-0.03921535</v>
+        <v>-0.60883407</v>
       </c>
       <c r="I144">
-        <v>-0.21640557</v>
+        <v>-0.21778682</v>
       </c>
       <c r="J144">
-        <v>0.97551565</v>
+        <v>0.76281713</v>
       </c>
     </row>
     <row r="145">
@@ -4643,31 +4643,31 @@
         <v>144</v>
       </c>
       <c r="B145">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C145">
-        <v>77.82457332</v>
+        <v>77.74025593</v>
       </c>
       <c r="D145">
-        <v>49.80979283</v>
+        <v>86.10249511</v>
       </c>
       <c r="E145">
-        <v>12.61622854</v>
+        <v>1.32843493</v>
       </c>
       <c r="F145">
-        <v>4.21811155</v>
+        <v>4.24687726</v>
       </c>
       <c r="G145">
-        <v>14.93446726</v>
+        <v>19.49869981</v>
       </c>
       <c r="H145">
-        <v>-0.63081143</v>
+        <v>-0.06642175</v>
       </c>
       <c r="I145">
-        <v>-0.21090558</v>
+        <v>-0.21234386</v>
       </c>
       <c r="J145">
-        <v>-0.74672336</v>
+        <v>-0.97493499</v>
       </c>
     </row>
     <row r="146">
@@ -4675,31 +4675,31 @@
         <v>145</v>
       </c>
       <c r="B146">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C146">
-        <v>78.14675736</v>
+        <v>78.05920132</v>
       </c>
       <c r="D146">
-        <v>187.31755688</v>
+        <v>223.61025916</v>
       </c>
       <c r="E146">
-        <v>-19.41412126</v>
+        <v>-14.16762684</v>
       </c>
       <c r="F146">
-        <v>4.1081117</v>
+        <v>4.13801802</v>
       </c>
       <c r="G146">
-        <v>-2.49305313</v>
+        <v>-13.49648683</v>
       </c>
       <c r="H146">
-        <v>0.97070606</v>
+        <v>0.70838134</v>
       </c>
       <c r="I146">
-        <v>-0.20540559</v>
+        <v>-0.2069009</v>
       </c>
       <c r="J146">
-        <v>0.12465266</v>
+        <v>0.67482434</v>
       </c>
     </row>
     <row r="147">
@@ -4707,31 +4707,31 @@
         <v>146</v>
       </c>
       <c r="B147">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C147">
-        <v>78.46856161</v>
+        <v>78.37777168</v>
       </c>
       <c r="D147">
-        <v>324.82532093</v>
+        <v>1.11802321</v>
       </c>
       <c r="E147">
-        <v>16.01800973</v>
+        <v>19.58621387</v>
       </c>
       <c r="F147">
-        <v>3.99811185</v>
+        <v>4.02915879</v>
       </c>
       <c r="G147">
-        <v>-11.28886469</v>
+        <v>0.38223795</v>
       </c>
       <c r="H147">
-        <v>-0.80090049</v>
+        <v>-0.97931069</v>
       </c>
       <c r="I147">
-        <v>-0.19990559</v>
+        <v>-0.20145794</v>
       </c>
       <c r="J147">
-        <v>0.56444323</v>
+        <v>-0.0191119</v>
       </c>
     </row>
     <row r="148">
@@ -4739,31 +4739,31 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C148">
-        <v>78.78999752</v>
+        <v>78.69597814</v>
       </c>
       <c r="D148">
-        <v>102.33308498</v>
+        <v>138.62578726</v>
       </c>
       <c r="E148">
-        <v>-4.19038834</v>
+        <v>-14.71702762</v>
       </c>
       <c r="F148">
-        <v>3.88811199</v>
+        <v>3.92029955</v>
       </c>
       <c r="G148">
-        <v>19.16567846</v>
+        <v>12.96303781</v>
       </c>
       <c r="H148">
-        <v>0.20951942</v>
+        <v>0.73585138</v>
       </c>
       <c r="I148">
-        <v>-0.1944056</v>
+        <v>-0.19601498</v>
       </c>
       <c r="J148">
-        <v>-0.95828392</v>
+        <v>-0.64815189</v>
       </c>
     </row>
     <row r="149">
@@ -4771,31 +4771,31 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C149">
-        <v>79.11107643</v>
+        <v>79.01383173</v>
       </c>
       <c r="D149">
-        <v>239.84084903</v>
+        <v>276.13355131</v>
       </c>
       <c r="E149">
-        <v>-9.86715965</v>
+        <v>2.09776338</v>
       </c>
       <c r="F149">
-        <v>3.77811214</v>
+        <v>3.81144032</v>
       </c>
       <c r="G149">
-        <v>-16.98131412</v>
+        <v>-19.52107352</v>
       </c>
       <c r="H149">
-        <v>0.49335798</v>
+        <v>-0.10488817</v>
       </c>
       <c r="I149">
-        <v>-0.18890561</v>
+        <v>-0.19057202</v>
       </c>
       <c r="J149">
-        <v>0.84906571</v>
+        <v>0.97605368</v>
       </c>
     </row>
     <row r="150">
@@ -4803,31 +4803,31 @@
         <v>149</v>
       </c>
       <c r="B150">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C150">
-        <v>79.43180958</v>
+        <v>79.33134337</v>
       </c>
       <c r="D150">
-        <v>17.34861308</v>
+        <v>53.64131536</v>
       </c>
       <c r="E150">
-        <v>18.76634267</v>
+        <v>11.65181316</v>
       </c>
       <c r="F150">
-        <v>3.66811229</v>
+        <v>3.70258108</v>
       </c>
       <c r="G150">
-        <v>5.86253658</v>
+        <v>15.82801767</v>
       </c>
       <c r="H150">
-        <v>-0.93831713</v>
+        <v>-0.58259066</v>
       </c>
       <c r="I150">
-        <v>-0.18340561</v>
+        <v>-0.18512905</v>
       </c>
       <c r="J150">
-        <v>-0.29312683</v>
+        <v>-0.79140088</v>
       </c>
     </row>
     <row r="151">
@@ -4835,31 +4835,31 @@
         <v>150</v>
       </c>
       <c r="B151">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C151">
-        <v>79.7522081</v>
+        <v>79.64852388</v>
       </c>
       <c r="D151">
-        <v>154.85637713</v>
+        <v>191.14907941</v>
       </c>
       <c r="E151">
-        <v>-17.81609373</v>
+        <v>-19.30317122</v>
       </c>
       <c r="F151">
-        <v>3.55811243</v>
+        <v>3.59372185</v>
       </c>
       <c r="G151">
-        <v>8.36221502</v>
+        <v>-3.80430602</v>
       </c>
       <c r="H151">
-        <v>0.89080469</v>
+        <v>0.96515856</v>
       </c>
       <c r="I151">
-        <v>-0.17790562</v>
+        <v>-0.17968609</v>
       </c>
       <c r="J151">
-        <v>-0.41811075</v>
+        <v>0.1902153</v>
       </c>
     </row>
     <row r="152">
@@ -4867,31 +4867,31 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C152">
-        <v>80.07228303</v>
+        <v>79.96538399</v>
       </c>
       <c r="D152">
-        <v>292.36414118</v>
+        <v>328.65684346</v>
       </c>
       <c r="E152">
-        <v>7.49588407</v>
+        <v>16.82004635</v>
       </c>
       <c r="F152">
-        <v>3.44811258</v>
+        <v>3.48486261</v>
       </c>
       <c r="G152">
-        <v>-18.21873326</v>
+        <v>-10.24410921</v>
       </c>
       <c r="H152">
-        <v>-0.3747942</v>
+        <v>-0.84100232</v>
       </c>
       <c r="I152">
-        <v>-0.17240563</v>
+        <v>-0.17424313</v>
       </c>
       <c r="J152">
-        <v>0.91093666</v>
+        <v>0.51220546</v>
       </c>
     </row>
     <row r="153">
@@ -4899,31 +4899,31 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C153">
-        <v>80.39204531</v>
+        <v>80.28193432</v>
       </c>
       <c r="D153">
-        <v>69.87190523</v>
+        <v>106.16460751</v>
       </c>
       <c r="E153">
-        <v>6.78586236</v>
+        <v>-5.48805874</v>
       </c>
       <c r="F153">
-        <v>3.33811273</v>
+        <v>3.37600338</v>
       </c>
       <c r="G153">
-        <v>18.51510398</v>
+        <v>18.93366875</v>
       </c>
       <c r="H153">
-        <v>-0.33929312</v>
+        <v>0.27440294</v>
       </c>
       <c r="I153">
-        <v>-0.16690564</v>
+        <v>-0.16880017</v>
       </c>
       <c r="J153">
-        <v>-0.9257552</v>
+        <v>-0.94668344</v>
       </c>
     </row>
     <row r="154">
@@ -4931,31 +4931,31 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C154">
-        <v>80.71150578</v>
+        <v>80.59818542</v>
       </c>
       <c r="D154">
-        <v>207.37966928</v>
+        <v>243.67237156</v>
       </c>
       <c r="E154">
-        <v>-17.52671164</v>
+        <v>-8.7509169</v>
       </c>
       <c r="F154">
-        <v>3.22811287</v>
+        <v>3.26714414</v>
       </c>
       <c r="G154">
-        <v>-9.0770957</v>
+        <v>-17.68466066</v>
       </c>
       <c r="H154">
-        <v>0.87633558</v>
+        <v>0.43754584</v>
       </c>
       <c r="I154">
-        <v>-0.16140564</v>
+        <v>-0.16335721</v>
       </c>
       <c r="J154">
-        <v>0.45385479</v>
+        <v>0.88423303</v>
       </c>
     </row>
     <row r="155">
@@ -4963,31 +4963,31 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C155">
-        <v>81.03067519</v>
+        <v>80.91414775</v>
       </c>
       <c r="D155">
-        <v>344.88743333</v>
+        <v>21.18013561</v>
       </c>
       <c r="E155">
-        <v>19.07220648</v>
+        <v>18.41499045</v>
       </c>
       <c r="F155">
-        <v>3.11811302</v>
+        <v>3.15828491</v>
       </c>
       <c r="G155">
-        <v>-5.15056416</v>
+        <v>7.13536007</v>
       </c>
       <c r="H155">
-        <v>-0.95361032</v>
+        <v>-0.92074952</v>
       </c>
       <c r="I155">
-        <v>-0.15590565</v>
+        <v>-0.15791425</v>
       </c>
       <c r="J155">
-        <v>0.25752821</v>
+        <v>-0.356768</v>
       </c>
     </row>
     <row r="156">
@@ -4995,31 +4995,31 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C156">
-        <v>81.34956422</v>
+        <v>81.22983167</v>
       </c>
       <c r="D156">
-        <v>122.39519738</v>
+        <v>158.68789966</v>
       </c>
       <c r="E156">
-        <v>-10.59322912</v>
+        <v>-18.41443926</v>
       </c>
       <c r="F156">
-        <v>3.00811317</v>
+        <v>3.04942567</v>
       </c>
       <c r="G156">
-        <v>16.69535121</v>
+        <v>7.18397035</v>
       </c>
       <c r="H156">
-        <v>0.52966146</v>
+        <v>0.92072196</v>
       </c>
       <c r="I156">
-        <v>-0.15040566</v>
+        <v>-0.15247128</v>
       </c>
       <c r="J156">
-        <v>-0.83476756</v>
+        <v>-0.35919852</v>
       </c>
     </row>
     <row r="157">
@@ -5027,31 +5027,31 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C157">
-        <v>81.66818346</v>
+        <v>81.54524748</v>
       </c>
       <c r="D157">
-        <v>259.90296143</v>
+        <v>296.19566371</v>
       </c>
       <c r="E157">
-        <v>-3.46930929</v>
+        <v>8.73281044</v>
       </c>
       <c r="F157">
-        <v>2.89811331</v>
+        <v>2.94056644</v>
       </c>
       <c r="G157">
-        <v>-19.48242367</v>
+        <v>-17.75080536</v>
       </c>
       <c r="H157">
-        <v>0.17346546</v>
+        <v>-0.43664052</v>
       </c>
       <c r="I157">
-        <v>-0.14490567</v>
+        <v>-0.14702832</v>
       </c>
       <c r="J157">
-        <v>0.97412118</v>
+        <v>0.88754027</v>
       </c>
     </row>
     <row r="158">
@@ -5059,31 +5059,31 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C158">
-        <v>81.98654342</v>
+        <v>81.8604054</v>
       </c>
       <c r="D158">
-        <v>37.41072548</v>
+        <v>73.70342776</v>
       </c>
       <c r="E158">
-        <v>15.73089685</v>
+        <v>5.55564887</v>
       </c>
       <c r="F158">
-        <v>2.78811346</v>
+        <v>2.8317072</v>
       </c>
       <c r="G158">
-        <v>12.03184556</v>
+        <v>19.00305765</v>
       </c>
       <c r="H158">
-        <v>-0.78654484</v>
+        <v>-0.27778244</v>
       </c>
       <c r="I158">
-        <v>-0.13940567</v>
+        <v>-0.14158536</v>
       </c>
       <c r="J158">
-        <v>-0.60159228</v>
+        <v>-0.95015288</v>
       </c>
     </row>
     <row r="159">
@@ -5091,31 +5091,31 @@
         <v>158</v>
       </c>
       <c r="B159">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C159">
-        <v>82.30465454</v>
+        <v>82.17531556</v>
       </c>
       <c r="D159">
-        <v>174.91848953</v>
+        <v>211.21119181</v>
       </c>
       <c r="E159">
-        <v>-19.74198354</v>
+        <v>-16.9459988</v>
       </c>
       <c r="F159">
-        <v>2.67811361</v>
+        <v>2.72284797</v>
       </c>
       <c r="G159">
-        <v>1.75550373</v>
+        <v>-10.26738641</v>
       </c>
       <c r="H159">
-        <v>0.98709918</v>
+        <v>0.84729994</v>
       </c>
       <c r="I159">
-        <v>-0.13390568</v>
+        <v>-0.1361424</v>
       </c>
       <c r="J159">
-        <v>-0.08777519</v>
+        <v>0.51336932</v>
       </c>
     </row>
     <row r="160">
@@ -5123,31 +5123,31 @@
         <v>159</v>
       </c>
       <c r="B160">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C160">
-        <v>82.62252719</v>
+        <v>82.48998805</v>
       </c>
       <c r="D160">
-        <v>312.42625358</v>
+        <v>348.71895586</v>
       </c>
       <c r="E160">
-        <v>13.38111648</v>
+        <v>19.44534402</v>
       </c>
       <c r="F160">
-        <v>2.56811375</v>
+        <v>2.61398873</v>
       </c>
       <c r="G160">
-        <v>-14.64071424</v>
+        <v>-3.87887339</v>
       </c>
       <c r="H160">
-        <v>-0.66905582</v>
+        <v>-0.9722672</v>
       </c>
       <c r="I160">
-        <v>-0.12840569</v>
+        <v>-0.13069944</v>
       </c>
       <c r="J160">
-        <v>0.73203571</v>
+        <v>0.19394367</v>
       </c>
     </row>
     <row r="161">
@@ -5155,31 +5155,31 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C161">
-        <v>82.94017165</v>
+        <v>82.80443288</v>
       </c>
       <c r="D161">
-        <v>89.93401763</v>
+        <v>126.22671991</v>
       </c>
       <c r="E161">
-        <v>0.02285756</v>
+        <v>-11.72655179</v>
       </c>
       <c r="F161">
-        <v>2.4581139</v>
+        <v>2.5051295</v>
       </c>
       <c r="G161">
-        <v>19.84835393</v>
+        <v>16.00663329</v>
       </c>
       <c r="H161">
-        <v>-0.00114288</v>
+        <v>0.58632759</v>
       </c>
       <c r="I161">
-        <v>-0.1229057</v>
+        <v>-0.12525647</v>
       </c>
       <c r="J161">
-        <v>-0.9924177</v>
+        <v>-0.80033166</v>
       </c>
     </row>
     <row r="162">
@@ -5187,31 +5187,31 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C162">
-        <v>83.25759818</v>
+        <v>83.11865998</v>
       </c>
       <c r="D162">
-        <v>227.44178168</v>
+        <v>263.73448396</v>
       </c>
       <c r="E162">
-        <v>-13.43322941</v>
+        <v>-2.16699793</v>
       </c>
       <c r="F162">
-        <v>2.34811405</v>
+        <v>2.39627026</v>
       </c>
       <c r="G162">
-        <v>-14.62992509</v>
+        <v>-19.73732527</v>
       </c>
       <c r="H162">
-        <v>0.67166147</v>
+        <v>0.1083499</v>
       </c>
       <c r="I162">
-        <v>-0.1174057</v>
+        <v>-0.11981351</v>
       </c>
       <c r="J162">
-        <v>0.73149625</v>
+        <v>0.98686626</v>
       </c>
     </row>
     <row r="163">
@@ -5219,31 +5219,31 @@
         <v>162</v>
       </c>
       <c r="B163">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C163">
-        <v>83.57481693</v>
+        <v>83.43267924</v>
       </c>
       <c r="D163">
-        <v>4.94954573</v>
+        <v>41.24224801</v>
       </c>
       <c r="E163">
-        <v>19.80026624</v>
+        <v>14.93989941</v>
       </c>
       <c r="F163">
-        <v>2.23811419</v>
+        <v>2.28741103</v>
       </c>
       <c r="G163">
-        <v>1.71473074</v>
+        <v>13.09836465</v>
       </c>
       <c r="H163">
-        <v>-0.99001331</v>
+        <v>-0.74699497</v>
       </c>
       <c r="I163">
-        <v>-0.11190571</v>
+        <v>-0.11437055</v>
       </c>
       <c r="J163">
-        <v>-0.08573654</v>
+        <v>-0.65491823</v>
       </c>
     </row>
     <row r="164">
@@ -5251,31 +5251,31 @@
         <v>163</v>
       </c>
       <c r="B164">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C164">
-        <v>83.89183802</v>
+        <v>83.74650048</v>
       </c>
       <c r="D164">
-        <v>142.45730978</v>
+        <v>178.75001206</v>
       </c>
       <c r="E164">
-        <v>-15.76796178</v>
+        <v>-19.87626269</v>
       </c>
       <c r="F164">
-        <v>2.12811434</v>
+        <v>2.17855179</v>
       </c>
       <c r="G164">
-        <v>12.11785916</v>
+        <v>0.43369741</v>
       </c>
       <c r="H164">
-        <v>0.78839809</v>
+        <v>0.99381313</v>
       </c>
       <c r="I164">
-        <v>-0.10640572</v>
+        <v>-0.10892759</v>
       </c>
       <c r="J164">
-        <v>-0.60589296</v>
+        <v>-0.02168487</v>
       </c>
     </row>
     <row r="165">
@@ -5283,31 +5283,31 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C165">
-        <v>84.20867151</v>
+        <v>84.06013349</v>
       </c>
       <c r="D165">
-        <v>279.96507383</v>
+        <v>316.25777611</v>
       </c>
       <c r="E165">
-        <v>3.44329184</v>
+        <v>14.37157938</v>
       </c>
       <c r="F165">
-        <v>2.01811449</v>
+        <v>2.06969256</v>
       </c>
       <c r="G165">
-        <v>-19.59772832</v>
+        <v>-13.75405681</v>
       </c>
       <c r="H165">
-        <v>-0.17216459</v>
+        <v>-0.71857897</v>
       </c>
       <c r="I165">
-        <v>-0.10090572</v>
+        <v>-0.10348463</v>
       </c>
       <c r="J165">
-        <v>0.97988642</v>
+        <v>0.68770284</v>
       </c>
     </row>
     <row r="166">
@@ -5315,31 +5315,31 @@
         <v>165</v>
       </c>
       <c r="B166">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C166">
-        <v>84.5253274</v>
+        <v>84.37358797</v>
       </c>
       <c r="D166">
-        <v>57.47283788</v>
+        <v>93.76554016</v>
       </c>
       <c r="E166">
-        <v>10.70493282</v>
+        <v>-1.30714754</v>
       </c>
       <c r="F166">
-        <v>1.90811463</v>
+        <v>1.96083332</v>
       </c>
       <c r="G166">
-        <v>16.78581281</v>
+        <v>19.86067718</v>
       </c>
       <c r="H166">
-        <v>-0.53524664</v>
+        <v>0.06535738</v>
       </c>
       <c r="I166">
-        <v>-0.09540573</v>
+        <v>-0.09804167</v>
       </c>
       <c r="J166">
-        <v>-0.83929064</v>
+        <v>-0.99303386</v>
       </c>
     </row>
     <row r="167">
@@ -5347,31 +5347,31 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C167">
-        <v>84.84181565</v>
+        <v>84.6868736</v>
       </c>
       <c r="D167">
-        <v>194.98060193</v>
+        <v>231.27330421</v>
       </c>
       <c r="E167">
-        <v>-19.24202624</v>
+        <v>-12.45836606</v>
       </c>
       <c r="F167">
-        <v>1.79811478</v>
+        <v>1.85197409</v>
       </c>
       <c r="G167">
-        <v>-5.14890371</v>
+        <v>-15.53574289</v>
       </c>
       <c r="H167">
-        <v>0.96210131</v>
+        <v>0.6229183</v>
       </c>
       <c r="I167">
-        <v>-0.08990574</v>
+        <v>-0.0925987</v>
       </c>
       <c r="J167">
-        <v>0.25744519</v>
+        <v>0.77678714</v>
       </c>
     </row>
   </sheetData>
